--- a/output/통합_클라우드보안위협_매트릭스_v4.xlsx
+++ b/output/통합_클라우드보안위협_매트릭스_v4.xlsx
@@ -991,7 +991,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>고유 기법 20/126개 적용(요약설명·참조·탐지·대응). 나머지는 기존 번역 설명 유지 — 후속 작성 예정</t>
+          <t>고유 기법 126/126개 적용(요약설명·참조·탐지·대응). 전 기법 완료</t>
         </is>
       </c>
     </row>
@@ -5225,20 +5225,21 @@
       </c>
       <c r="E25" s="17" t="inlineStr">
         <is>
-          <t>공격자는 환경 안의 피해 계정과 인스턴스에 대한 지속적인 접근을 유지하기 위해 클라우드 계정에 공격자가 제어하는 자격 증명을 추가할 수 있다.</t>
+          <t>- 공격자는 장악한 IAM 사용자·서비스 주체·앱에 자신의 액세스 키·비밀·인증서·SSH 키를 추가해 지속 접근 경로를 확보할 수 있음
+- 추가된 자격증명은 원 계정이 회수돼도 유효하고 MFA를 거치지 않으며, 대상이 고권한이면 권한 상승으로도 이어짐</t>
         </is>
       </c>
       <c r="F25" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례(사고 DB)
-- [실제 사고] Credentials exposed in public S3 buckets(2025-11, INC-0573): 공개 S3 버킷에 노출된 자격증명으로 침투해 Lambda 코드 주입, IAM 액세스 키 생성, 백도어 관리자 사용자 생성을 수행했다. 이후 LLMjacking과 GPU 인스턴스 생성에 악용했다(Sysdig 사례).
-■ ATT&amp;CK 사례(행위자, 총 6건)
-- TeamPCP(G1056) — GitHub·GitLab [SaaS·협업]
-- Shai-Hulud(S9008) — GitHub·GitLab [SaaS·협업]
-- C0027(C0027) — AWS [IaaS]
-- Pacu(S1091) — AWS [IaaS]
-■ 통합된 기법
-- T1098 Account Manipulation</t>
+          <t>■ 클라우드 관점
+- AWS: iam:CreateAccessKey로 기존 사용자에 두 번째 키 발급, CreateLoginProfile로 콘솔 비밀번호 추가, EC2 키페어 생성·가져오기 (AWS TTC T1098.001)
+- Entra ID: 앱·서비스 주체에 비밀·x509 인증서 추가(Azure ATRM AZT501.2·AZT405.3) — 애플리케이션 관리자 역할은 다른 앱 서비스 주체에 자격증명을 더해 그 앱 권한으로 로그인
+- GCP: 서비스 계정 키 생성, OS Login SSH 키 추가
+- 통합된 상위기법(T1098)에는 Cognito 리프레시 토큰 재사용(T1098.A006), 알림을 막는 AWS Support 케이스 종료(T1098.A001)도 포함
+■ 실제 사례
+- [실제 사고] 공개 S3 버킷 자격증명 악용(2025-11): 노출 자격증명으로 침투해 IAM 액세스 키와 백도어 관리자를 추가한 뒤 LLMjacking·GPU 인스턴스 생성에 악용 (사고DB INC-0573)
+- [ATT&amp;CK 사례] SolarWinds 침해: APT29가 OAuth 앱·서비스 주체에 자격증명을 추가해 지속 접근 (ATT&amp;CK C0024)
+- [ATT&amp;CK 사례] C0027: Scattered Spider가 가짜 사용자용 임시 페더레이션 자격증명을 만들어 침해 키를 숨기고 MFA 없이 콘솔 세션으로 전환 (ATT&amp;CK C0027)</t>
         </is>
       </c>
       <c r="G25" s="17" t="inlineStr">
@@ -5273,7 +5274,7 @@
       </c>
       <c r="M25" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N25" s="17" t="inlineStr">
@@ -5358,7 +5359,16 @@
           <t>https://attack.mitre.org/techniques/T1098/001</t>
         </is>
       </c>
-      <c r="AF25" s="17" t="inlineStr"/>
+      <c r="AF25" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 감사 로그의 CreateAccessKey·CreateLoginProfile·키페어 생성, 서비스 주체·앱 자격증명 추가 이벤트
+- 한 사용자에 다수 액세스 키 존재, 새 키가 낯선 출발지에서 즉시 사용되는 패턴
+■ 대응
+- 사용자당 액세스 키 수 제한·정기 회수, 자격증명 추가 권한(iam:CreateAccessKey 등) 최소화
+- 앱·서비스 주체 자격증명 추가에 대한 알림과 승인 절차</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="17" t="inlineStr">
@@ -5383,13 +5393,19 @@
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t>공격자는 자신이 제어하는 이메일 계정에 대한 지속적인 접근을 유지하기 위해 추가 권한 수준을 부여할 수 있다.</t>
+          <t>- 공격자는 Exchange Online·Google Workspace에서 사서함 위임·폴더 권한·앱 가장 권한을 부여해 다른 계정으로 대상 사서함을 계속 열람할 수 있음
+- 원 계정 비밀번호가 바뀌어도 위임 권한은 남아, 장기 첩보 수집과 BEC의 기반이 됨</t>
         </is>
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 1건)
-- APT29(G0016) — Entra ID [ID·인증]</t>
+          <t>■ 클라우드 관점
+- Exchange Online: Add-MailboxPermission으로 사서함 권한 부여, 받은편지함·최상위 폴더에 Default·Anonymous 권한을 주면 테넌트 내 어느 계정으로도 열람 가능
+- Google Workspace: 관리 콘솔·Gmail 설정의 메일 위임 기능
+- 서비스 주체에 사서함 가장 권한(ApplicationImpersonation 등)을 붙이면 사용자 로그인 없이 다수 사서함을 API로 수집 가능
+- BEC·내부 피싱(CTC-LM-02)과 이메일 숨김 규칙(CTC-ST-01.1)으로 이어짐
+■ 실제 사례
+- [ATT&amp;CK 사례] APT29: 침해한 전역 관리자 계정으로 ApplicationImpersonation 권한을 가진 서비스 주체를 백도어화해 대상 사서함에서 메일 수집 (ATT&amp;CK G0016)</t>
         </is>
       </c>
       <c r="G26" s="17" t="inlineStr">
@@ -5420,7 +5436,7 @@
       </c>
       <c r="M26" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N26" s="17" t="inlineStr">
@@ -5481,7 +5497,16 @@
           <t>https://attack.mitre.org/techniques/T1098/002</t>
         </is>
       </c>
-      <c r="AF26" s="17" t="inlineStr"/>
+      <c r="AF26" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- Add-MailboxPermission·위임 추가, 폴더에 Default·Anonymous 권한 부여, 서비스 주체 가장 권한 부여 이벤트
+- 사용자 로그인 없이 서비스 주체로 다수 사서함을 조회하는 패턴
+■ 대응
+- 사서함 위임·가장 권한 정기 검토와 최소화, ApplicationImpersonation 범위 제한
+- 고권한 역할 부여 알림과 조건부 액세스 적용</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="17" t="inlineStr">
@@ -5506,18 +5531,21 @@
       </c>
       <c r="E27" s="17" t="inlineStr">
         <is>
-          <t>공격자는 테넌트에 대한 지속적인 접근을 유지하기 위해 자신이 제어하는 클라우드 계정에 역할이나 권한을 추가할 수 있다. 예를 들어 클라우드 환경에서 IAM 정책을 수정하거나 Office 365 환경에 새 전역 관리자를 추가할 수 있다. 권한이 충분하면 침해된 계정이 데이터와 설정에 거의 무제한으로 접근할 수 있다(다른 관리자의 비밀번호 재설정 포함).</t>
+          <t>- 공격자는 장악·생성한 클라우드 계정에 IAM 역할·정책이나 전역 관리자 역할을 추가해 테넌트 전반에 지속 접근과 권한 상승을 확보할 수 있음
+- 피해 테넌트 밖의 공격자 계정에 역할을 부여하면 계정 생성·수정 없이도 내부 작업이 가능해 추적이 어려움</t>
         </is>
       </c>
       <c r="F27" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 5건)
-- Scattered Spider(G1015) — Azure [IaaS]
-- Storm-0501(G1053) — Azure [IaaS]
-- C0027(C0027) — AWS [IaaS]
-- LAPSUS$(G1004) — 클라우드(서비스 미상) [클라우드(복합)]
-■ 통합된 기법
-- T1078.003 Local Accounts</t>
+          <t>■ 클라우드 관점
+- AWS: iam:AttachUserPolicy·CreatePolicyVersion·AttachRolePolicy, IAM Identity Center 할당으로 권한 추가 (AWS TTC T1098.003)
+- Entra ID: 새 전역 관리자 추가, elevateAccess 토글로 테넌트 루트 관리 권한 획득(Azure ATRM AZT402)
+- K8s: cluster-admin RoleBinding 부여로 클러스터 전체 권한 (K8s MS-TA9019)
+- 외부 계정에 역할·권한을 부여하는 변형과 통합된 상위기법(T1078.003) 근거 포함
+■ 실제 사례
+- [ATT&amp;CK 사례] Storm-0501: elevateAccess·roleAssignments/write로 피해 구독의 User Access Administrator·Owner 역할 획득 (ATT&amp;CK G1053)
+- [ATT&amp;CK 사례] Scattered Spider: User Access Administrator 역할을 할당해 Azure 테넌트 루트 그룹 관리 권한 확보 (ATT&amp;CK G1015)
+- [ATT&amp;CK 사례] LAPSUS$: 피해 클라우드 인스턴스에 만든 계정에 전역 관리자 역할 부여 (ATT&amp;CK G1004)</t>
         </is>
       </c>
       <c r="G27" s="17" t="inlineStr">
@@ -5552,7 +5580,7 @@
       </c>
       <c r="M27" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N27" s="17" t="inlineStr">
@@ -5625,7 +5653,16 @@
           <t>https://attack.mitre.org/techniques/T1098/003</t>
         </is>
       </c>
-      <c r="AF27" s="17" t="inlineStr"/>
+      <c r="AF27" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- IAM 정책 연결·역할 생성·AssumeRolePolicy 변경, elevateAccess, 전역 관리자 추가 이벤트
+- 외부 계정을 신뢰 주체로 추가하는 역할 신뢰 정책 변경, cluster-admin 바인딩 생성
+■ 대응
+- 권한 변경을 PR·승인 워크플로로 통제, 고권한 역할 부여에 PIM·다중 승인
+- 외부 신뢰 계정 허용 목록화, RBAC 정기 검토</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="17" t="inlineStr">
@@ -5650,12 +5687,18 @@
       </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t>공격자는 SSH authorized_keys 파일을 수정해 피해 호스트에서 지속성을 유지할 수 있다. Linux 배포판, macOS, ESXi 하이퍼바이저는 원격 관리용 SSH 세션의 인증 과정을 보호하기 위해 보통 키 기반 인증을 사용한다. SSH의 authorized_keys 파일은 해당 파일이 설정된 사용자 계정에 로그인할 때 쓸 수 있는 SSH 키를 지정한다. 이 파일은 보통 사용자 홈 디렉터리의 &lt;user-home&gt;/.ssh/authorized_keys에 있다(ESXi는 /etc/ssh/keys-&lt;username&gt;/authorized_keys). 사용자는 시스템의 SSH 설정 파일에서 PubkeyAuthentication과 RSAAuthentication 지시어를 yes로 바꿔 공개 키 인증과 RSA 인증을 활성화하고, PermitRootLogin 지시어를 yes로 바꿔 SSH를 통한 root 인증을 허용할 수 있다. SSH 설정 파일은 보통 /etc/ssh/sshd_config에 있다.</t>
+          <t>- 공격자는 VM의 SSH authorized_keys를 클라우드 CLI·API로 수정해 자신의 공개키로 인스턴스에 지속 접근할 수 있음
+- 더 높은 권한 사용자에 키를 추가하면 권한 상승이 되며, 제어 평면 경유 변경이라 호스트 로그만으로는 탐지가 어려움</t>
         </is>
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- 호스트 직접 수정뿐 아니라 제어 평면 경로가 핵심: GCP compute os-login/add-metadata, Azure VM authorized_keys PATCH, AWS EC2 Instance Connect·키페어로 키 투입
+- 추가 키가 붙는 대상 사용자 권한에 따라 VM 내 권한 상승으로 이어짐
+- 네트워크 장비도 ip ssh pubkey-chain으로 유사 악용 가능
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB·ATT&amp;CK 클라우드 사례에 매핑된 건은 없음(제어 평면 키 투입 가능성은 ATT&amp;CK 원문에 문서화)</t>
         </is>
       </c>
       <c r="G28" s="17" t="inlineStr">
@@ -5686,7 +5729,7 @@
       </c>
       <c r="M28" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N28" s="17" t="inlineStr">
@@ -5747,7 +5790,16 @@
           <t>https://attack.mitre.org/techniques/T1098/004</t>
         </is>
       </c>
-      <c r="AF28" s="17" t="inlineStr"/>
+      <c r="AF28" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 제어 평면의 VM 메타데이터·authorized_keys 변경(GCP set-metadata, Azure VM PATCH), EC2 키페어 투입 이벤트
+- VM 내 authorized_keys 파일 변경과 신규 키로의 SSH 로그인
+■ 대응
+- VM 메타데이터·키 변경 권한 최소화, OS Login·중앙 키 관리로 개별 키 투입 차단
+- 불변 인프라·구성 드리프트 점검으로 비인가 키 탐지</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
@@ -5772,14 +5824,19 @@
       </c>
       <c r="E29" s="17" t="inlineStr">
         <is>
-          <t>공격자는 자신이 제어하는 계정에 장치를 등록할 수 있다. 장치는 네트워크 인증을 처리하는 다중 인증(MFA) 시스템이나, 장치 접근과 규정 준수를 관리하는 장치 관리 시스템에 등록될 수 있다.</t>
+          <t>- 공격자는 탈취한 자격증명으로 자신의 장치를 피해 계정의 MFA·장치 관리 시스템(Entra ID·Intune·Duo·Okta)에 등록해 지속 접근을 확보할 수 있음
+- 등록된 장치는 조건부 액세스의 '관리 장치' 조건을 충족해 이후 MFA·정책을 통과하고, 내부 발신 메일로 신뢰도 높은 피싱도 가능</t>
         </is>
       </c>
       <c r="F29" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 2건)
-- APT29(G0016) — Entra ID [ID·인증]
-- AADInternals(S0677) — Entra ID [ID·인증]</t>
+          <t>■ 클라우드 관점
+- 자격증명을 얻은 뒤 신규 MFA 장치를 등록하면 초기 MFA 요건을 우회하고 지속 접근을 확보 — 비활성 계정은 사용자명·비밀번호만으로 첫 장치 등록이 가능한 경우가 있음
+- Entra ID에 장치·VM을 등록하면 조건부 액세스 정책을 우회하고 민감 리소스 접근 가능
+- 대량 장치 등록으로 테넌트에 서비스 소모(DoS)를 유발하기도 함
+■ 실제 사례
+- [ATT&amp;CK 사례] APT29: 비활성 계정 암호 추측 성공 후 Entra ID에 자신의 장치를 MFA로 등록 (ATT&amp;CK G0016)
+- [ATT&amp;CK 사례] AADInternals: Entra ID에 장치를 등록하는 기능 제공 (ATT&amp;CK S0677)</t>
         </is>
       </c>
       <c r="G29" s="17" t="inlineStr">
@@ -5810,7 +5867,7 @@
       </c>
       <c r="M29" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N29" s="17" t="inlineStr">
@@ -5871,7 +5928,16 @@
           <t>https://attack.mitre.org/techniques/T1098/005</t>
         </is>
       </c>
-      <c r="AF29" s="17" t="inlineStr"/>
+      <c r="AF29" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 신규 MFA 장치·장치 등록 이벤트, 특히 비활성 계정·암호 추측 직후의 등록
+- 단기간 대량 장치 등록, 신규 등록 장치의 즉시 민감 리소스 접근
+■ 대응
+- 장치 등록에 추가 인증·관리자 승인, 조건부 액세스로 등록 가능 조건 제한
+- MFA 자가 등록 제한과 신규 장치 알림</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="17" t="inlineStr">
@@ -5896,13 +5962,19 @@
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t>공격자는 SaaS 환경의 OAuth 애플리케이션 통합을 이용해 지속성을 확보할 수 있다. 사용자 지정 애플리케이션을 만들거나, 정상 애플리케이션을 환경에 추가하거나, 기존 통합을 장악해 악의적 목적을 달성할 수 있다.</t>
+          <t>- 공격자는 SaaS 환경의 OAuth 앱 통합을 만들거나 장악해, 고권한 계정의 동의를 받아 메일·파일 데이터에 지속 접근할 수 있음
+- 앱 통합은 동의한 계정이 비활성화돼도 유효한 경우가 있고 앱 토큰으로 MFA를 우회해 자동 반출의 통로가 됨</t>
         </is>
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 1건)
-- Salesforce Data Exfiltration(C0059) — Salesforce [SaaS·협업]</t>
+          <t>■ 클라우드 관점
+- M365·Google Workspace·Salesforce에서 사용자 지정 앱을 만들거나 정상 앱을 추가·장악해 지속성 확보 — 앱 실행에는 전용 서비스 주체와 역할 부여가 수반됨 (Azure ATRM AZT502.2)
+- 앱 접근 토큰(CTC-LM-06.1)으로 MFA 우회, 시간이 지나며 자동 반출(CTC-EF-02) 가능
+- 동의 피싱(CTC-IA-03.1)과 결합되어 사용자 '수락'만으로 권한이 부여됨
+■ 실제 사례
+- [ATT&amp;CK 사례] Salesforce 데이터 반출 캠페인: 피해자를 속여 악성 연결 앱을 조직 Salesforce 포털에 승인하게 함 (ATT&amp;CK C0059)
+- [실제 사고] Salesloft Drift 통합 침해(2025-08): 신뢰된 OAuth 통합의 토큰을 악용해 700여 조직의 SaaS 데이터 반출 (CSA TT2026 SI-06)</t>
         </is>
       </c>
       <c r="G30" s="17" t="inlineStr">
@@ -5933,7 +6005,7 @@
       </c>
       <c r="M30" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N30" s="17" t="inlineStr">
@@ -5998,7 +6070,16 @@
           <t>https://attack.mitre.org/techniques/T1671</t>
         </is>
       </c>
-      <c r="AF30" s="17" t="inlineStr"/>
+      <c r="AF30" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 신규 OAuth 앱·연결 앱 등록과 고권한 위임 동의, 비검증 게시자 앱 추가
+- 앱 토큰으로 대량 메일·파일을 자동 조회하는 패턴
+■ 대응
+- 사용자 앱 동의 제한(관리자 승인), 과도한 위임 권한 차단, 앱 자격증명·권한 정기 검토
+- 사용하지 않는 통합 제거와 앱 활동 모니터링</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="17" t="inlineStr">
@@ -6023,22 +6104,21 @@
       </c>
       <c r="E31" s="17" t="inlineStr">
         <is>
-          <t>공격자는 피해 시스템에 대한 접근을 유지하기 위해 클라우드 계정을 만들 수 있다. 접근 수준이 충분하면, 시스템에 지속적인 원격 접근 도구를 배포하지 않고도 자격 증명 기반의 보조 접근 경로를 확보하는 데 이런 계정을 쓸 수 있다.</t>
+          <t>- 공격자는 피해 테넌트에 새 클라우드 사용자·서비스 주체·게스트 계정을 만들어 자격증명 기반 보조 접근 경로를 확보할 수 있음
+- 특정 서비스만 쓰는 계정으로 만들면 탐지 가능성을 낮추며, 생성 후 역할·자격증명을 더해 지속성을 강화함</t>
         </is>
       </c>
       <c r="F31" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례(사고 DB)
-- [실제 사고] Internet-exposed SSH with weak credentials (LiteLLM-Proxy)(2026-06, INC-0635): 약한 자격증명의 인터넷 노출 SSH(LiteLLM-Proxy)로 침투했다. 공격자는 IAM CreateUser와 Bedrock InvokeModel을 시도했고, XMRig 채굴과 LLMjacking 가능성이 확인되었다(Darktrace 사례).
-- [실제 사고] Compromised internet-facing application credentials(2026-06, INC-0637): 외부 노출 애플리케이션의 자격증명이 침해되었다. 공격자는 IAM 사용자 생성, 리버스 셸, CI/CD 파이프라인 변조, Secrets Manager·Parameter Store 접근을 수행해 RDS 데이터를 유출하고 갈취 목적으로 인프라를 장악했다(S
-- [실제 사고] Compromised credential in public s3(2024-07, INC-0364): 공개 S3에 있던 자격증명이 침해되었다. 공격자는 SES 권한을 가진 IAM 사용자를 만들어 SES를 악용했다(Rapid7 사례 2).
-- 외 7건(관련 사례 ID 열)
-■ ATT&amp;CK 사례(행위자, 총 3건)
-- APT29(G0016) — Entra ID [ID·인증]
-- AADInternals(S0677) — Entra ID [ID·인증]
-- LAPSUS$(G1004) — 클라우드(서비스 미상) [클라우드(복합)]
-■ 통합된 기법
-- T1136 Create Account</t>
+          <t>■ 클라우드 관점
+- AWS: iam:CreateUser·IAM Identity Center 사용자 생성, Organizations에 결제 수단이 연결된 신규 계정 생성 (AWS TTC T1136.003)
+- Entra ID: 사용자·서비스 주체·게스트 계정 생성(Azure ATRM AZT502.1~502.3)
+- 생성 계정에 추가 자격증명(CTC-PE-01.1)·역할(CTC-PE-01.3)을 더해 지속성·권한 강화
+- 통합된 상위기법(T1136) 근거 포함
+■ 실제 사례
+- [실제 사고] 노출 장기 자격증명 악용(2023-04): 접근 후 신규 사용자를 만들고 데이터를 유출·삭제한 뒤 랜섬 노트를 남김 (사고DB INC-0161)
+- [실제 사고] Code Spaces(2014-06): 탈취된 AWS 콘솔 자격증명으로 추가 계정·키를 생성, 이후 S3·EC2·스냅샷 삭제로 사업 중단 (사고DB INC-0006)
+- [ATT&amp;CK 사례] LAPSUS$: 피해 클라우드 인스턴스에 전역 관리자 계정을 생성해 지속성 확보 (ATT&amp;CK G1004)</t>
         </is>
       </c>
       <c r="G31" s="17" t="inlineStr">
@@ -6073,7 +6153,7 @@
       </c>
       <c r="M31" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N31" s="17" t="inlineStr">
@@ -6154,7 +6234,16 @@
           <t>https://attack.mitre.org/techniques/T1136/003</t>
         </is>
       </c>
-      <c r="AF31" s="17" t="inlineStr"/>
+      <c r="AF31" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 사용자·서비스 주체·게스트 생성 이벤트, 특히 탈취 자격증명 사용 직후의 계정 생성
+- 신규 계정의 즉시 역할·키 추가, 특정 서비스 전용 권한만 가진 계정
+■ 대응
+- 계정 생성 권한 최소화·알림, 신규 계정 승인 절차
+- 게스트 초대 제한과 유휴 계정 정리</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
@@ -6179,13 +6268,19 @@
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t>공격자는 개별 호스트에서 데몬, 에이전트, 서비스로 실행되는 컨테이너·컨테이너 클러스터 관리 도구를 만들거나 수정할 수 있다. 여기에는 Docker, Podman 같은 컨테이너 생성·관리 소프트웨어와 kubelet 같은 클러스터 노드 에이전트가 포함된다. 이러한 서비스를 수정하면 호스트에서 지속성을 확보하거나 권한을 높일 수 있다.</t>
+          <t>- 공격자는 컨테이너 런타임·노드 에이전트를 재시작 유지 설정으로 만들거나 수정해 호스트에서 지속성을 확보하고 권한을 높일 수 있음
+- DaemonSet·정적 파드·restart=always로 노드마다 자동 상주시키며, rootful Docker 접근은 그대로 호스트 권한 상승 경로가 됨</t>
         </is>
       </c>
       <c r="F32" s="17" t="inlineStr">
         <is>
-          <t>■ 통합된 기법
-- T1543 Create or Modify System Process</t>
+          <t>■ 클라우드 관점
+- docker/podman run --restart=always로 호스트에 상주 컨테이너 구성, DaemonSet으로 신규 노드 포함 전 노드에 배포(CTC-EX-04 연계)
+- API 서버가 관찰하지 않는 정적 파드(K8s MS-TA9017)와 백도어 컨테이너(MS-TA9012)로 은폐 지속
+- rootful docker 명령 접근자는 호스트 권한 상승 가능, 컨테이너를 systemd 서비스로 등록하는 변형 포함
+- 통합된 상위기법(T1543) 근거 포함
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB·ATT&amp;CK 클라우드 사례에 매핑된 건은 없음(K8s 위협 매트릭스 문서화 수준)</t>
         </is>
       </c>
       <c r="G32" s="17" t="inlineStr">
@@ -6220,7 +6315,7 @@
       </c>
       <c r="M32" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N32" s="17" t="inlineStr"/>
@@ -6282,7 +6377,16 @@
           <t>https://attack.mitre.org/techniques/T1543/005</t>
         </is>
       </c>
-      <c r="AF32" s="17" t="inlineStr"/>
+      <c r="AF32" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- restart=always 상주 컨테이너, 신규 DaemonSet·정적 파드, kubelet manifest 디렉터리 변경
+- 노드에 반복 재생성되는 컨테이너와 외부 통신
+■ 대응
+- 정책 엔진으로 위험 워크로드 차단, 정적 파드 경로·docker 소켓 접근 제한
+- rootless 컨테이너 전환과 노드 파일 무결성 점검</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="17" t="inlineStr">
@@ -6307,16 +6411,20 @@
       </c>
       <c r="E33" s="17" t="inlineStr">
         <is>
-          <t>공격자는 특정 이벤트를 계기로 실행을 일으키는 시스템 메커니즘을 이용해 지속성을 확보하거나 권한을 높일 수 있다. 여러 운영체제에는 로그온이나 특정 애플리케이션·바이너리 실행 같은 사용자 활동 이벤트를 모니터링하고 구독하는 수단이 있다. 클라우드 환경도 특정 클라우드 이벤트를 모니터링하고 이에 대응해 호출되는 다양한 함수와 서비스를 지원할 수 있다.</t>
+          <t>- 공격자는 클라우드 이벤트에 반응하는 함수·웹훅·정책(이벤트 규칙·HTTP 트리거 등)을 등록해 지속성과 권한 상승을 확보할 수 있음
+- 트리거는 관리 ID·서비스 계정 권한으로 실행되고 특정 조건에서만 발동해, 상시 프로세스가 없어 탐지가 어려움</t>
         </is>
       </c>
       <c r="F33" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 2건)
-- Mini Shai-Hulud(S9043) — Containers, IaaS, SaaS 플랫폼 소프트웨어 [클라우드(복합)]
-- Pacu(S1091) — AWS [IaaS]
-■ 통합된 기법
-- T1546.004 Unix Shell Configuration Modification</t>
+          <t>■ 클라우드 관점
+- Azure: HTTP 트리거로 인증 없는 명령 실행(AZT503.1~503.3), Watcher 작업으로 이벤트 시 Runbook 실행(AZT504), DeployIfNotExists 정책으로 트리거 시 백도어 생성(AZT508), CloudShell .bashrc 수정으로 권한 상승(AZT403)
+- AWS: EventBridge 규칙으로 사용자 생성 등 이벤트에 Lambda 연결, 무단 API Gateway로 함수 외부 노출(AT1667.001)
+- K8s: 악성 어드미션 컨트롤러로 API 요청 가로채기·수정(MS-TA9015), EKS 구성 변조(AT1668)
+- 통합된 상위기법(T1546.004, Unix 셸 설정) 근거 포함
+■ 실제 사례
+- [ATT&amp;CK 사례] Pacu: CloudFormation 업로드·사용자/역할 생성 시 악성 Lambda가 발동하도록 S3 알림·트리거 설정 (ATT&amp;CK S1091)
+- [ATT&amp;CK 사례] Mini Shai-Hulud: AI 코딩 에이전트 설정 파일에 훅·runOn 조건을 넣어 이벤트 기반 실행 생성 (ATT&amp;CK S9043)</t>
         </is>
       </c>
       <c r="G33" s="17" t="inlineStr">
@@ -6351,7 +6459,7 @@
       </c>
       <c r="M33" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N33" s="17" t="inlineStr"/>
@@ -6427,7 +6535,16 @@
           <t>https://attack.mitre.org/techniques/T1546</t>
         </is>
       </c>
-      <c r="AF33" s="17" t="inlineStr"/>
+      <c r="AF33" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 이벤트 규칙·HTTP 트리거·웹훅·Watcher·정책(DeployIfNotExists) 생성·변경 이벤트
+- 어드미션 컨트롤러·EKS 구성 변경, 트리거가 관리 ID로 수행하는 비정상 작업
+■ 대응
+- 이벤트·정책·자동화 리소스 수정 권한 최소화, 인증 없는 트리거 금지
+- 자동화·정책 목록 정기 검토와 변경 알림</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="17" t="inlineStr">
@@ -6589,12 +6706,19 @@
       </c>
       <c r="E35" s="17" t="inlineStr">
         <is>
-          <t>공격자는 환경에 접근한 뒤 지속성을 확보하기 위해 클라우드 이미지나 컨테이너 이미지에 악성 코드를 심을 수 있다. AWS의 AMI(Amazon Machine Image), GCP 이미지, Azure 이미지와 Docker 같은 대중적인 컨테이너 런타임 이미지에 악성 코드나 백도어를 심을 수 있다. 악성코드 업로드(Upload Malware)와 달리 이 기법은 공격자가 피해자 환경의 레지스트리에 이미지를 심는 데 초점을 둔다. 인프라 프로비저닝 방식에 따라, 프로비저닝 도구가 항상 최신 이미지를 쓰도록 설정되어 있으면 지속적인 접근을 제공할 수 있다.</t>
+          <t>- 공격자는 피해 환경의 이미지 레지스트리에 악성코드·웹셸을 심은 클라우드·컨테이너 이미지를 저장해 지속성을 확보할 수 있음
+- 프로비저닝 도구가 항상 최신 이미지를 쓰도록 설정돼 있으면 새 인스턴스·파드가 생길 때마다 백도어가 재배포됨</t>
         </is>
       </c>
       <c r="F35" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- 대상: AWS AMI, GCP·Azure 이미지, 내부 컨테이너 레지스트리(ECR·ACR·GCR) — 공개 저장소에 올리는 악성코드 업로드와 달리 피해자 내부 레지스트리에 심는 데 초점
+- 침해된 레지스트리 이미지를 실행하면 클러스터 침해로 이어짐 (K8s MS-TA9002)
+- 클라우드 컨테이너 이미지에 백도어(웹셸)를 심는 도구가 공개되어 있고, 이미지 열람 권한이 있으면 가능
+- 사용자 오배포를 노리는 악성 이미지(CTC-EX-09.1)와 구분됨
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB·ATT&amp;CK 클라우드 사례에 매핑된 건은 없음(도구·벤더 문서화 수준)</t>
         </is>
       </c>
       <c r="G35" s="17" t="inlineStr">
@@ -6625,7 +6749,7 @@
       </c>
       <c r="M35" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N35" s="17" t="inlineStr">
@@ -6690,7 +6814,16 @@
           <t>https://attack.mitre.org/techniques/T1525</t>
         </is>
       </c>
-      <c r="AF35" s="17" t="inlineStr"/>
+      <c r="AF35" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 내부 레지스트리 이미지 푸시·태그 변경, 기준에서 벗어난 레이어·웹셸 포함 이미지
+- 프로비저닝이 참조하는 최신 태그 이미지의 예기치 않은 변경
+■ 대응
+- 레지스트리 푸시 권한 최소화·이미지 서명 검증, 배포 시 서명·스캔 통과 이미지만 허용
+- 태그 고정(다이제스트 핀)과 이미지 취약점·악성코드 스캔</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="17" t="inlineStr">
@@ -6715,16 +6848,20 @@
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
-          <t>공격자는 침해한 계정에 지속적으로 접근하기 위해 다중 인증(MFA) 메커니즘을 비활성화하거나 수정할 수 있다.</t>
+          <t>- 공격자는 침해 계정 유지를 위해 MFA를 비활성화하거나 취약한 MFA 수단으로 교체할 수 있으며, 탈취한 세션 토큰으로 MFA 자체를 건너뛰기도 함
+- 조건부 액세스에서 사용자 제외·'실패 시 허용(fail open)' 설정을 악용하면 계정 단위를 넘어 그룹 전체의 MFA가 무력화됨</t>
         </is>
       </c>
       <c r="F36" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례(사고 DB)
-- [실제 사고] BitoPro(2025-05, INC-0506): BitoPro의 클라우드 운영 직원이 소셜 엔지니어링과 악성코드로 침해되었다. 탈취된 AWS 세션 토큰으로 MFA가 우회되었고, 1,100만 달러 상당의 암호화폐가 탈취되었다.
-- [실제 사고] ByBit hack(2025-02, INC-0470): 2025년 2월 21일 북한 연계 TraderTraitor(UNC4899)가 Safe{Wallet}을 공격했다. 개발자 노트북을 침해해 AWS 세션 토큰을 가로채고 MFA를 우회한 뒤 Safe{Wallet} 서버에 무단 접근했다(ByBit 해킹).
-■ ATT&amp;CK 사례(행위자, 총 1건)
-- AADInternals(S0677) — Entra ID [ID·인증]</t>
+          <t>■ 클라우드 관점
+- Entra ID 등에서 조건부 액세스 사용자 제외, 공격자 제어 MFA 수단 등록(CTC-PE-01.5 연계), MFA 자가 등록 악용으로 요건 무력화
+- 가장 흔한 실제 경로는 피싱·단말 침해로 얻은 유효 세션·액세스 토큰으로 MFA를 건너뛰는 것 — 토큰이 이미 인증된 세션을 담고 있어 재인증이 필요 없음
+- 지속성(PE)·방어 무력화(DI)·자격증명 접근(CA) 세 전술에 걸침
+■ 실제 사례
+- [실제 사고] ByBit/Safe{Wallet}(2025-02): TraderTraitor(UNC4899)가 개발자 노트북을 침해해 AWS 세션 토큰을 가로채 MFA를 우회하고 서버에 무단 접근 (사고DB INC-0470)
+- [실제 사고] BitoPro(2025-05): 클라우드 운영 직원 침해로 탈취한 AWS 세션 토큰으로 MFA를 우회, 약 1,100만 달러 암호화폐 탈취 (사고DB INC-0506)
+- [ATT&amp;CK 사례] AADInternals: Set-AADIntUserMFA로 지정 사용자의 MFA 비활성화 (ATT&amp;CK S0677)</t>
         </is>
       </c>
       <c r="G36" s="17" t="inlineStr">
@@ -6755,7 +6892,7 @@
       </c>
       <c r="M36" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N36" s="17" t="inlineStr">
@@ -6824,7 +6961,16 @@
           <t>https://attack.mitre.org/techniques/T1556/006</t>
         </is>
       </c>
-      <c r="AF36" s="17" t="inlineStr"/>
+      <c r="AF36" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- MFA 비활성화·조건부 액세스 제외·MFA 수단 변경 이벤트, 같은 세션 토큰의 다른 IP 재사용
+- 'fail open' 구성과 MFA 요구가 사라진 로그인 성공
+■ 대응
+- 피싱 저항형 MFA(FIDO2)와 'fail open' 금지, MFA·조건부 액세스 변경에 다중 관리자 승인
+- 토큰 보호·세션 수명 단축, 의심 세션 토큰 즉시 폐기</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="17" t="inlineStr">
@@ -6849,14 +6995,19 @@
       </c>
       <c r="E37" s="17" t="inlineStr">
         <is>
-          <t>공격자는 일반 인증 메커니즘을 우회하고, 자격 증명에 접근하고, 계정에 지속적으로 접근하기 위해 온프레미스 사용자 ID와 연결된 클라우드 인증 절차에 패치를 적용하거나, 이를 수정하거나, 백도어를 심을 수 있다.</t>
+          <t>- 공격자는 온프레미스-클라우드 하이브리드 ID 연결(PHS·PTA·AD FS)에 백도어를 심어 모든 인증을 통과시키고 자격증명을 수집할 수 있음
+- 연동 지점 하나를 장악하면 페더레이션된 모든 클라우드·SaaS에 지속적 특권 접근이 가능해 피해 범위가 테넌트 전체로 확대됨</t>
         </is>
       </c>
       <c r="F37" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 2건)
-- AADInternals(S0677) — Entra ID [ID·인증]
-- APT29(G0016) — 클라우드(서비스 미상) [클라우드(복합)]</t>
+          <t>■ 클라우드 관점
+- Entra ID 동기화 세 방식이 표적: PTA 에이전트 서버에 악성 DLL(PTASpy) 주입으로 모든 인증 승인·자격증명 기록, AD FS 구성 변조로 임의 사용자 토큰 위조(Golden SAML 계열)
+- AD FS는 AWS·GCP 등 타 클라우드 페더레이션에도 쓰여, 한 번의 변조가 여러 클라우드로 파급
+- 하이브리드 조인 서버는 조건부 액세스 우회에도 악용됨 (CTC-PE-08.3 연계)
+■ 실제 사례
+- [ATT&amp;CK 사례] APT29: Microsoft.IdentityServer.Servicehost 구성을 수정해 AD FS에 악성 DLL을 로드, 페더레이션된 서비스에 지속 접근 (ATT&amp;CK G0016)
+- [ATT&amp;CK 사례] AADInternals: PTASpy DLL을 PTA 에이전트 서비스에 주입해 Pass-Through 인증을 백도어화 (ATT&amp;CK S0677)</t>
         </is>
       </c>
       <c r="G37" s="17" t="inlineStr">
@@ -6887,7 +7038,7 @@
       </c>
       <c r="M37" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N37" s="17" t="inlineStr">
@@ -6948,7 +7099,16 @@
           <t>https://attack.mitre.org/techniques/T1556/007</t>
         </is>
       </c>
-      <c r="AF37" s="17" t="inlineStr"/>
+      <c r="AF37" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- PTA 에이전트·AD FS 서버의 DLL 로드·구성 파일 변경, 토큰 서명 인증서의 비정상 사용
+- 온프레미스 조인 서버에서 발급된 토큰의 광범위한 클라우드 접근
+■ 대응
+- 하이브리드 ID 연동 서버를 Tier0로 취급·접근 최소화, 토큰 서명 인증서 보호·정기 교체
+- AD FS → 클라우드 인증의 이상 토큰 탐지, 가능 시 클라우드 인증으로 전환</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="17" t="inlineStr">
@@ -6973,14 +7133,19 @@
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t>공격자는 침해한 계정에 지속적으로 접근하기 위해 조건부 액세스 정책을 비활성화하거나 수정할 수 있다. 조건부 액세스 정책은 ID 공급자와 ID·접근 관리 시스템이 사용자에게 리소스 접근을 허용할지 판단할 때 쓰는 추가 검증이다.</t>
+          <t>- 공격자는 조건부 액세스·IAM 조건 정책을 수정해(신뢰 IP 추가, MFA 요구 제거, 허용 리전 확대) 침해 계정의 접근을 지속할 수 있음
+- 정책 완화는 정상 관리 변경처럼 보여, 이후 탈취 자격증명이 통제를 그대로 통과하게 만듦</t>
         </is>
       </c>
       <c r="F38" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 2건)
-- Scattered Spider(G1015) — Entra ID [ID·인증]
-- Storm-0501(G1053) — 클라우드(서비스 미상) [클라우드(복합)]</t>
+          <t>■ 클라우드 관점
+- IdP(Entra ID·Okta·JumpCloud): 신뢰 위치 추가, MFA·장치 등록·위험 기반 차단 조건 완화
+- AWS·GCP: IAM 정책의 조건 속성(source IP·요청 시각·리전) 변경으로 제약 무력화
+- 미사용 리전 허용(CTC-ST-05)과 결합되어 탐지 사각에서 접근 지속
+■ 실제 사례
+- [ATT&amp;CK 사례] Scattered Spider: Azure 조건부 액세스 정책에 신뢰 위치를 추가 (ATT&amp;CK G1015)
+- [ATT&amp;CK 사례] Storm-0501: 자체 MFA 수단을 등록하고 하이브리드 조인 서버로 조건부 액세스를 우회 (ATT&amp;CK G1053)</t>
         </is>
       </c>
       <c r="G38" s="17" t="inlineStr">
@@ -7011,7 +7176,7 @@
       </c>
       <c r="M38" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N38" s="17" t="inlineStr">
@@ -7072,7 +7237,16 @@
           <t>https://attack.mitre.org/techniques/T1556/009</t>
         </is>
       </c>
-      <c r="AF38" s="17" t="inlineStr"/>
+      <c r="AF38" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 조건부 액세스·IAM 조건 정책 변경(신뢰 IP 추가·MFA 제거·리전 확대) 이벤트
+- 정책 완화 직후 새 위치·리전에서의 로그인 성공
+■ 대응
+- 조건부 액세스·IAM 정책 변경에 승인 워크플로와 변경 알림
+- 정책을 코드로 관리(IaC)하고 드리프트 자동 복원</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="17" t="inlineStr">
@@ -7097,12 +7271,17 @@
       </c>
       <c r="E39" s="17" t="inlineStr">
         <is>
-          <t>공격자는 Microsoft Office 템플릿을 악용해 침해한 시스템에서 지속성을 확보할 수 있다. Microsoft Office에는 일반 Office 애플리케이션에 포함되어 스타일을 사용자 지정하는 데 쓰이는 템플릿이 있다. 애플리케이션의 기본 템플릿은 애플리케이션이 시작될 때마다 사용된다.</t>
+          <t>- 공격자는 M365 Office의 기본 템플릿(Normal.dotm 등)에 악성 VBA 매크로를 넣어 Office 실행 때마다 코드가 돌게 할 수 있음
+- 공유 템플릿을 원격에서 가져오게 하거나 GlobalDotName을 바꿔 임의 템플릿을 로드시키는 변형이 있음</t>
         </is>
       </c>
       <c r="F39" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- Office Suite(M365) 클라이언트 지속성 기법으로, 클라우드 자체보다 M365 사용자 단말에 작용 — 침해한 메일·SharePoint로 악성 템플릿을 배포·동기화하는 경로와 연계될 수 있음
+- 매크로 실행은 조직 매크로 정책에 따라 제약되며, 신뢰 위치·신뢰 문서 등록이 전제되는 경우가 있음
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB·ATT&amp;CK 클라우드 사례에 매핑된 건은 없음(기법 문서화 수준)</t>
         </is>
       </c>
       <c r="G39" s="17" t="inlineStr">
@@ -7133,7 +7312,7 @@
       </c>
       <c r="M39" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N39" s="17" t="inlineStr"/>
@@ -7190,7 +7369,15 @@
           <t>https://attack.mitre.org/techniques/T1137/001</t>
         </is>
       </c>
-      <c r="AF39" s="17" t="inlineStr"/>
+      <c r="AF39" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- Normal.dotm 등 기본 템플릿 변경, GlobalDotName 레지스트리 변경, 원격 템플릿 로드
+- Office 프로세스의 매크로 기반 자식 프로세스 생성
+■ 대응
+- 신뢰 위치 외 매크로 차단·인터넷 출처 매크로 차단 정책(M365), 템플릿 파일 무결성 점검</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="17" t="inlineStr">
@@ -7215,12 +7402,17 @@
       </c>
       <c r="E40" s="17" t="inlineStr">
         <is>
-          <t>공격자는 Microsoft Office의 Office Test 레지스트리 키를 악용해 침해한 시스템에서 지속성을 확보할 수 있다. Office Test 레지스트리 위치를 이용하면 Office 애플리케이션이 시작될 때마다 실행될 임의의 DLL을 지정할 수 있다. 이 레지스트리 키는 Microsoft가 Office 애플리케이션을 개발하면서 테스트와 디버깅용 DLL을 불러오는 데 쓰는 것으로 알려져 있으며, Office 설치 시 기본으로 생성되지는 않는다.</t>
+          <t>- 공격자는 Office Test 레지스트리 키에 악성 DLL을 지정해 Office 실행 때마다 로드되게 할 수 있음
+- 기본 생성되지 않는 키라 존재 자체가 이상 징후이며, 단말 지속성 수단으로 쓰임</t>
         </is>
       </c>
       <c r="F40" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- Office Suite(M365) 클라이언트 단말 지속성 기법으로, 클라우드 제어 평면과 직접 관련은 낮음 — M365 계정 침해 후 단말 상주 수단으로 결합될 수 있음
+- HKCU·HKLM의 Office test\Special\Perf 키에 DLL 경로를 지정
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB·ATT&amp;CK 클라우드 사례에 매핑된 건은 없음(기법 문서화 수준)</t>
         </is>
       </c>
       <c r="G40" s="17" t="inlineStr">
@@ -7251,7 +7443,7 @@
       </c>
       <c r="M40" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N40" s="17" t="inlineStr"/>
@@ -7308,7 +7500,14 @@
           <t>https://attack.mitre.org/techniques/T1137/002</t>
         </is>
       </c>
-      <c r="AF40" s="17" t="inlineStr"/>
+      <c r="AF40" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- Office test\Special\Perf 레지스트리 키 생성과 지정 DLL 로드
+■ 대응
+- 해당 레지스트리 키 모니터링·차단, 단말 EDR로 Office의 비정상 DLL 로드 탐지</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="17" t="inlineStr">
@@ -7333,13 +7532,17 @@
       </c>
       <c r="E41" s="17" t="inlineStr">
         <is>
-          <t>공격자는 Microsoft Outlook 양식(form)을 악용해 침해한 시스템에서 지속성을 확보할 수 있다. Outlook 양식은 Outlook 메시지의 표시와 기능을 정의하는 템플릿으로 쓰인다. 사용자 지정 Outlook 양식을 만들어 두면, 공격자가 같은 사용자 지정 양식을 이용해 특수하게 만든 이메일을 보낼 때 코드가 실행되게 할 수 있다.</t>
+          <t>- 공격자는 침해한 사서함에 악성 Outlook 양식을 심어, 특수 제작 메일을 받을 때 코드가 실행되게 지속성을 확보할 수 있음
+- 사서함에 저장되므로 단말을 재설치해도 남고, M365 사서함 침해 후 지속 수단으로 쓰임</t>
         </is>
       </c>
       <c r="F41" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 1건)
-- Ruler(S0358) — Office Suite 플랫폼 소프트웨어 [SaaS·협업]</t>
+          <t>■ 클라우드 관점
+- Exchange Online(M365) 사서함에 작용하는 지속성 기법 — 사서함 데이터에 양식이 저장되어 Outlook 시작 시 로드됨
+- 사서함 권한 탈취(CTC-PE-01.2)와 결합되며, Ruler 같은 도구로 자동화됨
+■ 실제 사례
+- [ATT&amp;CK 사례] Ruler: Outlook 양식 악용을 자동화해 지속성 확보 (ATT&amp;CK S0358)</t>
         </is>
       </c>
       <c r="G41" s="17" t="inlineStr">
@@ -7370,7 +7573,7 @@
       </c>
       <c r="M41" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N41" s="17" t="inlineStr"/>
@@ -7427,7 +7630,14 @@
           <t>https://attack.mitre.org/techniques/T1137/003</t>
         </is>
       </c>
-      <c r="AF41" s="17" t="inlineStr"/>
+      <c r="AF41" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 사서함의 사용자 지정 Outlook 양식 추가, Ruler 사용 흔적(비정상 EWS/MAPI 요청)
+■ 대응
+- 사용자 지정 양식 사용 제한, 사서함 규칙·양식 정기 감사, 사서함 권한 최소화</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="17" t="inlineStr">
@@ -7452,13 +7662,17 @@
       </c>
       <c r="E42" s="17" t="inlineStr">
         <is>
-          <t>공격자는 Microsoft Outlook의 홈페이지 기능을 악용해 침해한 시스템에서 지속성을 확보할 수 있다. Outlook 홈페이지는 Outlook 폴더의 표시 방식을 사용자 지정하는 레거시 기능으로, 폴더를 열 때마다 내부 또는 외부 URL을 불러와 표시할 수 있다. Outlook 홈페이지가 불러올 때 코드가 실행되도록 악성 HTML 페이지를 만들 수 있다.</t>
+          <t>- 공격자는 Outlook 홈페이지 기능에 악성 URL을 지정해, 해당 폴더를 열 때마다 원격 코드가 실행되게 할 수 있음
+- 사서함 설정에 저장되어 단말 재설치에도 남으며, M365 사서함 지속성 수단이 됨</t>
         </is>
       </c>
       <c r="F42" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 1건)
-- Ruler(S0358) — Office Suite 플랫폼 소프트웨어 [SaaS·협업]</t>
+          <t>■ 클라우드 관점
+- Exchange Online(M365) 사서함 설정에 작용 — 폴더 로드 시 내부·외부 URL의 HTML을 불러와 코드 실행
+- 사서함 권한 탈취와 결합되며 Ruler로 자동화됨
+■ 실제 사례
+- [ATT&amp;CK 사례] Ruler: Outlook 홈페이지 악용을 자동화해 지속성 확보 (ATT&amp;CK S0358)</t>
         </is>
       </c>
       <c r="G42" s="17" t="inlineStr">
@@ -7489,7 +7703,7 @@
       </c>
       <c r="M42" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N42" s="17" t="inlineStr"/>
@@ -7546,7 +7760,14 @@
           <t>https://attack.mitre.org/techniques/T1137/004</t>
         </is>
       </c>
-      <c r="AF42" s="17" t="inlineStr"/>
+      <c r="AF42" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 사서함의 Outlook 홈페이지 URL 설정 추가·변경
+■ 대응
+- 홈페이지 기능 비활성화(그룹 정책), 사서함 설정 변경 감사</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="17" t="inlineStr">
@@ -7571,13 +7792,17 @@
       </c>
       <c r="E43" s="17" t="inlineStr">
         <is>
-          <t>공격자는 Microsoft Outlook 규칙을 악용해 침해한 시스템에서 지속성을 확보할 수 있다. Outlook 규칙은 사용자가 이메일 메시지를 관리하는 자동 동작을 정의할 수 있게 한다. 예를 들어 정상적인 규칙은 특정 발신자의 이메일에 특정 단어가 있으면 Outlook의 특정 폴더로 자동 이동시킬 수 있다. 공격자가 특수하게 만든 이메일을 해당 사용자에게 보내면 코드가 실행되도록 악성 Outlook 규칙을 만들 수 있다.</t>
+          <t>- 공격자는 악성 Outlook 규칙을 만들어, 특수 제작 메일 수신을 조건으로 코드가 실행되게 지속성을 확보할 수 있음
+- 사서함에 저장되는 규칙이라 단말과 무관하게 유지되며, 메일 숨김 규칙과 함께 은닉에도 쓰임</t>
         </is>
       </c>
       <c r="F43" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 1건)
-- Ruler(S0358) — Office Suite 플랫폼 소프트웨어 [SaaS·협업]</t>
+          <t>■ 클라우드 관점
+- Exchange Online(M365) 사서함 규칙에 작용 — 특정 조건 메일 수신 시 동작하도록 규칙 구성
+- 사서함 권한 탈취와 결합되며 Ruler로 자동화, 이메일 숨김 규칙(CTC-ST-01.1)과 연계
+■ 실제 사례
+- [ATT&amp;CK 사례] Ruler: Outlook 규칙 악용을 자동화해 지속성 확보 (ATT&amp;CK S0358)</t>
         </is>
       </c>
       <c r="G43" s="17" t="inlineStr">
@@ -7608,7 +7833,7 @@
       </c>
       <c r="M43" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N43" s="17" t="inlineStr"/>
@@ -7665,7 +7890,14 @@
           <t>https://attack.mitre.org/techniques/T1137/005</t>
         </is>
       </c>
-      <c r="AF43" s="17" t="inlineStr"/>
+      <c r="AF43" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 코드 실행과 연계된 Outlook 규칙 생성, Ruler 사용 흔적
+■ 대응
+- 클라이언트 측 규칙 제한, 사서함 규칙 정기 감사와 이상 규칙 알림</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="17" t="inlineStr">
@@ -7690,12 +7922,17 @@
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t>공격자는 Microsoft Office 추가 기능(add-in)을 악용해 침해한 시스템에서 지속성을 확보할 수 있다. Office 추가 기능은 Office 프로그램에 기능을 더하는 데 쓰인다. 여러 Office 제품에서 쓸 수 있는 추가 기능 유형은 다양하며, Word/Excel 추가 기능 라이브러리(WLL/XLL), VBA 추가 기능, Office COM(Component Object Model) 추가 기능, 자동화 추가 기능, VBA 편집기(VBE), VSTO(Visual Studio Tools for Office) 추가 기능, Outlook 추가 기능 등이 있다.</t>
+          <t>- 공격자는 Office 추가 기능(WLL/XLL·VBA·COM·VSTO·Outlook 추가 기능 등)을 등록해 Office 실행 시 코드가 실행되게 할 수 있음
+- 정상 확장 기능으로 보여 탐지가 어렵고, M365 단말 지속성 수단으로 쓰임</t>
         </is>
       </c>
       <c r="F44" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- Office Suite(M365) 클라이언트 지속성 기법으로 클라우드 제어 평면과 직접 관련은 낮음 — M365 계정 침해 후 단말 상주 수단으로 결합될 수 있음
+- 다양한 추가 기능 유형이 시작 시 코드 실행 지점으로 악용됨
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB·ATT&amp;CK 클라우드 사례에 매핑된 건은 없음(기법 문서화 수준)</t>
         </is>
       </c>
       <c r="G44" s="17" t="inlineStr">
@@ -7726,7 +7963,7 @@
       </c>
       <c r="M44" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N44" s="17" t="inlineStr"/>
@@ -7783,7 +8020,14 @@
           <t>https://attack.mitre.org/techniques/T1137/006</t>
         </is>
       </c>
-      <c r="AF44" s="17" t="inlineStr"/>
+      <c r="AF44" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- Office 추가 기능(WLL/XLL·VSTO·COM 등) 신규 등록과 시작 시 로드
+■ 대응
+- 서명된 추가 기능만 허용, 추가 기능 설치 제한 정책 적용</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="17" t="inlineStr">
@@ -8401,12 +8645,19 @@
       </c>
       <c r="E49" s="17" t="inlineStr">
         <is>
-          <t>공격자는 클라우드 리소스에 대한 일시적으로 높은 접근 권한을 얻을 수 있는 권한 구성을 악용할 수 있다. 많은 클라우드 환경에서는 관리자가 사용자나 서비스 계정에 역할에 대한 JIT(Just-in-Time) 접근 요청, 다른 계정 가장, 리소스·서비스에 역할 전달 등 자신과 다른 권한 집합에 단기간 접근하는 권한을 부여할 수 있다.</t>
+          <t>- 공격자는 JIT 접근 요청·계정 가장·역할 전달 같은 일시적 권한 상승 기능을 악용해 자신에게 없는 권한을 단기간 획득할 수 있음
+- 정상적인 권한 위임 기능을 쓰므로 별도 역할 부여 흔적이 적고, 자동 승인 설정이면 즉시 상승이 가능함</t>
         </is>
       </c>
       <c r="F49" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- JIT: 자동 승인으로 구성된 PIM 등 적격 역할 활성화로 권한 상승(Azure ATRM AZT401)
+- 계정 가장: GCP iam.serviceAccountTokenCreator로 서비스 계정 토큰 생성, 도메인 전체 위임으로 Workspace 계정 가장, Exchange ApplicationImpersonation
+- 역할 전달: AWS PassRole로 생성 리소스에 역할 부여, GCP iam.serviceAccountUser로 서비스 계정 연결 — 리소스를 통해 간접적으로 그 역할 권한 사용
+- Organizations 구성원 계정의 루트 역할 획득(AWS AT1669) 포함
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB에 이 기법으로 매핑된 사고는 없음(벤더 매트릭스·ATT&amp;CK 문서화 수준). 서버리스 함수에 역할을 붙이는 인접 기법은 CTC-EX-07에서 다룸</t>
         </is>
       </c>
       <c r="G49" s="17" t="inlineStr">
@@ -8437,7 +8688,7 @@
       </c>
       <c r="M49" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N49" s="17" t="inlineStr">
@@ -8506,7 +8757,16 @@
           <t>https://attack.mitre.org/techniques/T1548/005</t>
         </is>
       </c>
-      <c r="AF49" s="17" t="inlineStr"/>
+      <c r="AF49" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- PIM 역할 활성화, 서비스 계정 토큰 생성(serviceAccountTokenCreator), PassRole·역할 전달 이벤트
+- 활성화된 권한으로 수행되는 평소와 다른 고권한 작업
+■ 대응
+- JIT·가장·역할 전달 권한 최소화와 자동 승인 지양(수동 승인), 고권한 역할은 PIM·승인 연계
+- PassRole 대상 역할 범위 제한과 사용 감사</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="17" t="inlineStr">
@@ -8531,20 +8791,21 @@
       </c>
       <c r="E50" s="17" t="inlineStr">
         <is>
-          <t>공격자는 환경 안의 피해 계정과 인스턴스에 대한 지속적인 접근을 유지하기 위해 클라우드 계정에 공격자가 제어하는 자격 증명을 추가할 수 있다.</t>
+          <t>- 공격자는 장악한 IAM 사용자·서비스 주체·앱에 자신의 액세스 키·비밀·인증서·SSH 키를 추가해 지속 접근 경로를 확보할 수 있음
+- 추가된 자격증명은 원 계정이 회수돼도 유효하고 MFA를 거치지 않으며, 대상이 고권한이면 권한 상승으로도 이어짐</t>
         </is>
       </c>
       <c r="F50" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례(사고 DB)
-- [실제 사고] Credentials exposed in public S3 buckets(2025-11, INC-0573): 공개 S3 버킷에 노출된 자격증명으로 침투해 Lambda 코드 주입, IAM 액세스 키 생성, 백도어 관리자 사용자 생성을 수행했다. 이후 LLMjacking과 GPU 인스턴스 생성에 악용했다(Sysdig 사례).
-■ ATT&amp;CK 사례(행위자, 총 6건)
-- TeamPCP(G1056) — GitHub·GitLab [SaaS·협업]
-- Shai-Hulud(S9008) — GitHub·GitLab [SaaS·협업]
-- C0027(C0027) — AWS [IaaS]
-- Pacu(S1091) — AWS [IaaS]
-■ 통합된 기법
-- T1098 Account Manipulation</t>
+          <t>■ 클라우드 관점
+- AWS: iam:CreateAccessKey로 기존 사용자에 두 번째 키 발급, CreateLoginProfile로 콘솔 비밀번호 추가, EC2 키페어 생성·가져오기 (AWS TTC T1098.001)
+- Entra ID: 앱·서비스 주체에 비밀·x509 인증서 추가(Azure ATRM AZT501.2·AZT405.3) — 애플리케이션 관리자 역할은 다른 앱 서비스 주체에 자격증명을 더해 그 앱 권한으로 로그인
+- GCP: 서비스 계정 키 생성, OS Login SSH 키 추가
+- 통합된 상위기법(T1098)에는 Cognito 리프레시 토큰 재사용(T1098.A006), 알림을 막는 AWS Support 케이스 종료(T1098.A001)도 포함
+■ 실제 사례
+- [실제 사고] 공개 S3 버킷 자격증명 악용(2025-11): 노출 자격증명으로 침투해 IAM 액세스 키와 백도어 관리자를 추가한 뒤 LLMjacking·GPU 인스턴스 생성에 악용 (사고DB INC-0573)
+- [ATT&amp;CK 사례] SolarWinds 침해: APT29가 OAuth 앱·서비스 주체에 자격증명을 추가해 지속 접근 (ATT&amp;CK C0024)
+- [ATT&amp;CK 사례] C0027: Scattered Spider가 가짜 사용자용 임시 페더레이션 자격증명을 만들어 침해 키를 숨기고 MFA 없이 콘솔 세션으로 전환 (ATT&amp;CK C0027)</t>
         </is>
       </c>
       <c r="G50" s="17" t="inlineStr">
@@ -8579,7 +8840,7 @@
       </c>
       <c r="M50" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N50" s="17" t="inlineStr">
@@ -8664,7 +8925,16 @@
           <t>https://attack.mitre.org/techniques/T1098/001</t>
         </is>
       </c>
-      <c r="AF50" s="17" t="inlineStr"/>
+      <c r="AF50" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 감사 로그의 CreateAccessKey·CreateLoginProfile·키페어 생성, 서비스 주체·앱 자격증명 추가 이벤트
+- 한 사용자에 다수 액세스 키 존재, 새 키가 낯선 출발지에서 즉시 사용되는 패턴
+■ 대응
+- 사용자당 액세스 키 수 제한·정기 회수, 자격증명 추가 권한(iam:CreateAccessKey 등) 최소화
+- 앱·서비스 주체 자격증명 추가에 대한 알림과 승인 절차</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="17" t="inlineStr">
@@ -8689,13 +8959,19 @@
       </c>
       <c r="E51" s="17" t="inlineStr">
         <is>
-          <t>공격자는 자신이 제어하는 이메일 계정에 대한 지속적인 접근을 유지하기 위해 추가 권한 수준을 부여할 수 있다.</t>
+          <t>- 공격자는 Exchange Online·Google Workspace에서 사서함 위임·폴더 권한·앱 가장 권한을 부여해 다른 계정으로 대상 사서함을 계속 열람할 수 있음
+- 원 계정 비밀번호가 바뀌어도 위임 권한은 남아, 장기 첩보 수집과 BEC의 기반이 됨</t>
         </is>
       </c>
       <c r="F51" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 1건)
-- APT29(G0016) — Entra ID [ID·인증]</t>
+          <t>■ 클라우드 관점
+- Exchange Online: Add-MailboxPermission으로 사서함 권한 부여, 받은편지함·최상위 폴더에 Default·Anonymous 권한을 주면 테넌트 내 어느 계정으로도 열람 가능
+- Google Workspace: 관리 콘솔·Gmail 설정의 메일 위임 기능
+- 서비스 주체에 사서함 가장 권한(ApplicationImpersonation 등)을 붙이면 사용자 로그인 없이 다수 사서함을 API로 수집 가능
+- BEC·내부 피싱(CTC-LM-02)과 이메일 숨김 규칙(CTC-ST-01.1)으로 이어짐
+■ 실제 사례
+- [ATT&amp;CK 사례] APT29: 침해한 전역 관리자 계정으로 ApplicationImpersonation 권한을 가진 서비스 주체를 백도어화해 대상 사서함에서 메일 수집 (ATT&amp;CK G0016)</t>
         </is>
       </c>
       <c r="G51" s="17" t="inlineStr">
@@ -8726,7 +9002,7 @@
       </c>
       <c r="M51" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N51" s="17" t="inlineStr">
@@ -8787,7 +9063,16 @@
           <t>https://attack.mitre.org/techniques/T1098/002</t>
         </is>
       </c>
-      <c r="AF51" s="17" t="inlineStr"/>
+      <c r="AF51" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- Add-MailboxPermission·위임 추가, 폴더에 Default·Anonymous 권한 부여, 서비스 주체 가장 권한 부여 이벤트
+- 사용자 로그인 없이 서비스 주체로 다수 사서함을 조회하는 패턴
+■ 대응
+- 사서함 위임·가장 권한 정기 검토와 최소화, ApplicationImpersonation 범위 제한
+- 고권한 역할 부여 알림과 조건부 액세스 적용</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="17" t="inlineStr">
@@ -8812,18 +9097,21 @@
       </c>
       <c r="E52" s="17" t="inlineStr">
         <is>
-          <t>공격자는 테넌트에 대한 지속적인 접근을 유지하기 위해 자신이 제어하는 클라우드 계정에 역할이나 권한을 추가할 수 있다. 예를 들어 클라우드 환경에서 IAM 정책을 수정하거나 Office 365 환경에 새 전역 관리자를 추가할 수 있다. 권한이 충분하면 침해된 계정이 데이터와 설정에 거의 무제한으로 접근할 수 있다(다른 관리자의 비밀번호 재설정 포함).</t>
+          <t>- 공격자는 장악·생성한 클라우드 계정에 IAM 역할·정책이나 전역 관리자 역할을 추가해 테넌트 전반에 지속 접근과 권한 상승을 확보할 수 있음
+- 피해 테넌트 밖의 공격자 계정에 역할을 부여하면 계정 생성·수정 없이도 내부 작업이 가능해 추적이 어려움</t>
         </is>
       </c>
       <c r="F52" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 5건)
-- Scattered Spider(G1015) — Azure [IaaS]
-- Storm-0501(G1053) — Azure [IaaS]
-- C0027(C0027) — AWS [IaaS]
-- LAPSUS$(G1004) — 클라우드(서비스 미상) [클라우드(복합)]
-■ 통합된 기법
-- T1078.003 Local Accounts</t>
+          <t>■ 클라우드 관점
+- AWS: iam:AttachUserPolicy·CreatePolicyVersion·AttachRolePolicy, IAM Identity Center 할당으로 권한 추가 (AWS TTC T1098.003)
+- Entra ID: 새 전역 관리자 추가, elevateAccess 토글로 테넌트 루트 관리 권한 획득(Azure ATRM AZT402)
+- K8s: cluster-admin RoleBinding 부여로 클러스터 전체 권한 (K8s MS-TA9019)
+- 외부 계정에 역할·권한을 부여하는 변형과 통합된 상위기법(T1078.003) 근거 포함
+■ 실제 사례
+- [ATT&amp;CK 사례] Storm-0501: elevateAccess·roleAssignments/write로 피해 구독의 User Access Administrator·Owner 역할 획득 (ATT&amp;CK G1053)
+- [ATT&amp;CK 사례] Scattered Spider: User Access Administrator 역할을 할당해 Azure 테넌트 루트 그룹 관리 권한 확보 (ATT&amp;CK G1015)
+- [ATT&amp;CK 사례] LAPSUS$: 피해 클라우드 인스턴스에 만든 계정에 전역 관리자 역할 부여 (ATT&amp;CK G1004)</t>
         </is>
       </c>
       <c r="G52" s="17" t="inlineStr">
@@ -8858,7 +9146,7 @@
       </c>
       <c r="M52" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N52" s="17" t="inlineStr">
@@ -8931,7 +9219,16 @@
           <t>https://attack.mitre.org/techniques/T1098/003</t>
         </is>
       </c>
-      <c r="AF52" s="17" t="inlineStr"/>
+      <c r="AF52" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- IAM 정책 연결·역할 생성·AssumeRolePolicy 변경, elevateAccess, 전역 관리자 추가 이벤트
+- 외부 계정을 신뢰 주체로 추가하는 역할 신뢰 정책 변경, cluster-admin 바인딩 생성
+■ 대응
+- 권한 변경을 PR·승인 워크플로로 통제, 고권한 역할 부여에 PIM·다중 승인
+- 외부 신뢰 계정 허용 목록화, RBAC 정기 검토</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="17" t="inlineStr">
@@ -8956,12 +9253,18 @@
       </c>
       <c r="E53" s="17" t="inlineStr">
         <is>
-          <t>공격자는 SSH authorized_keys 파일을 수정해 피해 호스트에서 지속성을 유지할 수 있다. Linux 배포판, macOS, ESXi 하이퍼바이저는 원격 관리용 SSH 세션의 인증 과정을 보호하기 위해 보통 키 기반 인증을 사용한다. SSH의 authorized_keys 파일은 해당 파일이 설정된 사용자 계정에 로그인할 때 쓸 수 있는 SSH 키를 지정한다. 이 파일은 보통 사용자 홈 디렉터리의 &lt;user-home&gt;/.ssh/authorized_keys에 있다(ESXi는 /etc/ssh/keys-&lt;username&gt;/authorized_keys). 사용자는 시스템의 SSH 설정 파일에서 PubkeyAuthentication과 RSAAuthentication 지시어를 yes로 바꿔 공개 키 인증과 RSA 인증을 활성화하고, PermitRootLogin 지시어를 yes로 바꿔 SSH를 통한 root 인증을 허용할 수 있다. SSH 설정 파일은 보통 /etc/ssh/sshd_config에 있다.</t>
+          <t>- 공격자는 VM의 SSH authorized_keys를 클라우드 CLI·API로 수정해 자신의 공개키로 인스턴스에 지속 접근할 수 있음
+- 더 높은 권한 사용자에 키를 추가하면 권한 상승이 되며, 제어 평면 경유 변경이라 호스트 로그만으로는 탐지가 어려움</t>
         </is>
       </c>
       <c r="F53" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- 호스트 직접 수정뿐 아니라 제어 평면 경로가 핵심: GCP compute os-login/add-metadata, Azure VM authorized_keys PATCH, AWS EC2 Instance Connect·키페어로 키 투입
+- 추가 키가 붙는 대상 사용자 권한에 따라 VM 내 권한 상승으로 이어짐
+- 네트워크 장비도 ip ssh pubkey-chain으로 유사 악용 가능
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB·ATT&amp;CK 클라우드 사례에 매핑된 건은 없음(제어 평면 키 투입 가능성은 ATT&amp;CK 원문에 문서화)</t>
         </is>
       </c>
       <c r="G53" s="17" t="inlineStr">
@@ -8992,7 +9295,7 @@
       </c>
       <c r="M53" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N53" s="17" t="inlineStr">
@@ -9053,7 +9356,16 @@
           <t>https://attack.mitre.org/techniques/T1098/004</t>
         </is>
       </c>
-      <c r="AF53" s="17" t="inlineStr"/>
+      <c r="AF53" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 제어 평면의 VM 메타데이터·authorized_keys 변경(GCP set-metadata, Azure VM PATCH), EC2 키페어 투입 이벤트
+- VM 내 authorized_keys 파일 변경과 신규 키로의 SSH 로그인
+■ 대응
+- VM 메타데이터·키 변경 권한 최소화, OS Login·중앙 키 관리로 개별 키 투입 차단
+- 불변 인프라·구성 드리프트 점검으로 비인가 키 탐지</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="17" t="inlineStr">
@@ -9078,14 +9390,19 @@
       </c>
       <c r="E54" s="17" t="inlineStr">
         <is>
-          <t>공격자는 자신이 제어하는 계정에 장치를 등록할 수 있다. 장치는 네트워크 인증을 처리하는 다중 인증(MFA) 시스템이나, 장치 접근과 규정 준수를 관리하는 장치 관리 시스템에 등록될 수 있다.</t>
+          <t>- 공격자는 탈취한 자격증명으로 자신의 장치를 피해 계정의 MFA·장치 관리 시스템(Entra ID·Intune·Duo·Okta)에 등록해 지속 접근을 확보할 수 있음
+- 등록된 장치는 조건부 액세스의 '관리 장치' 조건을 충족해 이후 MFA·정책을 통과하고, 내부 발신 메일로 신뢰도 높은 피싱도 가능</t>
         </is>
       </c>
       <c r="F54" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 2건)
-- APT29(G0016) — Entra ID [ID·인증]
-- AADInternals(S0677) — Entra ID [ID·인증]</t>
+          <t>■ 클라우드 관점
+- 자격증명을 얻은 뒤 신규 MFA 장치를 등록하면 초기 MFA 요건을 우회하고 지속 접근을 확보 — 비활성 계정은 사용자명·비밀번호만으로 첫 장치 등록이 가능한 경우가 있음
+- Entra ID에 장치·VM을 등록하면 조건부 액세스 정책을 우회하고 민감 리소스 접근 가능
+- 대량 장치 등록으로 테넌트에 서비스 소모(DoS)를 유발하기도 함
+■ 실제 사례
+- [ATT&amp;CK 사례] APT29: 비활성 계정 암호 추측 성공 후 Entra ID에 자신의 장치를 MFA로 등록 (ATT&amp;CK G0016)
+- [ATT&amp;CK 사례] AADInternals: Entra ID에 장치를 등록하는 기능 제공 (ATT&amp;CK S0677)</t>
         </is>
       </c>
       <c r="G54" s="17" t="inlineStr">
@@ -9116,7 +9433,7 @@
       </c>
       <c r="M54" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N54" s="17" t="inlineStr">
@@ -9177,7 +9494,16 @@
           <t>https://attack.mitre.org/techniques/T1098/005</t>
         </is>
       </c>
-      <c r="AF54" s="17" t="inlineStr"/>
+      <c r="AF54" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 신규 MFA 장치·장치 등록 이벤트, 특히 비활성 계정·암호 추측 직후의 등록
+- 단기간 대량 장치 등록, 신규 등록 장치의 즉시 민감 리소스 접근
+■ 대응
+- 장치 등록에 추가 인증·관리자 승인, 조건부 액세스로 등록 가능 조건 제한
+- MFA 자가 등록 제한과 신규 장치 알림</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="17" t="inlineStr">
@@ -9202,13 +9528,19 @@
       </c>
       <c r="E55" s="17" t="inlineStr">
         <is>
-          <t>공격자는 개별 호스트에서 데몬, 에이전트, 서비스로 실행되는 컨테이너·컨테이너 클러스터 관리 도구를 만들거나 수정할 수 있다. 여기에는 Docker, Podman 같은 컨테이너 생성·관리 소프트웨어와 kubelet 같은 클러스터 노드 에이전트가 포함된다. 이러한 서비스를 수정하면 호스트에서 지속성을 확보하거나 권한을 높일 수 있다.</t>
+          <t>- 공격자는 컨테이너 런타임·노드 에이전트를 재시작 유지 설정으로 만들거나 수정해 호스트에서 지속성을 확보하고 권한을 높일 수 있음
+- DaemonSet·정적 파드·restart=always로 노드마다 자동 상주시키며, rootful Docker 접근은 그대로 호스트 권한 상승 경로가 됨</t>
         </is>
       </c>
       <c r="F55" s="17" t="inlineStr">
         <is>
-          <t>■ 통합된 기법
-- T1543 Create or Modify System Process</t>
+          <t>■ 클라우드 관점
+- docker/podman run --restart=always로 호스트에 상주 컨테이너 구성, DaemonSet으로 신규 노드 포함 전 노드에 배포(CTC-EX-04 연계)
+- API 서버가 관찰하지 않는 정적 파드(K8s MS-TA9017)와 백도어 컨테이너(MS-TA9012)로 은폐 지속
+- rootful docker 명령 접근자는 호스트 권한 상승 가능, 컨테이너를 systemd 서비스로 등록하는 변형 포함
+- 통합된 상위기법(T1543) 근거 포함
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB·ATT&amp;CK 클라우드 사례에 매핑된 건은 없음(K8s 위협 매트릭스 문서화 수준)</t>
         </is>
       </c>
       <c r="G55" s="17" t="inlineStr">
@@ -9243,7 +9575,7 @@
       </c>
       <c r="M55" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N55" s="17" t="inlineStr"/>
@@ -9305,7 +9637,16 @@
           <t>https://attack.mitre.org/techniques/T1543/005</t>
         </is>
       </c>
-      <c r="AF55" s="17" t="inlineStr"/>
+      <c r="AF55" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- restart=always 상주 컨테이너, 신규 DaemonSet·정적 파드, kubelet manifest 디렉터리 변경
+- 노드에 반복 재생성되는 컨테이너와 외부 통신
+■ 대응
+- 정책 엔진으로 위험 워크로드 차단, 정적 파드 경로·docker 소켓 접근 제한
+- rootless 컨테이너 전환과 노드 파일 무결성 점검</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="17" t="inlineStr">
@@ -9330,12 +9671,19 @@
       </c>
       <c r="E56" s="17" t="inlineStr">
         <is>
-          <t>공격자는 중앙에서 관리되는 환경에서 방어를 회피하거나 권한을 높이기 위해 도메인이나 ID 테넌트의 구성 설정을 수정할 수 있다. 이러한 서비스는 장치와 계정 같은 ID 리소스를 중앙에서 관리하는 수단을 제공하며, 신뢰 관계, ID 동기화, ID 페더레이션처럼 도메인이나 테넌트 사이에 적용되는 구성 설정을 포함하는 경우가 많다.</t>
+          <t>- 공격자는 ID 테넌트·도메인의 정책 설정(페더레이션 트러스트, ID 동기화, 그룹 정책, Azure Policy)을 수정해 방어를 우회하거나 권한을 높일 수 있음
+- 테넌트 전역에 적용되는 설정이라 한 번의 변경이 광범위한 영향을 미치고, 작업 후 원복해 흔적을 지우기도 함</t>
         </is>
       </c>
       <c r="F56" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- ID 테넌트: 공격자 제어 페더레이션 ID 공급자를 추가하면 테넌트의 어떤 사용자로도 인증 가능 (하위기법 Trust Modification은 CTC-DI-03.1)
+- Azure Policy: DeployIfNotExists 정책을 구성해 트리거 시 백도어를 생성하는 지속성 악용(Azure ATRM AZT508)
+- AD 연계 환경에서는 GPO 변경으로 도메인 전역에 악성 작업 배포, 신뢰 설정 변경으로 토큰 위조
+- 권한 상승(PV)·방어 무력화(DI) 두 전술에 걸치는 상위기법 행
+■ 실제 사례
+- 공개 사고 미확인 — 구체 사고는 하위기법 Trust Modification(CTC-DI-03.1)에 집계. 이 행은 하위기법으로 특정되지 않은 테넌트 정책 변경 근거를 보존</t>
         </is>
       </c>
       <c r="G56" s="17" t="inlineStr">
@@ -9366,7 +9714,7 @@
       </c>
       <c r="M56" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N56" s="17" t="inlineStr">
@@ -9435,7 +9783,16 @@
           <t>https://attack.mitre.org/techniques/T1484</t>
         </is>
       </c>
-      <c r="AF56" s="17" t="inlineStr"/>
+      <c r="AF56" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- ID 테넌트 정책·페더레이션 설정 변경, Azure Policy(DeployIfNotExists) 할당·수정 이벤트
+- 짧은 시간 변경 후 원복되는 정책 설정
+■ 대응
+- 테넌트 정책·페더레이션 변경에 다중 관리자 승인과 변경 알림
+- 정책을 코드로 관리하고 드리프트 자동 복원, 전역 관리자 수 최소화</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="17" t="inlineStr">
@@ -9460,16 +9817,20 @@
       </c>
       <c r="E57" s="17" t="inlineStr">
         <is>
-          <t>공격자는 방어를 회피하거나 권한을 높이기 위해 새 도메인 트러스트를 추가하거나, 기존 도메인 트러스트의 속성을 수정하거나, 도메인·테넌트 간 신뢰 관계 구성을 바꿀 수 있다. 사용자 ID의 페더레이션 여부 같은 신뢰 세부 정보에 따라, 공유 리소스 접근을 위해 도메인이나 테넌트 사이에 인증·인가 속성이 적용될 수 있다. 이러한 신뢰 객체에는 서버, 토큰, 도메인에 적용되는 계정, 자격 증명, 기타 인증 자료가 포함될 수 있다.</t>
+          <t>- 공격자는 피해 테넌트에 자신의 페더레이션 ID 공급자·SAML 서명 인증서를 추가하거나 신뢰 관계를 변경해, 임의 사용자로 인증하는 백도어를 만들 수 있음
+- 하나의 신뢰 변경이 그 ID를 쓰는 모든 클라우드·SaaS로 확대되어, AWS Organization에서는 전 구성원 계정에 페더레이션 접근이 가능해짐</t>
         </is>
       </c>
       <c r="F57" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 4건)
-- Storm-0501(G1053) — Entra ID [ID·인증]
-- SolarWinds Compromise(C0024) — Entra ID [ID·인증]
-- AADInternals(S0677) — Entra ID [ID·인증]
-- Scattered Spider(G1015) — 클라우드(서비스 미상) [ID·인증]</t>
+          <t>■ 클라우드 관점
+- Entra ID: 도메인을 페더레이션 도메인으로 전환하거나 클레임 발급 규칙을 바꿔 임의 자격증명으로 지정 사용자 로그인(Golden SAML 계열)
+- AWS: 새 SAML·OIDC ID 공급자 생성(iam:CreateSAMLProvider, sso:CreateInstance)으로 Organization 전 계정에 페더레이션 — 계정별 ID 생성 불필요 (AWS TTC T1484.002)
+- Azure: 외부 테넌트 관리 구성(AZT507), Lighthouse 위임(AZT507.1), ID 공급자·도메인 추가 백도어(AZT507.4)
+■ 실제 사례
+- [ATT&amp;CK 사례] SolarWinds 침해: APT29가 도메인 페더레이션 신뢰 설정을 바꿔 자체 SAML 서명 인증서로 서명한 토큰을 수용하도록 구성 (ATT&amp;CK C0024)
+- [ATT&amp;CK 사례] Storm-0501: 전역 관리자 권한으로 피해 Entra 테넌트에 새 페더레이션 도메인을 만들어 지속 백도어 확보 (ATT&amp;CK G1053)
+- [ATT&amp;CK 사례] Scattered Spider: 피해 SSO 테넌트에 페더레이션 ID 공급자를 추가하고 자동 계정 연결을 활성화 (ATT&amp;CK G1015)</t>
         </is>
       </c>
       <c r="G57" s="17" t="inlineStr">
@@ -9500,7 +9861,7 @@
       </c>
       <c r="M57" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N57" s="17" t="inlineStr">
@@ -9572,7 +9933,16 @@
           <t>https://attack.mitre.org/techniques/T1484/002</t>
         </is>
       </c>
-      <c r="AF57" s="17" t="inlineStr"/>
+      <c r="AF57" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 신규 페더레이션 도메인·ID 공급자 추가(CreateSAMLProvider·CreateOpenIDConnectProvider), 클레임 규칙·도메인 전환 이벤트
+- 외부에서 서명된 토큰·새 SAML 인증서로의 인증, 평소와 다른 발행자 토큰
+■ 대응
+- 페더레이션 신뢰·ID 공급자 변경에 강한 승인·알림, 토큰 서명 인증서 보호
+- AWS Organization·Entra의 ID 공급자 목록 정기 검토와 외부 신뢰 허용 목록화</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="17" t="inlineStr">
@@ -9597,12 +9967,19 @@
       </c>
       <c r="E58" s="17" t="inlineStr">
         <is>
-          <t>공격자는 기반 호스트에 접근하기 위해 컨테이너나 가상화 환경을 탈출할 수 있다. 이를 통해 호스트 수준에서 다른 컨테이너·가상화 리소스나 호스트 자체에 접근할 수 있다. 원칙적으로 컨테이너·가상화 리소스는 애플리케이션 기능을 명확히 분리하고 호스트 환경과 격리되어야 한다.</t>
+          <t>- 공격자는 컨테이너·VM 격리를 탈출해 기반 호스트에 접근하고, 같은 호스트의 다른 컨테이너·워크로드나 호스트 자체를 장악할 수 있음
+- 호스트 파일시스템 마운트·권한 있는 컨테이너·docker.sock 노출·하이퍼바이저 취약점이 경로이며, 노드 장악은 곧 클러스터·클라우드 확산으로 이어짐</t>
         </is>
       </c>
       <c r="F58" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- 경로: 호스트 파일시스템 bind 마운트, 권한 있는 컨테이너에서 커널 모듈 로드, docker.sock 등 관리 소켓 마운트(CTC-EX-03 연계), unshare·keyctl 악용, 심볼릭 링크 취약점
+- K8s: 쓰기 가능한 hostPath 마운트가 탈출 발판 (K8s MS-TA9013)
+- ESXi: 하이퍼바이저 취약점으로 VM→하이퍼바이저 탈출, 다수 테넌트 워크로드에 파급
+- 노드 장악 후 노드 자격증명·서비스 어카운트 토큰으로 클러스터·클라우드 계정 확산
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB·ATT&amp;CK 클라우드 사례에 매핑된 건은 없음(취약점·벤더 문서화 수준). 컨테이너 배포를 통한 호스트 접근 시도는 CTC-EX-04와 연계</t>
         </is>
       </c>
       <c r="G58" s="17" t="inlineStr">
@@ -9633,7 +10010,7 @@
       </c>
       <c r="M58" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N58" s="17" t="inlineStr"/>
@@ -9694,7 +10071,16 @@
           <t>https://attack.mitre.org/techniques/T1611</t>
         </is>
       </c>
-      <c r="AF58" s="17" t="inlineStr"/>
+      <c r="AF58" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 권한 있는 컨테이너·hostPath 마운트·docker.sock 마운트 파드 생성, 컨테이너에서의 커널 모듈 로드
+- 컨테이너 프로세스의 호스트 네임스페이스 접근, 노드에서의 비정상 자식 프로세스
+■ 대응
+- Pod Security Admission으로 privileged·hostPath·호스트 네임스페이스 차단, docker 소켓 마운트 금지
+- 런타임 샌드박스(gVisor 등)·최신 패치, ESXi 하이퍼바이저 긴급 패치</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="17" t="inlineStr">
@@ -9719,16 +10105,20 @@
       </c>
       <c r="E59" s="17" t="inlineStr">
         <is>
-          <t>공격자는 특정 이벤트를 계기로 실행을 일으키는 시스템 메커니즘을 이용해 지속성을 확보하거나 권한을 높일 수 있다. 여러 운영체제에는 로그온이나 특정 애플리케이션·바이너리 실행 같은 사용자 활동 이벤트를 모니터링하고 구독하는 수단이 있다. 클라우드 환경도 특정 클라우드 이벤트를 모니터링하고 이에 대응해 호출되는 다양한 함수와 서비스를 지원할 수 있다.</t>
+          <t>- 공격자는 클라우드 이벤트에 반응하는 함수·웹훅·정책(이벤트 규칙·HTTP 트리거 등)을 등록해 지속성과 권한 상승을 확보할 수 있음
+- 트리거는 관리 ID·서비스 계정 권한으로 실행되고 특정 조건에서만 발동해, 상시 프로세스가 없어 탐지가 어려움</t>
         </is>
       </c>
       <c r="F59" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 2건)
-- Mini Shai-Hulud(S9043) — Containers, IaaS, SaaS 플랫폼 소프트웨어 [클라우드(복합)]
-- Pacu(S1091) — AWS [IaaS]
-■ 통합된 기법
-- T1546.004 Unix Shell Configuration Modification</t>
+          <t>■ 클라우드 관점
+- Azure: HTTP 트리거로 인증 없는 명령 실행(AZT503.1~503.3), Watcher 작업으로 이벤트 시 Runbook 실행(AZT504), DeployIfNotExists 정책으로 트리거 시 백도어 생성(AZT508), CloudShell .bashrc 수정으로 권한 상승(AZT403)
+- AWS: EventBridge 규칙으로 사용자 생성 등 이벤트에 Lambda 연결, 무단 API Gateway로 함수 외부 노출(AT1667.001)
+- K8s: 악성 어드미션 컨트롤러로 API 요청 가로채기·수정(MS-TA9015), EKS 구성 변조(AT1668)
+- 통합된 상위기법(T1546.004, Unix 셸 설정) 근거 포함
+■ 실제 사례
+- [ATT&amp;CK 사례] Pacu: CloudFormation 업로드·사용자/역할 생성 시 악성 Lambda가 발동하도록 S3 알림·트리거 설정 (ATT&amp;CK S1091)
+- [ATT&amp;CK 사례] Mini Shai-Hulud: AI 코딩 에이전트 설정 파일에 훅·runOn 조건을 넣어 이벤트 기반 실행 생성 (ATT&amp;CK S9043)</t>
         </is>
       </c>
       <c r="G59" s="17" t="inlineStr">
@@ -9763,7 +10153,7 @@
       </c>
       <c r="M59" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N59" s="17" t="inlineStr"/>
@@ -9839,7 +10229,16 @@
           <t>https://attack.mitre.org/techniques/T1546</t>
         </is>
       </c>
-      <c r="AF59" s="17" t="inlineStr"/>
+      <c r="AF59" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 이벤트 규칙·HTTP 트리거·웹훅·Watcher·정책(DeployIfNotExists) 생성·변경 이벤트
+- 어드미션 컨트롤러·EKS 구성 변경, 트리거가 관리 ID로 수행하는 비정상 작업
+■ 대응
+- 이벤트·정책·자동화 리소스 수정 권한 최소화, 인증 없는 트리거 금지
+- 자동화·정책 목록 정기 검토와 변경 알림</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="17" t="inlineStr">
@@ -10457,13 +10856,18 @@
       </c>
       <c r="E64" s="17" t="inlineStr">
         <is>
-          <t>공격자는 이메일 규칙을 이용해 침해한 사용자의 사서함에서 수신 이메일을 숨길 수 있다. 많은 이메일 클라이언트는 이메일을 다른 폴더로 옮기기, 읽음으로 표시하기, 삭제하기 등 다양한 받은편지함 규칙을 만들 수 있게 한다. 규칙은 이메일 클라이언트 안에서 만들거나 수정할 수 있고, Windows 시스템의 New-InboxRule이나 Set-InboxRule PowerShell cmdlet 같은 외부 기능으로도 만들거나 수정할 수 있다.</t>
+          <t>- 공격자는 침해한 사서함에 이메일 숨김 규칙을 만들어 보안 경고·C2 응답·내부 피싱 회신을 자동으로 이동·삭제·읽음 처리할 수 있음
+- malware·phish 같은 키워드로 거르며, 조직 전역 전송 규칙(Exchange transport rule)을 악용하면 전사 보안 알림을 일괄 차단함</t>
         </is>
       </c>
       <c r="F64" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 1건)
-- Kali365(S9044) — IaaS 플랫폼 소프트웨어 [IaaS]</t>
+          <t>■ 클라우드 관점
+- Exchange Online: New-InboxRule·Set-InboxRule로 개별 사서함 규칙 생성, transport rule로 조직 전역 메일을 조건부 이동·삭제
+- BEC·내부 피싱(CTC-LM-02)으로 보낸 메일의 회신을 숨기거나, 보안 사고 알림 메일을 차단해 탐지를 지연
+- 사서함 권한 탈취·위임(CTC-PE-01.2)과 결합됨
+■ 실제 사례
+- [ATT&amp;CK 사례] Kali365: 피해자가 보기 전에 이메일 기반 알림을 삭제하도록 메일 규칙을 수정 (ATT&amp;CK S9044)</t>
         </is>
       </c>
       <c r="G64" s="17" t="inlineStr">
@@ -10494,7 +10898,7 @@
       </c>
       <c r="M64" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N64" s="17" t="inlineStr"/>
@@ -10551,7 +10955,16 @@
           <t>https://attack.mitre.org/techniques/T1564/008</t>
         </is>
       </c>
-      <c r="AF64" s="17" t="inlineStr"/>
+      <c r="AF64" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 보안 키워드로 메일을 이동·삭제하는 사서함 규칙 생성, 조직 전역 전송 규칙 변경
+- New-InboxRule·Set-InboxRule 호출과 알림 메일이 사라지는 패턴
+■ 대응
+- 위험 사서함 규칙 자동 탐지·차단, 전송 규칙 변경 감사
+- 보안 알림을 메일 외 채널로도 전달해 숨김 규칙 우회</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="17" t="inlineStr">
@@ -10576,12 +10989,19 @@
       </c>
       <c r="E65" s="17" t="inlineStr">
         <is>
-          <t>공격자는 자신의 존재 흔적을 줄이고 정상 활동에 섞이기 위해 생성된 산출물을 선택적으로 삭제하거나 수정할 수 있다. 증거를 광범위하게 지우기보다 이상해 보이거나 주목받기 쉬운 특정 산출물만 골라 처리하고, 정상적인 시스템 동작처럼 보이도록 충분한 데이터는 그대로 남겨 둘 수 있다.</t>
+          <t>- 공격자는 흔적을 줄이기 위해 로그·명령 이력·메타데이터나 자신이 만든 IAM 개체·컨테이너 로그 등을 선택적으로 삭제·변조할 수 있음
+- 정상 활동처럼 보이도록 일부만 손대며, 삭제·변조는 타임라인 재구성과 귀속을 어렵게 함</t>
         </is>
       </c>
       <c r="F65" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- AWS: 작업에 쓴 IAM 사용자·역할을 사후 삭제해 흔적 제거(AWS TTC T1070.A001, iam:DeleteRole·DeleteUser)
+- K8s: 침해 컨테이너의 앱·OS 로그 삭제(MS-TA9021), 클러스터 이벤트 삭제(MS-TA9022)
+- 클라우드 감사 로그 자체의 비활성화·삭제는 별도 행(CTC-DI-02.1 Disable or Modify Cloud Log)에서 다룸
+- 사서함 데이터 삭제(CTC-ST-02.1)가 하위 변형
+■ 실제 사례
+- 공개 사고 미확인 — 이 상위기법으로 직접 매핑된 사고는 없음(흔적 제거는 다른 침해 사고의 종속 단계로 나타남)</t>
         </is>
       </c>
       <c r="G65" s="17" t="inlineStr">
@@ -10612,7 +11032,7 @@
       </c>
       <c r="M65" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N65" s="17" t="inlineStr"/>
@@ -10679,7 +11099,16 @@
           <t>https://attack.mitre.org/techniques/T1070</t>
         </is>
       </c>
-      <c r="AF65" s="17" t="inlineStr"/>
+      <c r="AF65" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- IAM 개체 생성 직후 삭제(DeleteUser·DeleteRole), 컨테이너·클러스터 로그·이벤트 삭제
+- 로그 수집 공백 구간, 명령 이력·메타데이터의 비정상 변경
+■ 대응
+- 감사 로그를 쓰기 방지·별도 계정으로 중앙 집계(변조·삭제 방지), 로그 보존 정책 강제
+- IAM 삭제 이벤트 알림과 컨테이너 로그의 외부 전송</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="17" t="inlineStr">
@@ -10704,12 +11133,17 @@
       </c>
       <c r="E66" s="17" t="inlineStr">
         <is>
-          <t>공격자는 메일과 메일 애플리케이션 데이터를 수정해 자신의 활동 증거를 없앨 수 있다. 이메일 애플리케이션은 사용자와 다른 프로그램이 명령줄 도구나 API로 사서함 데이터를 내보내거나 삭제할 수 있게 한다. 메일 애플리케이션 데이터에는 이메일, 이메일 메타데이터, 내보내기 요청처럼 애플리케이션이나 운영체제가 생성한 로그가 포함될 수 있다.</t>
+          <t>- 공격자는 침해 사서함의 메일·메타데이터·내보내기 로그를 삭제해 피싱·수집·메일 기반 반출의 증거를 없앨 수 있음
+- ExchangePowerShell(Remove-MailboxExportRequest 등)이나 전송 규칙으로 특정 주제 메일을 자동 삭제해 탐지를 어렵게 함</t>
         </is>
       </c>
       <c r="F66" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- Exchange Online: Remove-MailboxExportRequest로 사서함 내보내기 흔적 제거, 전송 규칙으로 스팸·의심 메일의 헤더·메타데이터 제거
+- 메일 수집(CTC-CO-07)·이메일 반출의 후속 은닉 단계로 쓰임
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB·ATT&amp;CK 클라우드 사례에 매핑된 건은 없음(기법 문서화 수준)</t>
         </is>
       </c>
       <c r="G66" s="17" t="inlineStr">
@@ -10740,7 +11174,7 @@
       </c>
       <c r="M66" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N66" s="17" t="inlineStr"/>
@@ -10797,7 +11231,15 @@
           <t>https://attack.mitre.org/techniques/T1070/008</t>
         </is>
       </c>
-      <c r="AF66" s="17" t="inlineStr"/>
+      <c r="AF66" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- Remove-MailboxExportRequest 등 사서함 내보내기 삭제, 대량 메일 삭제, 전송 규칙 기반 자동 삭제
+■ 대응
+- 사서함 감사 로깅 활성화·중앙 보존, 메일 삭제·내보내기 이벤트 알림
+- 보존(litigation hold)으로 삭제 메일 복구 가능하게 구성</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="17" t="inlineStr">
@@ -10822,12 +11264,18 @@
       </c>
       <c r="E67" s="17" t="inlineStr">
         <is>
-          <t>공격자는 파일, 레지스트리 키 또는 기타 리소스의 이름이나 위치를 정할 때 정상 항목과 같거나 비슷하게 맞출 수 있다. 이는 방어와 관찰을 회피하기 위해서다.</t>
+          <t>- 공격자는 리소스 이름·위치를 정상 항목과 같거나 비슷하게 맞춰 방어·관찰을 회피할 수 있으며, 컨테이너 환경에서는 신뢰 네임스페이스나 파드 명명 규칙을 모방함
+- 정상 명명 규칙에 섞여 들어 운영자가 한눈에 이상을 알아채기 어려움</t>
         </is>
       </c>
       <c r="F67" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- 컨테이너: 신뢰 네임스페이스(kube-system 등)에 리소스를 만들거나, 컨트롤러가 붙이는 임의 접미사를 모방해 정상 파드처럼 위장 (K8s MS-TA9023)
+- 리소스 태그·이름을 정상 워크로드와 유사하게 지어 콘솔·인벤토리에서 눈에 띄지 않게 함
+- 계정 이름 위장은 별도 행(CTC-ST-03.2), 특정 인물·조직 사칭은 Impersonation(CTC-ST-04.1)과 구분
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB·ATT&amp;CK 클라우드 사례에 매핑된 건은 없음(기법 문서화 수준)</t>
         </is>
       </c>
       <c r="G67" s="17" t="inlineStr">
@@ -10858,7 +11306,7 @@
       </c>
       <c r="M67" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N67" s="17" t="inlineStr"/>
@@ -10919,7 +11367,16 @@
           <t>https://attack.mitre.org/techniques/T1036/005</t>
         </is>
       </c>
-      <c r="AF67" s="17" t="inlineStr"/>
+      <c r="AF67" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 시스템 네임스페이스의 비인가 리소스, 정상 파드명과 유사하나 소유 컨트롤러가 없는 리소스
+- 신뢰 위치·이름을 모방한 리소스 생성 이벤트
+■ 대응
+- 네임스페이스별 RBAC·정책으로 생성 제한, 리소스 소유권(ownerReferences)·태그 표준 검증
+- 이미지·리소스 인벤토리와 기준 대조</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="17" t="inlineStr">
@@ -10944,13 +11401,18 @@
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t>공격자는 새로 만든 계정이 무해해 보이도록 정상 계정과 같거나 비슷한 이름을 붙일 수 있다. 이는 보통 계정 생성(Create Account) 단계에서 일어나지만 나중에 계정 이름을 바꿀 수도 있다. 공격자가 계정을 먼저 삭제한 뒤 같은 이름으로 다시 만드는 경우에는 계정 접근 제거(Account Access Removal)와 함께 나타날 수도 있다.</t>
+          <t>- 공격자는 새로 만든 계정에 정상 계정·서비스 계정과 비슷한 이름(admin·backup·IT 지원 등)을 붙여 무해해 보이게 할 수 있음
+- 기존 계정명을 모방하거나 삭제 후 같은 이름으로 재생성하기도 하며, 계정 목록에서 이상 탐지를 어렵게 함</t>
         </is>
       </c>
       <c r="F68" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 1건)
-- Storm-1811(G1046) — Microsoft Teams [SaaS·협업]</t>
+          <t>■ 클라우드 관점
+- 서비스 계정·백업·클러스터 관리 계정처럼 보이는 이름을 써 콘솔·IAM 목록에서 정상으로 위장 — 계정 생성(CTC-PE-03.1)의 후속 행위
+- SaaS(Teams 등)에서 IT 지원·헬프데스크를 사칭하는 계정명으로 음성·앱 피싱에 활용
+- 삭제 후 재생성 시 계정 접근 제거(CTC-IM-01)와 함께 나타남
+■ 실제 사례
+- [ATT&amp;CK 사례] Storm-1811: IT 지원·헬프데스크를 사칭하는 Microsoft Teams 계정을 만들어 앱·음성 피싱에 사용 (ATT&amp;CK G1046)</t>
         </is>
       </c>
       <c r="G68" s="17" t="inlineStr">
@@ -10981,7 +11443,7 @@
       </c>
       <c r="M68" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N68" s="17" t="inlineStr"/>
@@ -11038,7 +11500,16 @@
           <t>https://attack.mitre.org/techniques/T1036/010</t>
         </is>
       </c>
-      <c r="AF68" s="17" t="inlineStr"/>
+      <c r="AF68" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- admin·backup·IT 지원 등 정상 명칭을 모방한 신규 계정, 서비스 계정 유사 이름
+- 삭제 직후 같은 이름 재생성, 협업 도구의 지원팀 사칭 계정
+■ 대응
+- 계정 명명 규칙·생성 승인, 서비스 계정 인벤토리와 대조
+- 협업 도구 외부·게스트 계정 표시와 제한</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="17" t="inlineStr">
@@ -11063,15 +11534,20 @@
       </c>
       <c r="E69" s="17" t="inlineStr">
         <is>
-          <t>공격자는 대상을 설득하고 속여 자신을 대신해 어떤 행동을 하게 만들기 위해 신뢰받는 사람이나 조직을 사칭할 수 있다. 예를 들어 임원, 동료, 외부 협력업체처럼 알려진 발신자를 사칭하면서 정보 수집용 피싱(Phishing for Information), 피싱(Phishing), 내부 스피어피싱(Internal Spearphishing)으로 피해자와 소통할 수 있다. 이렇게 쌓은 신뢰를 이용해 공격자의 최종 목표를 달성하며, 여러 피해자를 대상으로 할 수도 있다.</t>
+          <t>- 공격자는 임원·동료·협력업체·IT 지원 등 신뢰 주체를 사칭해 피해자가 송금하거나 정보를 넘기도록 유도할 수 있음
+- 정찰과 유사 도메인 확보로 신뢰를 꾸미며, SaaS 협업 도구(Teams·Salesforce)·메일로 접근해 BEC·금전 탈취로 이어짐</t>
         </is>
       </c>
       <c r="F69" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 3건)
-- Scattered Spider(G1015) — Microsoft Teams [SaaS·협업]
-- TeamPCP(G1056) — GitHub·GitLab [SaaS·협업]
-- Salesforce Data Exfiltration(C0059) — Salesforce [SaaS·협업]</t>
+          <t>■ 클라우드 관점
+- SaaS 협업 채널(Teams·Slack)과 M365 메일을 통해 IT 지원·헬프데스크를 사칭, MFA·비밀번호 재설정을 유도(CTC-IA-03.2 비싱과 연계)
+- 공급망에서는 정상 유지관리자를 사칭해 저장소에 커밋을 밀어넣는 형태로도 나타남
+- 긴급·결제·요청 같은 압박 문구로 신속한 행동을 유도, 유사 도메인(CTC-RD-01.1)으로 신원 위장을 뒷받침
+■ 실제 사례
+- [ATT&amp;CK 사례] Scattered Spider: IT 지원·헬프데스크를 사칭해 비밀번호·MFA 재설정을 유도, Teams로 내부 IT 지원 행세 (ATT&amp;CK G1015)
+- [ATT&amp;CK 사례] Salesforce 데이터 반출 캠페인: 음성 통화에서 IT 지원을 사칭하며 전사 연결 문제 해결을 명분으로 접근 (ATT&amp;CK C0059)
+- [ATT&amp;CK 사례] TeamPCP: 정상 유지관리자를 사칭해 Trivy 저장소에 위장 커밋을 푸시 (ATT&amp;CK G1056)</t>
         </is>
       </c>
       <c r="G69" s="17" t="inlineStr">
@@ -11102,7 +11578,7 @@
       </c>
       <c r="M69" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N69" s="17" t="inlineStr"/>
@@ -11159,7 +11635,16 @@
           <t>https://attack.mitre.org/techniques/T1684/001</t>
         </is>
       </c>
-      <c r="AF69" s="17" t="inlineStr"/>
+      <c r="AF69" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 협업 도구·메일에서 IT 지원·임원 사칭 패턴, 외부 게스트의 지원 사칭 메시지
+- 비밀번호·MFA 재설정 유도, 공급망 저장소의 사칭 커밋
+■ 대응
+- 헬프데스크 본인 확인 강화와 재설정 승인 절차, 외부 발신 표식
+- 사용자 사회공학 인식 교육과 신고 채널, 저장소 커밋 서명 검증</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="17" t="inlineStr">
@@ -11184,12 +11669,18 @@
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t>공격자는 관련 이메일 헤더 값을 수정해 발신자 신원을 위조함으로써 거짓 명분으로 피해자와 접촉할 수 있다. 실제 이메일 내용뿐 아니라 이메일 헤더(예: 발신자 이메일 주소가 담긴 FROM 헤더)도 수정할 수 있다. 이메일 클라이언트는 피해자의 받은편지함에 이메일이 표시될 때 이 헤더를 보여 주므로, 수정된 이메일이 위조한 대상이 보낸 것처럼 보일 수 있다.</t>
+          <t>- 공격자는 FROM 등 메일 헤더를 위조해 신뢰 발신자가 보낸 것처럼 꾸며 피해자와 자동 보안 도구를 속일 수 있음
+- SPF·DKIM·DMARC가 없거나 p=none이면 인증 실패 메일도 받은편지함에 배달되며, M365 Direct Send로 내부 사용자를 사칭하기도 함</t>
         </is>
       </c>
       <c r="F70" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- 약하거나 없는 DMARC(p=none) 정책을 악용해 인증 실패 메일을 통과시키고 사회공학을 은폐
+- M365 Direct Send 기능을 악용해 내부 프린터 등으로 인증 없이 내부 사용자 사칭 메일 발송
+- SPF(발신 서버 인가)·DKIM(무결성 서명)·DMARC(실패 처리 정책)의 올바른 구성·강제가 방어 핵심
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB·ATT&amp;CK 클라우드 사례에 매핑된 건은 없음(기법·구성 문서화 수준). 사칭 사회공학 사례는 CTC-ST-04.1 참조</t>
         </is>
       </c>
       <c r="G70" s="17" t="inlineStr">
@@ -11220,7 +11711,7 @@
       </c>
       <c r="M70" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N70" s="17" t="inlineStr"/>
@@ -11277,7 +11768,15 @@
           <t>https://attack.mitre.org/techniques/T1684/002</t>
         </is>
       </c>
-      <c r="AF70" s="17" t="inlineStr"/>
+      <c r="AF70" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- SPF·DKIM 실패에도 배달된 메일, 내부 도메인 사칭 발신, Direct Send 경로 메일
+■ 대응
+- DMARC를 p=reject로 강제하고 SPF·DKIM 정합성 확보, M365 Direct Send 제한
+- 외부 발신 표식과 사칭 의심 메일 격리</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="17" t="inlineStr">
@@ -11302,12 +11801,19 @@
       </c>
       <c r="E71" s="17" t="inlineStr">
         <is>
-          <t>공격자는 탐지를 회피하기 위해 사용하지 않는 지역 서비스 리전에 클라우드 인스턴스를 만들 수 있다. 이런 접근은 보통 클라우드 인프라 관리에 쓰이는 계정을 침해해 얻는다.</t>
+          <t>- 공격자는 조직이 쓰지 않거나 모니터링이 약한 클라우드 리전에 인스턴스를 만들어 탐지를 피할 수 있음
+- 고급 탐지 서비스가 없는 리전을 골라 채굴 등 활동을 숨기며, 미사용 리전은 과금·리소스 증가로만 뒤늦게 드러남</t>
         </is>
       </c>
       <c r="F71" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- 대부분 조직은 전체 리전 중 일부만 사용·모니터링하므로, 미사용 리전의 리소스 생성은 탐지 사각이 됨
+- 리전별 탐지 서비스(GuardDuty 등) 가용성 차이를 악용해 커버리지가 없는 리전을 선택
+- 보통 인프라 관리 계정 탈취로 수행되며, 크립토재킹(CTC-IM-09)과 결합되어 장기 과금 피해 유발
+- 리전 사용 제한은 조직 정책·SCP로 통제(허용 리전 외 배포 차단)
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB·ATT&amp;CK 클라우드 사례에 매핑된 건은 없음(기법 문서화 수준). 미사용 리전 채굴은 Resource Hijacking 사고(CTC-IM-09.0)의 한 양상으로 보고됨</t>
         </is>
       </c>
       <c r="G71" s="17" t="inlineStr">
@@ -11338,7 +11844,7 @@
       </c>
       <c r="M71" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N71" s="17" t="inlineStr">
@@ -11403,7 +11909,16 @@
           <t>https://attack.mitre.org/techniques/T1535</t>
         </is>
       </c>
-      <c r="AF71" s="17" t="inlineStr"/>
+      <c r="AF71" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 미사용 리전의 리소스 생성·실행(RunInstances 등), 평소 사용 리전 밖의 과금·사용량 증가
+- 탐지 서비스가 없는 리전에서의 API 활동
+■ 대응
+- SCP·조직 정책으로 허용 리전 외 배포 차단, 전 리전에 탐지 서비스·로깅 활성화
+- 전 리전 리소스·과금 모니터링</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="17" t="inlineStr">
@@ -11745,13 +12260,19 @@
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t>공격자는 클라우드 리소스 접근을 제한하는 통제를 우회하기 위해 클라우드 환경의 방화벽을 비활성화하거나 수정할 수 있다.</t>
+          <t>- 공격자는 보안 그룹·NSG 등 클라우드 방화벽 규칙을 수정·추가해 피해 환경으로의 접근 경로를 열거나 제어 평면에서 데이터 평면으로 이동할 수 있음
+- 인바운드 전체 허용 규칙을 넣거나 네트워크 제한을 풀어 C2·채굴 트래픽을 통과시키며, 정상 구성 변경처럼 보임</t>
         </is>
       </c>
       <c r="F74" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 1건)
-- Pacu(S1091) — AWS [IaaS]</t>
+          <t>■ 클라우드 관점
+- AWS: ec2:AuthorizeSecurityGroupIngress 등으로 보안 그룹에 임의 TCP/IP 허용 규칙 추가, 네트워크 ACL 변경 (AWS TTC T1562.007)
+- Azure: NSG 규칙 수정으로 추가 포트 개방(Azure ATRM AZT506)
+- GuardDuty 등 탐지 서비스에 공격자 IP를 허용 목록에 넣어 경보 회피
+- 제어 평면 권한으로 데이터 평면 네트워크 접근을 여는 전형적 경로
+■ 실제 사례
+- [ATT&amp;CK 사례] Pacu: AWS GuardDuty에 IP를 허용 목록으로 추가 (ATT&amp;CK S1091)</t>
         </is>
       </c>
       <c r="G74" s="17" t="inlineStr">
@@ -11782,7 +12303,7 @@
       </c>
       <c r="M74" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N74" s="17" t="inlineStr">
@@ -11851,7 +12372,16 @@
           <t>https://attack.mitre.org/techniques/T1686/001</t>
         </is>
       </c>
-      <c r="AF74" s="17" t="inlineStr"/>
+      <c r="AF74" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 보안 그룹·NSG·네트워크 ACL에 광범위 허용(0.0.0.0/0) 규칙 추가, 탐지 서비스 허용 목록 변경
+- 방화벽 변경 직후의 새 인바운드 연결
+■ 대응
+- 보안 그룹 변경 권한 최소화·변경 알림, 광범위 개방 규칙 자동 탐지·차단(정책 가드레일)
+- 네트워크 구성을 IaC로 관리하고 드리프트 복원</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="17" t="inlineStr">
@@ -11876,16 +12406,21 @@
       </c>
       <c r="E75" s="17" t="inlineStr">
         <is>
-          <t>공격자는 방어 기능의 가시성을 떨어뜨리거나 무력화하기 위해 보안 도구나 애플리케이션(예: EDR(엔드포인트 탐지 및 대응) 도구, 침입 탐지 시스템(IDS), 백신, 로깅 에이전트, 센서 등)을 비활성화하거나, 성능을 떨어뜨리거나, 변조할 수 있다. 여기에는 특정 서비스 중지, 프로세스 종료, 도구 구성 파일과 레지스트리 키 수정·삭제, 도구 업데이트 차단 등이 포함될 수 있다. 호스트, 네트워크, 클라우드 환경 전반의 예방·탐지·대응 메커니즘을 방해해 방어를 더 광범위하게 무력화하는 것도 포함될 수 있다.</t>
+          <t>- 공격자는 EDR·백신·로깅 에이전트·클라우드 모니터링 에이전트를 중지·삭제·변조해 방어 가시성을 떨어뜨릴 수 있음
+- 클라우드에서는 VM·컨테이너의 보안 에이전트 제거, DNS·iptables 변조로 텔레메트리를 끊어 탐지·대응을 무력화함</t>
         </is>
       </c>
       <c r="F75" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 4건)
-- Contagious Interview(G1052) — Docker [컨테이너·K8s]
-- Hildegard(S0601) — Containers, IaaS 플랫폼 소프트웨어 [IaaS]
-- Shai-Hulud(S9008) — Docker [컨테이너·K8s]
-- TeamTNT(G0139) — 클라우드(서비스 미상) [IaaS]</t>
+          <t>■ 클라우드 관점
+- 클라우드 모니터링 에이전트(Alibaba·Tencent·BMC 등) 제거, CI/CD·컨테이너 환경에서 DNS 설정·iptables 변조로 네트워크 통제 장악
+- AWS GuardDuty 탐지기 삭제·수정(AWS TTC T1562.A001)은 상위기법 Impair Defenses 전반과 연계
+- 클라우드 로그 자체의 비활성화는 별도 하위 행(CTC-DI-02.1)에서 다룸
+- 통합된 상위기법(T1562→v19.2 T1685) 근거 포함
+■ 실제 사례
+- [ATT&amp;CK 사례] TeamTNT: 클라우드 인프라에서 Alibaba·Tencent·BMC 클라우드 모니터링 에이전트를 비활성화·제거 (ATT&amp;CK G0139)
+- [ATT&amp;CK 사례] Shai-Hulud: CI 환경에서 /tmp/resolved.conf의 DNS 설정을 교체하고 iptables 규칙을 초기화 (ATT&amp;CK S9008)
+- [ATT&amp;CK 사례] Hildegard: DNS 리졸버를 변조해 DNS 모니터링 도구를 회피 (ATT&amp;CK S0601)</t>
         </is>
       </c>
       <c r="G75" s="17" t="inlineStr">
@@ -11916,7 +12451,7 @@
       </c>
       <c r="M75" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N75" s="17" t="inlineStr">
@@ -11982,7 +12517,16 @@
           <t>https://attack.mitre.org/techniques/T1685</t>
         </is>
       </c>
-      <c r="AF75" s="17" t="inlineStr"/>
+      <c r="AF75" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 보안·모니터링 에이전트 중지·제거, DNS·iptables 변경, 탐지기(GuardDuty) 삭제·수정
+- 에이전트 텔레메트리 수신 중단 구간
+■ 대응
+- 보안 에이전트 변조 방지·자동 복구, 에이전트 상태 중앙 모니터링
+- 탐지 서비스 삭제·수정에 SCP·알림, CI 환경 네트워크 설정 변경 제한</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="17" t="inlineStr">
@@ -12007,16 +12551,20 @@
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t>공격자는 자신의 활동에 대해 수집되는 데이터를 제한하고 탐지를 피하기 위해 클라우드 로깅 기능과 연동을 비활성화하거나 수정할 수 있다. 클라우드 환경에서는 사용자가 환경 안에서 어떤 활동을 하는지 보여 주는 감사 로그와 애플리케이션 로그를 수집·분석할 수 있다. 공격자는 권한이 충분하면 로깅을 비활성화하거나 수정해 자신의 활동이 탐지되지 않게 할 수 있다.</t>
+          <t>- 공격자는 CloudTrail·CloudWatch·M365 감사 로깅을 중지·삭제·축소해 자신의 활동이 기록되지 않게 할 수 있음
+- 다중 리전 로깅·로그 검증 해제, 특정 사용자 감사 우회, 라이선스 하향 등으로 선택적으로 가시성을 지움</t>
         </is>
       </c>
       <c r="F76" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례(사고 DB)
-- [실제 사고] APT29 targeting Microsoft 365(2022-08, INC-0114)
-■ ATT&amp;CK 사례(행위자, 총 2건)
-- APT29(G0016) — Microsoft 365 [SaaS·협업]
-- Pacu(S1091) — AWS [IaaS]</t>
+          <t>■ 클라우드 관점
+- AWS: cloudtrail:StopLogging·DeleteTrail·UpdateTrail(다중 리전·검증·암호화 해제), VPC Flow Logs·CloudWatch 로그 삭제 (AWS TTC T1562.008)
+- M365: Set-MailboxAuditBypassAssociation으로 특정 사용자 메일 감사 우회, 고급 감사 비활성화, E5→E3 라이선스 하향으로 로깅 기능 축소
+- 메일 수집(CTC-CO-07)·데이터 반출 직전에 선행되는 경우가 많음
+■ 실제 사례
+- [실제 사고] APT29 M365 공격(2022-08): ADFS 백도어·골든 SAML과 함께 감사 로깅을 비활성화한 뒤 메일 탈취 (사고DB INC-0114)
+- [ATT&amp;CK 사례] APT29: M365 테넌트에서 메일 탈취 전 대상 계정의 Purview 감사를 비활성화 (ATT&amp;CK G0016)
+- [ATT&amp;CK 사례] Pacu: CloudTrail·VPC Flow Logs 등 AWS 로깅 서비스를 비활성화·제한 (ATT&amp;CK S1091)</t>
         </is>
       </c>
       <c r="G76" s="17" t="inlineStr">
@@ -12047,7 +12595,7 @@
       </c>
       <c r="M76" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N76" s="17" t="inlineStr">
@@ -12120,7 +12668,16 @@
           <t>https://attack.mitre.org/techniques/T1685/002</t>
         </is>
       </c>
-      <c r="AF76" s="17" t="inlineStr"/>
+      <c r="AF76" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- CloudTrail StopLogging·DeleteTrail·UpdateTrail, VPC Flow Logs·CloudWatch 로그 삭제
+- M365 감사 우회(Set-MailboxAuditBypassAssociation)·라이선스 하향, 로그 수집 공백
+■ 대응
+- 로깅 변경을 SCP로 차단·조직 전역 로깅 강제(불변·별도 계정 저장), 로그 중단 즉시 알림
+- M365 감사 보존·고급 감사 유지</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="17" t="inlineStr">
@@ -12145,12 +12702,19 @@
       </c>
       <c r="E77" s="17" t="inlineStr">
         <is>
-          <t>공격자는 중앙에서 관리되는 환경에서 방어를 회피하거나 권한을 높이기 위해 도메인이나 ID 테넌트의 구성 설정을 수정할 수 있다. 이러한 서비스는 장치와 계정 같은 ID 리소스를 중앙에서 관리하는 수단을 제공하며, 신뢰 관계, ID 동기화, ID 페더레이션처럼 도메인이나 테넌트 사이에 적용되는 구성 설정을 포함하는 경우가 많다.</t>
+          <t>- 공격자는 ID 테넌트·도메인의 정책 설정(페더레이션 트러스트, ID 동기화, 그룹 정책, Azure Policy)을 수정해 방어를 우회하거나 권한을 높일 수 있음
+- 테넌트 전역에 적용되는 설정이라 한 번의 변경이 광범위한 영향을 미치고, 작업 후 원복해 흔적을 지우기도 함</t>
         </is>
       </c>
       <c r="F77" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- ID 테넌트: 공격자 제어 페더레이션 ID 공급자를 추가하면 테넌트의 어떤 사용자로도 인증 가능 (하위기법 Trust Modification은 CTC-DI-03.1)
+- Azure Policy: DeployIfNotExists 정책을 구성해 트리거 시 백도어를 생성하는 지속성 악용(Azure ATRM AZT508)
+- AD 연계 환경에서는 GPO 변경으로 도메인 전역에 악성 작업 배포, 신뢰 설정 변경으로 토큰 위조
+- 권한 상승(PV)·방어 무력화(DI) 두 전술에 걸치는 상위기법 행
+■ 실제 사례
+- 공개 사고 미확인 — 구체 사고는 하위기법 Trust Modification(CTC-DI-03.1)에 집계. 이 행은 하위기법으로 특정되지 않은 테넌트 정책 변경 근거를 보존</t>
         </is>
       </c>
       <c r="G77" s="17" t="inlineStr">
@@ -12181,7 +12745,7 @@
       </c>
       <c r="M77" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N77" s="17" t="inlineStr">
@@ -12250,7 +12814,16 @@
           <t>https://attack.mitre.org/techniques/T1484</t>
         </is>
       </c>
-      <c r="AF77" s="17" t="inlineStr"/>
+      <c r="AF77" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- ID 테넌트 정책·페더레이션 설정 변경, Azure Policy(DeployIfNotExists) 할당·수정 이벤트
+- 짧은 시간 변경 후 원복되는 정책 설정
+■ 대응
+- 테넌트 정책·페더레이션 변경에 다중 관리자 승인과 변경 알림
+- 정책을 코드로 관리하고 드리프트 자동 복원, 전역 관리자 수 최소화</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="17" t="inlineStr">
@@ -12275,16 +12848,20 @@
       </c>
       <c r="E78" s="17" t="inlineStr">
         <is>
-          <t>공격자는 방어를 회피하거나 권한을 높이기 위해 새 도메인 트러스트를 추가하거나, 기존 도메인 트러스트의 속성을 수정하거나, 도메인·테넌트 간 신뢰 관계 구성을 바꿀 수 있다. 사용자 ID의 페더레이션 여부 같은 신뢰 세부 정보에 따라, 공유 리소스 접근을 위해 도메인이나 테넌트 사이에 인증·인가 속성이 적용될 수 있다. 이러한 신뢰 객체에는 서버, 토큰, 도메인에 적용되는 계정, 자격 증명, 기타 인증 자료가 포함될 수 있다.</t>
+          <t>- 공격자는 피해 테넌트에 자신의 페더레이션 ID 공급자·SAML 서명 인증서를 추가하거나 신뢰 관계를 변경해, 임의 사용자로 인증하는 백도어를 만들 수 있음
+- 하나의 신뢰 변경이 그 ID를 쓰는 모든 클라우드·SaaS로 확대되어, AWS Organization에서는 전 구성원 계정에 페더레이션 접근이 가능해짐</t>
         </is>
       </c>
       <c r="F78" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 4건)
-- Storm-0501(G1053) — Entra ID [ID·인증]
-- SolarWinds Compromise(C0024) — Entra ID [ID·인증]
-- AADInternals(S0677) — Entra ID [ID·인증]
-- Scattered Spider(G1015) — 클라우드(서비스 미상) [ID·인증]</t>
+          <t>■ 클라우드 관점
+- Entra ID: 도메인을 페더레이션 도메인으로 전환하거나 클레임 발급 규칙을 바꿔 임의 자격증명으로 지정 사용자 로그인(Golden SAML 계열)
+- AWS: 새 SAML·OIDC ID 공급자 생성(iam:CreateSAMLProvider, sso:CreateInstance)으로 Organization 전 계정에 페더레이션 — 계정별 ID 생성 불필요 (AWS TTC T1484.002)
+- Azure: 외부 테넌트 관리 구성(AZT507), Lighthouse 위임(AZT507.1), ID 공급자·도메인 추가 백도어(AZT507.4)
+■ 실제 사례
+- [ATT&amp;CK 사례] SolarWinds 침해: APT29가 도메인 페더레이션 신뢰 설정을 바꿔 자체 SAML 서명 인증서로 서명한 토큰을 수용하도록 구성 (ATT&amp;CK C0024)
+- [ATT&amp;CK 사례] Storm-0501: 전역 관리자 권한으로 피해 Entra 테넌트에 새 페더레이션 도메인을 만들어 지속 백도어 확보 (ATT&amp;CK G1053)
+- [ATT&amp;CK 사례] Scattered Spider: 피해 SSO 테넌트에 페더레이션 ID 공급자를 추가하고 자동 계정 연결을 활성화 (ATT&amp;CK G1015)</t>
         </is>
       </c>
       <c r="G78" s="17" t="inlineStr">
@@ -12315,7 +12892,7 @@
       </c>
       <c r="M78" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N78" s="17" t="inlineStr">
@@ -12387,7 +12964,16 @@
           <t>https://attack.mitre.org/techniques/T1484/002</t>
         </is>
       </c>
-      <c r="AF78" s="17" t="inlineStr"/>
+      <c r="AF78" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 신규 페더레이션 도메인·ID 공급자 추가(CreateSAMLProvider·CreateOpenIDConnectProvider), 클레임 규칙·도메인 전환 이벤트
+- 외부에서 서명된 토큰·새 SAML 인증서로의 인증, 평소와 다른 발행자 토큰
+■ 대응
+- 페더레이션 신뢰·ID 공급자 변경에 강한 승인·알림, 토큰 서명 인증서 보호
+- AWS Organization·Entra의 ID 공급자 목록 정기 검토와 외부 신뢰 허용 목록화</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="17" t="inlineStr">
@@ -12412,16 +12998,20 @@
       </c>
       <c r="E79" s="17" t="inlineStr">
         <is>
-          <t>공격자는 침해한 계정에 지속적으로 접근하기 위해 다중 인증(MFA) 메커니즘을 비활성화하거나 수정할 수 있다.</t>
+          <t>- 공격자는 침해 계정 유지를 위해 MFA를 비활성화하거나 취약한 MFA 수단으로 교체할 수 있으며, 탈취한 세션 토큰으로 MFA 자체를 건너뛰기도 함
+- 조건부 액세스에서 사용자 제외·'실패 시 허용(fail open)' 설정을 악용하면 계정 단위를 넘어 그룹 전체의 MFA가 무력화됨</t>
         </is>
       </c>
       <c r="F79" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례(사고 DB)
-- [실제 사고] BitoPro(2025-05, INC-0506): BitoPro의 클라우드 운영 직원이 소셜 엔지니어링과 악성코드로 침해되었다. 탈취된 AWS 세션 토큰으로 MFA가 우회되었고, 1,100만 달러 상당의 암호화폐가 탈취되었다.
-- [실제 사고] ByBit hack(2025-02, INC-0470): 2025년 2월 21일 북한 연계 TraderTraitor(UNC4899)가 Safe{Wallet}을 공격했다. 개발자 노트북을 침해해 AWS 세션 토큰을 가로채고 MFA를 우회한 뒤 Safe{Wallet} 서버에 무단 접근했다(ByBit 해킹).
-■ ATT&amp;CK 사례(행위자, 총 1건)
-- AADInternals(S0677) — Entra ID [ID·인증]</t>
+          <t>■ 클라우드 관점
+- Entra ID 등에서 조건부 액세스 사용자 제외, 공격자 제어 MFA 수단 등록(CTC-PE-01.5 연계), MFA 자가 등록 악용으로 요건 무력화
+- 가장 흔한 실제 경로는 피싱·단말 침해로 얻은 유효 세션·액세스 토큰으로 MFA를 건너뛰는 것 — 토큰이 이미 인증된 세션을 담고 있어 재인증이 필요 없음
+- 지속성(PE)·방어 무력화(DI)·자격증명 접근(CA) 세 전술에 걸침
+■ 실제 사례
+- [실제 사고] ByBit/Safe{Wallet}(2025-02): TraderTraitor(UNC4899)가 개발자 노트북을 침해해 AWS 세션 토큰을 가로채 MFA를 우회하고 서버에 무단 접근 (사고DB INC-0470)
+- [실제 사고] BitoPro(2025-05): 클라우드 운영 직원 침해로 탈취한 AWS 세션 토큰으로 MFA를 우회, 약 1,100만 달러 암호화폐 탈취 (사고DB INC-0506)
+- [ATT&amp;CK 사례] AADInternals: Set-AADIntUserMFA로 지정 사용자의 MFA 비활성화 (ATT&amp;CK S0677)</t>
         </is>
       </c>
       <c r="G79" s="17" t="inlineStr">
@@ -12452,7 +13042,7 @@
       </c>
       <c r="M79" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N79" s="17" t="inlineStr">
@@ -12521,7 +13111,16 @@
           <t>https://attack.mitre.org/techniques/T1556/006</t>
         </is>
       </c>
-      <c r="AF79" s="17" t="inlineStr"/>
+      <c r="AF79" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- MFA 비활성화·조건부 액세스 제외·MFA 수단 변경 이벤트, 같은 세션 토큰의 다른 IP 재사용
+- 'fail open' 구성과 MFA 요구가 사라진 로그인 성공
+■ 대응
+- 피싱 저항형 MFA(FIDO2)와 'fail open' 금지, MFA·조건부 액세스 변경에 다중 관리자 승인
+- 토큰 보호·세션 수명 단축, 의심 세션 토큰 즉시 폐기</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="17" t="inlineStr">
@@ -12546,14 +13145,19 @@
       </c>
       <c r="E80" s="17" t="inlineStr">
         <is>
-          <t>공격자는 일반 인증 메커니즘을 우회하고, 자격 증명에 접근하고, 계정에 지속적으로 접근하기 위해 온프레미스 사용자 ID와 연결된 클라우드 인증 절차에 패치를 적용하거나, 이를 수정하거나, 백도어를 심을 수 있다.</t>
+          <t>- 공격자는 온프레미스-클라우드 하이브리드 ID 연결(PHS·PTA·AD FS)에 백도어를 심어 모든 인증을 통과시키고 자격증명을 수집할 수 있음
+- 연동 지점 하나를 장악하면 페더레이션된 모든 클라우드·SaaS에 지속적 특권 접근이 가능해 피해 범위가 테넌트 전체로 확대됨</t>
         </is>
       </c>
       <c r="F80" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 2건)
-- AADInternals(S0677) — Entra ID [ID·인증]
-- APT29(G0016) — 클라우드(서비스 미상) [클라우드(복합)]</t>
+          <t>■ 클라우드 관점
+- Entra ID 동기화 세 방식이 표적: PTA 에이전트 서버에 악성 DLL(PTASpy) 주입으로 모든 인증 승인·자격증명 기록, AD FS 구성 변조로 임의 사용자 토큰 위조(Golden SAML 계열)
+- AD FS는 AWS·GCP 등 타 클라우드 페더레이션에도 쓰여, 한 번의 변조가 여러 클라우드로 파급
+- 하이브리드 조인 서버는 조건부 액세스 우회에도 악용됨 (CTC-PE-08.3 연계)
+■ 실제 사례
+- [ATT&amp;CK 사례] APT29: Microsoft.IdentityServer.Servicehost 구성을 수정해 AD FS에 악성 DLL을 로드, 페더레이션된 서비스에 지속 접근 (ATT&amp;CK G0016)
+- [ATT&amp;CK 사례] AADInternals: PTASpy DLL을 PTA 에이전트 서비스에 주입해 Pass-Through 인증을 백도어화 (ATT&amp;CK S0677)</t>
         </is>
       </c>
       <c r="G80" s="17" t="inlineStr">
@@ -12584,7 +13188,7 @@
       </c>
       <c r="M80" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N80" s="17" t="inlineStr">
@@ -12645,7 +13249,16 @@
           <t>https://attack.mitre.org/techniques/T1556/007</t>
         </is>
       </c>
-      <c r="AF80" s="17" t="inlineStr"/>
+      <c r="AF80" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- PTA 에이전트·AD FS 서버의 DLL 로드·구성 파일 변경, 토큰 서명 인증서의 비정상 사용
+- 온프레미스 조인 서버에서 발급된 토큰의 광범위한 클라우드 접근
+■ 대응
+- 하이브리드 ID 연동 서버를 Tier0로 취급·접근 최소화, 토큰 서명 인증서 보호·정기 교체
+- AD FS → 클라우드 인증의 이상 토큰 탐지, 가능 시 클라우드 인증으로 전환</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="17" t="inlineStr">
@@ -12670,14 +13283,19 @@
       </c>
       <c r="E81" s="17" t="inlineStr">
         <is>
-          <t>공격자는 침해한 계정에 지속적으로 접근하기 위해 조건부 액세스 정책을 비활성화하거나 수정할 수 있다. 조건부 액세스 정책은 ID 공급자와 ID·접근 관리 시스템이 사용자에게 리소스 접근을 허용할지 판단할 때 쓰는 추가 검증이다.</t>
+          <t>- 공격자는 조건부 액세스·IAM 조건 정책을 수정해(신뢰 IP 추가, MFA 요구 제거, 허용 리전 확대) 침해 계정의 접근을 지속할 수 있음
+- 정책 완화는 정상 관리 변경처럼 보여, 이후 탈취 자격증명이 통제를 그대로 통과하게 만듦</t>
         </is>
       </c>
       <c r="F81" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 2건)
-- Scattered Spider(G1015) — Entra ID [ID·인증]
-- Storm-0501(G1053) — 클라우드(서비스 미상) [클라우드(복합)]</t>
+          <t>■ 클라우드 관점
+- IdP(Entra ID·Okta·JumpCloud): 신뢰 위치 추가, MFA·장치 등록·위험 기반 차단 조건 완화
+- AWS·GCP: IAM 정책의 조건 속성(source IP·요청 시각·리전) 변경으로 제약 무력화
+- 미사용 리전 허용(CTC-ST-05)과 결합되어 탐지 사각에서 접근 지속
+■ 실제 사례
+- [ATT&amp;CK 사례] Scattered Spider: Azure 조건부 액세스 정책에 신뢰 위치를 추가 (ATT&amp;CK G1015)
+- [ATT&amp;CK 사례] Storm-0501: 자체 MFA 수단을 등록하고 하이브리드 조인 서버로 조건부 액세스를 우회 (ATT&amp;CK G1053)</t>
         </is>
       </c>
       <c r="G81" s="17" t="inlineStr">
@@ -12708,7 +13326,7 @@
       </c>
       <c r="M81" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N81" s="17" t="inlineStr">
@@ -12769,7 +13387,16 @@
           <t>https://attack.mitre.org/techniques/T1556/009</t>
         </is>
       </c>
-      <c r="AF81" s="17" t="inlineStr"/>
+      <c r="AF81" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 조건부 액세스·IAM 조건 정책 변경(신뢰 IP 추가·MFA 제거·리전 확대) 이벤트
+- 정책 완화 직후 새 위치·리전에서의 로그인 성공
+■ 대응
+- 조건부 액세스·IAM 정책 변경에 승인 워크플로와 변경 알림
+- 정책을 코드로 관리(IaC)하고 드리프트 자동 복원</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="17" t="inlineStr">
@@ -12794,13 +13421,18 @@
       </c>
       <c r="E82" s="17" t="inlineStr">
         <is>
-          <t>공격자는 방어를 회피하기 위해 클라우드 계정 안에 스냅샷이나 데이터 백업을 만들 수 있다. 스냅샷은 가상 머신(VM), 가상 하드 드라이브, 볼륨 같은 기존 클라우드 컴퓨팅 구성 요소의 특정 시점 복사본이다. 공격자는 스냅샷 생성 권한을 이용해 기존 컴퓨팅 서비스 인프라에 대한 접근 제한을 우회할 수 있다. 이는 탐지를 회피하고 존재 증거를 없애기 위해 스냅샷으로 되돌리는 클라우드 인스턴스 되돌리기(Revert Cloud Instance)와는 다르다.</t>
+          <t>- 공격자는 EBS·디스크 볼륨의 스냅샷을 만들어, 기존 인스턴스 접근 제한을 우회해 데이터를 복사·반출할 수 있음
+- 스냅샷을 공격자 인스턴스에 마운트하거나 외부 계정에 공유해 원본 접근 통제를 거치지 않고 내용을 확보함</t>
         </is>
       </c>
       <c r="F82" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 1건)
-- Pacu(S1091) — IaaS 플랫폼 소프트웨어 [IaaS]</t>
+          <t>■ 클라우드 관점
+- AWS: ec2:CreateSnapshot으로 EBS 스냅샷 생성 후 공격자 인스턴스에 마운트, RDS 스냅샷 생성 (AWS TTC T1578.001)
+- 스냅샷을 외부 계정에 공유하거나 공개로 바꾸는 변형은 데이터 반출(CTC-EF-03) 경로가 됨
+- 탐지 회피·증거 제거용 인스턴스 되돌리기(CTC-DI-05.4)와는 목적이 다름
+■ 실제 사례
+- [ATT&amp;CK 사례] Pacu: EBS 볼륨·RDS 인스턴스의 스냅샷을 생성 (ATT&amp;CK S1091)</t>
         </is>
       </c>
       <c r="G82" s="17" t="inlineStr">
@@ -12831,7 +13463,7 @@
       </c>
       <c r="M82" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N82" s="17" t="inlineStr">
@@ -12896,7 +13528,16 @@
           <t>https://attack.mitre.org/techniques/T1578/001</t>
         </is>
       </c>
-      <c r="AF82" s="17" t="inlineStr"/>
+      <c r="AF82" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- EBS·RDS 스냅샷 생성(CreateSnapshot), 스냅샷의 외부 계정 공유·공개 전환
+- 스냅샷을 새 인스턴스에 마운트하는 패턴
+■ 대응
+- 스냅샷 생성·공유 권한 최소화, 스냅샷 공개·외부 공유 차단 정책
+- 스냅샷 암호화와 공유 이벤트 알림</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="17" t="inlineStr">
@@ -12921,17 +13562,20 @@
       </c>
       <c r="E83" s="17" t="inlineStr">
         <is>
-          <t>공격자는 방어를 회피하기 위해 클라우드 계정의 컴퓨팅 서비스 안에 새 인스턴스나 가상 머신(VM)을 만들 수 있다. 새 인스턴스를 만들면 계정에 이미 있는 인스턴스에 적용된 방화벽 규칙과 권한을 우회할 수 있다. 공격자는 계정의 볼륨 하나 이상에 대해 스냅샷 생성(Create Snapshot)을 하고, 새 인스턴스를 만들어 스냅샷을 마운트한 뒤, 덜 제한적인 보안 정책을 적용해 로컬 시스템의 데이터(Data from Local System)를 수집하거나 원격 데이터 스테이징(Remote Data Staging)을 할 수 있다.</t>
+          <t>- 공격자는 피해 계정에 새 인스턴스·VM·클러스터를 만들어 기존 인스턴스에 걸린 방화벽·권한·모니터링을 우회할 수 있음
+- 스냅샷을 마운트해 데이터를 수집하거나 덜 제한적인 정책으로 새 워크로드를 돌려, 운영 중 인스턴스에 영향 없이 활동함</t>
         </is>
       </c>
       <c r="F83" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 3건)
-- Scattered Spider(G1015) — AWS [IaaS]
-- C0027(C0027) — Azure [IaaS]
-- LAPSUS$(G1004) — 클라우드(서비스 미상) [IaaS]
-■ 통합된 기법
-- T1578 Modify Cloud Compute Infrastructure</t>
+          <t>■ 클라우드 관점
+- AWS: ec2:RunInstances, ECS·EKS 클러스터·서비스 생성(AWS TTC T1578.002)으로 통제가 적용되지 않은 새 워크로드 기동
+- 스냅샷 마운트(CTC-DI-05.1)와 결합해 로컬 데이터 수집·원격 스테이징, 크립토재킹(CTC-IM-09)의 발판
+- 통합된 상위기법(T1578) 근거 포함
+■ 실제 사례
+- [ATT&amp;CK 사례] Scattered Spider: 피해 환경에 EC2 인스턴스를 생성 (ATT&amp;CK G1015)
+- [ATT&amp;CK 사례] C0027: Scattered Spider가 피해 Azure 테넌트 접근으로 Azure VM 생성 (ATT&amp;CK C0027)
+- [ATT&amp;CK 사례] LAPSUS$: 자격증명 접근 후 피해 클라우드 환경에 새 VM 생성 (ATT&amp;CK G1004)</t>
         </is>
       </c>
       <c r="G83" s="17" t="inlineStr">
@@ -12966,7 +13610,7 @@
       </c>
       <c r="M83" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N83" s="17" t="inlineStr">
@@ -13032,7 +13676,16 @@
           <t>https://attack.mitre.org/techniques/T1578/002</t>
         </is>
       </c>
-      <c r="AF83" s="17" t="inlineStr"/>
+      <c r="AF83" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- RunInstances·클러스터/서비스 생성이 평소와 다른 주체·리전·인스턴스 유형으로 발생
+- 새 인스턴스에 덜 제한적인 보안 정책 적용
+■ 대응
+- 인스턴스·클러스터 생성 권한 최소화, 승인된 이미지·구성만 허용(정책 가드레일)
+- 신규 리소스 생성 알림과 과금 모니터링</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="17" t="inlineStr">
@@ -13057,14 +13710,19 @@
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t>공격자는 악의적 활동을 마친 뒤 탐지를 회피하고 존재 증거를 없애기 위해 클라우드 인스턴스를 삭제할 수 있다. 인스턴스를 복구할 수 없으면, 인스턴스나 가상 머신을 삭제하는 것만으로 중요한 포렌식 산출물과 기타 의심 행위 증거가 사라질 수 있다.</t>
+          <t>- 공격자는 작업을 마친 뒤 인스턴스·VM을 삭제해 포렌식 산출물과 활동 증거를 없앨 수 있음
+- 복구 불가능하게 삭제하면 조사 단서가 사라지며, 대량 삭제는 방어 회피를 넘어 업무 중단(파괴) 효과도 냄</t>
         </is>
       </c>
       <c r="F84" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 2건)
-- Storm-0501(G1053) — Azure [IaaS]
-- LAPSUS$(G1004) — 클라우드(서비스 미상) [IaaS]</t>
+          <t>■ 클라우드 관점
+- AWS: 무단 작업 후 인스턴스 종료로 증거 제거 (AWS TTC T1578.003)
+- 생성 후 목적 달성 시 종료(CTC-DI-05.2와 짝)하는 패턴, 대량 삭제는 데이터 파괴(CTC-IM-02)·업무 중단으로 이어짐
+- 백업·스냅샷 보존과 삭제 방지(복구 가능성 확보)가 방어 핵심
+■ 실제 사례
+- [ATT&amp;CK 사례] Storm-0501: Azure 구독의 클라우드 데이터 저장소·리소스를 대량 삭제 (ATT&amp;CK G1053)
+- [ATT&amp;CK 사례] LAPSUS$: 조직의 사고·위기 대응을 유발하려 클라우드 시스템·리소스를 삭제 (ATT&amp;CK G1004)</t>
         </is>
       </c>
       <c r="G84" s="17" t="inlineStr">
@@ -13095,7 +13753,7 @@
       </c>
       <c r="M84" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N84" s="17" t="inlineStr">
@@ -13160,7 +13818,15 @@
           <t>https://attack.mitre.org/techniques/T1578/003</t>
         </is>
       </c>
-      <c r="AF84" s="17" t="inlineStr"/>
+      <c r="AF84" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 인스턴스·VM 종료·삭제, 특히 작업 직후·대량 삭제, 데이터 저장소 대량 삭제
+■ 대응
+- 종료 방지(termination protection)·삭제 권한 최소화, 중요 리소스 삭제에 승인
+- 백업·스냅샷 별도 계정 보존으로 복구 가능성 확보</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="17" t="inlineStr">
@@ -13185,12 +13851,18 @@
       </c>
       <c r="E85" s="17" t="inlineStr">
         <is>
-          <t>공격자는 악의적 활동을 마친 뒤 탐지를 회피하고 존재 증거를 없애기 위해 클라우드 인스턴스의 변경 사항을 되돌릴 수 있다. 클라우드 기반 인프라처럼 가상화 수준이 높은 환경에서는 클라우드 관리 대시보드나 클라우드 API로 가상 머신(VM)이나 데이터 스토리지 스냅샷을 복원해 이를 수행할 수 있다.</t>
+          <t>- 공격자는 활동 후 VM·스토리지를 이전 스냅샷으로 되돌려 변경·침해 흔적을 제거할 수 있음
+- 클라우드 대시보드·API로 쉽게 복원되고, 임시(ephemeral) 스토리지는 재시작만으로 초기화되어 증거가 사라짐</t>
         </is>
       </c>
       <c r="F85" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- 관리 콘솔·API로 VM·스토리지 스냅샷 복원 — 침해 중 생긴 산출물을 일괄 제거
+- 임시 스토리지는 중지·재시작 시 초기화되는 특성을 악용(증거 자체가 비영속)
+- 되돌리기는 탐지 회피가 목적이라, 데이터 복사가 목적인 스냅샷 생성(CTC-DI-05.1)과 구분
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB·ATT&amp;CK 클라우드 사례에 매핑된 건은 없음(기법 문서화 수준)</t>
         </is>
       </c>
       <c r="G85" s="17" t="inlineStr">
@@ -13221,7 +13893,7 @@
       </c>
       <c r="M85" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N85" s="17" t="inlineStr">
@@ -13282,7 +13954,14 @@
           <t>https://attack.mitre.org/techniques/T1578/004</t>
         </is>
       </c>
-      <c r="AF85" s="17" t="inlineStr"/>
+      <c r="AF85" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- VM·스토리지 스냅샷 복원(되돌리기) 이벤트, 변경 이력이 사라지는 구간
+■ 대응
+- 복원 권한 최소화와 복원 이벤트 알림, 중요 로그·산출물을 비영속 스토리지 밖에 보존</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="17" t="inlineStr">
@@ -13307,12 +13986,18 @@
       </c>
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t>공격자는 방어를 회피하기 위해 클라우드 컴퓨팅 인프라의 규모, 위치, 사용 가능한 자원에 직접 영향을 주는 설정을 수정할 수 있다. 이러한 설정에는 서비스 할당량, 구독 연결, 테넌트 전체 정책 등 사용 가능한 컴퓨팅 자원에 영향을 주는 구성이 포함될 수 있다. 이런 수정을 통해 공격자는 실행 중인 인스턴스에 영향을 주거나 피해자에게 활동을 드러내지 않고도 피해자의 컴퓨팅 자원을 악용해 목표를 달성할 수 있다.</t>
+          <t>- 공격자는 서비스 할당량·VM 크기 제한·배포 가능 리전 같은 컴퓨팅 구성을 변경해, 피해자 모르게 자원 사용량을 늘릴 수 있음
+- 할당량 상향·정책 완화로 전체 쿼터를 소진하지 않고 채굴 등을 확대하며, 미사용 리전 활성화로 탐지 사각을 넓힘</t>
         </is>
       </c>
       <c r="F86" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- 할당량(quota) 상향 요청으로 크립토재킹을 티 나지 않게 확대, 테넌트 정책의 VM 크기 제한 완화 (AWS TTC T1578.005)
+- 배포 가능 리전 설정을 바꿔 미사용 리전(CTC-ST-05) 활성화
+- 자원 고갈·과금 폭탄(CTC-IM-09)의 선행 단계가 될 수 있음
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB·ATT&amp;CK 클라우드 사례에 매핑된 건은 없음(벤더·ATT&amp;CK 문서화 수준)</t>
         </is>
       </c>
       <c r="G86" s="17" t="inlineStr">
@@ -13343,7 +14028,7 @@
       </c>
       <c r="M86" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N86" s="17" t="inlineStr">
@@ -13408,7 +14093,16 @@
           <t>https://attack.mitre.org/techniques/T1578/005</t>
         </is>
       </c>
-      <c r="AF86" s="17" t="inlineStr"/>
+      <c r="AF86" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 서비스 할당량 상향 요청, VM 크기·테넌트 정책 변경, 배포 리전 설정 변경
+- 구성 변경 직후 자원 사용량 급증
+■ 대응
+- 할당량·컴퓨팅 정책 변경 권한 최소화·승인, 쿼터·사용량 급증 알림
+- 리전·인스턴스 유형 허용 목록 유지</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="17" t="inlineStr">
@@ -13433,12 +14127,18 @@
       </c>
       <c r="E87" s="17" t="inlineStr">
         <is>
-          <t>공격자는 방어를 회피하기 위해 IaaS(Infrastructure-as-a-Service) 환경의 계층 구조를 수정하려 할 수 있다.</t>
+          <t>- 공격자는 IaaS 리소스 계층(AWS Organization, Azure 관리 그룹·구독)을 수정해 통제·로깅을 벗어난 공간을 만들 수 있음
+- 신규 구독·계정 생성, Organization 탈퇴로 SCP·가드레일 제거, 구독 하이재킹으로 피해 테넌트 로그 없이 자원을 사용함</t>
         </is>
       </c>
       <c r="F87" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- AWS: organizations:CreateAccount로 SCP·탐지가 적용 안 된 새 계정 생성(AWS TTC T1666.A001), LeaveOrganization으로 계정을 Organization에서 분리해 가드레일 제거(T1666.A002), 공격자 Organization으로 초대 수락(T1666.A003)
+- Azure: 전역 관리자 권한으로 새 구독 생성, 종량제 구독을 공격자 테넌트로 이전하는 구독 하이재킹(Azure ATRM AZT507.3) — 피해 테넌트에 로그가 남지 않음
+- 테넌트 전역 통제(SCP·정책)를 우회하는 심각도 높은 방어 무력화
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB·ATT&amp;CK 클라우드 사례에 매핑된 건은 없음(벤더·ATT&amp;CK 문서화 수준)</t>
         </is>
       </c>
       <c r="G87" s="17" t="inlineStr">
@@ -13469,7 +14169,7 @@
       </c>
       <c r="M87" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N87" s="17" t="inlineStr">
@@ -13541,7 +14241,16 @@
           <t>https://attack.mitre.org/techniques/T1666</t>
         </is>
       </c>
-      <c r="AF87" s="17" t="inlineStr"/>
+      <c r="AF87" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 신규 계정·구독 생성, LeaveOrganization 호출, 구독 이전(소유자 변경) 이벤트
+- SCP·가드레일이 적용 안 된 계정의 활동
+■ 대응
+- Organization 변경·구독 이전 권한을 최소 인원으로 제한하고 승인·알림
+- 신규 계정에 기준 SCP·로깅 자동 적용, 구독 이전 차단 정책</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="17" t="inlineStr">
@@ -13566,14 +14275,20 @@
       </c>
       <c r="E88" s="17" t="inlineStr">
         <is>
-          <t>공격자는 AiTM(adversary-in-the-middle) 기법으로 둘 이상의 네트워크 장치 사이에 자리 잡아 네트워크 스니핑(Network Sniffing), 전송 데이터 조작(Transmitted Data Manipulation), 재전송 공격(자격 증명 접근을 위한 익스플로잇(Exploitation for Credential Access)) 같은 후속 행위를 도울 수 있다. ARP, DNS, LLMNR 등 네트워크 트래픽 흐름을 결정하는 일반 네트워크 프로토콜의 기능을 악용해, 장치가 공격자가 제어하는 시스템을 거쳐 통신하도록 강제하고 정보를 수집하거나 추가 작업을 수행할 수 있다.</t>
+          <t>- 공격자는 네트워크 경로 중간에 자리 잡아(AiTM 프록시, DNS·ARP 조작, 캡티브 포털 침해) 자격증명·세션 토큰·MFA 응답을 가로챌 수 있음
+- 리버스 프록시형 피싱은 MFA를 거친 세션 쿠키까지 탈취해 다단계 인증을 무력화하며, 정상 로그인처럼 보임</t>
         </is>
       </c>
       <c r="F88" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례(사고 DB)
-- [실제 사고] UNC6671 Rebrands: Multi-Brand Vishing Extortion Targets Financial Services and Enterprise Cloud Environments(2026-08, INC-0670): GTIG에 따르면 UNC6671은 BlackFile 브랜드 은퇴 발표 이후에도 Redact, Pink, Helix, Falcon 등 여러 갈취 브랜드로 활동을 이어갔다. IT 헬프데스크를 사칭한 비싱으로 직원을 가짜 로그인 포털로 유도하고, AiTM 
-- [실제 사고] CaptiveCrunch: Midnight Blizzard Hospitality Network AiTM Campaign(2026-07, INC-0666): Microsoft가 확인한 Midnight Blizzard 하위 그룹 Storm-2945의 첩보 캠페인 CaptiveCrunch다. 숙박업 캡티브 포털 인프라를 침해해 AiTM(중간자) 공격을 수행했다.</t>
+          <t>■ 클라우드 관점
+- 피싱과 결합된 AiTM 리버스 프록시가 M365·Okta 로그인을 중계해 자격증명·MFA 토큰·세션 쿠키를 가로챔(세션 쿠키 탈취는 CTC-CA-09, 앱 토큰은 CTC-CA-07과 연계)
+- 숙박업 캡티브 포털 등 네트워크 경유 지점을 장악해 중간자 위치 확보
+- K8s: CoreDNS 포이즈닝(MS-TA9035), CNI 수준의 ARP 스푸핑·IP 스푸핑(MS-TA9036)으로 클러스터 내부 트래픽 가로채기
+- 다운그레이드 공격으로 약한 프로토콜을 강제하는 변형 포함
+■ 실제 사례
+- [실제 사고] UNC6671 비싱·AiTM(2026-08): 가짜 로그인 포털과 AiTM 인프라로 자격증명·MFA 토큰을 가로채 M365·Okta에서 데이터 유출 (사고DB INC-0670)
+- [실제 사고] CaptiveCrunch / Storm-2945(2026-07): 숙박업 캡티브 포털 인프라를 침해해 중간자 공격 수행 (사고DB INC-0666)</t>
         </is>
       </c>
       <c r="G88" s="17" t="inlineStr">
@@ -13604,7 +14319,7 @@
       </c>
       <c r="M88" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N88" s="17" t="inlineStr"/>
@@ -13674,7 +14389,16 @@
           <t>https://attack.mitre.org/techniques/T1557</t>
         </is>
       </c>
-      <c r="AF88" s="17" t="inlineStr"/>
+      <c r="AF88" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 알려진 AiTM 프록시 도메인·리버스 프록시 패턴, 같은 세션 토큰의 다른 IP 재사용
+- 비정상 DNS 응답·CoreDNS 설정 변경, 클러스터 내 ARP·IP 스푸핑 징후
+■ 대응
+- 피싱 저항형 MFA(FIDO2)로 AiTM 세션 탈취 무력화, 토큰 바인딩·세션 IP 고정
+- CoreDNS·CNI 보안 설정, 캡티브 포털·네트워크 경로 무결성 점검</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="17" t="inlineStr">
@@ -13699,18 +14423,20 @@
       </c>
       <c r="E89" s="17" t="inlineStr">
         <is>
-          <t>시스템이나 환경의 정상 자격 증명을 전혀 모르는 공격자는 비밀번호를 추측해 계정 접근을 시도할 수 있다. 계정의 비밀번호를 모르면 반복적인 방식으로 비밀번호를 체계적으로 추측할 수 있다. 작전 중에 시스템이나 환경의 비밀번호를 모르는 상태에서 흔히 쓰이는 비밀번호 목록으로 로그인 자격 증명을 추측할 수 있다. 비밀번호 추측은 대상의 비밀번호 복잡도 정책이나 여러 번 실패하면 계정을 잠그는 정책을 고려할 수도 있고 고려하지 않을 수도 있다.</t>
+          <t>- 공격자는 특정 계정에 비밀번호를 반복 추측해 SSO·클라우드 애플리케이션·외부 노출 메일(M365)·관리 서비스에 접근을 시도할 수 있음
+- 계정 잠금·로그인 실패 경보를 유발할 수 있으나, 페더레이션 인증 경로는 고가시성 이벤트를 덜 남겨 탐지가 늦어짐</t>
         </is>
       </c>
       <c r="F89" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 3건)
-- Kinsing(S0599) — Containers 플랫폼 소프트웨어 [컨테이너·K8s]
-- Pysa(S0583) — Entra ID [ID·인증]
-- APT28(G0007) — Kubernetes [컨테이너·K8s]
-■ 통합된 기법
-- T1110 Brute Force
-- T1110.002 Password Cracking</t>
+          <t>■ 클라우드 관점
+- SSO·페더레이션 인증 프로토콜을 쓰는 클라우드 앱과 M365 같은 외부 노출 메일이 주 표적
+- 관리 서비스(SSH·RDP·DB 등) 포트에 대한 추측과 결합되며, 컨테이너·K8s 환경에서도 수행됨
+- 통합된 상위기법(T1110)과 해시 크래킹(T1110.002, 오프라인 해시 복원) 근거 포함 — 비밀번호 스프레이(CTC-CA-02.2)·크리덴셜 스터핑(CTC-CA-02.3)은 별도 행
+■ 실제 사례
+- [ATT&amp;CK 사례] APT28: 계정당 시간당 300여 회 인증을 시도하는 무차별 대입 도구 사용, K8s 클러스터를 경유 (ATT&amp;CK G0007)
+- [ATT&amp;CK 사례] Kinsing: SSH로 호스트에 무차별 대입 시도 (ATT&amp;CK S0599)
+- [ATT&amp;CK 사례] Pysa: 중앙 관리 콘솔과 일부 AD 계정에 무차별 대입 (ATT&amp;CK S0583)</t>
         </is>
       </c>
       <c r="G89" s="17" t="inlineStr">
@@ -13745,7 +14471,7 @@
       </c>
       <c r="M89" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N89" s="17" t="inlineStr">
@@ -13806,7 +14532,16 @@
           <t>https://attack.mitre.org/techniques/T1110/001</t>
         </is>
       </c>
-      <c r="AF89" s="17" t="inlineStr"/>
+      <c r="AF89" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 계정당 다수 인증 실패, SSO·M365 로그인 실패 급증, 페더레이션 인증의 반복 실패
+- 관리 서비스 포트에 대한 반복 로그인 시도
+■ 대응
+- 계정 잠금·지능형 잠금 정책, 피싱 저항형 MFA, 외부 노출 관리 서비스 최소화
+- 강한 비밀번호 정책과 레거시 인증 프로토콜 차단</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="17" t="inlineStr">
@@ -13831,19 +14566,20 @@
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t>공격자는 흔히 쓰이는 비밀번호 하나 또는 소수의 비밀번호 목록을 여러 계정에 시도해 유효한 계정 자격 증명을 얻으려 할 수 있다. 비밀번호 스프레이는 도메인의 복잡도 정책을 충족할 수 있는 비밀번호 하나(예: Password01)나 흔히 쓰이는 비밀번호 몇 개를 사용한다. 한 계정에 여러 비밀번호로 무차별 대입할 때 발생하는 계정 잠금을 피하기 위해, 같은 비밀번호로 네트워크의 여러 계정에 로그인을 시도한다.</t>
+          <t>- 공격자는 흔한 비밀번호 하나를 여러 계정에 시도해 계정 잠금을 피하면서 유효 자격증명을 찾을 수 있음
+- SSO·M365 대상 스프레이는 임계값을 피하려 속도를 조절하며, 침해한 계정은 곧 크립토재킹·데이터 유출의 발판이 됨</t>
         </is>
       </c>
       <c r="F90" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례(사고 DB)
-- [실제 사고] Financially Motivated Threat Actor BREEZE COMET Targets Brazil(2026-09, INC-0677): Mandiant가 2024년부터 조사한 브라질 금융, 유통, 전자상거래 조직 침해 사례다. GTIG는 결제 시스템과 뱅킹 소프트웨어를 조작해 부정 이체를 하는 금전 목적 행위자 BREEZE COMET(구 UNC5669)으로 추적하고 있으며, 생성형 A
-- [실제 사고] Password spray attack leads to containers being used for cryptomining(2025-04, INC-0501): Microsoft는 지난 1년간 AzureChecker(Storm-1977)가 교육 부문 클라우드 테넌트에 패스워드 스프레이 공격을 하는 것을 관측했다. 침해 후 컨테이너가 크립토마이닝에 사용되었다.
-- [실제 사고] USAID cryptojacking incident(2025-01, INC-0459): 미국 국제개발처(USAID)의 Azure 구독 테스트 환경에서 전역 관리자 계정이 패스워드 스프레이로 침해되었고, 이 계정이 크립토재킹에 악용되었다.
-- 외 4건(관련 사례 ID 열)
-■ ATT&amp;CK 사례(행위자, 총 2건)
-- APT28(G0007) — Kubernetes [컨테이너·K8s]
-- MailSniper(S0413) — Microsoft 365 [SaaS·협업]</t>
+          <t>■ 클라우드 관점
+- SSO·페더레이션 앱과 M365가 주 표적(Azure ATRM AZT202), 탐지 임계값을 피하려 계정당 시도를 의도적으로 조절
+- 레거시·비운영 테넌트 계정, 테스트 구독의 관리자 계정처럼 모니터링이 약한 계정이 자주 뚫림
+- 침해 후 크립토재킹(CTC-IM-09)·메일 유출(CTC-CO-07)로 이어짐
+■ 실제 사례
+- [실제 사고] USAID 크립토재킹(2025-01): Azure 테스트 환경의 전역 관리자 계정이 스프레이로 침해되어 크립토재킹에 악용 (사고DB INC-0459)
+- [실제 사고] Storm-1977(2025-04): 교육 부문 클라우드 테넌트에 스프레이 후 컨테이너를 크립토마이닝에 사용 (사고DB INC-0501)
+- [실제 사고] Nobelium/APT29(2023-11~): 레거시 비운영 테넌트 계정을 스프레이로 침해해 Microsoft 임직원 메일 유출 (사고DB INC-0264)</t>
         </is>
       </c>
       <c r="G90" s="17" t="inlineStr">
@@ -13874,7 +14610,7 @@
       </c>
       <c r="M90" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N90" s="17" t="inlineStr">
@@ -13947,7 +14683,16 @@
           <t>https://attack.mitre.org/techniques/T1110/003</t>
         </is>
       </c>
-      <c r="AF90" s="17" t="inlineStr"/>
+      <c r="AF90" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 다수 계정에 동일 비밀번호로의 로그인 시도, 느린 속도로 분산된 인증 실패
+- 레거시 인증 엔드포인트 사용, 비정상 위치·ASN에서의 대량 로그인
+■ 대응
+- 레거시 인증 차단·조건부 액세스, 피싱 저항형 MFA, 지능형 잠금
+- 테스트·레거시 테넌트 계정 정리와 관리자 계정 MFA 강제</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="17" t="inlineStr">
@@ -13972,12 +14717,18 @@
       </c>
       <c r="E91" s="17" t="inlineStr">
         <is>
-          <t>공격자는 관련 없는 계정의 유출 덤프에서 얻은 자격 증명으로 자격 증명이 겹치는 대상 계정에 접근할 수 있다. 웹사이트나 서비스가 침해되어 사용자 계정 자격 증명이 유출되면 대량의 사용자 이름과 비밀번호 쌍이 온라인에 공개되기도 한다. 사용자가 개인 계정과 업무 계정에 같은 비밀번호를 쓰는 경향이 있으므로, 이 정보는 계정을 침해하려는 공격자에게 유용할 수 있다.</t>
+          <t>- 공격자는 타 유출 덤프의 사용자명·비밀번호 쌍을 대상 서비스에 대입해, 비밀번호를 재사용하는 계정에 접근할 수 있음
+- 개인·업무 계정 비밀번호 재사용을 노리며, SSO·M365 등 외부 노출 서비스에서 유효 조합을 찾음</t>
         </is>
       </c>
       <c r="F91" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- 유출 자격증명 목록을 SSO·페더레이션 앱·M365에 대입 — 비밀번호 재사용이 전제
+- 추측(CTC-CA-02.1)·스프레이(CTC-CA-02.2)와 달리 이미 알려진 평문 쌍을 사용해 성공률이 높음
+- 피싱 저항형 MFA와 유출 자격증명 모니터링이 핵심 방어
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB에 이 하위기법으로 특정 매핑된 사고는 없음(유출 자격증명 재사용은 유효 계정 악용 사고 CTC-IA-06.2와 겹침)</t>
         </is>
       </c>
       <c r="G91" s="17" t="inlineStr">
@@ -14008,7 +14759,7 @@
       </c>
       <c r="M91" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N91" s="17" t="inlineStr">
@@ -14069,7 +14820,16 @@
           <t>https://attack.mitre.org/techniques/T1110/004</t>
         </is>
       </c>
-      <c r="AF91" s="17" t="inlineStr"/>
+      <c r="AF91" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 유출 자격증명 목록과 일치하는 로그인, 여러 계정에서 1회 성공 후 멈추는 패턴
+- 비정상 위치·자동화 도구 사용자 에이전트
+■ 대응
+- 유출 비밀번호 검사·차단(비밀번호 보호), 피싱 저항형 MFA
+- 비밀번호 재사용 금지 정책과 침해 자격증명 모니터링</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="17" t="inlineStr">
@@ -14094,18 +14854,21 @@
       </c>
       <c r="E92" s="17" t="inlineStr">
         <is>
-          <t>공격자는 AWS Secrets Manager, GCP Secret Manager, Azure Key Vault, Terraform Vault 같은 클라우드 네이티브 비밀 관리 솔루션에서 자격 증명을 획득할 수 있다.</t>
+          <t>- 공격자는 충분한 권한을 얻으면 AWS Secrets Manager·GCP Secret Manager·Azure Key Vault에서 비밀·API 키·인증서를 직접 조회할 수 있음
+- 비밀 저장소는 다수 서비스 자격증명을 한곳에 모아, 조회 권한 하나가 환경 전반 장악으로 이어짐</t>
         </is>
       </c>
       <c r="F92" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 10건)
-- TeamPCP Cloud Stealer(S9041) — Containers, SaaS 플랫폼 소프트웨어 [SaaS·협업]
-- HAFNIUM(G0125) — Azure [IaaS]
-- Storm-0501(G1053) — Azure [IaaS]
-- TeamPCP(G1056) — Azure, AWS, GCP [IaaS]
-■ 통합된 기법
-- T1555 Credentials from Password Stores</t>
+          <t>■ 클라우드 관점
+- 조회 명령: AWS get-secret-value, GCP gcloud secrets, Azure az keyvault secret show(Azure ATRM AZT604 계열) — IMDS 경유가 아닌 비밀 저장소에 직접 요청하는 점이 CTC-CA-10.2와 구분
+- 비밀을 조회할 권한을 가진 서비스·고권한 계정을 장악하면 다수 서비스 자격증명을 한 번에 수집
+- 일시 삭제(soft-delete) 상태의 Key Vault 객체 복구(AZT704.1)로도 비밀 확보 가능
+- 통합된 상위기법(T1555) 근거 포함, 공급망 악성코드의 주요 수집 대상
+■ 실제 사례
+- [ATT&amp;CK 사례] Shai-Hulud: AWS Secrets·GCP Secret Manager·Azure Key Vault에서 비밀 수집 (ATT&amp;CK S9008)
+- [ATT&amp;CK 사례] TeamPCP: 악성코드로 AWS·GCP·Azure 환경의 클라우드 비밀을 반출 (ATT&amp;CK G1056)
+- [ATT&amp;CK 사례] HAFNIUM: 온프레미스에서 횡적 이동해 Azure Key Vault의 비밀번호를 탈취 (ATT&amp;CK G0125)</t>
         </is>
       </c>
       <c r="G92" s="17" t="inlineStr">
@@ -14140,7 +14903,7 @@
       </c>
       <c r="M92" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N92" s="17" t="inlineStr">
@@ -14209,7 +14972,16 @@
           <t>https://attack.mitre.org/techniques/T1555/006</t>
         </is>
       </c>
-      <c r="AF92" s="17" t="inlineStr"/>
+      <c r="AF92" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 비밀 저장소 대량 조회(get-secret-value·KeyVault getSecret 등), 평소 접근하지 않던 주체의 비밀 조회
+- 짧은 시간 다수 비밀 열람, soft-delete 객체 복구
+■ 대응
+- 비밀 조회 권한 최소화·비밀별 접근 정책, 비밀 접근 로깅·이상 조회 알림
+- 비밀 정기 교체와 접근 가능 주체 정기 검토</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="17" t="inlineStr">
@@ -14234,12 +15006,18 @@
       </c>
       <c r="E93" s="17" t="inlineStr">
         <is>
-          <t>공격자는 웹 애플리케이션이나 인터넷 서비스에 접근하는 데 쓸 수 있는 웹 쿠키를 위조할 수 있다. 클라우드 SaaS 환경이나 온프레미스 서버에 호스팅된 웹 애플리케이션과 서비스는 사용자 접근을 인증·인가하기 위해 세션 쿠키를 쓰는 경우가 많다.</t>
+          <t>- 공격자는 서명 비밀·키를 확보하면 웹 세션 쿠키를 새로 위조해, 탈취 없이도 웹 애플리케이션·SaaS에 접근할 수 있음
+- 위조 쿠키는 정상 발급 쿠키와 구분이 어렵고 MFA 등 인증 통제를 우회함</t>
         </is>
       </c>
       <c r="F93" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- SaaS·웹 애플리케이션의 표준화된 쿠키 값을 서명 비밀(비밀번호·개인 키·시드)로 생성 — 사용자에게서 가로채는 세션 쿠키 탈취(CTC-CA-09)와 달리 새로 만들어 냄
+- 위조 쿠키로 리소스 접근(CTC-LM-06.2) 시 MFA·인증 통제를 우회
+- 쿠키 서명 비밀의 안전한 보관·교체가 방어 핵심
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB·ATT&amp;CK 클라우드 사례에 매핑된 건은 없음(기법 문서화 수준). 실제 사고는 쿠키 탈취(CTC-CA-09)·토큰 위조(CTC-CA-04.2)에 집중</t>
         </is>
       </c>
       <c r="G93" s="17" t="inlineStr">
@@ -14270,7 +15048,7 @@
       </c>
       <c r="M93" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N93" s="17" t="inlineStr">
@@ -14331,7 +15109,15 @@
           <t>https://attack.mitre.org/techniques/T1606/001</t>
         </is>
       </c>
-      <c r="AF93" s="17" t="inlineStr"/>
+      <c r="AF93" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 발급 기록이 없는 세션으로의 접근, 동일 쿠키의 비정상 위치 사용
+■ 대응
+- 쿠키 서명 비밀·키의 안전 보관·정기 교체, 세션 IP·장치 바인딩
+- 민감 작업에 재인증 요구</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="17" t="inlineStr">
@@ -14356,16 +15142,20 @@
       </c>
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t>공격자는 유효한 SAML 토큰 서명 인증서를 가지고 있으면 임의의 권한 클레임과 유효 기간을 가진 SAML 토큰을 위조할 수 있다. SAML 토큰의 기본 유효 기간은 1시간이지만, 토큰의 conditions 요소에 있는 NotOnOrAfter 값으로 유효 기간을 지정할 수 있다. 이 값은 LifetimeTokenPolicy의 AccessTokenLifetime으로 바꿀 수 있다. 위조된 SAML 토큰을 이용하면 SAML 2.0을 SSO(Single Sign-On) 방식으로 쓰는 여러 서비스에 인증할 수 있다.</t>
+          <t>- 공격자는 유효한 SAML 토큰 서명 인증서를 확보하면 임의 권한·유효기간의 SAML 토큰을 위조해(Golden SAML) SSO 기반 서비스에 인증할 수 있음
+- 고권한 계정을 사칭한 토큰으로 관리자 권한을 얻으며, 비밀번호 재설정·MFA로도 막히지 않음</t>
         </is>
       </c>
       <c r="F94" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례(사고 DB)
-- [실제 사고] The ‘Ghost’ in the Database: Recovering Active ADFS Signing Keys via Machine DPAPI(2026-07, INC-0654): Mandiant 레드팀이 ADFS 인증서를 수동 교체하는 환경(AutoCertificateRollover 비활성)에서 활성 토큰 서명 키가 Machine DPAPI에 노출된 채 남을 수 있음을 발견한 연구다. 이를 통해 Golden SAML로 MFA와
-- [실제 사고] APT29 targeting Microsoft 365(2022-08, INC-0114)
-■ ATT&amp;CK 사례(행위자, 총 1건)
-- AADInternals(S0677) — Entra ID [ID·인증]</t>
+          <t>■ 클라우드 관점
+- AD FS 토큰 서명 인증서(개인 키)를 탈취하거나 자체 페더레이션 신뢰를 세워 서명 인증서를 생성(CTC-DI-03.1과 연계) — 임의 사용자·권한 클레임으로 토큰 위조
+- 위조 SAML 토큰으로 Entra ID·AWS·GCP 등 SSO 연동 서비스에 인증, 대체 인증 자료(CTC-LM-06)로 MFA 우회
+- AutoCertificateRollover 비활성 환경에서 서명 키가 Machine DPAPI에 노출돼 복구되는 경로가 연구로 확인됨
+■ 실제 사례
+- [실제 사고] APT29 M365 공격(2022-08): ADFS 접근으로 골든 SAML 토큰 서명을 이용해 테넌트 인증 (사고DB INC-0114)
+- [실증·연구] ADFS 서명 키 복구(2026-07): Machine DPAPI에 노출된 활성 토큰 서명 키로 골든 SAML을 통해 MFA·ID 통제 우회 가능성 입증 (사고DB INC-0654)
+- [ATT&amp;CK 사례] AADInternals: AD FS 토큰 서명 인증서로 SAML 토큰 생성 (ATT&amp;CK S0677)</t>
         </is>
       </c>
       <c r="G94" s="17" t="inlineStr">
@@ -14396,7 +15186,7 @@
       </c>
       <c r="M94" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N94" s="17" t="inlineStr">
@@ -14465,7 +15255,16 @@
           <t>https://attack.mitre.org/techniques/T1606/002</t>
         </is>
       </c>
-      <c r="AF94" s="17" t="inlineStr"/>
+      <c r="AF94" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 발행자·서명 인증서가 평소와 다른 SAML 토큰, 비정상적으로 긴 유효기간 토큰
+- ADFS 토큰 서명 인증서 접근·내보내기, 신규 페더레이션 신뢰 추가
+■ 대응
+- 토큰 서명 인증서 보호(HSM)·정기 교체, ADFS 서버 Tier0 격리
+- 발행자·클레임 이상 탐지, 가능 시 클라우드 인증으로 전환</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="17" t="inlineStr">
@@ -14490,16 +15289,20 @@
       </c>
       <c r="E95" s="17" t="inlineStr">
         <is>
-          <t>공격자는 침해한 계정에 지속적으로 접근하기 위해 다중 인증(MFA) 메커니즘을 비활성화하거나 수정할 수 있다.</t>
+          <t>- 공격자는 침해 계정 유지를 위해 MFA를 비활성화하거나 취약한 MFA 수단으로 교체할 수 있으며, 탈취한 세션 토큰으로 MFA 자체를 건너뛰기도 함
+- 조건부 액세스에서 사용자 제외·'실패 시 허용(fail open)' 설정을 악용하면 계정 단위를 넘어 그룹 전체의 MFA가 무력화됨</t>
         </is>
       </c>
       <c r="F95" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례(사고 DB)
-- [실제 사고] BitoPro(2025-05, INC-0506): BitoPro의 클라우드 운영 직원이 소셜 엔지니어링과 악성코드로 침해되었다. 탈취된 AWS 세션 토큰으로 MFA가 우회되었고, 1,100만 달러 상당의 암호화폐가 탈취되었다.
-- [실제 사고] ByBit hack(2025-02, INC-0470): 2025년 2월 21일 북한 연계 TraderTraitor(UNC4899)가 Safe{Wallet}을 공격했다. 개발자 노트북을 침해해 AWS 세션 토큰을 가로채고 MFA를 우회한 뒤 Safe{Wallet} 서버에 무단 접근했다(ByBit 해킹).
-■ ATT&amp;CK 사례(행위자, 총 1건)
-- AADInternals(S0677) — Entra ID [ID·인증]</t>
+          <t>■ 클라우드 관점
+- Entra ID 등에서 조건부 액세스 사용자 제외, 공격자 제어 MFA 수단 등록(CTC-PE-01.5 연계), MFA 자가 등록 악용으로 요건 무력화
+- 가장 흔한 실제 경로는 피싱·단말 침해로 얻은 유효 세션·액세스 토큰으로 MFA를 건너뛰는 것 — 토큰이 이미 인증된 세션을 담고 있어 재인증이 필요 없음
+- 지속성(PE)·방어 무력화(DI)·자격증명 접근(CA) 세 전술에 걸침
+■ 실제 사례
+- [실제 사고] ByBit/Safe{Wallet}(2025-02): TraderTraitor(UNC4899)가 개발자 노트북을 침해해 AWS 세션 토큰을 가로채 MFA를 우회하고 서버에 무단 접근 (사고DB INC-0470)
+- [실제 사고] BitoPro(2025-05): 클라우드 운영 직원 침해로 탈취한 AWS 세션 토큰으로 MFA를 우회, 약 1,100만 달러 암호화폐 탈취 (사고DB INC-0506)
+- [ATT&amp;CK 사례] AADInternals: Set-AADIntUserMFA로 지정 사용자의 MFA 비활성화 (ATT&amp;CK S0677)</t>
         </is>
       </c>
       <c r="G95" s="17" t="inlineStr">
@@ -14530,7 +15333,7 @@
       </c>
       <c r="M95" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N95" s="17" t="inlineStr">
@@ -14599,7 +15402,16 @@
           <t>https://attack.mitre.org/techniques/T1556/006</t>
         </is>
       </c>
-      <c r="AF95" s="17" t="inlineStr"/>
+      <c r="AF95" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- MFA 비활성화·조건부 액세스 제외·MFA 수단 변경 이벤트, 같은 세션 토큰의 다른 IP 재사용
+- 'fail open' 구성과 MFA 요구가 사라진 로그인 성공
+■ 대응
+- 피싱 저항형 MFA(FIDO2)와 'fail open' 금지, MFA·조건부 액세스 변경에 다중 관리자 승인
+- 토큰 보호·세션 수명 단축, 의심 세션 토큰 즉시 폐기</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="17" t="inlineStr">
@@ -14624,14 +15436,19 @@
       </c>
       <c r="E96" s="17" t="inlineStr">
         <is>
-          <t>공격자는 일반 인증 메커니즘을 우회하고, 자격 증명에 접근하고, 계정에 지속적으로 접근하기 위해 온프레미스 사용자 ID와 연결된 클라우드 인증 절차에 패치를 적용하거나, 이를 수정하거나, 백도어를 심을 수 있다.</t>
+          <t>- 공격자는 온프레미스-클라우드 하이브리드 ID 연결(PHS·PTA·AD FS)에 백도어를 심어 모든 인증을 통과시키고 자격증명을 수집할 수 있음
+- 연동 지점 하나를 장악하면 페더레이션된 모든 클라우드·SaaS에 지속적 특권 접근이 가능해 피해 범위가 테넌트 전체로 확대됨</t>
         </is>
       </c>
       <c r="F96" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 2건)
-- AADInternals(S0677) — Entra ID [ID·인증]
-- APT29(G0016) — 클라우드(서비스 미상) [클라우드(복합)]</t>
+          <t>■ 클라우드 관점
+- Entra ID 동기화 세 방식이 표적: PTA 에이전트 서버에 악성 DLL(PTASpy) 주입으로 모든 인증 승인·자격증명 기록, AD FS 구성 변조로 임의 사용자 토큰 위조(Golden SAML 계열)
+- AD FS는 AWS·GCP 등 타 클라우드 페더레이션에도 쓰여, 한 번의 변조가 여러 클라우드로 파급
+- 하이브리드 조인 서버는 조건부 액세스 우회에도 악용됨 (CTC-PE-08.3 연계)
+■ 실제 사례
+- [ATT&amp;CK 사례] APT29: Microsoft.IdentityServer.Servicehost 구성을 수정해 AD FS에 악성 DLL을 로드, 페더레이션된 서비스에 지속 접근 (ATT&amp;CK G0016)
+- [ATT&amp;CK 사례] AADInternals: PTASpy DLL을 PTA 에이전트 서비스에 주입해 Pass-Through 인증을 백도어화 (ATT&amp;CK S0677)</t>
         </is>
       </c>
       <c r="G96" s="17" t="inlineStr">
@@ -14662,7 +15479,7 @@
       </c>
       <c r="M96" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N96" s="17" t="inlineStr">
@@ -14723,7 +15540,16 @@
           <t>https://attack.mitre.org/techniques/T1556/007</t>
         </is>
       </c>
-      <c r="AF96" s="17" t="inlineStr"/>
+      <c r="AF96" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- PTA 에이전트·AD FS 서버의 DLL 로드·구성 파일 변경, 토큰 서명 인증서의 비정상 사용
+- 온프레미스 조인 서버에서 발급된 토큰의 광범위한 클라우드 접근
+■ 대응
+- 하이브리드 ID 연동 서버를 Tier0로 취급·접근 최소화, 토큰 서명 인증서 보호·정기 교체
+- AD FS → 클라우드 인증의 이상 토큰 탐지, 가능 시 클라우드 인증으로 전환</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="17" t="inlineStr">
@@ -14748,14 +15574,19 @@
       </c>
       <c r="E97" s="17" t="inlineStr">
         <is>
-          <t>공격자는 침해한 계정에 지속적으로 접근하기 위해 조건부 액세스 정책을 비활성화하거나 수정할 수 있다. 조건부 액세스 정책은 ID 공급자와 ID·접근 관리 시스템이 사용자에게 리소스 접근을 허용할지 판단할 때 쓰는 추가 검증이다.</t>
+          <t>- 공격자는 조건부 액세스·IAM 조건 정책을 수정해(신뢰 IP 추가, MFA 요구 제거, 허용 리전 확대) 침해 계정의 접근을 지속할 수 있음
+- 정책 완화는 정상 관리 변경처럼 보여, 이후 탈취 자격증명이 통제를 그대로 통과하게 만듦</t>
         </is>
       </c>
       <c r="F97" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 2건)
-- Scattered Spider(G1015) — Entra ID [ID·인증]
-- Storm-0501(G1053) — 클라우드(서비스 미상) [클라우드(복합)]</t>
+          <t>■ 클라우드 관점
+- IdP(Entra ID·Okta·JumpCloud): 신뢰 위치 추가, MFA·장치 등록·위험 기반 차단 조건 완화
+- AWS·GCP: IAM 정책의 조건 속성(source IP·요청 시각·리전) 변경으로 제약 무력화
+- 미사용 리전 허용(CTC-ST-05)과 결합되어 탐지 사각에서 접근 지속
+■ 실제 사례
+- [ATT&amp;CK 사례] Scattered Spider: Azure 조건부 액세스 정책에 신뢰 위치를 추가 (ATT&amp;CK G1015)
+- [ATT&amp;CK 사례] Storm-0501: 자체 MFA 수단을 등록하고 하이브리드 조인 서버로 조건부 액세스를 우회 (ATT&amp;CK G1053)</t>
         </is>
       </c>
       <c r="G97" s="17" t="inlineStr">
@@ -14786,7 +15617,7 @@
       </c>
       <c r="M97" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N97" s="17" t="inlineStr">
@@ -14847,7 +15678,16 @@
           <t>https://attack.mitre.org/techniques/T1556/009</t>
         </is>
       </c>
-      <c r="AF97" s="17" t="inlineStr"/>
+      <c r="AF97" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 조건부 액세스·IAM 조건 정책 변경(신뢰 IP 추가·MFA 제거·리전 확대) 이벤트
+- 정책 완화 직후 새 위치·리전에서의 로그인 성공
+■ 대응
+- 조건부 액세스·IAM 정책 변경에 승인 워크플로와 변경 알림
+- 정책을 코드로 관리(IaC)하고 드리프트 자동 복원</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="17" t="inlineStr">
@@ -14872,12 +15712,18 @@
       </c>
       <c r="E98" s="17" t="inlineStr">
         <is>
-          <t>공격자는 사용자에게 다중 인증(MFA) 요청을 보내는 방식으로 MFA 메커니즘을 우회하고 계정에 접근하려 할 수 있다.</t>
+          <t>- 공격자는 유효 자격증명을 가진 상태에서 MFA 푸시 알림을 반복 발생시켜(MFA 피로) 사용자가 승인하도록 유도할 수 있음
+- 자가 비밀번호 재설정(SSPR)의 자동 알림도 악용되며, 반복 푸시·SMS·전화로 사용자의 수락을 노림</t>
         </is>
       </c>
       <c r="F98" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- Duo Push·Microsoft Authenticator·Okta 등 클라우드 IdP의 푸시 승인을 반복 유발해 사용자의 피로성 승인을 노림
+- 유효 자격증명이 있으나 MFA가 막는 상황에서 쓰이며, 비싱(CTC-IA-03.2)과 결합되기도 함
+- 숫자 매칭(number matching)·푸시 횟수 제한 같은 MFA 강화로 완화
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB에 이 기법으로 특정 매핑된 사고는 없음(여러 계정 탈취 사고의 MFA 우회 단계로 나타남)</t>
         </is>
       </c>
       <c r="G98" s="17" t="inlineStr">
@@ -14908,7 +15754,7 @@
       </c>
       <c r="M98" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N98" s="17" t="inlineStr">
@@ -14969,7 +15815,16 @@
           <t>https://attack.mitre.org/techniques/T1621</t>
         </is>
       </c>
-      <c r="AF98" s="17" t="inlineStr"/>
+      <c r="AF98" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 짧은 시간 반복되는 MFA 푸시·SMS, 다수 거부 후 1회 승인 패턴
+- SSPR 자동 알림의 비정상 발생
+■ 대응
+- 숫자 매칭 MFA·푸시 횟수 제한, 피싱 저항형 MFA
+- MFA 피로 패턴 알림과 사용자 교육</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="17" t="inlineStr">
@@ -14994,21 +15849,21 @@
       </c>
       <c r="E99" s="17" t="inlineStr">
         <is>
-          <t>공격자는 원격 시스템과 리소스에 접근할 자격 증명을 얻는 수단으로 애플리케이션 액세스 토큰을 탈취할 수 있다.</t>
+          <t>- 공격자는 OAuth 앱 토큰·관리 ID 토큰·K8s 서비스 어카운트 토큰·CI/CD 토큰을 탈취해 사용자·서비스 권한으로 API 작업을 수행할 수 있음
+- 토큰은 MFA를 우회하고 권한 범위만큼 즉시 작동해, 한 건의 토큰 탈취가 다수 조직·서비스로 번짐</t>
         </is>
       </c>
       <c r="F99" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례(사고 DB)
-- [실제 사고] Context.ai OAuth Token Compromise(2026-04, INC-0616): 2026년 4월 19일 Vercel이 내부 시스템 무단 접근 사고를 공개했다. 서드파티 AI 도구 Context.ai 직원 기기의 인포스틸러(Lumma Stealer)에서 시작되었으며, 공격자는 Context.ai의 AWS 환경에서 고객 OAuth 토
-- [실제 사고] Stolen SaaS Integration Tokens Enable Data Theft Across Snowflake Environments(2026-04, INC-0613): SaaS 분석 플랫폼 Anodot의 보안 사고에서 시작된 것으로 보도되었다. 공격자는 Snowflake, S3 등 연동용 인증 토큰을 확보해 여러 Snowflake 환경에서 데이터를 탈취했다.
-- [실제 사고] Kiln(2025-10, INC-0562): Kiln의 GitHub 액세스 토큰이 침해되었다. 공격자는 GitHub Actions에서 자격증명을 훔치고 운영 중인 API 로직을 변조해 암호화폐를 탈취했다.
-- 외 5건(관련 사례 ID 열)
-■ ATT&amp;CK 사례(행위자, 총 11건)
-- APT28(G0007) — Google Workspace [SaaS·협업]
-- ShinyHunters(G1057) — GitHub·GitLab [SaaS·협업]
-- CanisterWorm(S9042) — Containers 플랫폼 소프트웨어 [컨테이너·K8s]
-- Kali365(S9044) — IaaS 플랫폼 소프트웨어 [IaaS]</t>
+          <t>■ 클라우드 관점
+- K8s: 침해 컨테이너에서 서비스 어카운트 토큰 탈취로 API 서버 접근(K8s MS-TA9016)
+- Azure: 관리 ID가 붙은 VM·Function·Logic App·Runbook에서 IMDS·로직 조작으로 JWT 획득(Azure ATRM AZT601 계열)
+- CI/CD: 러너 메모리·파이프라인에서 토큰 추출, SaaS 통합 OAuth 토큰 탈취로 다운스트림 조직 침해
+- 동의 피싱(AZT203)·AiTM로도 토큰 확보 — 세션 쿠키(CTC-CA-09)와 함께 다단계 인증 우회
+■ 실제 사례
+- [실제 사고] Salesloft Drift 공급망 침해(2025-08): GitHub 저장소·AWS 환경 접근으로 OAuth 토큰을 탈취해 700여 Salesforce 인스턴스 침해 (사고DB INC-0549·INC-0555)
+- [실제 사고] Context.ai OAuth 토큰 침해(2026-04): 인포스틸러로 시작해 Context.ai AWS 환경에서 고객 OAuth 토큰을 탈취, Vercel 직원 Workspace 접근 (사고DB INC-0616)
+- [ATT&amp;CK 사례] TeamPCP Cloud Stealer: runner.worker 프로세스 메모리를 읽어 평문 토큰 추출 (ATT&amp;CK S9041)</t>
         </is>
       </c>
       <c r="G99" s="17" t="inlineStr">
@@ -15039,7 +15894,7 @@
       </c>
       <c r="M99" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N99" s="17" t="inlineStr">
@@ -15124,7 +15979,16 @@
           <t>https://attack.mitre.org/techniques/T1528</t>
         </is>
       </c>
-      <c r="AF99" s="17" t="inlineStr"/>
+      <c r="AF99" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 서비스 어카운트·관리 ID·OAuth 토큰의 비정상 출발지 사용, 러너 프로세스 메모리 접근
+- 관리 ID JWT를 반환하도록 리소스 로직 수정, SaaS 통합 토큰의 대량 데이터 조회
+■ 대응
+- 토큰 수명 단축·IMDSv2·토큰 바인딩, 서비스 어카운트 토큰 자동 마운트 최소화
+- CI/CD 비밀 최소화·단기 자격증명, 통합 앱 토큰 범위 제한·이상 사용 알림</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="17" t="inlineStr">
@@ -15149,14 +16013,19 @@
       </c>
       <c r="E100" s="17" t="inlineStr">
         <is>
-          <t>공격자는 원격 시스템이나 리소스에 접근하기 위해 인증에 쓰이는 인증서를 탈취하거나 위조할 수 있다. 디지털 인증서는 메시지나 파일의 서명과 암호화에 자주 쓰이며 인증 자료로도 쓰인다. 예를 들어 Entra ID 장치 인증서와 AD CS(Active Directory Certificate Services) 인증서는 ID에 연결되어 도메인 계정의 자격 증명으로 쓰일 수 있다.</t>
+          <t>- 공격자는 인증 인증서를 탈취하거나 위조해(AD CS, Entra 장치 인증서, 서비스 주체 인증서) 계정·장치를 가장하고 지속·횡적 이동할 수 있음
+- 인증서는 비밀번호 재설정에도 유효기간 동안 유효하며, CA 개인 키를 얻으면 임의 인증서를 위조해 장기 지속성을 확보함</t>
         </is>
       </c>
       <c r="F100" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 2건)
-- Mini Shai-Hulud(S9043) — Azure [IaaS]
-- AADInternals(S0677) — Entra ID [ID·인증]</t>
+          <t>■ 클라우드 관점
+- Azure: 서비스 주체 인증서 탈취(Azure ATRM AZT602), Key Vault에서 인증서 덤프(AZT604.2), Entra 조인·등록 장치 인증서 생성·내보내기
+- AD CS 발급·등록 권한 오구성은 권한 상승·사칭(SAN 악용) 경로가 되며, 페더레이션 서명 인증서는 골든 SAML(CTC-CA-04.2)과 연결
+- 인증서는 유효기간 동안 비밀번호 재설정과 무관하게 유효 — 교체·폐기 체계가 핵심
+■ 실제 사례
+- [ATT&amp;CK 사례] AADInternals: Entra 조인·등록 장치 관련 인증서를 생성·내보내기 (ATT&amp;CK S0677)
+- [ATT&amp;CK 사례] Mini Shai-Hulud: 피해자 클라이언트 인증서를 수집해 Azure 환경 서명 인증 어설션에 활용 (ATT&amp;CK S9043)</t>
         </is>
       </c>
       <c r="G100" s="17" t="inlineStr">
@@ -15187,7 +16056,7 @@
       </c>
       <c r="M100" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N100" s="17" t="inlineStr">
@@ -15253,7 +16122,16 @@
           <t>https://attack.mitre.org/techniques/T1649</t>
         </is>
       </c>
-      <c r="AF100" s="17" t="inlineStr"/>
+      <c r="AF100" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- AD CS 비정상 인증서 발급·등록, 서비스 주체·장치 인증서 생성·내보내기, Key Vault 인증서 덤프
+- 인증서 기반 인증의 비정상 사용(새 SAN·장기 유효기간)
+■ 대응
+- CA 개인 키 보호(HSM)·발급 권한·템플릿 점검, 인증서 정기 교체·폐기
+- 서비스 주체 인증서 접근 로깅과 이상 발급 알림</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="17" t="inlineStr">
@@ -15278,14 +16156,19 @@
       </c>
       <c r="E101" s="17" t="inlineStr">
         <is>
-          <t>공격자는 웹 애플리케이션이나 서비스의 세션 쿠키를 탈취해, 자격 증명 없이도 인증된 사용자로서 웹 애플리케이션이나 인터넷 서비스에 접근할 수 있다. 웹 애플리케이션과 서비스는 사용자가 웹사이트에 인증한 뒤 세션 쿠키를 인증 토큰으로 사용하는 경우가 많다.</t>
+          <t>- 공격자는 브라우저·프로세스 메모리·네트워크에서 웹 세션 쿠키를 탈취해, 자격증명 없이 인증된 사용자로 SaaS·M365에 접근할 수 있음
+- 세션 쿠키는 장기간 유효하고 MFA를 거친 세션을 담고 있어, 탈취 시 다단계 인증을 그대로 우회함</t>
         </is>
       </c>
       <c r="F101" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 2건)
-- Kali365(S9044) — IaaS 플랫폼 소프트웨어 [IaaS]
-- evilginx2(S9003) — IaaS, Identity Provider, Office Suite, SaaS 플랫폼 소프트웨어 [클라우드(복합)]</t>
+          <t>■ 클라우드 관점
+- 인포스틸러가 브라우저·앱 메모리의 클라우드 세션 쿠키를 수집, AiTM 리버스 프록시(Evilginx2·Muraena)가 피싱 중계로 쿠키 탈취(CTC-CA-01과 연계)
+- 악성 JavaScript 주입·사용자 실행으로도 쿠키 수집
+- 탈취 쿠키로 웹 세션 재사용(CTC-LM-06.2) 시 MFA 우회 — 위조 쿠키(CTC-CA-04.1)와 달리 정상 쿠키를 가로챔
+■ 실제 사례
+- [ATT&amp;CK 사례] evilginx2: 피해자와의 각 세션에서 세션 쿠키 등 정보를 수집하는 공격 프레임워크 (ATT&amp;CK S9003)
+- [ATT&amp;CK 사례] Kali365: 피싱 미끼가 정상 로그인 서비스의 프록시로 동작할 때 세션 쿠키·세션 산출물을 수집 (ATT&amp;CK S9044)</t>
         </is>
       </c>
       <c r="G101" s="17" t="inlineStr">
@@ -15316,7 +16199,7 @@
       </c>
       <c r="M101" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N101" s="17" t="inlineStr">
@@ -15377,7 +16260,16 @@
           <t>https://attack.mitre.org/techniques/T1539</t>
         </is>
       </c>
-      <c r="AF101" s="17" t="inlineStr"/>
+      <c r="AF101" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 같은 세션 쿠키의 다른 IP·장치 재사용, 인포스틸러 감염 징후, AiTM 프록시 도메인 접속
+- MFA를 거치지 않은 세션 재개
+■ 대응
+- 피싱 저항형 MFA·세션 토큰 바인딩(장치·IP), 세션 수명 단축
+- 민감 작업 재인증, 의심 세션 즉시 폐기</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="17" t="inlineStr">
@@ -15402,13 +16294,19 @@
       </c>
       <c r="E102" s="17" t="inlineStr">
         <is>
-          <t>공격자는 침해한 시스템을 검색해 안전하지 않게 저장된 자격 증명을 찾아 확보할 수 있다. 이런 자격 증명은 평문 파일(예: 셸 기록(Shell History)), 운영체제나 애플리케이션 전용 저장소(예: 레지스트리의 자격 증명(Credentials in Registry)), 기타 특수 파일·산출물(예: 개인 키(Private Keys)) 등 시스템의 여러 위치에 저장되거나 잘못 놓여 있을 수 있다.</t>
+          <t>- 공격자는 침해 시스템·클라우드 리소스에서 안전하지 않게 저장된 자격증명(구성 파일·환경변수·배포 기록·스토리지 키)을 찾아 확보할 수 있음
+- 클라우드·컨테이너 환경은 자격증명을 로컬 구성·로그에 남기기 쉬워, 코드 실행만으로 추가 접근 수단을 얻게 됨</t>
         </is>
       </c>
       <c r="F102" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 1건)
-- Pacu(S1091) — AWS [IaaS]</t>
+          <t>■ 클라우드 관점
+- Azure: Function App 로직 조작으로 서비스 주체 비밀 노출(AZT603), 스토리지 계정 액세스 키 덤프(AZT605.1), Automation 자격증명·배포 기록의 비밀 노출(AZT605.2)
+- K8s: 파드 구성·환경변수에 저장된 비밀(MS-TA9027)
+- 하위 변형으로 파일 내 자격증명(CTC-CA-10.1), IMDS(CTC-CA-10.2), 컨테이너 API(CTC-CA-10.3), 채팅 메시지(CTC-CA-10.4)가 있음
+- 이 행은 하위기법으로 특정되지 않은 보호되지 않은 자격증명 근거를 보존
+■ 실제 사례
+- [ATT&amp;CK 사례] Pacu: CodeBuild 환경변수·EC2 UserData·CloudFormation 템플릿에서 민감 데이터 탐색 (ATT&amp;CK S1091)</t>
         </is>
       </c>
       <c r="G102" s="17" t="inlineStr">
@@ -15439,7 +16337,7 @@
       </c>
       <c r="M102" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N102" s="17" t="inlineStr">
@@ -15515,7 +16413,16 @@
           <t>https://attack.mitre.org/techniques/T1552</t>
         </is>
       </c>
-      <c r="AF102" s="17" t="inlineStr"/>
+      <c r="AF102" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 서비스 주체 비밀·스토리지 키·배포 기록 열람(listkeys·deployments/read 등), 구성·환경변수 대량 조회
+- Function App 로직 수정 후 비밀 노출
+■ 대응
+- 비밀을 전용 비밀 저장소로 이관(환경변수·구성 파일 지양), 스토리지 키 대신 임시 토큰·RBAC
+- 비밀 접근 로깅과 비밀 스캐닝(코드·배포 기록)</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="17" t="inlineStr">
@@ -15540,16 +16447,20 @@
       </c>
       <c r="E103" s="17" t="inlineStr">
         <is>
-          <t>공격자는 로컬 파일 시스템과 원격 파일 공유를 검색해 안전하지 않게 저장된 자격 증명이 담긴 파일을 찾을 수 있다. 사용자가 자기 자격 증명을 보관하려고 만든 파일, 여러 사람이 함께 쓰는 자격 증명 저장소, 시스템이나 서비스의 비밀번호가 담긴 구성 파일, 비밀번호가 하드코딩된 소스 코드·바이너리 파일 등이 여기에 해당한다.</t>
+          <t>- 공격자는 로컬·공유 파일시스템과 컨테이너·CI 환경을 뒤져 구성 파일·크리덴셜 파일·소스코드의 평문 자격증명을 수집할 수 있음
+- ~/.aws/credentials·kubeconfig·.env·배포 로그 등 정형화된 경로에 키가 남기 쉬워, 공급망 악성코드의 주요 수확 대상이 됨</t>
         </is>
       </c>
       <c r="F103" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 8건)
-- TeamTNT(G0139) — AWS, Docker [IaaS]
-- Hildegard(S0601) — Kubernetes, Docker [컨테이너·K8s]
-- Kali365(S9044) — IaaS 플랫폼 소프트웨어 [IaaS]
-- Mini Shai-Hulud(S9043) — Containers, IaaS, SaaS 플랫폼 소프트웨어 [클라우드(복합)]</t>
+          <t>■ 클라우드 관점
+- 표적 경로: ~/.aws/credentials, azureProfile.json, GCP application_default_credentials.json, kubeconfig(K8s MS-TA9003), .env, git-credentials, 배포 명령 인자·컨테이너 로그
+- Azure: 리소스 그룹 배포 기록의 ARM 템플릿 비밀 노출(AZT605.3), 컨테이너에서 마운트된 서비스 주체로 클라우드 자격증명 획득(MS-TA9026)
+- 공급망 악성코드가 50여 개 경로를 뒤져 자격증명을 대량 수집 — IMDS(CTC-CA-10.2)·비밀 저장소(CTC-CA-03.1)와 함께 수확
+■ 실제 사례
+- [ATT&amp;CK 사례] TeamPCP Cloud Stealer: CI/CD·클라우드·컨테이너 환경의 50여 개 파일 경로에서 자격증명 점검 (ATT&amp;CK S9041)
+- [ATT&amp;CK 사례] Shai-Hulud: process.env와 ~/.aws/credentials 등 구성·크리덴셜 파일의 자격증명·API 키 수집 (ATT&amp;CK S9008)
+- [ATT&amp;CK 사례] TeamTNT: 보호되지 않은 AWS 자격증명과 Docker API 자격증명 탐색 (ATT&amp;CK G0139)</t>
         </is>
       </c>
       <c r="G103" s="17" t="inlineStr">
@@ -15580,7 +16491,7 @@
       </c>
       <c r="M103" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N103" s="17" t="inlineStr">
@@ -15658,7 +16569,16 @@
           <t>https://attack.mitre.org/techniques/T1552/001</t>
         </is>
       </c>
-      <c r="AF103" s="17" t="inlineStr"/>
+      <c r="AF103" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 자격증명 파일 경로(~/.aws/credentials·kubeconfig·.env 등) 대량 접근, 짧은 시간 다수 파일 읽기
+- CI 러너·컨테이너에서의 비정상 파일 탐색
+■ 대응
+- 비밀 스캐닝(코드·이미지·CI), 하드코딩 금지와 단기 자격증명(OIDC) 전환
+- 크리덴셜 파일 최소화·권한 제한, 노출 시 즉시 교체</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="17" t="inlineStr">
@@ -15683,21 +16603,20 @@
       </c>
       <c r="E104" s="17" t="inlineStr">
         <is>
-          <t>공격자는 자격 증명과 기타 민감한 데이터를 수집하기 위해 클라우드 인스턴스 메타데이터 API에 접근하려 할 수 있다.</t>
+          <t>- 공격자는 인스턴스 메타데이터 API(169.254.169.254)에 접근해 워크로드에 연결된 역할·관리 ID 자격증명과 UserData 비밀을 탈취할 수 있음
+- SSRF 취약점으로 외부에서도 접근 가능하며, 탈취한 역할 자격증명으로 클라우드 API를 호출해 환경 전반으로 확산함</t>
         </is>
       </c>
       <c r="F104" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례(사고 DB)
-- [실제 사고] Hugging Face(2026-07, INC-0651): Hugging Face에서 자율 AI 에이전트가 HDF5 파일 읽기와 Jinja2 템플릿 인젝션을 악용했다. 공격자는 IMDS 자격증명 탈취, EKS 노드 루트 권한 획득, VPN 경유 확산을 거쳐 AWS 키와 자격증명을 침해했으며, 데이터셋 5개에 
-- [실제 사고] Shai-Hulud worm via poisoned npm/PyPI packages (TeamPCP)(2026-05, INC-0624): TeamPCP의 오염된 npm/PyPI 패키지(Shai-Hulud 웜)로 침투했다. 공격자는 IMDS에서 자격증명을 탈취하고 IAM 관리자 사용자를 만든 뒤 Redshift에 접근해 데이터를 유출했다(Fortinet 사례).
-- [실제 사고] GENESIS PANDA's Cloud Intrusions: Persistent Control Plane Exploitation and Access Brokerage(2025-08, INC-0550): GENESIS PANDA는 Jenkins 등 노출 서비스를 악용하고, 침해한 클라우드 VM의 IMDS를 조회해 자격증명을 수집했다. 이를 이용해 클라우드 컨트롤 플레인으로 확산했으며, 접근 권한 중개도 수행했다.
-- 외 4건(관련 사례 ID 열)
-■ ATT&amp;CK 사례(행위자, 총 6건)
-- TeamTNT(G0139) — AWS [IaaS]
-- Hildegard(S0601) — Containers, IaaS 플랫폼 소프트웨어 [IaaS]
-- Mini Shai-Hulud(S9043) — Azure, AWS, GCP [IaaS]
-- Shai-Hulud(S9008) — AWS, GCP [IaaS]</t>
+          <t>■ 클라우드 관점
+- AWS: EC2 인스턴스 프로파일 자격증명을 IMDS에서 획득(AWS TTC T1552.005) — IMDSv1은 SSRF에 특히 취약, IMDSv2(세션 토큰)로 완화
+- Azure: VM·AKS에서 IMDS로 관리 ID JWT 요청(Azure ATRM AZT601.1·601.2), GCP도 메타데이터 서버로 서비스 계정 토큰 제공
+- 외부 노출 웹앱의 SSRF(CTC-IA-01)로 원격에서 IMDS에 도달하는 경로가 반복 악용됨
+■ 실제 사례
+- [실제 사고] Hugging Face 자율 에이전트 악용(2026-07): 템플릿 인젝션으로 IMDS 자격증명을 탈취하고 EKS 노드 루트 권한 획득 후 AWS 키 침해 (사고DB INC-0651)
+- [실제 사고] GENESIS PANDA(2025-08): 침해한 클라우드 VM의 IMDS를 조회해 자격증명을 수집하고 제어 평면으로 확산 (사고DB INC-0550)
+- [실제 사고] SSRF via CVE·IMDSv1(2023-04): SSRF로 IMDSv1에서 자격증명을 얻어 IAM 역할 백도어 설정 후 크립토재킹·DDoS에 악용 (사고DB INC-0167)</t>
         </is>
       </c>
       <c r="G104" s="17" t="inlineStr">
@@ -15728,7 +16647,7 @@
       </c>
       <c r="M104" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N104" s="17" t="inlineStr">
@@ -15811,7 +16730,16 @@
           <t>https://attack.mitre.org/techniques/T1552/005</t>
         </is>
       </c>
-      <c r="AF104" s="17" t="inlineStr"/>
+      <c r="AF104" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 웹 프로세스에서 169.254.169.254로의 요청(SSRF 징후), IMDS 자격증명이 외부 IP에서 사용됨
+- 다수 메타데이터 엔드포인트(AWS·GCP·Azure) 연속 조회
+■ 대응
+- IMDSv2(세션 토큰) 강제·홉 제한, 워크로드 역할 최소 권한
+- SSRF 방지(출력 URL 검증·메타데이터 차단), 앱에서 메타데이터 접근 차단</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="17" t="inlineStr">
@@ -15836,12 +16764,18 @@
       </c>
       <c r="E105" s="17" t="inlineStr">
         <is>
-          <t>공격자는 컨테이너 환경의 API를 통해 자격 증명을 수집할 수 있다. Docker API, Kubernetes API 같은 이 환경의 API는 사용자가 컨테이너 리소스와 클러스터 구성 요소를 원격으로 관리할 수 있게 한다.</t>
+          <t>- 공격자는 Docker API·Kubernetes API를 통해 컨테이너 로그·클러스터 비밀에서 자격증명을 수집할 수 있음
+- 파드 서비스 어카운트 권한이 과하면 API 서버에서 클러스터 시크릿을 조회할 수 있어, 컨테이너 침해가 클러스터 자격증명 탈취로 이어짐</t>
         </is>
       </c>
       <c r="F105" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- Docker API 로그에서 클라우드·컨테이너 자격증명 수집, Kubernetes API로 시크릿 조회(list secrets, K8s MS-TA9025)
+- 과도한 서비스 어카운트 RBAC가 전제 — 파드에서 API 서버로 시크릿 요청 가능
+- 노출 Docker·Kubernetes API(CTC-IA-02)와 결합되면 외부에서도 가능
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB·ATT&amp;CK 클라우드 사례에 이 하위기법으로 매핑된 건은 없음(벤더 문서화 수준). 관련 컨테이너 자격증명 탈취는 CTC-CA-10.1 참조</t>
         </is>
       </c>
       <c r="G105" s="17" t="inlineStr">
@@ -15872,7 +16806,7 @@
       </c>
       <c r="M105" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N105" s="17" t="inlineStr">
@@ -15937,7 +16871,16 @@
           <t>https://attack.mitre.org/techniques/T1552/007</t>
         </is>
       </c>
-      <c r="AF105" s="17" t="inlineStr"/>
+      <c r="AF105" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- Kubernetes API의 secrets list·get 요청, Docker API 로그 접근
+- 파드 서비스 어카운트의 비정상 시크릿 조회
+■ 대응
+- 서비스 어카운트 RBAC 최소화(secrets 접근 제한), etcd·시크릿 암호화
+- Docker·K8s API 비공개·인증 강제</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="17" t="inlineStr">
@@ -15962,13 +16905,18 @@
       </c>
       <c r="E106" s="17" t="inlineStr">
         <is>
-          <t>공격자는 사용자 커뮤니케이션 서비스에 저장되거나 전달된 보호되지 않은 자격 증명을 직접 수집할 수 있다. 자격 증명은 이메일, Slack이나 Teams 같은 채팅 서비스, Jira나 Trello 같은 협업 도구 등 사용자 간 소통을 지원하는 서비스를 통해 전송되고 저장될 수 있다. 사용자는 사내 비공개·공개 커뮤니케이션 채널에서 사용자 이름과 비밀번호, API 키, 인증 토큰 등 여러 형태의 자격 증명을 공유할 수 있다.</t>
+          <t>- 공격자는 Slack·Teams·Jira 같은 협업 도구에 공유·저장된 자격증명(비밀번호·API 키·토큰)을 직접 수집할 수 있음
+- 사용자가 채널·이슈에 비밀을 공유하는 관행을 노리며, Slack 워크플로 같은 통합을 악용해 메시지를 자동 검색하기도 함</t>
         </is>
       </c>
       <c r="F106" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 1건)
-- LAPSUS$(G1004) — Slack [SaaS·협업]</t>
+          <t>■ 클라우드 관점
+- Slack·Teams·Jira·Confluence 등 SaaS 협업 채널의 평문 자격증명이 표적 — 저장 로그 파일 접근(CTC-CA-10.1)과 달리 서비스 내에서 직접 수집
+- 통합 도구(Slack 워크플로)를 악용해 메시지에서 자격증명 자동 추출
+- 수집한 자격증명은 권한 상승·횡적 이동의 발판이 됨
+■ 실제 사례
+- [ATT&amp;CK 사례] LAPSUS$: Slack·Teams·Jira·Confluence 등 협업 도구에서 노출 자격증명을 찾아 권한 상승·횡적 이동에 활용 (ATT&amp;CK G1004)</t>
         </is>
       </c>
       <c r="G106" s="17" t="inlineStr">
@@ -15999,7 +16947,7 @@
       </c>
       <c r="M106" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N106" s="17" t="inlineStr">
@@ -16060,7 +17008,16 @@
           <t>https://attack.mitre.org/techniques/T1552/008</t>
         </is>
       </c>
-      <c r="AF106" s="17" t="inlineStr"/>
+      <c r="AF106" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 협업 도구 메시지의 대량 검색, 통합 워크플로의 비정상 메시지 접근
+- 채널에 공유된 비밀 패턴(키·토큰)
+■ 대응
+- 협업 도구 DLP·비밀 탐지, 채널 내 비밀 공유 금지 정책
+- 통합 앱 권한 최소화와 공유 비밀 즉시 교체</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="17" t="inlineStr">
@@ -16085,16 +17042,20 @@
       </c>
       <c r="E107" s="17" t="inlineStr">
         <is>
-          <t>공격자는 이메일 주소와 계정 목록을 확보하려 할 수 있다. 공격자는 전역 주소 목록(GAL) 같은 Exchange 주소 목록을 덤프하려 할 수 있다.</t>
+          <t>- 공격자는 인증된 세션으로 Exchange·Google Workspace 전역 주소 목록(GAL)·디렉터리를 덤프해 이메일 주소·계정 목록을 수집할 수 있음
+- 수집한 목록은 내부 피싱·BEC·계정 탈취의 표적 선정에 쓰이며, 정상 조회처럼 보여 탐지가 어려움</t>
         </is>
       </c>
       <c r="F107" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 4건)
-- C0027(C0027) — Entra ID [ID·인증]
-- Kali365(S9044) — IaaS 플랫폼 소프트웨어 [IaaS]
-- MailSniper(S0413) — Microsoft 365 [SaaS·협업]
-- Ruler(S0358) — Office Suite 플랫폼 소프트웨어 [SaaS·협업]</t>
+          <t>■ 클라우드 관점
+- Exchange Online: Get-GlobalAddressList로 GAL 덤프, Graph·Exchange 관리 모듈로 사서함 열거
+- Google Workspace: 디렉터리로 조직 내 사용자 목록 조회
+- 내부 스피어피싱(CTC-LM-02)·사칭(CTC-ST-04.1)의 선행 정찰 — 열람 위주라 직접 피해는 낮음
+■ 실제 사례
+- [ATT&amp;CK 사례] MailSniper: Get-GlobalAddressList로 Exchange·O365 계정명 수집 (ATT&amp;CK S0413)
+- [ATT&amp;CK 사례] Kali365: Graph 기반 Exchange 관리 모듈로 피해 환경 사서함 열거 (ATT&amp;CK S9044)
+- [ATT&amp;CK 사례] C0027: Scattered Spider가 Entra ID에 접근해 이메일 주소 식별 (ATT&amp;CK C0027)</t>
         </is>
       </c>
       <c r="G107" s="17" t="inlineStr">
@@ -16125,7 +17086,7 @@
       </c>
       <c r="M107" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N107" s="17" t="inlineStr">
@@ -16186,7 +17147,16 @@
           <t>https://attack.mitre.org/techniques/T1087/003</t>
         </is>
       </c>
-      <c r="AF107" s="17" t="inlineStr"/>
+      <c r="AF107" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- GAL 덤프(Get-GlobalAddressList), Graph·관리 모듈의 대량 사서함 열거
+- 디렉터리 사용자 대량 조회
+■ 대응
+- 주소 목록·디렉터리 조회 권한 최소화, 대량 열거 알림
+- 외부·비관리 앱의 디렉터리 접근 제한</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="17" t="inlineStr">
@@ -16211,18 +17181,20 @@
       </c>
       <c r="E108" s="17" t="inlineStr">
         <is>
-          <t>공격자는 클라우드 계정 목록을 확보하려 할 수 있다. 클라우드 계정은 조직이 클라우드 서비스 제공자나 SaaS 애플리케이션 안에서 사용자, 원격 지원, 서비스 또는 리소스 관리 용도로 만들고 구성한 계정이다.</t>
+          <t>- 공격자는 인증된 접근으로 IAM 사용자·역할·서비스 계정·디렉터리 사용자 목록을 열거해 환경의 계정 구조를 파악할 수 있음
+- 고권한 계정·서비스 계정을 식별해 후속 무차별 대입·스피어피싱·계정 탈취의 표적을 좁힘</t>
         </is>
       </c>
       <c r="F108" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 7건)
-- APT29(G0016) — Entra ID [ID·인증]
-- Storm-0501(G1053) — Azure [IaaS]
-- C0027(C0027) — Entra ID [ID·인증]
-- Mini Shai-Hulud(S9043) — Containers, IaaS, SaaS 플랫폼 소프트웨어 [클라우드(복합)]
-■ 통합된 기법
-- T1087 Account Discovery</t>
+          <t>■ 클라우드 관점
+- AWS: iam:ListUsers·ListRoles·GetUser(AWS TTC T1087.004), GCP: gcloud iam service-accounts list·projects get-iam-policy
+- Entra ID: az ad user list, Get-MsolRoleMember, AzureHound·ROADTools로 사용자·역할·리소스 열거(Azure ATRM AZT104·AZT105)
+- 통합된 상위기법(T1087) 근거 포함 — 열람 위주라 직접 피해는 낮으나 권한 상승 경로 설계에 기여
+■ 실제 사례
+- [ATT&amp;CK 사례] Storm-0501: AzureHound로 피해 Azure 테넌트의 사용자·역할·리소스 열거 (ATT&amp;CK G1053)
+- [ATT&amp;CK 사례] C0027: Scattered Spider가 Entra ID에서 그룹 구성원 목록을 대량 내려받고 특권 사용자 식별 (ATT&amp;CK C0027)
+- [ATT&amp;CK 사례] Pacu: IAM 사용자·역할·그룹 열거 (ATT&amp;CK S1091)</t>
         </is>
       </c>
       <c r="G108" s="17" t="inlineStr">
@@ -16257,7 +17229,7 @@
       </c>
       <c r="M108" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N108" s="17" t="inlineStr">
@@ -16328,7 +17300,16 @@
           <t>https://attack.mitre.org/techniques/T1087/004</t>
         </is>
       </c>
-      <c r="AF108" s="17" t="inlineStr"/>
+      <c r="AF108" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- IAM·디렉터리 대량 열거(ListUsers·ListRoles·az ad user list), AzureHound·ROADTools 사용 패턴
+- 짧은 시간 다수 사용자·역할 조회
+■ 대응
+- 열거 권한 최소화, 대량 디렉터리·IAM 조회 알림
+- 특권 계정 가시성 제한과 이상 조회 모니터링</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="17" t="inlineStr">
@@ -16353,21 +17334,20 @@
       </c>
       <c r="E109" s="17" t="inlineStr">
         <is>
-          <t>공격자는 IaaS(Infrastructure-as-a-Service) 환경에서 사용 가능한 인프라와 리소스를 파악하려 할 수 있다. 여기에는 인스턴스, 가상 머신, 스냅샷 같은 컴퓨팅 서비스 리소스와 스토리지·데이터베이스 서비스 등 다른 서비스의 리소스가 포함된다.</t>
+          <t>- 공격자는 클라우드 API·CLI로 인스턴스·스토리지·DB·네트워크 등 IaaS 리소스를 열거해 환경 구성과 공격 대상 가치를 파악할 수 있음
+- 탈취한 액세스 키로 접근 가능한 리소스를 식별하고, 버킷·DB의 권한·공개 여부를 확인해 다음 단계(지속성·데이터 접근)를 설계함</t>
         </is>
       </c>
       <c r="F109" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 17건)
-- Scattered Spider(G1015) — AWS [IaaS]
-- ShinyHunters(G1057) — AWS [IaaS]
-- TeamPCP Cloud Stealer(S9041) — GitHub·GitLab [SaaS·협업]
-- Pacu(S1091) — AWS [IaaS]
-■ 통합된 기법
-- T1046 Network Service Discovery
-- T1082 System Information Discovery
-- T1614 System Location Discovery
-- T1049 System Network Connections Discovery</t>
+          <t>■ 클라우드 관점
+- AWS: DescribeInstances·ListBuckets·HeadBucket·GetPublicAccessBlock·DescribeDBInstances(AWS TTC AT1023), GCP: gcloud compute instances list, Azure: az vm list·NSG·IP 조회(Azure ATRM AZT101·AZT102·AZT107)
+- 통합된 상위기법: 네트워크 서비스 스캔(T1046), 시스템·위치·네트워크 연결 탐색(T1082·T1614·T1049)을 클라우드 인프라 탐색으로 흡수
+- 워드리스트 스캔으로 스토리지 탐색, 컨테이너 환경은 클러스터 네트워크 매핑(MS-TA9031)
+■ 실제 사례
+- [ATT&amp;CK 사례] Scattered Spider: AWS S3 버킷 등 클라우드 환경을 열거해 백업·DB·스토리지 인프라 식별 (ATT&amp;CK G1015)
+- [ATT&amp;CK 사례] TeamTNT: masscan으로 열린 Docker API 포트·K8s 클러스터 탐색 (ATT&amp;CK G0139)
+- [ATT&amp;CK 사례] Storm-0501: 침해 클라우드 환경을 열거해 핵심 자산·데이터 저장소·백업 리소스 식별 (ATT&amp;CK G1053)</t>
         </is>
       </c>
       <c r="G109" s="17" t="inlineStr">
@@ -16402,7 +17382,7 @@
       </c>
       <c r="M109" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N109" s="17" t="inlineStr">
@@ -16479,7 +17459,16 @@
           <t>https://attack.mitre.org/techniques/T1580</t>
         </is>
       </c>
-      <c r="AF109" s="17" t="inlineStr"/>
+      <c r="AF109" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 대량 Describe·List 호출(DescribeInstances·ListBuckets 등), 워드리스트 기반 스토리지 스캔
+- 탈취 키의 광범위 리소스 열거, 컨테이너 환경 포트·네트워크 스캔
+■ 대응
+- 최소 권한·열거 API 제한, 대량 탐색 호출 알림
+- 스토리지 공개 차단(퍼블릭 액세스 블록)과 리소스 접근 모니터링</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="17" t="inlineStr">
@@ -16504,13 +17493,18 @@
       </c>
       <c r="E110" s="17" t="inlineStr">
         <is>
-          <t>공격자는 탈취한 자격 증명으로 클라우드 서비스 대시보드 GUI를 사용해 운영 중인 클라우드 환경에서 특정 서비스, 리소스, 기능 같은 유용한 정보를 얻을 수 있다. 예를 들어 GCP Command Center로 모든 자산을 보고, 잠재적 보안 위험에 대한 발견 사항을 검토하고, 공인 IP 주소와 열린 포트 찾기 같은 추가 쿼리를 실행할 수 있다.</t>
+          <t>- 공격자는 탈취한 자격증명으로 클라우드 관리 콘솔 GUI에 로그인해 서비스·리소스·보안 발견 사항을 한눈에 파악할 수 있음
+- 콘솔은 API 요청 없이도 많은 정보를 보여 줘, 수동 API 호출 흔적을 남기지 않고 환경을 정찰함</t>
         </is>
       </c>
       <c r="F110" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 1건)
-- Scattered Spider(G1015) — AWS [IaaS]</t>
+          <t>■ 클라우드 관점
+- AWS Management Console(signin:ConsoleLogin·SwitchRole), GCP Security Command Center, Azure Portal로 자산·보안 위험·공인 IP·열린 포트 등을 GUI로 열람
+- 콘솔 열람은 개별 API 호출보다 로그가 적게 남아 탐지가 어려움 — 콘솔 로그인 이벤트가 핵심 단서
+- SSM Inventory 등 관리 기능을 정찰에 전용하기도 함
+■ 실제 사례
+- [ATT&amp;CK 사례] Scattered Spider: 횡적 이동 전 AWS Systems Manager Inventory를 악용해 대상 식별 (ATT&amp;CK G1015)</t>
         </is>
       </c>
       <c r="G110" s="17" t="inlineStr">
@@ -16541,7 +17535,7 @@
       </c>
       <c r="M110" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N110" s="17" t="inlineStr">
@@ -16606,7 +17600,15 @@
           <t>https://attack.mitre.org/techniques/T1538</t>
         </is>
       </c>
-      <c r="AF110" s="17" t="inlineStr"/>
+      <c r="AF110" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 콘솔 로그인(ConsoleLogin)의 비정상 위치·시간, 역할 전환(SwitchRole), 보안 콘솔 대량 열람
+■ 대응
+- 콘솔 접근에 피싱 저항형 MFA·조건부 액세스, 콘솔 로그인 알림
+- 관리 콘솔 접근 출발지 제한</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="17" t="inlineStr">
@@ -16631,19 +17633,21 @@
       </c>
       <c r="E111" s="17" t="inlineStr">
         <is>
-          <t>공격자는 접근을 확보한 뒤 시스템에서 실행 중인 클라우드 서비스를 열거하려 할 수 있다. 방법은 PaaS, IaaS, SaaS에 따라 다를 수 있다. 클라우드 제공자마다 다양한 서비스가 있으며, CI/CD(지속적 통합·지속적 전달), Lambda 함수, Entra ID 등이 포함될 수 있다. AWS GuardDuty나 Microsoft Defender for Cloud 같은 보안 서비스와 AWS CloudTrail, Google Cloud Audit Logs 같은 로깅 서비스도 포함될 수 있다.</t>
+          <t>- 공격자는 Graph·Resource Manager API나 열거 도구(Pacu·Stormspotter·ROADTools)로 환경에 활성화된 클라우드 서비스·앱·정책·보안 도구를 파악할 수 있음
+- 어떤 서비스·방어가 있는지 알아내 데이터·자격증명 표적과 방어 무력화 대상을 정하는 선행 정찰 단계임</t>
         </is>
       </c>
       <c r="F111" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 9건)
-- Storm-0501(G1053) — Azure [IaaS]
-- TeamPCP Cloud Stealer(S9041) — GitHub·GitLab [SaaS·협업]
-- AADInternals(S0677) — Entra ID, Microsoft 365, SharePoint [SaaS·협업]
-- Pacu(S1091) — AWS [IaaS]
-■ 통합된 기법
-- T1518 Software Discovery
-- T1518.001 Security Software Discovery</t>
+          <t>■ 클라우드 관점
+- Azure: Microsoft Graph·ARM API로 앱·관리 그룹·리소스·정책 관계 열거(Stormspotter·ROADTools)
+- AWS: Pacu로 CloudTrail·CloudWatch 등 서비스 열거
+- 식별 결과로 보안 서비스·로깅(CTC-DS 전반)을 파악해 방어 무력화(CTC-DI-02)·데이터 표적화로 연결
+- 통합된 상위기법(소프트웨어 탐색 T1518, 보안 소프트웨어 탐색 T1518.001) 근거 포함 — 열람 위주라 직접 피해는 낮음
+■ 실제 사례
+- [ATT&amp;CK 사례] Storm-0501: Azure 정책·리소스 잠금·스토리지 불변성 정책 등 피해 환경의 방어 수단을 식별 (ATT&amp;CK G1053)
+- [ATT&amp;CK 사례] AADInternals: O365·SharePoint·OpenID 구성 등 다양한 클라우드 서비스 정보 열거 (ATT&amp;CK S0677)
+- [ATT&amp;CK 사례] ROADTools: Entra ID 애플리케이션·서비스 주체 열거 (ATT&amp;CK S0684)</t>
         </is>
       </c>
       <c r="G111" s="17" t="inlineStr">
@@ -16678,7 +17682,7 @@
       </c>
       <c r="M111" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N111" s="17" t="inlineStr">
@@ -16739,7 +17743,16 @@
           <t>https://attack.mitre.org/techniques/T1526</t>
         </is>
       </c>
-      <c r="AF111" s="17" t="inlineStr"/>
+      <c r="AF111" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- Graph·ARM 대량 열거, Pacu·ROADTools·Stormspotter 사용 패턴, 서비스·정책 연속 조회
+- 보안 서비스·로깅 구성 조회 직후의 방어 무력화 시도
+■ 대응
+- 열거 권한 최소화, 대량 서비스·정책 조회 알림
+- 정찰 직후 이어지는 로깅·방어 변경을 연계 탐지</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="17" t="inlineStr">
@@ -16764,16 +17777,20 @@
       </c>
       <c r="E112" s="17" t="inlineStr">
         <is>
-          <t>공격자는 클라우드 스토리지 인프라의 객체를 열거할 수 있다. 자동화된 탐색 과정에서 이 정보를 바탕으로 클라우드 스토리지의 전체 또는 특정 객체를 요청하는 등 후속 행동을 정할 수 있다. 로컬 호스트의 파일 및 디렉터리 탐색(File and Directory Discovery)처럼, 사용 가능한 스토리지 서비스를 파악한 뒤(즉, 클라우드 인프라 탐색(Cloud Infrastructure Discovery)) 클라우드 인프라에 저장된 콘텐츠·객체에 접근할 수 있다.</t>
+          <t>- 공격자는 클라우드 스토리지 객체 열거 API(S3 ListObjects, Azure List Blobs)로 버킷·객체 목록을 파악할 수 있음
+- 어떤 데이터가 어디에 있는지 식별해 유출 대상을 좁히며, 공개 설정된 스토리지를 찾는 선행 정찰로 쓰임</t>
         </is>
       </c>
       <c r="F112" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 4건)
-- ShinyHunters(G1057) — AWS [IaaS]
-- Pacu(S1091) — AWS [IaaS]
-- Peirates(S0683) — AWS [IaaS]
-- TruffleHog(S9009) — AWS, GCP [IaaS]</t>
+          <t>■ 클라우드 관점
+- AWS: s3:ListBuckets·ListObjects로 버킷·객체 열거(AWS TTC T1619.A001), Azure List Blobs, GCP 버킷 열거
+- 인프라 탐색(CTC-DS-02)으로 스토리지 서비스를 파악한 뒤 객체 수준으로 내려가 유출(CTC-CO-03) 대상 선정
+- 열람 위주라 직접 피해는 낮으나, 공개 버킷 발견 시 비인증 데이터 노출로 직결
+■ 실제 사례
+- [ATT&amp;CK 사례] ShinyHunters: S3 Browser·WinSCP로 S3 객체에 접근 (ATT&amp;CK G1057)
+- [ATT&amp;CK 사례] Pacu: S3 버킷·EBS 볼륨 등 AWS 스토리지 서비스 열거 (ATT&amp;CK S1091)
+- [ATT&amp;CK 사례] TruffleHog: AWS S3·GCS 버킷 등 클라우드 스토리지 환경 열거 (ATT&amp;CK S9009)</t>
         </is>
       </c>
       <c r="G112" s="17" t="inlineStr">
@@ -16804,7 +17821,7 @@
       </c>
       <c r="M112" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N112" s="17" t="inlineStr">
@@ -16870,7 +17887,16 @@
           <t>https://attack.mitre.org/techniques/T1619</t>
         </is>
       </c>
-      <c r="AF112" s="17" t="inlineStr"/>
+      <c r="AF112" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- ListBuckets·ListObjects·List Blobs 대량 호출, 공개 설정 버킷 탐색 패턴
+- 탈취 키의 광범위 객체 열거
+■ 대응
+- 스토리지 열거 권한 최소화, 퍼블릭 액세스 블록·버킷 정책으로 공개 차단
+- 대량 객체 열거 알림과 접근 로깅</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="17" t="inlineStr">
@@ -16895,12 +17921,18 @@
       </c>
       <c r="E113" s="17" t="inlineStr">
         <is>
-          <t>공격자는 컨테이너 환경에서 사용 가능한 컨테이너와 기타 리소스를 파악하려 할 수 있다. 기타 리소스에는 이미지, 배포, 파드, 노드와 클러스터 상태 같은 정보가 포함될 수 있다.</t>
+          <t>- 공격자는 Kubernetes 대시보드·Docker/Kubernetes API로 컨테이너·이미지·파드·노드·클러스터 상태를 열거할 수 있음
+- Docker 로그가 환경 구성·클라우드 제공자 정보를 흘려, 횡적 이동과 실행 방법을 설계하는 단서가 됨</t>
         </is>
       </c>
       <c r="F113" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- Kubernetes API 서버(MS-TA9029)·kubelet API(MS-TA9030)·Docker API로 리소스 열거, Kubernetes 대시보드 UI로 조회
+- Docker 로그에서 환경 구성·가용 서비스·클라우드 제공자 정보 유출
+- 노출 API(CTC-IA-02)와 결합되면 외부에서도 가능 — 열람 위주라 직접 피해는 낮음
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB·ATT&amp;CK 클라우드 사례에 매핑된 건은 없음(벤더 문서화 수준)</t>
         </is>
       </c>
       <c r="G113" s="17" t="inlineStr">
@@ -16931,7 +17963,7 @@
       </c>
       <c r="M113" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N113" s="17" t="inlineStr"/>
@@ -16993,7 +18025,16 @@
           <t>https://attack.mitre.org/techniques/T1613</t>
         </is>
       </c>
-      <c r="AF113" s="17" t="inlineStr"/>
+      <c r="AF113" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- Kubernetes API·kubelet·Docker API의 리소스 열거 요청, 대시보드 접근
+- Docker 로그 조회를 통한 환경 정보 수집
+■ 대응
+- API 서버·kubelet 인증 강제·비공개, RBAC로 조회 권한 제한
+- 대시보드 비공개와 로그 접근 통제</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="17" t="inlineStr">
@@ -17018,13 +18059,18 @@
       </c>
       <c r="E114" s="17" t="inlineStr">
         <is>
-          <t>공격자는 유용한 데이터를 찾기 위해 시스템 및 서비스 로그를 열거할 수 있다. 이러한 로그에서 사용자 인증 기록(계정 탐색(Account Discovery)), 보안 소프트웨어나 취약한 소프트웨어(소프트웨어 탐색(Software Discovery)), 침해한 네트워크 안의 호스트(원격 시스템 탐색(Remote System Discovery)) 등 공격자에게 가치 있는 다양한 정보를 얻을 수 있다.</t>
+          <t>- 공격자는 시스템·서비스 로그를 열거해 인증 기록·보안 소프트웨어·네트워크 호스트 등 가치 있는 정보를 수집할 수 있음
+- 클라우드 로그·SIEM을 표적으로 하며, 사고 대응 로그를 실시간 관찰해 자신의 기법을 조정하기도 함</t>
         </is>
       </c>
       <c r="F114" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 1건)
-- Pacu(S1091) — AWS [IaaS]</t>
+          <t>■ 클라우드 관점
+- 클라우드 호스트 로그 수집(Azure VM Agent CollectGuestLogs 등), CloudTrail·CloudWatch 로그 조회, SIEM 등 중앙 로깅 표적
+- 로그를 대량 내보내 오프라인 분석하거나 실시간 관찰로 사고 대응 절차 추적 → 방어 무력화(CTC-DI-02)와 연계
+- 열람 위주라 직접 피해는 낮으나, 로그 접근 권한 과다가 전제
+■ 실제 사례
+- [ATT&amp;CK 사례] Pacu: CloudTrail 이벤트 기록과 CloudWatch 로그 수집 (ATT&amp;CK S1091)</t>
         </is>
       </c>
       <c r="G114" s="17" t="inlineStr">
@@ -17055,7 +18101,7 @@
       </c>
       <c r="M114" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N114" s="17" t="inlineStr"/>
@@ -17112,7 +18158,16 @@
           <t>https://attack.mitre.org/techniques/T1654</t>
         </is>
       </c>
-      <c r="AF114" s="17" t="inlineStr"/>
+      <c r="AF114" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 로그 대량 조회·내보내기(CloudTrail·CloudWatch), 호스트 로그 수집 유틸리티 실행
+- SIEM·중앙 로깅에 대한 비정상 접근
+■ 대응
+- 로그 조회·내보내기 권한 최소화, 대량 로그 접근 알림
+- 로그를 별도 계정에 불변 저장해 관찰·변조 제한</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="17" t="inlineStr">
@@ -17137,18 +18192,20 @@
       </c>
       <c r="E115" s="17" t="inlineStr">
         <is>
-          <t>공격자는 클라우드 그룹과 권한 설정을 찾으려 할 수 있다. 클라우드 권한 그룹 정보는 환경 안에서 사용자와 그룹이 맡은 역할, 그리고 특정 그룹에 어떤 사용자가 연결되어 있는지 파악하는 데 도움이 된다.</t>
+          <t>- 공격자는 클라우드 그룹·역할·정책·ACL을 열거해 어떤 계정이 어떤 권한을 가지는지 파악할 수 있음
+- 고권한 그룹·객체 접근 권한을 식별해 권한 상승·데이터 접근의 표적 계정을 정하는 선행 정찰 단계임</t>
         </is>
       </c>
       <c r="F115" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 6건)
-- Siloscape(S0623) — Kubernetes [컨테이너·K8s]
-- ShinyHunters(G1057) — AWS [IaaS]
-- C0027(C0027) — Entra ID [ID·인증]
-- AADInternals(S0677) — Entra ID [ID·인증]
-■ 통합된 기법
-- T1069 Permission Groups Discovery</t>
+          <t>■ 클라우드 관점
+- AWS: ListRolePolicies·ListAttachedRolePolicies로 역할 정책 열거, GetBucketAcl로 객체 ACL 확인
+- Entra ID: az ad user get-member-groups, Get-MsolRole, 역할 할당 수집(Azure ATRM AZT106 계열), GCP: Cloud Identity groups API
+- 통합된 상위기법(T1069) 근거 포함 — 열람 위주라 직접 피해는 낮으나 권한 상승 경로 설계에 기여
+■ 실제 사례
+- [ATT&amp;CK 사례] ShinyHunters: 침해 AWS 계정의 권한을 열거하는 API 호출 수행 (ATT&amp;CK G1057)
+- [ATT&amp;CK 사례] C0027: Scattered Spider가 Entra ID에서 그룹 구성원과 AD 속성을 대량 내려받음 (ATT&amp;CK C0027)
+- [ATT&amp;CK 사례] ROADTools: Entra ID 그룹 열거 (ATT&amp;CK S0684)</t>
         </is>
       </c>
       <c r="G115" s="17" t="inlineStr">
@@ -17183,7 +18240,7 @@
       </c>
       <c r="M115" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N115" s="17" t="inlineStr">
@@ -17251,7 +18308,16 @@
           <t>https://attack.mitre.org/techniques/T1069/003</t>
         </is>
       </c>
-      <c r="AF115" s="17" t="inlineStr"/>
+      <c r="AF115" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 역할·그룹·정책·ACL 대량 열거(ListRolePolicies·GetBucketAcl·az ad ... 등)
+- 권한 매핑 도구(ROADTools·AADInternals) 사용 패턴
+■ 대응
+- 권한·그룹 열거 권한 최소화, 대량 조회 알림
+- 특권 그룹 가시성 제한과 정기 권한 검토</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="17" t="inlineStr">
@@ -17276,12 +18342,18 @@
       </c>
       <c r="E116" s="17" t="inlineStr">
         <is>
-          <t>공격자는 네트워크 내부에 들어온 뒤 원격 서비스를 익스플로잇해 내부 시스템에 무단으로 접근할 수 있다. 소프트웨어 취약점 익스플로잇은 공격자가 프로그램, 서비스, 운영체제 소프트웨어나 커널의 프로그래밍 오류를 이용해 자신이 제어하는 코드를 실행하는 것이다. 침해 이후 원격 서비스를 익스플로잇하는 흔한 목적은 원격 시스템에 접근하기 위한 측면 이동이다.</t>
+          <t>- 공격자는 내부망 진입 후 취약한 원격 서비스(SMB·RDP·DB, vCenter·ESXi 등)를 익스플로잇해 다른 시스템으로 횡적 이동할 수 있음
+- 취약 서비스 권한에 따라 권한 상승도 가능하며, vCenter 침해는 VM·하이퍼바이저로의 이동 발판이 됨</t>
         </is>
       </c>
       <c r="F116" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- 하이브리드 환경에서 클라우드-온프레미스 연결을 통해 내부 취약 서비스로 이동, vCenter 취약점으로 VM·ESXi 하이퍼바이저 장악
+- K8s: 기본 허용된 클러스터 내부 파드 간 네트워크(MS-TA9034)를 통해 서비스 익스플로잇 확산
+- 네트워크 서비스 탐색(CTC-DS-02)으로 취약 대상 식별 후 수행 (CSA TT2026 SI-11)
+■ 실제 사례
+- 공개 사고 미확인 — 이 기법으로 직접 매핑된 사고는 없음(원격 서비스 익스플로잇 초기 침투는 CTC-IA-01에 집계)</t>
         </is>
       </c>
       <c r="G116" s="17" t="inlineStr">
@@ -17312,7 +18384,7 @@
       </c>
       <c r="M116" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N116" s="17" t="inlineStr">
@@ -17377,7 +18449,16 @@
           <t>https://attack.mitre.org/techniques/T1210</t>
         </is>
       </c>
-      <c r="AF116" s="17" t="inlineStr"/>
+      <c r="AF116" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 내부 서비스(SMB·RDP·DB·vCenter)에 대한 익스플로잇 트래픽, 패치 미적용 서비스로의 비정상 접근
+- 클러스터 내부 파드 간 익스플로잇 시도
+■ 대응
+- 내부 긴급 패치·세분화(마이크로세그멘테이션), vCenter·ESXi 접근 제한
+- K8s 네트워크 정책으로 파드 간 트래픽 제한</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="17" t="inlineStr">
@@ -17402,12 +18483,18 @@
       </c>
       <c r="E117" s="17" t="inlineStr">
         <is>
-          <t>공격자는 환경 안의 계정이나 시스템에 이미 접근한 뒤, 내부 스피어피싱으로 추가 정보에 접근하거나 같은 조직의 다른 사용자를 침해할 수 있다. 내부 스피어피싱은 다단계 캠페인으로, 먼저 사용자의 장치를 장악하거나 사용자의 계정 자격 증명을 침해해 정상 계정을 확보한다. 이후 신뢰받는 내부 계정을 이용해 더 많은 피해자가 피싱에 속을 가능성을 높이며, 사칭(Impersonation)을 함께 쓰는 경우가 많다.</t>
+          <t>- 공격자는 침해한 내부 계정으로 동료에게 스피어피싱을 보내 추가 정보·계정을 확보할 수 있음
+- 신뢰받는 내부 발신자라 수신자가 쉽게 속으며, Teams 같은 내부 협업 채널로도 악성 콘텐츠를 퍼뜨림</t>
         </is>
       </c>
       <c r="F117" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- 침해한 M365·Workspace 계정으로 내부 메일 발송 — 내부 발신이라 스팸·피싱 필터를 쉽게 통과
+- Microsoft Teams 등 내부 채팅으로 악성 링크·콘텐츠 전파, 사칭(CTC-ST-04.1)·사서함 위임(CTC-PE-01.2)과 결합
+- 이메일 숨김 규칙(CTC-ST-01.1)으로 회신을 가려 탐지를 지연
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB·ATT&amp;CK 클라우드 사례에 매핑된 건은 없음(기법 문서화 수준). 관련 계정 탈취 후 확산 사례는 CTC-IA-06.2 참조</t>
         </is>
       </c>
       <c r="G117" s="17" t="inlineStr">
@@ -17438,7 +18525,7 @@
       </c>
       <c r="M117" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N117" s="17" t="inlineStr"/>
@@ -17495,7 +18582,16 @@
           <t>https://attack.mitre.org/techniques/T1534</t>
         </is>
       </c>
-      <c r="AF117" s="17" t="inlineStr"/>
+      <c r="AF117" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 내부 계정의 비정상 대량 발송, 내부 메일·Teams의 악성 링크 유포
+- 침해 계정의 평소와 다른 수신자·시간대 발송
+■ 대응
+- 내부 피싱 탐지(링크·첨부 검사), 침해 의심 계정 격리
+- Teams 외부·게스트 제한과 사용자 신고 체계</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="17" t="inlineStr">
@@ -17520,16 +18616,20 @@
       </c>
       <c r="E118" s="17" t="inlineStr">
         <is>
-          <t>공격자는 온프레미스 사용자 ID와 동기화되거나 페더레이션된 유효한 계정(Valid Accounts)으로 침해한 환경에서 접근 가능한 클라우드 서비스에 로그인할 수 있다. 이후 공격자는 로그인한 사용자로서 관리 작업을 수행하거나 클라우드에 호스팅된 리소스에 접근할 수 있다.</t>
+          <t>- 공격자는 동기화·페더레이션된 유효 계정으로 클라우드 서비스에 로그인해 관리 작업·리소스 접근으로 횡적 이동할 수 있음
+- 도메인 자격증명이나 앱 토큰으로 콘솔·CLI에 접속하며, 온프레미스-클라우드를 오가는 이동 경로가 됨</t>
         </is>
       </c>
       <c r="F118" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 5건)
-- APT29(G0016) — Entra ID, Microsoft 365 [ID·인증]
-- Scattered Spider(G1015) — AWS [IaaS]
-- Storm-0501(G1053) — Entra ID [ID·인증]
-- C0027(C0027) — Azure [IaaS]</t>
+          <t>■ 클라우드 관점
+- 콘솔·CLI 로그인: Connect-AzAccount, Connect-MgGraph, gcloud auth login — 비밀번호 대신 앱 토큰(CTC-CA-07)으로도 인증
+- 온프레미스 동기화 계정(Entra Connect)을 발판으로 온프레미스↔클라우드 양방향 이동
+- 유효 계정 악용(CTC-IA-06.2)의 횡적 이동 측면 — 기존 EC2 인스턴스·SSM도 이동에 활용
+■ 실제 사례
+- [ATT&amp;CK 사례] APT29: O365에 동기화된 고권한 온프레미스 계정으로 Azure AD PowerShell을 통해 클라우드로 횡적 이동 (ATT&amp;CK G0016)
+- [ATT&amp;CK 사례] Storm-0501: 침해한 Entra Connect Sync 서버로 피해 환경 내 횡적 이동 (ATT&amp;CK G1053)
+- [ATT&amp;CK 사례] Mini Shai-Hulud: SSM Send-Command로 AWS EC2 인스턴스에 접근·전파 (ATT&amp;CK S9043)</t>
         </is>
       </c>
       <c r="G118" s="17" t="inlineStr">
@@ -17560,7 +18660,7 @@
       </c>
       <c r="M118" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N118" s="17" t="inlineStr">
@@ -17621,7 +18721,16 @@
           <t>https://attack.mitre.org/techniques/T1021/007</t>
         </is>
       </c>
-      <c r="AF118" s="17" t="inlineStr"/>
+      <c r="AF118" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 동기화·페더레이션 계정의 비정상 콘솔·CLI 로그인, 온프레미스↔클라우드 교차 인증
+- 앱 토큰 기반 로그인의 비정상 출발지
+■ 대응
+- 조건부 액세스·피싱 저항형 MFA, 동기화 서버(Entra Connect) Tier0 보호
+- 고권한 동기화 계정 최소화와 이상 로그인 알림</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="17" t="inlineStr">
@@ -17646,12 +18755,18 @@
       </c>
       <c r="E119" s="17" t="inlineStr">
         <is>
-          <t>공격자는 유효한 계정(Valid Accounts)을 이용해 클라우드 네이티브 방식으로 접근 가능한 클라우드 호스팅 컴퓨팅 인프라에 직접 로그인할 수 있다. 많은 클라우드 제공자는 Azure Serial Console, AWS EC2 Instance Connect, AWS System Manager처럼 Cloud API로 접근할 수 있는 가상 인프라 대화형 연결 기능을 제공한다.</t>
+          <t>- 공격자는 유효 계정으로 클라우드 네이티브 대화형 연결(Azure Serial Console, EC2 Instance Connect, SSM)에 직접 로그인해 VM에 접근할 수 있음
+- 이들 연결은 기본적으로 SYSTEM·root 수준 콘솔 접근을 주는 경우가 있어, 환경을 가로질러 피벗하는 데 쓰임</t>
         </is>
       </c>
       <c r="F119" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- 연결 수단: Azure Serial Console(AZT301.7), AWS EC2 Instance Connect·Systems Manager, 인증은 비밀번호·앱 토큰·SSH 키
+- 스크립트 실행(CTC-EX-01)과 달리 VM에 직접 콘솔 접근을 제공 — 기본 설정에서 고권한 접근이 가능
+- 제어 평면 권한으로 데이터 평면 VM에 진입하는 횡적 이동 경로
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB·ATT&amp;CK 클라우드 사례에 매핑된 건은 없음(벤더 문서화 수준). VM 원격 명령 실행 사례는 CTC-EX-01 참조</t>
         </is>
       </c>
       <c r="G119" s="17" t="inlineStr">
@@ -17682,7 +18797,7 @@
       </c>
       <c r="M119" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N119" s="17" t="inlineStr">
@@ -17747,7 +18862,16 @@
           <t>https://attack.mitre.org/techniques/T1021/008</t>
         </is>
       </c>
-      <c r="AF119" s="17" t="inlineStr"/>
+      <c r="AF119" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- Serial Console·EC2 Instance Connect·SSM 연결 이벤트의 비정상 주체·대상
+- VM 직접 콘솔 접근 직후의 고권한 작업
+■ 대응
+- 네이티브 VM 연결 권한 최소화·승인, 중개 접근(배스천)으로 대체
+- 연결 이벤트 알림과 SSH 키·토큰 관리</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="17" t="inlineStr">
@@ -17913,12 +19037,18 @@
       </c>
       <c r="E121" s="17" t="inlineStr">
         <is>
-          <t>공격자는 네트워크 드라이브나 내부 코드 저장소 같은 공유 저장 위치에 콘텐츠를 추가해 원격 시스템에 페이로드를 전달할 수 있다. 네트워크 드라이브나 기타 공유 위치에 저장된 콘텐츠는 정상 파일에 악성 프로그램, 스크립트, 익스플로잇 코드를 추가하는 방식으로 오염될 수 있다. 사용자가 오염된 공유 콘텐츠를 열면 악성 부분이 실행되어 원격 시스템에서 공격자의 코드가 동작할 수 있다. 공격자는 오염된 공유 콘텐츠를 이용해 측면 이동할 수 있다.</t>
+          <t>- 공격자는 공유 드라이브·코드 저장소·공유 문서에 악성 콘텐츠를 심어, 사용자가 열 때 코드가 실행되게 횡적 이동할 수 있음
+- 정상 파일에 악성 코드·바로가기를 섞어 자주 쓰는 공유 위치에 두면 반복 재감염과 광범위 확산이 일어남</t>
         </is>
       </c>
       <c r="F121" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- 클라우드 저장소·협업 문서(OneDrive·SharePoint·Google Drive)와 내부 코드 저장소의 공유 콘텐츠를 오염 — 정상 파일에 악성 매크로·스크립트 추가
+- 공유 디렉터리의 위장 .LNK·바이너리 감염으로 사용자 접근 시 실행
+- 이미지·템플릿 심기(CTC-PE-07)와 달리 사용자 공유 접근에 의존
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB·ATT&amp;CK 클라우드 사례에 매핑된 건은 없음(기법 문서화 수준)</t>
         </is>
       </c>
       <c r="G121" s="17" t="inlineStr">
@@ -17949,7 +19079,7 @@
       </c>
       <c r="M121" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N121" s="17" t="inlineStr"/>
@@ -18006,7 +19136,16 @@
           <t>https://attack.mitre.org/techniques/T1080</t>
         </is>
       </c>
-      <c r="AF121" s="17" t="inlineStr"/>
+      <c r="AF121" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 공유 저장소·문서의 악성 매크로·스크립트·위장 .LNK 추가, 공유 바이너리 변경
+- 공유 콘텐츠 열람 직후의 비정상 실행
+■ 대응
+- 공유 저장소 쓰기 권한 최소화·버전 관리, 문서 매크로 차단
+- 공유 코드·문서 무결성 점검과 악성코드 스캔</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="17" t="inlineStr">
@@ -18031,18 +19170,20 @@
       </c>
       <c r="E122" s="17" t="inlineStr">
         <is>
-          <t>공격자는 탈취한 애플리케이션 액세스 토큰으로 일반 인증 절차를 우회해 원격 시스템의 제한된 계정, 정보, 서비스에 접근할 수 있다. 이런 토큰은 보통 사용자나 서비스에게서 탈취되어 로그인 자격 증명 대신 사용된다.</t>
+          <t>- 공격자는 탈취한 OAuth 앱 토큰·서비스 어카운트 토큰·임시 자격증명으로 정상 인증을 우회해 클라우드·SaaS 리소스에 접근·횡적 이동할 수 있음
+- 리프레시 토큰은 장기 백그라운드 접근을 주고 MFA를 우회하며, 한 토큰이 메일·파일·연결 서비스로 접근을 확장함</t>
         </is>
       </c>
       <c r="F122" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 11건)
-- SolarWinds Compromise(C0024) — 클라우드(서비스 미상) [클라우드(복합)]
-- APT28(G0007) — Google Workspace [SaaS·협업]
-- SolarWinds Compromise(C0024) — Microsoft 365 [SaaS·협업]
-- CanisterWorm(S9042) — Containers 플랫폼 소프트웨어 [컨테이너·K8s]
-■ 통합된 기법
-- T1550 Use Alternate Authentication Material</t>
+          <t>■ 클라우드 관점
+- OAuth 앱 토큰으로 REST API 호출(메일 검색·연락처 열거), 리프레시 토큰으로 지속 접근 — 비밀번호 재설정 루틴을 통해 다른 서비스로 확장
+- AWS·GCP에서 다른 사용자 권한의 단기 토큰을 요청해 그 계정 권한으로 작업, K8s 서비스 어카운트 토큰으로 계정 전환(Peirates)
+- 통합된 상위기법(T1550, 대체 인증 자료) 근거 포함 — 토큰 탈취(CTC-CA-07)·동의 피싱과 연계
+■ 실제 사례
+- [ATT&amp;CK 사례] ShinyHunters: 탈취한 OAuth 키로 클라우드 인프라에 접근하고 2단계 인증 우회 (ATT&amp;CK G1057)
+- [ATT&amp;CK 사례] SolarWinds 침해: 침해한 서비스 주체로 O365 환경을 변경 (ATT&amp;CK C0024)
+- [ATT&amp;CK 사례] CreepyDrive: 정상 OAuth 리프레시 토큰으로 OneDrive에 인증 (ATT&amp;CK S1023)</t>
         </is>
       </c>
       <c r="G122" s="17" t="inlineStr">
@@ -18077,7 +19218,7 @@
       </c>
       <c r="M122" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N122" s="17" t="inlineStr">
@@ -18138,7 +19279,16 @@
           <t>https://attack.mitre.org/techniques/T1550/001</t>
         </is>
       </c>
-      <c r="AF122" s="17" t="inlineStr"/>
+      <c r="AF122" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- OAuth 앱·서비스 어카운트 토큰의 비정상 출발지 사용, 리프레시 토큰의 장기 백그라운드 접근
+- 토큰으로 수행된 평소와 다른 API(메일 검색·연락처 열거 등)
+■ 대응
+- 토큰 수명 단축·범위 최소화, 리프레시 토큰 보호·조건부 액세스
+- 과도 권한 OAuth 앱 제거와 토큰 이상 사용 알림</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="17" t="inlineStr">
@@ -18163,16 +19313,19 @@
       </c>
       <c r="E123" s="17" t="inlineStr">
         <is>
-          <t>공격자는 탈취한 세션 쿠키로 웹 애플리케이션과 서비스에 인증할 수 있다. 세션이 이미 인증된 상태이므로 이 기법은 일부 다중 인증(MFA) 프로토콜을 우회한다.</t>
+          <t>- 공격자는 탈취한 웹 세션 쿠키를 자신의 브라우저에 주입해, 세션이 유효한 동안 피해 사용자로 SaaS·클라우드에 접근할 수 있음
+- 이미 인증된 세션이라 MFA를 우회하며, 쿠키가 장기 유효해 사용자 활동이 없어도 접근이 유지됨</t>
         </is>
       </c>
       <c r="F123" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례(사고 DB)
-- [실제 사고] Malware via job opportunity premise(2025-07, INC-0528): 채용 제안을 가장한 악성코드로 침투했다. 공격자는 세션 쿠키를 탈취하고 CloudFront·S3의 JavaScript를 변조해 암호화폐를 탈취했다(Google Cloud Threat Horizons UNC4899 사례).
-■ ATT&amp;CK 사례(행위자, 총 2건)
-- Star Blizzard(G1033) — 클라우드(서비스 미상) [클라우드(복합)]
-- SolarWinds Compromise(C0024) — 클라우드(서비스 미상) [클라우드(복합)]</t>
+          <t>■ 클라우드 관점
+- 세션 쿠키 탈취(CTC-CA-09)·위조(CTC-CA-04.1)로 얻은 쿠키를 브라우저에 가져와 사용자로 로그인 — M365·클라우드 콘솔에서 메일 열람·작업 수행
+- AiTM 프록시(EvilGinx)·위조 쿠키로 MFA 우회, 세션 수명 동안 지속 접근
+■ 실제 사례
+- [실제 사고] UNC4899 채용 미끼 악성코드(2025-07): 세션 쿠키를 탈취하고 CloudFront·S3의 JavaScript를 변조해 암호화폐 탈취 (사고DB INC-0528)
+- [ATT&amp;CK 사례] Star Blizzard: EvilGinx으로 탈취한 세션 쿠키로 피해 메일 계정의 MFA 우회 (ATT&amp;CK G1033)
+- [ATT&amp;CK 사례] SolarWinds 침해: 탈취 쿠키와 위조 duo-sid 쿠키로 클라우드 리소스 접근·MFA 우회 (ATT&amp;CK C0024)</t>
         </is>
       </c>
       <c r="G123" s="17" t="inlineStr">
@@ -18203,7 +19356,7 @@
       </c>
       <c r="M123" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N123" s="17" t="inlineStr">
@@ -18272,7 +19425,16 @@
           <t>https://attack.mitre.org/techniques/T1550/004</t>
         </is>
       </c>
-      <c r="AF123" s="17" t="inlineStr"/>
+      <c r="AF123" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 동일 세션 쿠키의 다른 IP·장치 재사용, 위조 쿠키(비정상 duo-sid 등)로의 접근
+- MFA 없이 재개된 세션
+■ 대응
+- 세션 토큰 장치·IP 바인딩, 세션 수명 단축, 피싱 저항형 MFA
+- 민감 작업 재인증과 의심 세션 폐기</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="17" t="inlineStr">
@@ -18297,14 +19459,20 @@
       </c>
       <c r="E124" s="17" t="inlineStr">
         <is>
-          <t>공격자는 AiTM(adversary-in-the-middle) 기법으로 둘 이상의 네트워크 장치 사이에 자리 잡아 네트워크 스니핑(Network Sniffing), 전송 데이터 조작(Transmitted Data Manipulation), 재전송 공격(자격 증명 접근을 위한 익스플로잇(Exploitation for Credential Access)) 같은 후속 행위를 도울 수 있다. ARP, DNS, LLMNR 등 네트워크 트래픽 흐름을 결정하는 일반 네트워크 프로토콜의 기능을 악용해, 장치가 공격자가 제어하는 시스템을 거쳐 통신하도록 강제하고 정보를 수집하거나 추가 작업을 수행할 수 있다.</t>
+          <t>- 공격자는 네트워크 경로 중간에 자리 잡아(AiTM 프록시, DNS·ARP 조작, 캡티브 포털 침해) 자격증명·세션 토큰·MFA 응답을 가로챌 수 있음
+- 리버스 프록시형 피싱은 MFA를 거친 세션 쿠키까지 탈취해 다단계 인증을 무력화하며, 정상 로그인처럼 보임</t>
         </is>
       </c>
       <c r="F124" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례(사고 DB)
-- [실제 사고] UNC6671 Rebrands: Multi-Brand Vishing Extortion Targets Financial Services and Enterprise Cloud Environments(2026-08, INC-0670): GTIG에 따르면 UNC6671은 BlackFile 브랜드 은퇴 발표 이후에도 Redact, Pink, Helix, Falcon 등 여러 갈취 브랜드로 활동을 이어갔다. IT 헬프데스크를 사칭한 비싱으로 직원을 가짜 로그인 포털로 유도하고, AiTM 
-- [실제 사고] CaptiveCrunch: Midnight Blizzard Hospitality Network AiTM Campaign(2026-07, INC-0666): Microsoft가 확인한 Midnight Blizzard 하위 그룹 Storm-2945의 첩보 캠페인 CaptiveCrunch다. 숙박업 캡티브 포털 인프라를 침해해 AiTM(중간자) 공격을 수행했다.</t>
+          <t>■ 클라우드 관점
+- 피싱과 결합된 AiTM 리버스 프록시가 M365·Okta 로그인을 중계해 자격증명·MFA 토큰·세션 쿠키를 가로챔(세션 쿠키 탈취는 CTC-CA-09, 앱 토큰은 CTC-CA-07과 연계)
+- 숙박업 캡티브 포털 등 네트워크 경유 지점을 장악해 중간자 위치 확보
+- K8s: CoreDNS 포이즈닝(MS-TA9035), CNI 수준의 ARP 스푸핑·IP 스푸핑(MS-TA9036)으로 클러스터 내부 트래픽 가로채기
+- 다운그레이드 공격으로 약한 프로토콜을 강제하는 변형 포함
+■ 실제 사례
+- [실제 사고] UNC6671 비싱·AiTM(2026-08): 가짜 로그인 포털과 AiTM 인프라로 자격증명·MFA 토큰을 가로채 M365·Okta에서 데이터 유출 (사고DB INC-0670)
+- [실제 사고] CaptiveCrunch / Storm-2945(2026-07): 숙박업 캡티브 포털 인프라를 침해해 중간자 공격 수행 (사고DB INC-0666)</t>
         </is>
       </c>
       <c r="G124" s="17" t="inlineStr">
@@ -18335,7 +19503,7 @@
       </c>
       <c r="M124" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N124" s="17" t="inlineStr"/>
@@ -18405,7 +19573,16 @@
           <t>https://attack.mitre.org/techniques/T1557</t>
         </is>
       </c>
-      <c r="AF124" s="17" t="inlineStr"/>
+      <c r="AF124" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 알려진 AiTM 프록시 도메인·리버스 프록시 패턴, 같은 세션 토큰의 다른 IP 재사용
+- 비정상 DNS 응답·CoreDNS 설정 변경, 클러스터 내 ARP·IP 스푸핑 징후
+■ 대응
+- 피싱 저항형 MFA(FIDO2)로 AiTM 세션 탈취 무력화, 토큰 바인딩·세션 IP 고정
+- CoreDNS·CNI 보안 설정, 캡티브 포털·네트워크 경로 무결성 점검</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="17" t="inlineStr">
@@ -18430,16 +19607,20 @@
       </c>
       <c r="E125" s="17" t="inlineStr">
         <is>
-          <t>시스템이나 네트워크에 자리를 잡은 공격자는 자동화된 기법으로 내부 데이터를 수집할 수 있다. 예를 들어 명령 및 스크립트 인터프리터(Command and Scripting Interpreter)를 이용해 정해진 시간 간격마다 파일 형식, 위치, 이름 같은 기준에 맞는 정보를 검색하고 복사할 수 있다.</t>
+          <t>- 공격자는 클라우드 API·CLI·데이터 파이프라인·ETL로 내부 데이터를 자동 수집할 수 있음
+- 정해진 기준으로 다수 서비스에서 대량·반복 수집해 유출 규모를 키우며, 정상 데이터 처리와 섞여 탐지가 어려움</t>
         </is>
       </c>
       <c r="F125" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 6건)
-- HAFNIUM(G0125) — Microsoft 365, SharePoint, OneDrive [SaaS·협업]
-- Mini Shai-Hulud(S9043) — Containers, IaaS, SaaS 플랫폼 소프트웨어 [클라우드(복합)]
-- Shai-Hulud(S9008) — SaaS 플랫폼 소프트웨어 [SaaS·협업]
-- TeamPCP Cloud Stealer(S9041) — Containers, SaaS 플랫폼 소프트웨어 [SaaS·협업]</t>
+          <t>■ 클라우드 관점
+- 클라우드 API·CLI·파이프라인·ETL로 메일·스토리지·디렉터리 데이터를 자동 수집(Microsoft Graph·Azure Graph API 등)
+- 스토리지 객체 탐색(CTC-DS-05)·콘솔 열거(CTC-DS-03)와 결합해 대상 식별 후 대량 수집
+- 공급망 악성코드가 자격증명·호스트 데이터를 자동 압축·수집 → 자동 반출(CTC-EF-02)로 연결
+■ 실제 사례
+- [ATT&amp;CK 사례] HAFNIUM: MSGraph로 메일·OneDrive·SharePoint 데이터를 자동 수집·반출 (ATT&amp;CK G0125)
+- [ATT&amp;CK 사례] ROADTools: Azure Graph API로 Entra 환경 데이터를 자동 수집 (ATT&amp;CK S0684)
+- [ATT&amp;CK 사례] TeamPCP Cloud Stealer: 클라우드·CI/CD·컨테이너 환경의 50여 경로에서 자격증명을 식별·수집 (ATT&amp;CK S9041)</t>
         </is>
       </c>
       <c r="G125" s="17" t="inlineStr">
@@ -18470,7 +19651,7 @@
       </c>
       <c r="M125" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N125" s="17" t="inlineStr">
@@ -18531,7 +19712,16 @@
           <t>https://attack.mitre.org/techniques/T1119</t>
         </is>
       </c>
-      <c r="AF125" s="17" t="inlineStr"/>
+      <c r="AF125" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 짧은 시간 대량 데이터 조회(Graph·ETL·파이프라인), 다수 서비스에 걸친 반복 수집 패턴
+- 비정상 주체의 대량 파일·메일 수집
+■ 대응
+- 대량 접근 임계값 알림·DLP, 데이터 접근 권한 최소화
+- 파이프라인·ETL 권한 통제와 이상 수집 모니터링</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="17" t="inlineStr">
@@ -18556,21 +19746,20 @@
       </c>
       <c r="E126" s="17" t="inlineStr">
         <is>
-          <t>공격자는 클라우드 스토리지의 데이터에 접근할 수 있다.</t>
+          <t>- 공격자는 S3·Blob·GCS 등 클라우드 스토리지와 OneDrive·Drive의 데이터에 접근해 민감 정보를 대량 수집할 수 있음
+- 공개·과도 허용 설정이나 탈취 키로 API를 통해 직접 접근하며, SAS URI·스냅샷 공유로 인증 없이 반출하기도 함</t>
         </is>
       </c>
       <c r="F126" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례(사고 DB)
-- [실제 사고] JetBrains Cadence Compromised via Exploitation of TeamCity Vulnerability(2026-09, INC-0676): JetBrains Cadence는 클라우드 워크로드 오케스트레이션에 TeamCity를 사용했는데, api.cadence.jetbrains.com 서버가 패치 예정이었음에도 CVE-2026-63077에 취약한 상태로 남아 있었다. 공격자는 8월 8일부터
-- [실제 사고] Credentials exposed in public S3 buckets(2025-11, INC-0573): 공개 S3 버킷에 노출된 자격증명으로 침투해 Lambda 코드 주입, IAM 액세스 키 생성, 백도어 관리자 사용자 생성을 수행했다. 이후 LLMjacking과 GPU 인스턴스 생성에 악용했다(Sysdig 사례).
-- [실제 사고] Otelier data breach(2025-01, INC-0453): Otelier 직원 워크스테이션이 인포스틸러에 감염되어 Jira 자격증명이 침해되었다. 공격자는 Jira·Bitbucket에서 S3 접근 자격증명을 찾아 S3에서 8TB의 데이터를 유출했다.
-- 외 14건(관련 사례 ID 열)
-■ ATT&amp;CK 사례(행위자, 총 12건)
-- APT42(G1044) — Microsoft 365 [SaaS·협업]
-- HAFNIUM(G0125) — OneDrive [SaaS·협업]
-- Storm-0501(G1053) — Azure [IaaS]
-- 2025 Poland Wiper Attacks(C0063) — SharePoint [SaaS·협업]</t>
+          <t>■ 클라우드 관점
+- AWS: s3:GetObject·CopyObject로 객체 수집(AWS TTC T1530.A001), Azure: SAS URI 생성으로 인증 없는 추출(AZT701 계열)·파일 공유 마운트(AZT702)·soft-delete 객체 복구(AZT704.2)
+- 공개·과도 허용 설정(퍼블릭 액세스)이 반복된 유출 원인 — IAM 밖 익명 접근까지 허용되는 경우가 있음
+- 인프라·객체 탐색(CTC-DS-02·05)으로 대상 파악 후 수집, SaaS는 백엔드 스토리지·API로 직접 접근
+■ 실제 사례
+- [실제 사고] JetBrains Cadence 침해(2026-09): TeamCity 취약점으로 IAM 자격증명 침해 후 S3 버킷에서 백업·소스코드·고객 자격증명 유출 (사고DB INC-0676)
+- [실제 사고] MobiKwik(2021-03): 침해된 AWS 액세스 키로 S3에 접근해 9,900만 명 데이터·KYC 문서 8.2TB 유출 (사고DB INC-0070)
+- [실제 사고] Otelier(2025-01): Jira·Bitbucket에서 찾은 S3 자격증명으로 S3에서 8TB 유출 (사고DB INC-0453)</t>
         </is>
       </c>
       <c r="G126" s="17" t="inlineStr">
@@ -18601,7 +19790,7 @@
       </c>
       <c r="M126" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N126" s="17" t="inlineStr">
@@ -18689,7 +19878,16 @@
           <t>https://attack.mitre.org/techniques/T1530</t>
         </is>
       </c>
-      <c r="AF126" s="17" t="inlineStr"/>
+      <c r="AF126" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 대량 GetObject·CopyObject, SAS URI 생성·파일 공유 마운트, soft-delete 객체 복구
+- 공개 전환된 버킷·스토리지, 비정상 주체의 대량 다운로드
+■ 대응
+- 퍼블릭 액세스 블록·버킷 정책으로 공개 차단, SAS·스냅샷 공유 제한
+- 스토리지 암호화·접근 로깅과 대량 반출 알림</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="17" t="inlineStr">
@@ -18714,16 +19912,20 @@
       </c>
       <c r="E127" s="17" t="inlineStr">
         <is>
-          <t>공격자는 정보 저장소를 이용해 가치 있는 정보를 캐낼 수 있다. 정보 저장소는 보통 사용자 간 협업이나 정보 공유를 위해 정보를 저장하는 도구로, 자격 증명 접근(Credential Access), 측면 이동(Lateral Movement), 방어 회피(Defense Evasion) 같은 추가 목표나 목표 정보에 대한 직접 접근에 도움이 되는 다양한 데이터를 담고 있을 수 있다. 공격자는 외부 공유 기능을 악용해 민감한 문서를 조직 외부 수신자와 공유할 수도 있다(즉, 클라우드 계정으로 데이터 전송(Transfer Data to Cloud Account)).</t>
+          <t>- 공격자는 SharePoint·Confluence·코드 저장소·DB·협업 메시지 같은 정보 저장소에서 가치 있는 데이터와 자격증명을 수집할 수 있음
+- 과도 허용·공개 설정된 저장소나 백엔드 API로 직접 접근하며, 외부 공유 기능으로 민감 문서를 조직 밖으로 내보내기도 함</t>
         </is>
       </c>
       <c r="F127" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례(사고 DB)
-- [실제 사고] 8X8 INC /DE/ — Form 8-K Item 1.05 (2026-06-23)(2026-06, INC-0647): 8x8이 2026년 6월 23일 Item 1.05(중대 사이버보안 사고)로 8-K를 제출했다. 매핑 근거 발췌에 따르면 공격자가 8x8의 Salesforce 시스템에 무단 접근해 일부 정보를 유출했다. 최초 사건일은 2026년 6월 17일로 기재되었다
-- [실제 사고] Klue Supply Chain Breach Leads to Salesforce Data Exfiltration(2026-06, INC-0646): 공격자가 Klue 백엔드 시스템에 접근해, 고객이 Klue와 Salesforce, Gong, SharePoint, HubSpot, Slack 등을 연동할 때 쓰는 OAuth 토큰을 수집하는 코드를 배포했다. 이를 통해 Salesforce 데이터가 유출
-- [실제 사고] Salesloft Drift supply chain compromise(2025-08, INC-0549): UNC6395가 Salesloft(Drift)의 GitHub 저장소를 침해하고 AWS 환경에 접근해 OAuth 토큰을 탈취했다. 이 토큰으로 700개 이상의 Salesforce 인스턴스가 침해되었다(공급망 공격).
-- 외 2건(관련 사례 ID 열)</t>
+          <t>■ 클라우드 관점
+- 대상: IaaS DB(RDS·Redis·Elasticsearch), SharePoint·Confluence, 코드 저장소, Slack·Teams — 과도 허용·공개 설정이 흔한 노출 원인
+- AWS RDS 인스턴스 조회·수정·복사(AWS TTC T1213.A013), 외부 공유로 조직 밖 전송(CTC-EF-03과 연계)
+- 하위 변형: Confluence·SharePoint·코드 저장소·CRM·메시징·DB(CTC-CO-04.1~04.6) — 이 행은 하위로 특정되지 않은 저장소 근거 보존
+■ 실제 사례
+- [실제 사고] Salesloft Drift 공급망 침해(2025-08): OAuth 토큰으로 700여 Salesforce 인스턴스에서 데이터 수집 (사고DB INC-0549)
+- [실제 사고] Klue 공급망 침해(2026-06): 고객의 Salesforce·SharePoint·Slack 연동 OAuth 토큰을 수집해 Salesforce 데이터 유출 (사고DB INC-0646)
+- [실제 사고] Dropbox GitHub 침해(2022-11): CircleCI 사칭 피싱으로 탈취한 자격증명으로 GitHub 저장소 130개 탈취 (사고DB INC-0126)</t>
         </is>
       </c>
       <c r="G127" s="17" t="inlineStr">
@@ -18754,7 +19956,7 @@
       </c>
       <c r="M127" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N127" s="17" t="inlineStr">
@@ -18828,7 +20030,16 @@
           <t>https://attack.mitre.org/techniques/T1213</t>
         </is>
       </c>
-      <c r="AF127" s="17" t="inlineStr"/>
+      <c r="AF127" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 정보 저장소(DB·SharePoint·코드·메시징)의 대량 조회·외부 공유, 백엔드 API 직접 접근
+- 과도 허용·공개 설정된 저장소 접근
+■ 대응
+- 저장소 접근 최소 권한·외부 공유 제한, 공개 설정 점검
+- 대량 조회·외부 공유 알림과 DLP</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="17" t="inlineStr">
@@ -18853,23 +20064,18 @@
       </c>
       <c r="E128" s="17" t="inlineStr">
         <is>
-          <t>공격자는 Confluence 저장소를 이용해 가치 있는 정보를 캐낼 수 있다. Confluence는 개발 환경에서 Atlassian JIRA와 함께 쓰이는 경우가 많고 주로 개발 관련 문서를 저장하지만, 다음과 같이 더 다양한 유용한 정보를 담고 있을 수 있다 (세부 항목은 참조 열 참조)</t>
+          <t>- 공격자는 Confluence 위키에서 네트워크 구성도·시스템 문서·테스트 자격증명·소스코드 조각 등 가치 있는 정보를 수집할 수 있음
+- 개발·운영 문서가 모여 있어 추가 자격증명·고권한 계정 단서를 얻는 수집 대상이 됨</t>
         </is>
       </c>
       <c r="F128" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 원문 목록
-- Policies, procedures, and standards
-- Physical / logical network diagrams
-- System architecture diagrams
-- Technical system documentation
-- Testing / development credentials (i.e., Unsecured Credentials)
-- Work / project schedules
-- Source code snippets
-- Links to network shares and other internal resources
-■ ATT&amp;CK 사례(행위자, 총 2건)
-- TruffleHog(S9009) — IaaS, SaaS 플랫폼 소프트웨어 [클라우드(복합)]
-- LAPSUS$(G1004) — 클라우드(서비스 미상) [SaaS·협업]</t>
+          <t>■ 클라우드 관점
+- SaaS Confluence의 정책·네트워크/아키텍처 도면·기술 문서·테스트 자격증명(CTC-CA-10 연계)·소스 조각 수집
+- 과도 공유·공개 공간이 노출 원인 — JIRA와 함께 쓰여 고권한 계정 단서 탐색에 활용
+■ 실제 사례
+- [ATT&amp;CK 사례] LAPSUS$: 피해 네트워크에서 Confluence·JIRA를 뒤져 추가 고권한 계정 자격증명 탐색 (ATT&amp;CK G1004)
+- [ATT&amp;CK 사례] TruffleHog: Confluence 관련 자격증명·데이터 수집 (ATT&amp;CK S9009)</t>
         </is>
       </c>
       <c r="G128" s="17" t="inlineStr">
@@ -18900,7 +20106,7 @@
       </c>
       <c r="M128" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N128" s="17" t="inlineStr">
@@ -18961,7 +20167,15 @@
           <t>https://attack.mitre.org/techniques/T1213/001</t>
         </is>
       </c>
-      <c r="AF128" s="17" t="inlineStr"/>
+      <c r="AF128" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- Confluence 공간 대량 열람·검색, 자격증명 패턴 포함 페이지 접근
+■ 대응
+- 공간 접근 권한 최소화·공개 공간 점검, 문서 내 비밀 제거
+- 대량 열람 알림과 외부 공유 제한</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="17" t="inlineStr">
@@ -18986,25 +20200,19 @@
       </c>
       <c r="E129" s="17" t="inlineStr">
         <is>
-          <t>공격자는 SharePoint 저장소를 가치 있는 정보를 캐내는 출처로 이용할 수 있다. SharePoint에는 내부 네트워크와 시스템의 구조와 기능을 파악하는 데 유용한 정보가 들어 있는 경우가 많다. 예를 들어 공격자에게 잠재적 가치가 있고 SharePoint에서 찾을 수 있는 정보는 다음과 같다 (세부 항목은 참조 열 참조)</t>
+          <t>- 공격자는 SharePoint에서 내부 구조·절차 문서·테스트 자격증명·네트워크 공유 링크 등 민감 정보를 수집할 수 있음
+- 조직 지식이 집중돼 있어 횡적 이동·추가 자격증명 확보의 핵심 수집 대상이 됨</t>
         </is>
       </c>
       <c r="F129" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 원문 목록
-- Policies, procedures, and standards
-- Physical / logical network diagrams
-- System architecture diagrams
-- Technical system documentation
-- Testing / development credentials (i.e., Unsecured Credentials)
-- Work / project schedules
-- Source code snippets
-- Links to network shares and other internal resources
-■ ATT&amp;CK 사례(행위자, 총 9건)
-- Akira(G1024) — SharePoint [SaaS·협업]
-- APT28(G0007) — SharePoint [SaaS·협업]
-- Chimera(G0114) — SharePoint [SaaS·협업]
-- HAFNIUM(G0125) — SharePoint [SaaS·협업]</t>
+          <t>■ 클라우드 관점
+- M365 SharePoint의 정책·아키텍처 문서·테스트 자격증명·내부 리소스 링크 수집, spwebmember 등 전용 열거 도구 사용
+- 침해 자격증명으로 대량 다운로드(CTC-IA-06.2 연계), VPN·MFA 등록 안내·헬프데스크 문서 탐색으로 후속 공격 설계
+■ 실제 사례
+- [ATT&amp;CK 사례] HAFNIUM: 침해 자격증명을 악용해 SharePoint에서 데이터 반출 (ATT&amp;CK G0125)
+- [ATT&amp;CK 사례] Akira: SharePoint에 접근해 데이터 수집·반출 (ATT&amp;CK G1024)
+- [ATT&amp;CK 사례] C0027: Scattered Spider가 SharePoint에서 VPN·MFA 등록 정보와 헬프데스크·신입 안내 문서 탐색 (ATT&amp;CK C0027)</t>
         </is>
       </c>
       <c r="G129" s="17" t="inlineStr">
@@ -19035,7 +20243,7 @@
       </c>
       <c r="M129" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N129" s="17" t="inlineStr">
@@ -19096,7 +20304,15 @@
           <t>https://attack.mitre.org/techniques/T1213/002</t>
         </is>
       </c>
-      <c r="AF129" s="17" t="inlineStr"/>
+      <c r="AF129" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- SharePoint 대량 다운로드·열거(spwebmember 등), 침해 자격증명의 대량 접근
+■ 대응
+- 사이트 접근 권한 최소화·민감 라이브러리 보호, 외부 공유 제한
+- 대량 다운로드 알림과 DLP</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="17" t="inlineStr">
@@ -19121,16 +20337,19 @@
       </c>
       <c r="E130" s="17" t="inlineStr">
         <is>
-          <t>공격자는 코드 저장소를 이용해 가치 있는 정보를 수집할 수 있다. 코드 저장소는 소스 코드를 저장하고 소프트웨어 빌드를 자동화하는 도구·서비스로, 내부에 호스팅하거나 GitHub, GitLab, SourceForge, Bitbucket 같은 외부 사이트에 비공개로 호스팅할 수 있다. 사용자는 보통 웹 애플리케이션이나 git 같은 명령줄 유틸리티로 코드 저장소를 사용한다.</t>
+          <t>- 공격자는 GitHub·GitLab·Bitbucket 등 코드 저장소에서 소스코드와 하드코딩된 자격증명을 수집할 수 있음
+- 소스코드로 익스플로잇을 개발하고, 코드 속 비밀로 클라우드 리소스에 접근하는 고가치 수집 대상임</t>
         </is>
       </c>
       <c r="F130" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 10건)
-- LAPSUS$(G1004) — GitHub·GitLab [SaaS·협업]
-- Scattered Spider(G1015) — GitHub·GitLab [SaaS·협업]
-- ShinyHunters(G1057) — GitHub·GitLab [SaaS·협업]
-- GlassWorm(S9010) — GitHub·GitLab [SaaS·협업]</t>
+          <t>■ 클라우드 관점
+- 침해 네트워크·비공개 저장소에서 소스코드·하드코딩 자격증명(CTC-CA-10.1) 수집 — 공개 저장소 정찰(CTC-RD-01.1)과 달리 내부 접근 후 수집
+- 탈취한 npm·GitHub 토큰으로 저장소 열거·복제, 자격증명으로 클라우드 리소스 접근(CTC-IA-06.2)
+■ 실제 사례
+- [ATT&amp;CK 사례] Scattered Spider: 내부 GitHub 저장소의 데이터 열거 (ATT&amp;CK G1015)
+- [ATT&amp;CK 사례] GlassWorm: npm·GitHub 저장소 인증 자료와 _authToken 수집 (ATT&amp;CK S9010)
+- [ATT&amp;CK 사례] APT41: 침입 중 피해자 Git 저장소를 복제 (ATT&amp;CK G0096)</t>
         </is>
       </c>
       <c r="G130" s="17" t="inlineStr">
@@ -19161,7 +20380,7 @@
       </c>
       <c r="M130" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N130" s="17" t="inlineStr">
@@ -19222,7 +20441,16 @@
           <t>https://attack.mitre.org/techniques/T1213/003</t>
         </is>
       </c>
-      <c r="AF130" s="17" t="inlineStr"/>
+      <c r="AF130" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 코드 저장소 대량 복제·열거, 탈취 토큰(_authToken 등)의 비정상 사용
+- 비밀 패턴 검색·접근
+■ 대응
+- 저장소 접근 최소화·토큰 범위 제한, 비밀 스캐닝으로 하드코딩 제거
+- 대량 복제·다운로드 알림</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="17" t="inlineStr">
@@ -19247,13 +20475,18 @@
       </c>
       <c r="E131" s="17" t="inlineStr">
         <is>
-          <t>공격자는 고객 관계 관리(CRM) 소프트웨어를 이용해 가치 있는 정보를 캐낼 수 있다. CRM 소프트웨어는 조직이 고객과의 상호작용을 추적·관리하고 고객 데이터를 저장하는 데 쓰인다.</t>
+          <t>- 공격자는 Salesforce·Dynamics 365·HubSpot 등 CRM에서 고객 PII·구매 이력·지원 상호작용을 수집할 수 있음
+- 수집한 고객 정보로 맞춤 피싱·SIM 스와핑을 하거나 하위 조직을 노려 금전 이득·추가 침해로 이어감</t>
         </is>
       </c>
       <c r="F131" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 1건)
-- Salesforce Data Exfiltration(C0059) — Salesforce [SaaS·협업]</t>
+          <t>■ 클라우드 관점
+- SaaS CRM(Salesforce·Dynamics 365·Zoho·Zendesk·HubSpot)의 고객 PII·구매 이력·IT 지원 기록 수집
+- OAuth 통합·악성 연결 앱(CTC-PE-02)이나 탈취 자격증명으로 접근, 수집 데이터로 고객 대상 맞춤 피싱·SIM 스와핑
+■ 실제 사례
+- [ATT&amp;CK 사례] Salesforce 데이터 반출 캠페인: 침해한 Salesforce 인스턴스에서 민감 정보 접근·반출 (ATT&amp;CK C0059)
+- [실제 사고] 8x8 Salesforce 무단 접근(2026-06): Salesforce 시스템 침해로 일부 정보 유출 (사고DB INC-0647)</t>
         </is>
       </c>
       <c r="G131" s="17" t="inlineStr">
@@ -19284,7 +20517,7 @@
       </c>
       <c r="M131" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N131" s="17" t="inlineStr">
@@ -19345,7 +20578,15 @@
           <t>https://attack.mitre.org/techniques/T1213/004</t>
         </is>
       </c>
-      <c r="AF131" s="17" t="inlineStr"/>
+      <c r="AF131" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- CRM 대량 레코드 조회·내보내기, 연결 앱·통합 토큰의 비정상 대량 접근
+■ 대응
+- CRM 접근 최소화·대량 내보내기 제한, 연결 앱 권한 검토
+- 대량 조회 알림과 이상 행위 모니터링</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="17" t="inlineStr">
@@ -19370,16 +20611,19 @@
       </c>
       <c r="E132" s="17" t="inlineStr">
         <is>
-          <t>공격자는 Microsoft Teams, Google Chat, Slack 같은 채팅·메시징 애플리케이션을 이용해 가치 있는 정보를 캐낼 수 있다.</t>
+          <t>- 공격자는 Teams·Slack·Google Chat 등 메시징 앱에서 테스트 자격증명·소스조각·내부 논의·사고 대응 정보를 수집할 수 있음
+- 채팅으로 환경을 파악하고 진행 중인 사고 대응을 관찰해 자신의 기법을 조정함</t>
         </is>
       </c>
       <c r="F132" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 4건)
-- Fox Kitten(G0117) — Microsoft Teams [SaaS·협업]
-- LAPSUS$(G1004) — Slack [SaaS·협업]
-- Scattered Spider(G1015) — Microsoft Teams, Slack [SaaS·협업]
-- TruffleHog(S9009) — Slack [SaaS·협업]</t>
+          <t>■ 클라우드 관점
+- SaaS 메시징(Teams·Slack)의 테스트 자격증명(CTC-CA-10.4)·소스 조각·내부 리소스 링크·사고 대응 논의 수집
+- 침해 계정의 개인 데이터 접근(Azure ATRM AZT108)으로 메시지 열람, 수집 정보로 표적 고도화·대응 회피
+■ 실제 사례
+- [ATT&amp;CK 사례] Scattered Spider: 피해자 Slack·Teams에서 침입·사고 대응 관련 대화 검색 (ATT&amp;CK G1015)
+- [ATT&amp;CK 사례] LAPSUS$: Teams·Slack에서 고권한 계정 자격증명 탐색 (ATT&amp;CK G1004)
+- [ATT&amp;CK 사례] Fox Kitten: 보안·IT 환경과 Teams에 접근해 가치 있는 정보 수집 (ATT&amp;CK G0117)</t>
         </is>
       </c>
       <c r="G132" s="17" t="inlineStr">
@@ -19410,7 +20654,7 @@
       </c>
       <c r="M132" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N132" s="17" t="inlineStr">
@@ -19475,7 +20719,15 @@
           <t>https://attack.mitre.org/techniques/T1213/005</t>
         </is>
       </c>
-      <c r="AF132" s="17" t="inlineStr"/>
+      <c r="AF132" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 메시징 앱 대량 검색·내보내기, 사고 대응 키워드 검색, 침해 계정의 대화 열람
+■ 대응
+- 메시징 DLP·비밀 탐지, 접근 최소화와 통합 앱 권한 통제
+- 대량 검색·내보내기 알림</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="17" t="inlineStr">
@@ -19500,15 +20752,20 @@
       </c>
       <c r="E133" s="17" t="inlineStr">
         <is>
-          <t>공격자는 데이터베이스를 이용해 가치 있는 정보를 캐낼 수 있다. 이러한 데이터베이스는 온프레미스나 클라우드(PaaS와 SaaS 환경 모두)에 호스팅될 수 있다.</t>
+          <t>- 공격자는 관리형·클라우드 DB(RDS·Azure SQL·Firebase·Snowflake, MySQL·MongoDB 등)에서 사용자·해시·PII·금융 데이터를 수집할 수 있음
+- DB 설정 파일의 자격증명으로 접근하거나 과도 허용·공개 DB에 직접 붙으며, 수집 데이터는 횡적 이동·갈취·판매에 쓰임</t>
         </is>
       </c>
       <c r="F133" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 3건)
-- ShinyHunters(G1057) — Salesforce [SaaS·협업]
-- Turla(G0010) — Entra ID [ID·인증]
-- TeamPCP Cloud Stealer(S9041) — Containers, SaaS 플랫폼 소프트웨어 [SaaS·협업]</t>
+          <t>■ 클라우드 관점
+- 대상: Amazon RDS·Aurora, Azure SQL, Google Firebase, Snowflake와 PaaS/IaaS에 올린 MySQL·PostgreSQL·MongoDB
+- DB 설정 파일(~/.pgpass·~/.my.cnf·~/.mongorc.js)에서 자격증명 수집(TeamPCP Cloud Stealer), 공개·약인증 DB 직접 접근
+- 통합 상위기법(CTC-CO-04.0)의 하위 — 수집 데이터는 반출(CTC-EF)·갈취로 연결
+■ 실제 사례
+- [ATT&amp;CK 사례] ShinyHunters: 항공·유통 피해자의 Salesforce 데이터셋 수집 (ATT&amp;CK G1057)
+- [ATT&amp;CK 사례] TeamPCP Cloud Stealer: 다수 DB 설정 파일에서 자격증명 추출 (ATT&amp;CK S9041)
+- 참고: DeepSeek 인증 없는 ClickHouse 노출(2025)은 설정 오류(CTC 범위 밖 AI 인프라)로 분류, DB 노출의 대표 사례</t>
         </is>
       </c>
       <c r="G133" s="17" t="inlineStr">
@@ -19539,7 +20796,7 @@
       </c>
       <c r="M133" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N133" s="17" t="inlineStr">
@@ -19600,7 +20857,16 @@
           <t>https://attack.mitre.org/techniques/T1213/006</t>
         </is>
       </c>
-      <c r="AF133" s="17" t="inlineStr"/>
+      <c r="AF133" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- DB 대량 조회·덤프, 공개·약인증 DB 접근, DB 설정 파일(~/.pgpass 등) 읽기
+- 관리형 DB의 비정상 대량 SELECT·export
+■ 대응
+- DB 접근 최소 권한·네트워크 격리(프라이빗 엔드포인트), 공개 노출 차단
+- DB 자격증명 비밀 저장소화·암호화, 대량 조회 알림·DLP</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="17" t="inlineStr">
@@ -19625,12 +20891,18 @@
       </c>
       <c r="E134" s="17" t="inlineStr">
         <is>
-          <t>공격자는 유출(Exfiltration)에 앞서 파일 시스템, 구성 파일, 로컬 데이터베이스, 가상 머신 파일, 프로세스 메모리 같은 로컬 시스템 소스를 검색해 관심 파일과 민감한 데이터를 찾을 수 있다.</t>
+          <t>- 공격자는 반출에 앞서 VM·호스트의 파일시스템·구성 파일·로컬 DB·프로세스 메모리에서 관심 데이터를 수집할 수 있음
+- 셸·CLI로 로컬을 뒤지며, 컨테이너 환경에서는 관리 명령으로 파드 내부 데이터를 직접 접근하지 않고도 수집함</t>
         </is>
       </c>
       <c r="F134" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- 침해한 클라우드 VM·컨테이너의 로컬 파일·구성·메모리에서 데이터 수집, 자동 수집(CTC-CO-02)과 결합
+- K8s: 관리 명령으로 파드에서 정보 수집(MS-TA9041) — 파드 직접 접근 없이도 가능
+- 수집 후 스테이징(CTC-CO-06.1)·반출로 연결
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB·ATT&amp;CK 클라우드 사례에 매핑된 건은 없음(기법 문서화 수준)</t>
         </is>
       </c>
       <c r="G134" s="17" t="inlineStr">
@@ -19661,7 +20933,7 @@
       </c>
       <c r="M134" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N134" s="17" t="inlineStr"/>
@@ -19722,7 +20994,16 @@
           <t>https://attack.mitre.org/techniques/T1005</t>
         </is>
       </c>
-      <c r="AF134" s="17" t="inlineStr"/>
+      <c r="AF134" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- VM·컨테이너 내 대량 파일 탐색·읽기, 프로세스 메모리 접근
+- 파드에서의 비정상 데이터 수집 명령
+■ 대응
+- 워크로드 최소 권한·민감 데이터 암호화, EDR로 비정상 파일 접근 탐지
+- 컨테이너 읽기 전용 파일시스템과 수집 도구 차단</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="17" t="inlineStr">
@@ -19747,15 +21028,18 @@
       </c>
       <c r="E135" s="17" t="inlineStr">
         <is>
-          <t>공격자는 유출(Exfiltration)에 앞서 여러 시스템에서 수집한 데이터를 한 시스템의 중앙 위치나 디렉터리에 모아 둘 수 있다. 데이터는 개별 파일로 두거나 수집 데이터 압축(Archive Collected Data) 같은 기법으로 하나의 파일로 합칠 수 있다. 대화형 명령 셸을 쓸 수 있으며, cmd와 bash의 일반 기능으로 데이터를 스테이징 위치에 복사할 수 있다.</t>
+          <t>- 공격자는 반출 전 여러 시스템의 수집 데이터를 한 인스턴스·중앙 DB에 모아 둘 수 있음
+- 공격자가 만든 클라우드 인스턴스에 스테이징하면 C2 연결 수를 줄여 탐지를 피하고 반출을 효율화함</t>
         </is>
       </c>
       <c r="F135" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 1건)
-- Scattered Spider(G1015) — Entra ID [ID·인증]
-■ 통합된 기법
-- T1074 Data Staged</t>
+          <t>■ 클라우드 관점
+- 수집 데이터를 특정 인스턴스·VM에 모음 — 공격자가 만든 인스턴스(CTC-DI-05.2)에 스테이징해 외부 연결 최소화
+- 중앙 DB·스토리지에 모은 뒤 클라우드 계정 간 전송(CTC-EF-03)·웹 서비스 반출(CTC-EF-02)로 연결
+- 통합된 상위기법(T1074) 근거 포함
+■ 실제 사례
+- [ATT&amp;CK 사례] Scattered Spider: 반출 전 데이터를 중앙 DB에 스테이징 (ATT&amp;CK G1015)</t>
         </is>
       </c>
       <c r="G135" s="17" t="inlineStr">
@@ -19790,7 +21074,7 @@
       </c>
       <c r="M135" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N135" s="17" t="inlineStr"/>
@@ -19847,7 +21131,16 @@
           <t>https://attack.mitre.org/techniques/T1074/002</t>
         </is>
       </c>
-      <c r="AF135" s="17" t="inlineStr"/>
+      <c r="AF135" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 다수 시스템 데이터가 한 인스턴스·DB로 모이는 패턴, 비정상 대용량 복사·압축
+- 공격자 생성 인스턴스로의 데이터 집결
+■ 대응
+- 대용량 내부 전송·압축 알림, 인스턴스 생성·네트워크 흐름 모니터링
+- 중요 데이터 접근 로깅과 비정상 집결 탐지</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="17" t="inlineStr">
@@ -19872,17 +21165,20 @@
       </c>
       <c r="E136" s="17" t="inlineStr">
         <is>
-          <t>공격자는 민감한 정보를 수집하기 위해 Exchange 서버, Office 365, Google Workspace를 노릴 수 있다. 사용자의 자격 증명을 이용해 Exchange 서버와 직접 상호작용하며 네트워크 안의 정보를 얻을 수 있다. 외부에 공개된 Exchange 서비스, Office 365, Google Workspace에 자격 증명이나 액세스 토큰으로 접근해 이메일을 볼 수도 있다. MailSniper 같은 도구로 특정 키워드 검색을 자동화할 수 있다.</t>
+          <t>- 공격자는 탈취 자격증명·토큰으로 Exchange Online·M365·Google Workspace 사서함에 접근해 이메일을 대량 수집할 수 있음
+- Graph·EWS·MailSniper로 키워드 검색을 자동화하며, 외부 노출 메일 서비스에 직접 붙어 민감 정보를 캐냄</t>
         </is>
       </c>
       <c r="F136" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례(사고 DB)
-- [실제 사고] IEH Corp — Form 8-K Item 8.01 (2026-08-06)(2026-08, INC-0669): IEH Corp가 2026년 8월 6일 Item 8.01로 8-K를 제출했으며, 최초 사건일은 2026년 8월 4일로 기재되었다. 매핑 근거 발췌에 따르면 침해는 피싱 공격에서 시작되었고, 공격자가 이메일 메시지 등 메일함 내용에 접근했다.
-■ ATT&amp;CK 사례(행위자, 총 3건)
-- HAFNIUM(G0125) — Microsoft 365 [SaaS·협업]
-- MailSniper(S0413) — Microsoft 365 [SaaS·협업]
-- 2025 Poland Wiper Attacks(C0063) — 클라우드(서비스 미상) [SaaS·협업]</t>
+          <t>■ 클라우드 관점
+- M365·Workspace 사서함을 Graph·EWS·웹 인터페이스로 접근, MailSniper로 키워드 자동 검색
+- 침해 계정 개인 데이터 접근(Azure ATRM AZT108), 웹셸·MSGraph로 사서함 반출 — 사서함 위임(CTC-PE-01.2)·앱 토큰(CTC-CA-07)과 결합
+- APT의 장기 첩보 수집과 BEC의 핵심 수집 단계 (CSA TT2026 SI-07)
+■ 실제 사례
+- [실제 사고] IEH Corp 8-K(2026-08): 피싱에서 시작해 공격자가 사서함 내용에 접근 (사고DB INC-0669)
+- [ATT&amp;CK 사례] HAFNIUM: 웹셸·MSGraph로 사서함 데이터 반출 (ATT&amp;CK G0125)
+- [ATT&amp;CK 사례] 2025 Poland Wiper 캠페인: 탈취 자격증명으로 Exchange에서 OT 관련 메일 수집 (ATT&amp;CK C0063)</t>
         </is>
       </c>
       <c r="G136" s="17" t="inlineStr">
@@ -19913,7 +21209,7 @@
       </c>
       <c r="M136" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N136" s="17" t="inlineStr">
@@ -19986,7 +21282,16 @@
           <t>https://attack.mitre.org/techniques/T1114/002</t>
         </is>
       </c>
-      <c r="AF136" s="17" t="inlineStr"/>
+      <c r="AF136" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- Graph·EWS 대량 사서함 조회, MailSniper 등 키워드 검색 패턴, 웹셸 기반 메일 반출
+- 침해 계정의 비정상 대량 메일 접근
+■ 대응
+- 사서함 접근 최소화·앱 토큰 범위 제한, 대량 메일 조회 알림·DLP
+- 감사 로깅 유지와 의심 세션 폐기</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="17" t="inlineStr">
@@ -20011,15 +21316,19 @@
       </c>
       <c r="E137" s="17" t="inlineStr">
         <is>
-          <t>공격자는 민감한 정보를 수집하기 위해 이메일 전달 규칙을 설정할 수 있다. 이메일 전달 규칙을 악용해 피해자의 활동을 감시하고, 정보를 탈취하고, 이후 공격이나 작전에 쓸 피해자나 피해 조직에 관한 정보를 더 수집할 수 있다. 또한 이메일 전달 규칙을 이용하면 관리자가 침해된 자격 증명을 재설정한 뒤에도 피해자의 이메일에 계속 접근할 수 있다. 대부분의 이메일 클라이언트는 다른 수신자에게 전달하는 기능을 포함해 다양한 받은편지함 규칙을 만들 수 있게 한다. 이 규칙은 로컬 이메일 애플리케이션, 웹 인터페이스, 명령줄 인터페이스로 만들 수 있다. 메시지는 내부나 외부 수신자에게 전달될 수 있으며 규칙의 범위에 제한이 없다. 관리자도 사용자 계정에 전달 규칙을 만들 수 있으며, 고려 사항과 결과는 같다.</t>
+          <t>- 공격자는 이메일 전달 규칙을 설정해 피해자의 메일을 외부·내부 계정으로 자동 전달받아 지속 수집할 수 있음
+- 규칙은 사서함에 남아 비밀번호 재설정 후에도 유효하고, MAPI로 숨기거나 조직 전역 전송 규칙으로 전사 메일을 전달받기도 함</t>
         </is>
       </c>
       <c r="F137" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례(사고 DB)
-- [실제 사고] Public and Private Medical Community Targeted by China-Nexus Threat Actor Pursuing Artificial Intelligence, Cyber, Medical, and National Defense Research(2026-06, INC-0643): GTIG가 중국 연계 UNC6508이 북미 학술·의료·군사 연구 기관을 노린 캠페인을 확인했다. 공격자는 1년 넘게 탐지되지 않은 채 외부 웹 애플리케이션을 침해하고 맞춤형 악성코드를 배포했으며, 내부 시스템으로 확산해 기업 관리 도구로 데이터를 은밀
-■ ATT&amp;CK 사례(행위자, 총 1건)
-- LAPSUS$(G1004) — Microsoft 365 [SaaS·협업]</t>
+          <t>■ 클라우드 관점
+- Exchange Online·Workspace에서 개별 사서함 전달 규칙이나 조직 전역 transport rule로 메일 자동 전달
+- MAPI로 규칙을 숨겨 Outlook·OWA·관리 도구에서 보이지 않게 함 — 비밀번호 재설정 후에도 메일 접근 지속
+- 이메일 숨김 규칙(CTC-ST-01.1)과 결합해 탐지 회피
+■ 실제 사례
+- [실제 사고] UNC6508 의료·연구 표적 캠페인(2026-06): 내부 시스템 확산 후 기업 도구로 데이터를 은밀히 유출 (사고DB INC-0643)
+- [ATT&amp;CK 사례] LAPSUS$: O365 테넌트 수준 전송 규칙으로 조직 입출 메일을 신규 계정으로 전달 (ATT&amp;CK G1004)</t>
         </is>
       </c>
       <c r="G137" s="17" t="inlineStr">
@@ -20050,7 +21359,7 @@
       </c>
       <c r="M137" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N137" s="17" t="inlineStr">
@@ -20119,7 +21428,16 @@
           <t>https://attack.mitre.org/techniques/T1114/003</t>
         </is>
       </c>
-      <c r="AF137" s="17" t="inlineStr"/>
+      <c r="AF137" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 외부 전달 규칙 생성, 조직 전역 transport rule 변경, MAPI로 숨겨진 규칙
+- 메일이 외부로 자동 전달되는 패턴
+■ 대응
+- 자동 외부 전달 차단 정책, 전달 규칙 정기 감사(숨김 규칙 포함)
+- 전송 규칙 변경 알림과 외부 전달 모니터링</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="17" t="inlineStr">
@@ -20144,12 +21462,18 @@
       </c>
       <c r="E138" s="17" t="inlineStr">
         <is>
-          <t>공격자는 자신의 인프라에 직접 연결되지 않도록 연결 프록시를 사용해 시스템 간 네트워크 트래픽을 중계하거나 명령 및 제어(C2) 서버와의 네트워크 통신을 중개할 수 있다. HTRAN, ZXProxy, ZXPortMap 등 프록시나 포트 리디렉션으로 트래픽을 우회시키는 도구가 많이 있다. 공격자는 이런 프록시를 이용해 C2 통신을 관리하고, 동시에 발생하는 외부 네트워크 연결 수를 줄이고, 연결이 끊겨도 복원력을 확보하거나, 피해 대상 사이의 기존 신뢰 통신 경로를 타고 의심을 피한다. 공격자는 여러 프록시를 연쇄로 연결해 악성 트래픽의 출처를 더 감출 수 있다.</t>
+          <t>- 공격자는 연결 프록시·포트 리디렉션·CDN 라우팅으로 C2 트래픽을 중계해 자신의 인프라를 숨길 수 있음
+- 여러 프록시를 연쇄해 출처를 감추고, 신뢰 통신 경로에 섞여 외부 연결 수를 줄이며 탐지·차단을 피함</t>
         </is>
       </c>
       <c r="F138" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- 침해한 클라우드 VM·CDN을 프록시로 삼아 C2 트래픽 중계(출발지 IP 은닉, MS-TA9024), CDN 라우팅으로 도메인 프론팅 유사 은폐
+- 정상 클라우드 서비스 대역·신뢰 경로에 섞여 네트워크 탐지를 회피
+- 프록시 연쇄로 추적을 어렵게 함
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB·ATT&amp;CK 클라우드 사례에 매핑된 건은 없음(기법 문서화 수준)</t>
         </is>
       </c>
       <c r="G138" s="17" t="inlineStr">
@@ -20180,7 +21504,7 @@
       </c>
       <c r="M138" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N138" s="17" t="inlineStr"/>
@@ -20241,7 +21565,16 @@
           <t>https://attack.mitre.org/techniques/T1090</t>
         </is>
       </c>
-      <c r="AF138" s="17" t="inlineStr"/>
+      <c r="AF138" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 알려진 프록시·리디렉션 도구 패턴, CDN 경유 비정상 C2, 다단 프록시 연쇄
+- 침해 VM에서의 중계 트래픽
+■ 대응
+- 아웃바운드 필터링·허용 목록, 비정상 장기 연결 탐지
+- 침해 VM 격리와 CDN 라우팅 모니터링</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="17" t="inlineStr">
@@ -20266,12 +21599,18 @@
       </c>
       <c r="E139" s="17" t="inlineStr">
         <is>
-          <t>공격자는 침해한 인프라를 통한 데이터 유출을 자동화하기 위해 트래픽 미러링을 악용할 수 있다. 트래픽 미러링은 일부 장비에 기본으로 있는 기능으로 주로 네트워크 분석에 쓰인다. 예를 들어 장비가 네트워크 트래픽을 하나 이상의 목적지로 전달해 네트워크 분석기나 기타 모니터링 장비가 분석하도록 설정될 수 있다.</t>
+          <t>- 공격자는 클라우드·네트워크 장비의 트래픽 미러링 기능(AWS Traffic Mirroring, Azure vTap 등)을 악용해 트래픽을 자신의 대상으로 복제·반출할 수 있음
+- 정상 분석용 기능을 전용해 지속적으로 데이터를 빼내며, 네트워크 스니핑·AiTM과 결합됨</t>
         </is>
       </c>
       <c r="F139" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- AWS Traffic Mirroring·GCP Packet Mirroring·Azure vTap으로 지정 인스턴스 트래픽을 공격자 대상으로 복제
+- 네트워크 장비 변조(ROMMONkit·이미지 패치)로도 리디렉션 — 네트워크 스니핑·AiTM(CTC-CA-01)과 결합
+- 미러링 세션 생성 권한이 전제이며, 설정 변경이 곧 지속 반출 통로가 됨
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB·ATT&amp;CK 클라우드 사례에 매핑된 건은 없음(벤더·ATT&amp;CK 문서화 수준)</t>
         </is>
       </c>
       <c r="G139" s="17" t="inlineStr">
@@ -20302,7 +21641,7 @@
       </c>
       <c r="M139" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N139" s="17" t="inlineStr"/>
@@ -20359,7 +21698,16 @@
           <t>https://attack.mitre.org/techniques/T1020/001</t>
         </is>
       </c>
-      <c r="AF139" s="17" t="inlineStr"/>
+      <c r="AF139" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 트래픽 미러링 세션 생성·변경(AWS Traffic Mirroring·GCP Packet Mirroring·Azure vTap), 네트워크 장비 이미지 변조
+- 미러 대상이 비인가 리소스로 지정됨
+■ 대응
+- 미러링 세션 생성 권한 최소화·변경 알림, 미러 대상 허용 목록
+- 네트워크 장비 무결성 점검과 설정 드리프트 복원</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="17" t="inlineStr">
@@ -20384,16 +21732,20 @@
       </c>
       <c r="E140" s="17" t="inlineStr">
         <is>
-          <t>공격자는 주 명령 및 제어(C2) 채널 대신 이미 존재하는 정상적인 외부 웹 서비스를 이용해 데이터를 유출할 수 있다. 네트워크 안의 호스트가 침해 전부터 이런 인기 웹 서비스와 통신하고 있을 가능성이 높아, 이를 유출 수단으로 쓰면 상당한 은폐 효과를 얻을 수 있다. 이런 서비스로 가는 트래픽을 허용하는 방화벽 규칙이 이미 있을 수도 있다.</t>
+          <t>- 공격자는 C2 채널 대신 Google Drive·Salesforce·M365 같은 정상 웹 서비스로 데이터를 반출할 수 있음
+- 피해 조직이 평소 쓰는 서비스라 방화벽 허용·TLS 암호화에 묻혀 탐지가 어려움</t>
         </is>
       </c>
       <c r="F140" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 5건)
-- APT28(G0007) — Google Workspace [SaaS·협업]
-- ShinyHunters(G1057) — Salesforce [SaaS·협업]
-- APT28 Nearest Neighbor Campaign(C0051) — Google Workspace [SaaS·협업]
-- Salesforce Data Exfiltration(C0059) — Salesforce [SaaS·협업]</t>
+          <t>■ 클라우드 관점
+- 정상 SaaS(Google Drive·Salesforce·M365)를 반출 통로로 사용 — 기존 허용 규칙·TLS로 은폐
+- Salesforce Data Loader 등 정상 API·도구로 대량 반출(CTC-CO-04.4와 연계)
+- 하위 변형: 웹훅 반출(CTC-EF-02.1), 클라우드 계정 간 전송(CTC-EF-03)
+■ 실제 사례
+- [ATT&amp;CK 사례] ShinyHunters: 침해한 Salesforce CRM 대시보드로 대량 데이터 반출 (ATT&amp;CK G1057)
+- [ATT&amp;CK 사례] Salesforce 데이터 반출 캠페인: Salesforce Data Loader 등 정상 API 채널로 반출 (ATT&amp;CK C0059)
+- [ATT&amp;CK 사례] APT28: Google Drive로 데이터 반출 (ATT&amp;CK G0007)</t>
         </is>
       </c>
       <c r="G140" s="17" t="inlineStr">
@@ -20424,7 +21776,7 @@
       </c>
       <c r="M140" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N140" s="17" t="inlineStr">
@@ -20485,7 +21837,16 @@
           <t>https://attack.mitre.org/techniques/T1567</t>
         </is>
       </c>
-      <c r="AF140" s="17" t="inlineStr"/>
+      <c r="AF140" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 정상 SaaS(Drive·Salesforce·M365)로의 비정상 대량 업로드, Data Loader 등 대량 반출 도구 사용
+- 평소와 다른 양·시간대의 외부 서비스 전송
+■ 대응
+- 아웃바운드 DLP·업로드 제한, 승인되지 않은 SaaS로의 전송 차단
+- 대량 업로드 알림과 API 반출 모니터링</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="17" t="inlineStr">
@@ -20510,14 +21871,18 @@
       </c>
       <c r="E141" s="17" t="inlineStr">
         <is>
-          <t>공격자는 주 명령 및 제어(C2) 채널 대신 웹훅 엔드포인트로 데이터를 유출할 수 있다. 웹훅은 클라이언트가 서버를 계속 폴링하지 않아도 서버가 HTTP/S로 클라이언트에 데이터를 보낼 수 있게 하는 간단한 방식이다. Discord, Slack, webhook.site 등 많은 공개·상용 서비스가 GitHub, Jira, Trello 같은 다른 서비스에서 쓸 수 있는 웹훅 엔드포인트 생성을 지원한다. 연결된 서비스에서 변경(저장소 업데이트 푸시, 티켓 수정 등)이 생기면 해당 서비스가 데이터를 웹훅 엔드포인트로 자동 전송하고, 이를 사용하는 애플리케이션이 그 데이터를 활용한다.</t>
+          <t>- 공격자는 Discord·Slack·webhook.site 같은 웹훅 엔드포인트로 데이터를 반출할 수 있음
+- 공격자 환경을 피해 SaaS에 연결해 메일·메시지를 반복 자동 반출하거나, 스테이징 데이터를 URL에 직접 올리며 정상 트래픽에 섞임</t>
         </is>
       </c>
       <c r="F141" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 2건)
-- 2025 Poland Wiper Attacks(C0063) — Slack [SaaS·협업]
-- Shai-Hulud(S9008) — SaaS 플랫폼 소프트웨어 [SaaS·협업]</t>
+          <t>■ 클라우드 관점
+- Slack·Discord·webhook.site 등 웹훅 URL로 저장소 비밀·메일·메시지 반출 — HTTPS·정상 협업 서비스라 은폐
+- 공격자 환경을 피해 SaaS에 연결해 반복 자동 반출(CTC-EF-02 상위) 또는 스테이징 데이터 직접 POST
+■ 실제 사례
+- [ATT&amp;CK 사례] Shai-Hulud: 저장소 비밀을 webhook.site로 반출 (ATT&amp;CK S9008)
+- [ATT&amp;CK 사례] 2025 Poland Wiper 캠페인: 공격자 통제 Slack 채널로 데이터 반출 (ATT&amp;CK C0063)</t>
         </is>
       </c>
       <c r="G141" s="17" t="inlineStr">
@@ -20548,7 +21913,7 @@
       </c>
       <c r="M141" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N141" s="17" t="inlineStr">
@@ -20609,7 +21974,16 @@
           <t>https://attack.mitre.org/techniques/T1567/004</t>
         </is>
       </c>
-      <c r="AF141" s="17" t="inlineStr"/>
+      <c r="AF141" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 웹훅 엔드포인트(Discord·Slack·webhook.site)로의 비정상 전송, 저장소 비밀의 외부 POST
+- 공격자 환경에 연결된 SaaS 통합
+■ 대응
+- 아웃바운드로의 웹훅 도메인 제한·DLP, 비인가 SaaS 통합 차단
+- 저장소 비밀 유출 탐지와 웹훅 트래픽 모니터링</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="17" t="inlineStr">
@@ -20634,17 +22008,19 @@
       </c>
       <c r="E142" s="17" t="inlineStr">
         <is>
-          <t>공격자는 공유·동기화나 클라우드 환경 백업 생성 등을 통해, 같은 서비스에서 자신이 제어하는 다른 클라우드 계정으로 데이터를 옮겨 유출할 수 있다.</t>
+          <t>- 공격자는 같은 클라우드 제공자 내 자신의 계정으로 스냅샷·백업·공유 링크를 통해 데이터를 전송해 반출할 수 있음
+- 제공자 내부 주소·API를 쓰므로 외부 대량 전송 감시를 피하며, SAS URI·익명 공유 링크로 인증 없이 빼내기도 함</t>
         </is>
       </c>
       <c r="F142" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례(사고 DB)
-- [실제 사고] DNC Hack by the GRU(2016-06, INC-0008): GRU에 의한 DNC 해킹 사례로, 테스트 클러스터가 침해된 뒤(초기 경로 미상) EC2 스냅샷이 공격자 AWS 계정으로 복사되었고 Tableau·Vertica 쿼리 데이터가 영향을 받았다.
-■ ATT&amp;CK 사례(행위자, 총 3건)
-- INC Ransom(G1032) — 클라우드(서비스 미상) [클라우드(복합)]
-- RedCurl(G1039) — 클라우드(서비스 미상) [클라우드(복합)]
-- Storm-0501(G1053) — 클라우드(서비스 미상) [클라우드(복합)]</t>
+          <t>■ 클라우드 관점
+- 같은 제공자 내 공격자 계정으로 스냅샷·백업 복사(AzCopy·Replication, Azure ATRM AZT703) — 외부 네트워크 인터페이스를 거치지 않아 탐지 회피
+- SAS URI·익명 공유 링크(CTC-CO-03 연계)로 인증 없이 반출, 인스턴스 백업을 별도 계정으로 이전
+■ 실제 사례
+- [실제 사고] DNC 해킹(2016-06): 침해한 테스트 클러스터의 EC2 스냅샷을 공격자 AWS 계정으로 복사 (사고DB INC-0008)
+- [ATT&amp;CK 사례] Storm-0501: AzCopy CLI로 피해 환경 데이터를 공격자 인프라로 복사 (ATT&amp;CK G1053)
+- [ATT&amp;CK 사례] RedCurl: megatools로 Mega 클라우드 스토리지에 데이터 반출 (ATT&amp;CK G1039)</t>
         </is>
       </c>
       <c r="G142" s="17" t="inlineStr">
@@ -20675,7 +22051,7 @@
       </c>
       <c r="M142" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N142" s="17" t="inlineStr">
@@ -20748,7 +22124,16 @@
           <t>https://attack.mitre.org/techniques/T1537</t>
         </is>
       </c>
-      <c r="AF142" s="17" t="inlineStr"/>
+      <c r="AF142" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 제공자 내 다른 계정으로의 스냅샷·백업 복사(AzCopy·Replication), SAS URI·익명 공유 링크 생성
+- 스냅샷·이미지의 외부 계정 공유
+■ 대응
+- 스냅샷·백업 공유 권한 최소화·외부 공유 차단, SAS·익명 링크 제한
+- 계정 간 복사 알림과 스냅샷 공유 모니터링</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="17" t="inlineStr">
@@ -20773,12 +22158,18 @@
       </c>
       <c r="E143" s="17" t="inlineStr">
         <is>
-          <t>공격자는 정상 사용자가 쓰는 계정에 대한 접근을 막아 시스템과 네트워크 리소스의 가용성을 방해할 수 있다. 계정 접근을 없애기 위해 계정을 삭제하거나, 잠그거나, 조작할 수 있다(예: 자격 증명 변경, SharePoint 같은 SaaS 플랫폼의 권한 회수). 이후 악의적 변경을 적용하기 위해 로그오프하거나 시스템 종료·재부팅(System Shutdown/Reboot)을 수행할 수도 있다.</t>
+          <t>- 공격자는 계정을 삭제·잠그거나 자격증명·권한을 변경해 정상 사용자의 클라우드·SaaS 접근을 차단할 수 있음
+- 랜섬·파괴 공격 전 관리자 접근을 끊어 사고 대응·복구를 방해하는 용도로 쓰임</t>
         </is>
       </c>
       <c r="F143" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- IAM 사용자·역할 삭제(AWS TTC T1531), SaaS 권한 회수, 비밀번호·MFA 강제 변경으로 정상 사용자·관리자 로그아웃
+- 랜섬웨어·데이터 파괴(CTC-IM-02)·암호화(CTC-IM-03) 직전에 수행해 대응·복구를 지연
+- 관리자 접근까지 끊기면 사고 대응 자체가 막혀 피해가 커짐
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB·ATT&amp;CK 클라우드 사례에 이 기법으로 특정 매핑된 건은 없음(랜섬 사고의 선행 단계로 나타남, 벤더 문서화 수준)</t>
         </is>
       </c>
       <c r="G143" s="17" t="inlineStr">
@@ -20809,7 +22200,7 @@
       </c>
       <c r="M143" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N143" s="17" t="inlineStr"/>
@@ -20870,7 +22261,16 @@
           <t>https://attack.mitre.org/techniques/T1531</t>
         </is>
       </c>
-      <c r="AF143" s="17" t="inlineStr"/>
+      <c r="AF143" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- IAM 사용자·역할 삭제, 다수 계정 비밀번호·MFA 강제 변경, SaaS 권한 대량 회수
+- 관리자 계정의 비정상 잠금·삭제
+■ 대응
+- 계정 삭제·대량 변경에 승인·알림, 관리자 계정 보호와 복구 경로 분리
+- 변경 불가 감사 로그와 긴급 접근(break-glass) 계정 보존</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="17" t="inlineStr">
@@ -20895,16 +22295,20 @@
       </c>
       <c r="E144" s="17" t="inlineStr">
         <is>
-          <t>공격자는 시스템, 서비스, 네트워크 리소스의 가용성을 방해하기 위해 특정 시스템이나 네트워크 전반의 데이터와 파일을 대량으로 파괴할 수 있다. 데이터 파괴는 로컬·원격 드라이브의 파일이나 데이터를 덮어써서 포렌식 기법으로도 복구할 수 없게 만드는 경우가 많다. del이나 rm 같은 일반적인 운영체제 파일 삭제 명령은 파일 내용을 지우지 않고 파일 포인터만 제거하는 경우가 많아 적절한 포렌식 방법으로 복구할 수 있다. 이 행위는 저장 디스크의 영역이나 디스크의 논리 구조가 아니라 개별 파일을 파괴한다는 점에서 디스크 콘텐츠 삭제(Disk Content Wipe), 디스크 구조 삭제(Disk Structure Wipe)와 구별된다.</t>
+          <t>- 공격자는 클라우드 스토리지 객체·머신 이미지·DB 인스턴스·백업을 대량 삭제해 가용성을 파괴할 수 있음
+- 복구 불가능하게 지우며, 웜 기능으로 전파되거나 랜섬·갈취의 압박 수단으로 쓰임</t>
         </is>
       </c>
       <c r="F144" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 5건)
-- TeamPCP(G1056) — Kubernetes [컨테이너·K8s]
-- CanisterWorm(S9042) — Containers 플랫폼 소프트웨어 [컨테이너·K8s]
-- Mini Shai-Hulud(S9043) — GitHub·GitLab [SaaS·협업]
-- Shai-Hulud(S9008) — SaaS 플랫폼 소프트웨어 [SaaS·협업]</t>
+          <t>■ 클라우드 관점
+- AWS: RDS 인스턴스·백업 삭제(T1485.A001), AMI 등록 해제(A002), S3 객체·버킷 삭제·버저닝 변경(A003) — 재해 복구·시스템 복원 자산을 노림
+- K8s: 권한 있는 DaemonSet으로 클러스터 파일·리소스 삭제(MS-TA9038)
+- 개별 파일 파괴에 초점(디스크 와이프와 구분), 수명주기 정책 악용 삭제(CTC-IM-02.1)가 하위 변형
+■ 실제 사례
+- [ATT&amp;CK 사례] TeamPCP: 권한 있는 DaemonSet으로 K8s 클러스터 파일 삭제, 비컨테이너 호스트에 재귀 삭제 (ATT&amp;CK G1056)
+- [ATT&amp;CK 사례] Shai-Hulud: 사용자 홈 디렉터리의 쓰기 가능한 파일을 덮어쓰고 삭제, Linux에서 shred 사용 (ATT&amp;CK S9008)
+- [ATT&amp;CK 사례] LAPSUS$: 온프레미스·클라우드의 시스템·리소스 삭제 (ATT&amp;CK G1004)</t>
         </is>
       </c>
       <c r="G144" s="17" t="inlineStr">
@@ -20935,7 +22339,7 @@
       </c>
       <c r="M144" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N144" s="17" t="inlineStr"/>
@@ -21003,7 +22407,16 @@
           <t>https://attack.mitre.org/techniques/T1485</t>
         </is>
       </c>
-      <c r="AF144" s="17" t="inlineStr"/>
+      <c r="AF144" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 스토리지 객체·버킷·스냅샷·DB·AMI 대량 삭제(DeleteObject·DeleteDBInstance·DeregisterImage 등)
+- 권한 있는 DaemonSet의 파일 삭제, 재귀 삭제·와이프 패턴
+■ 대응
+- 버전 관리·객체 잠금·삭제 방지(MFA Delete), 백업을 별도 계정에 불변 보존
+- 대량 삭제 알림과 삭제 권한 최소화</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="17" t="inlineStr">
@@ -21028,12 +22441,18 @@
       </c>
       <c r="E145" s="17" t="inlineStr">
         <is>
-          <t>공격자는 클라우드 스토리지 버킷의 수명 주기 정책을 수정해 버킷에 저장된 모든 객체를 파괴할 수 있다.</t>
+          <t>- 공격자는 스토리지 버킷의 수명주기 정책을 수정해 저장 객체 전체를 자동 삭제되게 만들 수 있음
+- 하루 뒤 전체 삭제 같은 정책을 걸어 한 번에 파괴하며, 로그 버킷에 적용하면 흔적 제거에도 쓰임</t>
         </is>
       </c>
       <c r="F145" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- AWS: PutLifecycleConfiguration 권한으로 S3 버킷에 '1일 후 전체 삭제' 정책 적용(AWS TTC T1485.001) — 직접 삭제보다 눈에 덜 띔
+- 갈취·금전 탈취(CTC-IM-07) 목적뿐 아니라 로그 버킷에 적용해 흔적 제거(CTC-ST-02)로도 활용
+- 버전 관리·객체 잠금(Object Lock)·삭제 방지가 핵심 방어
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB·ATT&amp;CK 클라우드 사례에 이 하위기법으로 매핑된 건은 없음(벤더 문서화 수준)</t>
         </is>
       </c>
       <c r="G145" s="17" t="inlineStr">
@@ -21064,7 +22483,7 @@
       </c>
       <c r="M145" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N145" s="17" t="inlineStr"/>
@@ -21125,7 +22544,15 @@
           <t>https://attack.mitre.org/techniques/T1485/001</t>
         </is>
       </c>
-      <c r="AF145" s="17" t="inlineStr"/>
+      <c r="AF145" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 버킷 수명주기 정책 생성·변경(PutBucketLifecycleConfiguration), 짧은 만료 기간 설정
+■ 대응
+- 수명주기 정책 변경 권한 최소화·알림, 객체 잠금·버전 관리로 자동 삭제 무력화
+- 로그 버킷에 불변 보존 적용</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="17" t="inlineStr">
@@ -21150,16 +22577,20 @@
       </c>
       <c r="E146" s="17" t="inlineStr">
         <is>
-          <t>공격자는 시스템과 네트워크 리소스의 가용성을 방해하기 위해 대상 시스템이나 네트워크 내 다수 시스템의 데이터를 암호화할 수 있다. 로컬·원격 드라이브의 파일이나 데이터를 암호화하고 복호화 키를 넘겨주지 않는 방식으로 저장된 데이터에 접근하지 못하게 만들 수 있다. 이는 복호화나 복호화 키를 대가로 피해자에게 금전을 요구하기 위해서(랜섬웨어) 하거나, 키를 저장하거나 전송하지 않아 데이터를 영구히 접근 불가능하게 만들기 위해 할 수 있다.</t>
+          <t>- 공격자는 VM·스토리지·DB의 데이터를 암호화해 가용성을 차단하고 복호화 대가로 금전을 요구할 수 있음
+- ESXi·하이퍼바이저 대량 암호화나 SSE-C 같은 클라우드 네이티브 암호화를 악용하며, 웜 기능으로 네트워크 전반에 전파됨</t>
         </is>
       </c>
       <c r="F146" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례(사고 DB)
-- [실제 사고] DragonForce Exploits SimpleHelp Vulnerabilities in Ransomware Campaign(2025-05, INC-0514): DragonForce가 MSP의 SimpleHelp 인스턴스에 접근해, 원격관리 기능으로 고객 환경에 악성 설치 파일을 배포했다. 이 설치 파일로 자격증명 수집, 네트워크 정찰, 랜섬웨어 배포가 이루어졌다.
-- [실제 사고] CrazyHunter Ransomware Group Targets Critical Sectors in Taiwan(2025-04, INC-0495): 신생 랜섬웨어 그룹 CrazyHunter가 대만의 의료, 교육, 제조 등 핵심 부문을 집중 공격한 캠페인이다.
-- [실제 사고] Black Basta Exploiting Vulnerabilities in Multiple Products(2025-02, INC-0464): 2025년 2월 11일 Black Basta 내부 채팅 로그가 대량 유출되어 내부 갈등, 리더십 불안정, 금융 사기 정황이 드러났다(제목상 다수 제품 취약점 악용 캠페인).
-- 외 8건(관련 사례 ID 열)</t>
+          <t>■ 클라우드 관점
+- AWS: SSE-C로 S3 객체 암호화(T1486.A001), EC2/EBS 암호화 설정 조작(A002), RDS 스냅샷 암호화(A003) — 공격자 키로 암호화해 복구 차단
+- ESXi·vCenter 대량 암호화가 특히 파괴적이며, 하이브리드 환경에서 온프레미스→클라우드로 확산
+- 복구 억제(CTC-IM-08)·데이터 파괴(CTC-IM-02)와 결합되는 랜섬웨어의 최종 단계
+■ 실제 사례
+- [실제 사고] 침해 AWS 자격증명 SSE-C 랜섬(2025-01): S3 SSE-C 암호화를 악용해 데이터를 암호화하고 몸값 요구 (사고DB INC-0446)
+- [실제 사고] Storm-0501 하이브리드 랜섬(2024-09): 온프레미스→클라우드 횡적 이동 후 데이터 유출·랜섬웨어 배포 (사고DB INC-0395)
+- [실제 사고] ESXi 취약점 랜섬(2024-07): CVE-2024-37085로 도메인 가입 ESXi 관리 권한을 얻어 파일시스템 암호화 (사고DB INC-0372)</t>
         </is>
       </c>
       <c r="G146" s="17" t="inlineStr">
@@ -21190,7 +22621,7 @@
       </c>
       <c r="M146" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N146" s="17" t="inlineStr"/>
@@ -21262,7 +22693,16 @@
           <t>https://attack.mitre.org/techniques/T1486</t>
         </is>
       </c>
-      <c r="AF146" s="17" t="inlineStr"/>
+      <c r="AF146" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- SSE-C 암호화 PUT/Copy, EBS·RDS 암호화 설정·스냅샷 조작, 대량 파일 암호화·확장자 변경
+- ESXi·vCenter에서의 대량 암호화 행위
+■ 대응
+- 백업 불변 보존·오프라인 사본, SSE-C 사용 제한·키 관리 통제
+- 대량 암호화 탐지와 ESXi 접근 강화, 신속 격리·복구 체계</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="17" t="inlineStr">
@@ -21287,13 +22727,18 @@
       </c>
       <c r="E147" s="17" t="inlineStr">
         <is>
-          <t>공격자는 기업 네트워크 내부나 외부에서 볼 수 있는 시각적 콘텐츠를 변조해 원본 콘텐츠의 무결성에 영향을 줄 수 있다. 변조(Defacement)의 목적에는 메시지 전달, 위협, 침입에 대한 (거짓일 수 있는) 공적 주장 등이 있다. 사용자에게 불쾌감을 주거나 함께 게시한 메시지에 따르도록 압박하기 위해 불쾌하거나 혐오스러운 이미지를 사용할 수도 있다.</t>
+          <t>- 공격자는 외부 노출 웹사이트·리소스의 시각적 콘텐츠를 변조하거나 하위 도메인을 탈취해 메시지 전달·협박·선전을 할 수 있음
+- 방치된 DNS 레코드가 가리키는 리소스를 재프로비저닝해 콘텐츠를 장악하며, 시스템 신뢰를 떨어뜨림</t>
         </is>
       </c>
       <c r="F147" s="17" t="inlineStr">
         <is>
-          <t>■ 통합된 기법
-- T1491.002 External Defacement</t>
+          <t>■ 클라우드 관점
+- 하위 도메인 탈취: 삭제된 클라우드 리소스를 여전히 가리키는 DNS 레코드(Route 53 등)를 공격자가 재프로비저닝해 콘텐츠 장악(AWS TTC T1491.A001)
+- 외부 노출 웹사이트 변조로 선전·협박 — 통합된 상위기법(T1491.002 외부 변조) 근거 포함
+- 미사용 DNS 레코드 정리와 리소스 소유권 검증이 핵심 방어
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB·ATT&amp;CK 클라우드 사례에 매핑된 건은 없음(벤더·ATT&amp;CK 문서화 수준)</t>
         </is>
       </c>
       <c r="G147" s="17" t="inlineStr">
@@ -21328,7 +22773,7 @@
       </c>
       <c r="M147" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N147" s="17" t="inlineStr"/>
@@ -21390,7 +22835,15 @@
           <t>https://attack.mitre.org/techniques/T1491</t>
         </is>
       </c>
-      <c r="AF147" s="17" t="inlineStr"/>
+      <c r="AF147" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 외부 웹사이트 콘텐츠 변경, 방치 DNS 레코드가 가리키는 리소스 재생성(하위 도메인 탈취)
+■ 대응
+- 미사용 DNS 레코드 정리·소유권 검증, 웹 콘텐츠 무결성 모니터링
+- 리소스 삭제 시 DNS 레코드 동반 정리</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="17" t="inlineStr">
@@ -21415,12 +22868,18 @@
       </c>
       <c r="E148" s="17" t="inlineStr">
         <is>
-          <t>공격자는 대상 이메일 주소에 감당할 수 없을 만큼 많은 메시지를 퍼부을 수 있다. 이로 인해 정상 이메일이 스팸 더미에 묻히고 업무가 방해받을 수 있다.</t>
+          <t>- 공격자는 대상 이메일 주소에 대량 메시지를 퍼부어 정상 메일을 묻고 업무를 방해할 수 있음
+- 뉴스레터 자동 가입 등으로 수천 통을 발생시켜 보안 경고를 가리며, 이어지는 비싱의 사전 단계로도 쓰임</t>
         </is>
       </c>
       <c r="F148" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- M365·Workspace 사서함을 자동 가입 봇으로 폭주시켜 보안 알림·헬프데스크 티켓 등 정상 메일을 묻음
+- 비싱(CTC-IA-03.2)의 선행 단계로 결합 — 폭주 후 지원을 가장한 전화로 원격 도구 설치·자격증명 탈취 유도
+- 메일 폭주 탐지·격리와 가입 검증이 방어 요소
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB·ATT&amp;CK 클라우드 사례에 매핑된 건은 없음(기법 문서화 수준)</t>
         </is>
       </c>
       <c r="G148" s="17" t="inlineStr">
@@ -21451,7 +22910,7 @@
       </c>
       <c r="M148" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N148" s="17" t="inlineStr"/>
@@ -21508,7 +22967,16 @@
           <t>https://attack.mitre.org/techniques/T1667</t>
         </is>
       </c>
-      <c r="AF148" s="17" t="inlineStr"/>
+      <c r="AF148" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 짧은 시간 대량 수신 메일(뉴스레터 가입 폭주), 특정 사용자 대상 메일량 급증
+- 메일 폭주 직후의 비싱 전화 패턴
+■ 대응
+- 메일 폭주 탐지·격리·레이트 제한, 가입 확인(double opt-in) 활용
+- 폭주 중 보안 알림을 대체 채널로 전달</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="17" t="inlineStr">
@@ -21533,18 +23001,18 @@
       </c>
       <c r="E149" s="17" t="inlineStr">
         <is>
-          <t>공격자는 엔드포인트 서비스 거부(DoS) 공격으로 사용자에 대한 서비스 가용성을 떨어뜨리거나 차단할 수 있다. 엔드포인트 DoS는 서비스가 호스팅된 시스템의 자원을 고갈시키거나 시스템을 익스플로잇해 지속적인 중단 상태를 일으키는 방식으로 수행할 수 있다. 대상 서비스의 예로는 웹사이트, 이메일 서비스, DNS, 웹 기반 애플리케이션이 있다. 공격자가 정치적 목적으로, 또는 주의 분산, 핵티비즘, 금전 갈취 같은 다른 악의적 활동을 돕기 위해 DoS 공격을 수행한 사례가 관찰되었다.</t>
+          <t>- 공격자는 엔드포인트·네트워크 DoS로 클라우드 웹·API·DNS 서비스의 가용성을 떨어뜨리거나 차단할 수 있음
+- 자원 고갈 플러드·애플리케이션 익스플로잇·대역폭 플러드·반사 증폭을 쓰며, 봇넷·IP 스푸핑으로 추적과 필터링을 어렵게 함</t>
         </is>
       </c>
       <c r="F149" s="17" t="inlineStr">
         <is>
-          <t>■ 통합된 기법
-- T1499.002 Service Exhaustion Flood
-- T1499.003 Application Exhaustion Flood
-- T1499.004 Application or System Exploitation
-- T1498 Network Denial of Service
-- T1498.001 Direct Network Flood
-- T1498.002 Reflection Amplification</t>
+          <t>■ 클라우드 관점
+- 통합 범위: 엔드포인트 DoS(서비스·애플리케이션 고갈, 익스플로잇 크래시)와 네트워크 DoS(직접 플러드·반사 증폭)를 하나로 묶음
+- 클라우드 웹앱·API·DNS가 표적이며, 레이트 리밋 없는 API(CTC-IA-01 맥락)는 자원 고갈에 취약
+- 자동 스케일링은 DoS를 과금 폭탄으로 전환할 수 있어 WAF·DDoS 보호가 필요 (K8s MS-TA9040)
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB·ATT&amp;CK 클라우드 사례에 매핑된 건은 없음(기법 문서화 수준). 자원 소모·과금 피해는 Resource Hijacking(CTC-IM-09)과 인접</t>
         </is>
       </c>
       <c r="G149" s="17" t="inlineStr">
@@ -21579,7 +23047,7 @@
       </c>
       <c r="M149" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N149" s="17" t="inlineStr"/>
@@ -21640,7 +23108,16 @@
           <t>https://attack.mitre.org/techniques/T1499</t>
         </is>
       </c>
-      <c r="AF149" s="17" t="inlineStr"/>
+      <c r="AF149" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 웹·API·DNS로의 트래픽 급증, 자원 고갈 플러드·반사 증폭 패턴, 애플리케이션 크래시 반복
+- 자동 스케일링 급증과 과금 급증
+■ 대응
+- WAF·DDoS 보호·레이트 리밋·스케일 상한, 반사 증폭 방지(출발지 검증)
+- 애플리케이션 패치와 자원 고갈 지점 보완</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="17" t="inlineStr">
@@ -21665,13 +23142,19 @@
       </c>
       <c r="E150" s="17" t="inlineStr">
         <is>
-          <t>공격자는 피해자가 해당 자원을 쓸 수 없게 만들면서 자신의 금전적 이득을 얻기 위해 금품 갈취, 사회공학, 기술적 탈취 등의 방법으로 대상의 금전 자원을 탈취할 수 있다. 금전 탈취는 랜섬웨어를 이용한 갈취, 비즈니스 이메일 침해(BEC)와 사기, 돼지 도살(pig butchering) 사기, 은행 해킹, 암호화폐 네트워크 악용 등 여러 대표적인 캠페인 유형의 최종 목표다.</t>
+          <t>- 공격자는 갈취·BEC·사기·암호화폐 악용으로 대상의 금전 자원을 직접 탈취할 수 있음
+- 침해 계정과 신뢰 주체 사칭으로 부정 이체를 유도하거나, 데이터 암호화·유출 후 공개 위협으로 금전을 요구함</t>
         </is>
       </c>
       <c r="F150" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 1건)
-- TeamPCP Cloud Stealer(S9041) — Containers, SaaS 플랫폼 소프트웨어 [SaaS·협업]</t>
+          <t>■ 클라우드 관점
+- 침해 M365·SaaS 계정과 사칭(CTC-ST-04.1)으로 BEC·부정 이체 유도, 랜섬웨어 암호화(CTC-IM-03)·유출 후 유출 사이트 공개 위협으로 갈취
+- 침해 환경의 암호화폐 지갑 파일 탐색(TeamPCP Cloud Stealer)으로 직접 탈취
+- 금전 탈취를 데이터 파괴 등 진짜 목적을 가리는 미끼로 쓰기도 함
+■ 실제 사례
+- [ATT&amp;CK 사례] TeamPCP Cloud Stealer: 파일시스템에서 Bitcoin·Monero 등 암호화폐 지갑 탐색 (ATT&amp;CK S9041)
+- 참고: BEC·갈취 사고는 사회공학(CTC-ST-04.1)·랜섬(CTC-IM-03)의 최종 목적으로 여러 사고에 나타남</t>
         </is>
       </c>
       <c r="G150" s="17" t="inlineStr">
@@ -21702,7 +23185,7 @@
       </c>
       <c r="M150" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N150" s="17" t="inlineStr"/>
@@ -21759,7 +23242,16 @@
           <t>https://attack.mitre.org/techniques/T1657</t>
         </is>
       </c>
-      <c r="AF150" s="17" t="inlineStr"/>
+      <c r="AF150" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 부정 이체·결제 변경 요청, 사칭 메일·BEC 패턴, 암호화폐 지갑 파일 탐색
+- 유출 후 공개 위협·갈취 메시지
+■ 대응
+- 송금·결제 변경 다중 승인·대역외 확인, BEC 탐지와 사칭 메일 차단
+- 지갑·결제 자격증명 보호와 사용자 교육</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="17" t="inlineStr">
@@ -21784,13 +23276,18 @@
       </c>
       <c r="E151" s="17" t="inlineStr">
         <is>
-          <t>공격자는 손상된 시스템의 복구를 막기 위해 복구를 돕는 내장 데이터를 삭제하고 관련 서비스를 끌 수 있다. 이로 인해 사용 가능한 백업과 복구 옵션에 접근하지 못하게 될 수 있다.</t>
+          <t>- 공격자는 스냅샷·백업·복원 지점·섀도 복사본을 삭제·비활성화해 암호화·파괴 후 복구를 막을 수 있음
+- 클라우드 백업 자격증명 삭제, ESXi 스냅샷 삭제·암호화로 복구 옵션을 없애 랜섬 압박을 키움</t>
         </is>
       </c>
       <c r="F151" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 1건)
-- Storm-0501(G1053) — Azure [IaaS]</t>
+          <t>■ 클라우드 관점
+- Azure: 백업 구성 삭제·soft-delete 비활성화(Azure ATRM AZT705), 스냅샷·복원 지점·스토리지 계정·백업 서비스 삭제
+- ESXi 스냅샷 삭제·암호화, 네트워크 장비 백업 펌웨어 삭제로 복구 불가 상태 유도
+- 데이터 파괴(CTC-IM-02)·암호화(CTC-IM-03)의 효과를 극대화하는 선행·병행 단계 — 백업 불변·삭제 방지가 핵심 방어
+■ 실제 사례
+- [ATT&amp;CK 사례] Storm-0501: 스냅샷·복원 지점·스토리지 계정·백업 서비스를 삭제해 복구·교정 차단 (ATT&amp;CK G1053)</t>
         </is>
       </c>
       <c r="G151" s="17" t="inlineStr">
@@ -21821,7 +23318,7 @@
       </c>
       <c r="M151" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N151" s="17" t="inlineStr"/>
@@ -21882,7 +23379,16 @@
           <t>https://attack.mitre.org/techniques/T1490</t>
         </is>
       </c>
-      <c r="AF151" s="17" t="inlineStr"/>
+      <c r="AF151" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 스냅샷·복원 지점·백업 서비스 삭제, soft-delete·백업 구성 비활성화
+- ESXi 스냅샷 삭제·암호화, 네트워크 장비 백업 펌웨어 삭제
+■ 대응
+- 백업 불변·삭제 방지·별도 계정 보존, soft-delete·논리적 삭제 방지 강제
+- 백업 삭제·구성 변경 알림과 복구 테스트</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="17" t="inlineStr">
@@ -21907,16 +23413,21 @@
       </c>
       <c r="E152" s="17" t="inlineStr">
         <is>
-          <t>공격자는 장악한 시스템의 자원을 이용해 자원을 많이 소모하는 작업을 수행할 수 있으며, 이는 시스템이나 호스팅된 서비스의 가용성에 영향을 줄 수 있다.</t>
+          <t>- 공격자는 장악한 클라우드 컴퓨팅 자원을 크립토마이닝·LLM 추론(LLMjacking)·SMS 발송·스팸에 악용해 과금·가용성 피해를 입힐 수 있음
+- 노출·약인증 서비스나 탈취 자격증명으로 대량 인스턴스·컨테이너·관리형 AI를 가동하며, 비용이 피해 계정에 청구됨</t>
         </is>
       </c>
       <c r="F152" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례(사고 DB)
-- [실제 사고] Cryptomining campaign targeting Linux SSH servers(2026-07, INC-0658): AhnLab ASEC이 확인한 크립토마이닝 캠페인이다. 약한 자격증명의 인터넷 노출 Linux SSH 서버를 무차별 대입으로 침해한 뒤, Go 기반 다운로더 등 다단계 악성 도구를 배포했다.
-- [실제 사고] Cryptojacking Campaign Targeting K8s Clusters(2026-06, INC-0649): 2026년 6월 13~23일 Realm C2 프레임워크로 Linux 호스트 수천 대를 침해한 캠페인이다. 대형 관리형 Kubernetes 클러스터를 주로 노렸으며, Argo Workflows와 Gogs 취약점으로 초기 접근해 크립토재킹을 수행했다.
-- [실제 사고] Internet-exposed SSH with weak credentials (LiteLLM-Proxy)(2026-06, INC-0635): 약한 자격증명의 인터넷 노출 SSH(LiteLLM-Proxy)로 침투했다. 공격자는 IAM CreateUser와 Bedrock InvokeModel을 시도했고, XMRig 채굴과 LLMjacking 가능성이 확인되었다(Darktrace 사례).
-- 외 124건(관련 사례 ID 열)</t>
+          <t>■ 클라우드 관점
+- 유형: 컴퓨트로 암호화폐 채굴(EC2·ECS·EKS·WorkSpaces, AWS TTC T1496.A006·A008·A010), SES로 스팸·발송(A001), Bedrock 등 관리형 LLM 무단 호출(LLMjacking, A007)
+- 진입: 인증 없는 노출 서비스(Ray·Open WebUI·LiteLLM-Proxy), 약인증 SSH, 공개 버킷 자격증명 — 침해 후 할당량 상향(CTC-DI-05.5)으로 규모 확대
+- CSA 2026은 LLMjacking 등 AI 자원 악용 맥락에서 SI-06으로 연계하나, 본 기법의 본질은 자원·과금 악용
+- 사고 DB에서 가장 많이 매핑된 기법(127건), 하위기법(CTC-IM-09.1~09.4)으로 세분
+■ 실제 사례
+- [실제 사고] Operation Bizarre Bazaar(2026-01): 노출 LLM·MCP 인프라를 노린 상업화된 LLMjacking 캠페인 (사고DB INC-0589)
+- [실제 사고] K8s 클러스터 크립토재킹(2026-06): Argo Workflows·Gogs 취약점으로 관리형 클러스터에 접근해 채굴 (사고DB INC-0649)
+- [실제 사고] ShadowRay 2.0(2025-11): 인증 없이 노출된 Ray 대시보드·Jobs API를 악용한 크립토마이닝 (사고DB INC-0579)</t>
         </is>
       </c>
       <c r="G152" s="17" t="inlineStr">
@@ -21947,7 +23458,7 @@
       </c>
       <c r="M152" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N152" s="17" t="inlineStr">
@@ -22030,7 +23541,16 @@
           <t>https://attack.mitre.org/techniques/T1496</t>
         </is>
       </c>
-      <c r="AF152" s="17" t="inlineStr"/>
+      <c r="AF152" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 비정상 대량 인스턴스·컨테이너 생성(RunInstances·ECS·EKS), Bedrock 등 LLM 대량 호출, SES 발송 급증
+- GPU·고사양 인스턴스 급증과 과금 급증, 노출 서비스(Ray·Open WebUI)로의 작업 투입
+■ 대응
+- 할당량·인스턴스 유형 상한과 리전 제한, 노출 AI·관리 서비스 인증 강제·비공개
+- 과금·사용량 이상 알림, SES·Bedrock 권한 최소화</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="17" t="inlineStr">
@@ -22055,15 +23575,20 @@
       </c>
       <c r="E153" s="17" t="inlineStr">
         <is>
-          <t>공격자는 장악한 시스템의 컴퓨팅 자원을 이용해 자원을 많이 소모하는 작업을 수행할 수 있으며, 이는 시스템이나 호스팅된 서비스의 가용성에 영향을 줄 수 있다.</t>
+          <t>- 공격자는 장악한 EC2·컨테이너·클러스터의 컴퓨팅 자원을 크립토마이닝에 악용해 가용성과 과금에 피해를 줄 수 있음
+- 노출 API로 컨테이너를 쉽게 배포·확장하며, 자원을 소진시켜 정상 워크로드를 지연·중단시킴</t>
         </is>
       </c>
       <c r="F153" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 3건)
-- TeamTNT(G0139) — Kubernetes, Docker [컨테이너·K8s]
-- Hildegard(S0601) — Containers, IaaS 플랫폼 소프트웨어 [IaaS]
-- Kinsing(S0599) — Containers 플랫폼 소프트웨어 [컨테이너·K8s]</t>
+          <t>■ 클라우드 관점
+- AWS: EC2 인스턴스 생성(T1496.A008)·ECS 서비스 가동(A006)으로 채굴, 노출 Docker·K8s API로 채굴 컨테이너 대량 배포·확장(CTC-IA-02 연계)
+- 침해 계정에 비용이 청구되며, 일부 채굴 악성코드는 경쟁 악성코드를 종료해 자원을 독점
+- 상위기법(CTC-IM-09.0)의 컴퓨트 변형 — 할당량 상향(CTC-DI-05.5)과 결합해 규모 확대
+■ 실제 사례
+- [ATT&amp;CK 사례] TeamTNT: Docker 컨테이너·K8s 클러스터에 XMRig를 배포해 채굴 (ATT&amp;CK G0139)
+- [ATT&amp;CK 사례] Hildegard: xmrig로 암호화폐 채굴 (ATT&amp;CK S0601)
+- [ATT&amp;CK 사례] Kinsing: 비트코인 채굴기 생성·실행 (ATT&amp;CK S0599)</t>
         </is>
       </c>
       <c r="G153" s="17" t="inlineStr">
@@ -22094,7 +23619,7 @@
       </c>
       <c r="M153" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N153" s="17" t="inlineStr">
@@ -22161,7 +23686,16 @@
           <t>https://attack.mitre.org/techniques/T1496/001</t>
         </is>
       </c>
-      <c r="AF153" s="17" t="inlineStr"/>
+      <c r="AF153" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 비정상 EC2·ECS·컨테이너 생성과 지속적 고CPU, 채굴 풀 도메인·스트라툼 프로토콜 통신
+- 노출 Docker·K8s API로의 컨테이너 대량 배포
+■ 대응
+- 인스턴스·컨테이너 생성 권한 최소화·유형 상한, 노출 API 비공개·인증 강제
+- CPU·과금 이상 알림과 채굴 풀 통신 차단</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="17" t="inlineStr">
@@ -22186,12 +23720,18 @@
       </c>
       <c r="E154" s="17" t="inlineStr">
         <is>
-          <t>공격자는 장악한 시스템의 네트워크 대역폭을 이용해 자원을 많이 소모하는 작업을 수행할 수 있으며, 이는 시스템이나 호스팅된 서비스의 가용성에 영향을 줄 수 있다.</t>
+          <t>- 공격자는 장악한 시스템의 네트워크 대역폭을 봇넷·프록시재킹·토렌트 시딩에 악용할 수 있음
+- 피해 IP·대역폭을 프록시웨어에 팔거나 DDoS에 쓰며, 불법 활동에 쓰여 평판 피해까지 유발함</t>
         </is>
       </c>
       <c r="F154" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- 침해한 클라우드 VM·컨테이너의 대역폭을 봇넷 DDoS(CTC-IM-06 연계)·악성 토렌트 시딩에 사용, 프록시재킹으로 IP·대역폭을 프록시웨어에 판매
+- 인터넷 전역 스캔으로 추가 표적 탐색 — 과금·가용성 피해에 더해 피해 조직 IP가 불법 활동에 연루되는 평판 피해
+- 상위기법(CTC-IM-09.0)의 대역폭 변형
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB·ATT&amp;CK 클라우드 사례에 이 하위기법으로 매핑된 건은 없음(기법 문서화 수준). 자원 악용 사고는 CTC-IM-09.0에 집계</t>
         </is>
       </c>
       <c r="G154" s="17" t="inlineStr">
@@ -22222,7 +23762,7 @@
       </c>
       <c r="M154" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N154" s="17" t="inlineStr">
@@ -22283,7 +23823,16 @@
           <t>https://attack.mitre.org/techniques/T1496/002</t>
         </is>
       </c>
-      <c r="AF154" s="17" t="inlineStr"/>
+      <c r="AF154" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 비정상 대역폭 급증·장기 외부 연결, 프록시웨어·토렌트 트래픽 패턴
+- 피해 IP의 스캔·DDoS 출발 흔적
+■ 대응
+- 아웃바운드 필터링·대역폭 이상 알림, 프록시웨어·토렌트 통신 차단
+- 침해 워크로드 격리와 평판 모니터링</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="17" t="inlineStr">
@@ -22308,12 +23857,18 @@
       </c>
       <c r="E155" s="17" t="inlineStr">
         <is>
-          <t>공격자는 메시징 서비스를 SMS 펌핑에 악용할 수 있으며, 이는 시스템이나 호스팅된 서비스의 가용성에 영향을 줄 수 있다. SMS 펌핑은 통신 사기의 한 유형으로, 위협 행위자가 먼저 통신 사업자로부터 전화번호 묶음을 확보한 뒤 피해자의 메시징 인프라를 이용해 그 번호들로 대량의 SMS를 보내는 방식이다. 위협 행위자는 자신이 확보한 번호로 SMS 트래픽을 발생시켜 통신 사업자로부터 대가를 받을 수 있다.</t>
+          <t>- 공격자는 피해자의 OTP·가입 폼이 쓰는 SMS 발송 인프라(Twilio·SNS·Cognito)를 악용해 자신이 확보한 고요율 번호로 대량 SMS를 발생시킬 수 있음
+- 통신 사업자로부터 대가를 받는 사기이며, 피해자는 급증한 SMS 비용과 통신 채널 과부하를 겪음</t>
         </is>
       </c>
       <c r="F155" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- 공개 웹 폼(OTP·계정 확인)이 뒤에서 호출하는 Amazon SNS·Cognito·Twilio를 악용 — cognito:SignUp·ForgotPassword·sns:Publish로 SMS 트래픽 유발(AWS TTC T1496.003)
+- 공격자가 확보한 고요율 번호로 발송을 유도해 수익을 얻고, 피해자에게 SMS 과금 급증·채널 과부하 발생
+- 상위기법(CTC-IM-09.0)의 메시징 변형 — 폼 레이트 제한·CAPTCHA·발송 상한이 방어 핵심
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB·ATT&amp;CK 클라우드 사례에 매핑된 건은 없음(벤더·ATT&amp;CK 문서화 수준)</t>
         </is>
       </c>
       <c r="G155" s="17" t="inlineStr">
@@ -22344,7 +23899,7 @@
       </c>
       <c r="M155" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N155" s="17" t="inlineStr">
@@ -22409,7 +23964,16 @@
           <t>https://attack.mitre.org/techniques/T1496/003</t>
         </is>
       </c>
-      <c r="AF155" s="17" t="inlineStr"/>
+      <c r="AF155" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- OTP·가입 폼의 비정상 대량 요청(cognito:SignUp·sns:Publish), 특정 번호대로의 SMS 급증
+- SMS 비용 급증
+■ 대응
+- 폼 레이트 제한·CAPTCHA·봇 방어, SMS 발송 상한·지역 제한
+- SNS·Cognito 권한 최소화와 비용 알림</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="17" t="inlineStr">
@@ -22434,12 +23998,19 @@
       </c>
       <c r="E156" s="17" t="inlineStr">
         <is>
-          <t>공격자는 침해한 SaaS(Software-as-a-Service) 애플리케이션을 이용해 자원을 많이 소모하는 작업을 수행할 수 있으며, 이는 호스팅된 서비스의 가용성에 영향을 줄 수 있다.</t>
+          <t>- 공격자는 침해한 SaaS·관리형 서비스(SES·SNS·SendGrid·Twilio, 관리형 LLM)를 자원 소모 작업에 악용할 수 있음
+- 대량 스팸·피싱 발송이나 리버스 프록시를 통한 LLMjacking으로 과금·할당량·가용성에 피해를 주며, 필요 시 서비스를 먼저 활성화함</t>
         </is>
       </c>
       <c r="F156" s="17" t="inlineStr">
         <is>
-          <t>■ 실제 사례 미확인 — ATT&amp;CK·벤더 매트릭스상 가능 기법</t>
+          <t>■ 클라우드 관점
+- 메일·메시징 서비스(SES·SNS·SendGrid·Twilio)로 대량 스팸·피싱(T1496.A001), 관리형 LLM(Amazon Bedrock) 무단 호출로 LLMjacking(A007)
+- 피해자가 이미 쓰는 서비스를 악용하거나, 플랫폼 일부인 서비스를 공격자가 먼저 활성화 — 과금 급증·할당량 소진·가용성 저하
+- AI 매트릭스 UT-30.2(과금 폭탄)와 연계되는 상위기법(CTC-IM-09.0)의 SaaS 변형
+■ 실제 사례
+- [실제 사고] SES 샌드박스 해제 악용(2025-09): 탈취 자격증명으로 지원 요청을 통해 SES 샌드박스를 풀고 피싱 발송에 악용 (사고DB INC-0554)
+- [실제 사고] LiteLLM-Proxy 노출 침해(2026-06): 약인증 SSH로 침투해 Bedrock InvokeModel을 시도, LLMjacking 가능성 확인 (사고DB INC-0635)</t>
         </is>
       </c>
       <c r="G156" s="17" t="inlineStr">
@@ -22470,7 +24041,7 @@
       </c>
       <c r="M156" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N156" s="17" t="inlineStr">
@@ -22541,7 +24112,16 @@
           <t>https://attack.mitre.org/techniques/T1496/004</t>
         </is>
       </c>
-      <c r="AF156" s="17" t="inlineStr"/>
+      <c r="AF156" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- SES·SNS 발송 급증, Bedrock 등 LLM 대량 호출, 비활성 서비스의 갑작스런 활성화
+- 리버스 프록시를 통한 LLM 접근 패턴
+■ 대응
+- 메일·메시징·LLM 서비스 권한 최소화·발송 상한, 샌드박스 해제·서비스 활성화 승인
+- 과금·호출량 이상 알림과 LLMjacking 탐지</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="17" t="inlineStr">
@@ -22566,13 +24146,18 @@
       </c>
       <c r="E157" s="17" t="inlineStr">
         <is>
-          <t>공격자는 시스템의 서비스를 중지하거나 비활성화해 정상 사용자가 해당 서비스를 쓸 수 없게 만들 수 있다. 중요한 서비스나 프로세스를 중지하면 침해 사고 대응을 방해하거나 멈추게 할 수 있고, 환경에 피해를 입히려는 공격자의 전체 목표에 도움이 될 수 있다.</t>
+          <t>- 공격자는 중요한 서비스·프로세스를 중지·비활성화해 가용성을 떨어뜨리고 사고 대응을 방해할 수 있음
+- 데이터 파괴·암호화 전 DB·메일·백업 서비스를 멈춰 효과를 키우며, 클라우드에서는 API로 서비스 접근을 차단하기도 함</t>
         </is>
       </c>
       <c r="F157" s="17" t="inlineStr">
         <is>
-          <t>■ ATT&amp;CK 사례(행위자, 총 1건)
-- Wizard Spider(G0102) — 클라우드(서비스 미상) [IaaS]</t>
+          <t>■ 클라우드 관점
+- 실행 중 잠긴 데이터 저장소(Exchange·SQL·ESXi VM)를 암호화·파괴하려 선행으로 서비스 중지
+- AWS: DisableAPIServiceAccess 등으로 Organization 신규 계정의 서비스 연결 역할 생성 차단 — 클라우드 서비스 접근 자체를 무력화
+- 데이터 파괴(CTC-IM-02)·암호화(CTC-IM-03)·복구 억제(CTC-IM-08)와 결합되는 랜섬 단계
+■ 실제 사례
+- [ATT&amp;CK 사례] Wizard Spider: 네트워크 암호화 전 taskkill·net으로 백업·카탈로그·클라우드 서비스 중지 (ATT&amp;CK G0102)</t>
         </is>
       </c>
       <c r="G157" s="17" t="inlineStr">
@@ -22603,7 +24188,7 @@
       </c>
       <c r="M157" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N157" s="17" t="inlineStr"/>
@@ -22660,7 +24245,16 @@
           <t>https://attack.mitre.org/techniques/T1489</t>
         </is>
       </c>
-      <c r="AF157" s="17" t="inlineStr"/>
+      <c r="AF157" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 중요 서비스·프로세스 중지(taskkill·net stop 등), 클라우드 서비스 접근 차단 API 호출
+- 데이터 저장소 서비스 중지 직후의 암호화·삭제
+■ 대응
+- 서비스 중지·비활성화 권한 최소화·알림, 중요 서비스 보호·자동 복구
+- 데이터 저장소 접근 변경 모니터링</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="17" t="inlineStr">
@@ -22685,13 +24279,18 @@
       </c>
       <c r="E158" s="17" t="inlineStr">
         <is>
-          <t>공격자는 일시 삭제(soft delete) 상태의 리소스를 찾아 복원한 뒤, 삭제될 예정이던 내용을 가져와 공격을 진전시킬 수 있다.</t>
+          <t>- 공격자는 일시 삭제(soft-delete) 상태의 VM·백업·스토리지·Key Vault 객체를 복원해, 삭제 예정이던 내용을 되살려 공격에 활용할 수 있음
+- 삭제로 끝난 것처럼 보이는 리소스가 복구 기간 동안 남아 있어, 자격증명·데이터를 다시 확보하는 경로가 됨</t>
         </is>
       </c>
       <c r="F158" s="17" t="inlineStr">
         <is>
-          <t>■ 통합된 기법
-- AZT704.3 Soft-Delete Recovery: Recovery Services Vault</t>
+          <t>■ 클라우드 관점
+- Azure의 soft-delete 보존 기간 동안 Recovery Services Vault의 VM 객체(AZT704.3), Key Vault 비밀·인증서(CTC-CA-03.1 연계), 스토리지 객체를 복원
+- ATT&amp;CK에 대응 기법이 없는 Azure 전용 항목(통합된 AZT704.3 포함)
+- 복구 기간 설정·접근 통제와 복원 이벤트 감사가 방어 핵심
+■ 실제 사례
+- 공개 사고 미확인 — 사고 DB에 매핑된 사고는 없음(Azure ATRM 문서화 수준). soft-delete 복구는 비밀 탈취(CTC-CA-03.1)·데이터 수집(CTC-CO-03)과 연계</t>
         </is>
       </c>
       <c r="G158" s="17" t="inlineStr">
@@ -22726,7 +24325,7 @@
       </c>
       <c r="M158" s="17" t="inlineStr">
         <is>
-          <t>기존 번역</t>
+          <t>사용자 입력</t>
         </is>
       </c>
       <c r="N158" s="17" t="inlineStr"/>
@@ -22788,7 +24387,15 @@
           <t>https://microsoft.github.io/Azure-Threat-Research-Matrix/Impact/AZT704/AZT704/</t>
         </is>
       </c>
-      <c r="AF158" s="17" t="inlineStr"/>
+      <c r="AF158" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- soft-delete 객체 복원(Recovery Services Vault·Key Vault·스토리지), 삭제 예정 리소스의 재활성화
+■ 대응
+- 복원 권한 최소화·복원 이벤트 알림, soft-delete 보존 기간·접근 통제
+- 삭제 예정 민감 리소스의 조기 영구 삭제·격리</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:AF158"/>
@@ -24494,7 +26101,8 @@
       </c>
       <c r="E23" s="17" t="inlineStr">
         <is>
-          <t>공격자는 환경 안의 피해 계정과 인스턴스에 대한 지속적인 접근을 유지하기 위해 클라우드 계정에 공격자가 제어하는 자격 증명을 추가할 수 있다.</t>
+          <t>- 공격자는 장악한 IAM 사용자·서비스 주체·앱에 자신의 액세스 키·비밀·인증서·SSH 키를 추가해 지속 접근 경로를 확보할 수 있음
+- 추가된 자격증명은 원 계정이 회수돼도 유효하고 MFA를 거치지 않으며, 대상이 고권한이면 권한 상승으로도 이어짐</t>
         </is>
       </c>
       <c r="F23" s="17" t="inlineStr">
@@ -24538,7 +26146,16 @@
       <c r="N23" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="O23" s="17" t="inlineStr"/>
+      <c r="O23" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 감사 로그의 CreateAccessKey·CreateLoginProfile·키페어 생성, 서비스 주체·앱 자격증명 추가 이벤트
+- 한 사용자에 다수 액세스 키 존재, 새 키가 낯선 출발지에서 즉시 사용되는 패턴
+■ 대응
+- 사용자당 액세스 키 수 제한·정기 회수, 자격증명 추가 권한(iam:CreateAccessKey 등) 최소화
+- 앱·서비스 주체 자격증명 추가에 대한 알림과 승인 절차</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="17" t="inlineStr">
@@ -24563,7 +26180,8 @@
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t>공격자는 자신이 제어하는 이메일 계정에 대한 지속적인 접근을 유지하기 위해 추가 권한 수준을 부여할 수 있다.</t>
+          <t>- 공격자는 Exchange Online·Google Workspace에서 사서함 위임·폴더 권한·앱 가장 권한을 부여해 다른 계정으로 대상 사서함을 계속 열람할 수 있음
+- 원 계정 비밀번호가 바뀌어도 위임 권한은 남아, 장기 첩보 수집과 BEC의 기반이 됨</t>
         </is>
       </c>
       <c r="F24" s="17" t="inlineStr">
@@ -24607,7 +26225,16 @@
       <c r="N24" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="O24" s="17" t="inlineStr"/>
+      <c r="O24" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- Add-MailboxPermission·위임 추가, 폴더에 Default·Anonymous 권한 부여, 서비스 주체 가장 권한 부여 이벤트
+- 사용자 로그인 없이 서비스 주체로 다수 사서함을 조회하는 패턴
+■ 대응
+- 사서함 위임·가장 권한 정기 검토와 최소화, ApplicationImpersonation 범위 제한
+- 고권한 역할 부여 알림과 조건부 액세스 적용</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="17" t="inlineStr">
@@ -24632,7 +26259,8 @@
       </c>
       <c r="E25" s="17" t="inlineStr">
         <is>
-          <t>공격자는 테넌트에 대한 지속적인 접근을 유지하기 위해 자신이 제어하는 클라우드 계정에 역할이나 권한을 추가할 수 있다. 예를 들어 클라우드 환경에서 IAM 정책을 수정하거나 Office 365 환경에 새 전역 관리자를 추가할 수 있다. 권한이 충분하면 침해된 계정이 데이터와 설정에 거의 무제한으로 접근할 수 있다(다른 관리자의 비밀번호 재설정 포함).</t>
+          <t>- 공격자는 장악·생성한 클라우드 계정에 IAM 역할·정책이나 전역 관리자 역할을 추가해 테넌트 전반에 지속 접근과 권한 상승을 확보할 수 있음
+- 피해 테넌트 밖의 공격자 계정에 역할을 부여하면 계정 생성·수정 없이도 내부 작업이 가능해 추적이 어려움</t>
         </is>
       </c>
       <c r="F25" s="17" t="inlineStr">
@@ -24676,7 +26304,16 @@
       <c r="N25" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="O25" s="17" t="inlineStr"/>
+      <c r="O25" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- IAM 정책 연결·역할 생성·AssumeRolePolicy 변경, elevateAccess, 전역 관리자 추가 이벤트
+- 외부 계정을 신뢰 주체로 추가하는 역할 신뢰 정책 변경, cluster-admin 바인딩 생성
+■ 대응
+- 권한 변경을 PR·승인 워크플로로 통제, 고권한 역할 부여에 PIM·다중 승인
+- 외부 신뢰 계정 허용 목록화, RBAC 정기 검토</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="17" t="inlineStr">
@@ -24701,7 +26338,8 @@
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t>공격자는 SSH authorized_keys 파일을 수정해 피해 호스트에서 지속성을 유지할 수 있다. Linux 배포판, macOS, ESXi 하이퍼바이저는 원격 관리용 SSH 세션의 인증 과정을 보호하기 위해 보통 키 기반 인증을 사용한다. SSH의 authorized_keys 파일은 해당 파일이 설정된 사용자 계정에 로그인할 때 쓸 수 있는 SSH 키를 지정한다. 이 파일은 보통 사용자 홈 디렉터리의 &lt;user-home&gt;/.ssh/authorized_keys에 있다(ESXi는 /etc/ssh/keys-&lt;username&gt;/authorized_keys). 사용자는 시스템의 SSH 설정 파일에서 PubkeyAuthentication과 RSAAuthentication 지시어를 yes로 바꿔 공개 키 인증과 RSA 인증을 활성화하고, PermitRootLogin 지시어를 yes로 바꿔 SSH를 통한 root 인증을 허용할 수 있다. SSH 설정 파일은 보통 /etc/ssh/sshd_config에 있다.</t>
+          <t>- 공격자는 VM의 SSH authorized_keys를 클라우드 CLI·API로 수정해 자신의 공개키로 인스턴스에 지속 접근할 수 있음
+- 더 높은 권한 사용자에 키를 추가하면 권한 상승이 되며, 제어 평면 경유 변경이라 호스트 로그만으로는 탐지가 어려움</t>
         </is>
       </c>
       <c r="F26" s="17" t="inlineStr">
@@ -24745,7 +26383,16 @@
       <c r="N26" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O26" s="17" t="inlineStr"/>
+      <c r="O26" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 제어 평면의 VM 메타데이터·authorized_keys 변경(GCP set-metadata, Azure VM PATCH), EC2 키페어 투입 이벤트
+- VM 내 authorized_keys 파일 변경과 신규 키로의 SSH 로그인
+■ 대응
+- VM 메타데이터·키 변경 권한 최소화, OS Login·중앙 키 관리로 개별 키 투입 차단
+- 불변 인프라·구성 드리프트 점검으로 비인가 키 탐지</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="17" t="inlineStr">
@@ -24770,7 +26417,8 @@
       </c>
       <c r="E27" s="17" t="inlineStr">
         <is>
-          <t>공격자는 자신이 제어하는 계정에 장치를 등록할 수 있다. 장치는 네트워크 인증을 처리하는 다중 인증(MFA) 시스템이나, 장치 접근과 규정 준수를 관리하는 장치 관리 시스템에 등록될 수 있다.</t>
+          <t>- 공격자는 탈취한 자격증명으로 자신의 장치를 피해 계정의 MFA·장치 관리 시스템(Entra ID·Intune·Duo·Okta)에 등록해 지속 접근을 확보할 수 있음
+- 등록된 장치는 조건부 액세스의 '관리 장치' 조건을 충족해 이후 MFA·정책을 통과하고, 내부 발신 메일로 신뢰도 높은 피싱도 가능</t>
         </is>
       </c>
       <c r="F27" s="17" t="inlineStr">
@@ -24814,7 +26462,16 @@
       <c r="N27" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="O27" s="17" t="inlineStr"/>
+      <c r="O27" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 신규 MFA 장치·장치 등록 이벤트, 특히 비활성 계정·암호 추측 직후의 등록
+- 단기간 대량 장치 등록, 신규 등록 장치의 즉시 민감 리소스 접근
+■ 대응
+- 장치 등록에 추가 인증·관리자 승인, 조건부 액세스로 등록 가능 조건 제한
+- MFA 자가 등록 제한과 신규 장치 알림</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="17" t="inlineStr">
@@ -24839,7 +26496,8 @@
       </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t>공격자는 SaaS 환경의 OAuth 애플리케이션 통합을 이용해 지속성을 확보할 수 있다. 사용자 지정 애플리케이션을 만들거나, 정상 애플리케이션을 환경에 추가하거나, 기존 통합을 장악해 악의적 목적을 달성할 수 있다.</t>
+          <t>- 공격자는 SaaS 환경의 OAuth 앱 통합을 만들거나 장악해, 고권한 계정의 동의를 받아 메일·파일 데이터에 지속 접근할 수 있음
+- 앱 통합은 동의한 계정이 비활성화돼도 유효한 경우가 있고 앱 토큰으로 MFA를 우회해 자동 반출의 통로가 됨</t>
         </is>
       </c>
       <c r="F28" s="17" t="inlineStr">
@@ -24883,7 +26541,16 @@
       <c r="N28" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="O28" s="17" t="inlineStr"/>
+      <c r="O28" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 신규 OAuth 앱·연결 앱 등록과 고권한 위임 동의, 비검증 게시자 앱 추가
+- 앱 토큰으로 대량 메일·파일을 자동 조회하는 패턴
+■ 대응
+- 사용자 앱 동의 제한(관리자 승인), 과도한 위임 권한 차단, 앱 자격증명·권한 정기 검토
+- 사용하지 않는 통합 제거와 앱 활동 모니터링</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
@@ -24908,7 +26575,8 @@
       </c>
       <c r="E29" s="17" t="inlineStr">
         <is>
-          <t>공격자는 피해 시스템에 대한 접근을 유지하기 위해 클라우드 계정을 만들 수 있다. 접근 수준이 충분하면, 시스템에 지속적인 원격 접근 도구를 배포하지 않고도 자격 증명 기반의 보조 접근 경로를 확보하는 데 이런 계정을 쓸 수 있다.</t>
+          <t>- 공격자는 피해 테넌트에 새 클라우드 사용자·서비스 주체·게스트 계정을 만들어 자격증명 기반 보조 접근 경로를 확보할 수 있음
+- 특정 서비스만 쓰는 계정으로 만들면 탐지 가능성을 낮추며, 생성 후 역할·자격증명을 더해 지속성을 강화함</t>
         </is>
       </c>
       <c r="F29" s="17" t="inlineStr">
@@ -24952,7 +26620,16 @@
       <c r="N29" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="O29" s="17" t="inlineStr"/>
+      <c r="O29" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 사용자·서비스 주체·게스트 생성 이벤트, 특히 탈취 자격증명 사용 직후의 계정 생성
+- 신규 계정의 즉시 역할·키 추가, 특정 서비스 전용 권한만 가진 계정
+■ 대응
+- 계정 생성 권한 최소화·알림, 신규 계정 승인 절차
+- 게스트 초대 제한과 유휴 계정 정리</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="17" t="inlineStr">
@@ -24977,7 +26654,8 @@
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t>공격자는 개별 호스트에서 데몬, 에이전트, 서비스로 실행되는 컨테이너·컨테이너 클러스터 관리 도구를 만들거나 수정할 수 있다. 여기에는 Docker, Podman 같은 컨테이너 생성·관리 소프트웨어와 kubelet 같은 클러스터 노드 에이전트가 포함된다. 이러한 서비스를 수정하면 호스트에서 지속성을 확보하거나 권한을 높일 수 있다.</t>
+          <t>- 공격자는 컨테이너 런타임·노드 에이전트를 재시작 유지 설정으로 만들거나 수정해 호스트에서 지속성을 확보하고 권한을 높일 수 있음
+- DaemonSet·정적 파드·restart=always로 노드마다 자동 상주시키며, rootful Docker 접근은 그대로 호스트 권한 상승 경로가 됨</t>
         </is>
       </c>
       <c r="F30" s="17" t="inlineStr">
@@ -25017,7 +26695,16 @@
       <c r="N30" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O30" s="17" t="inlineStr"/>
+      <c r="O30" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- restart=always 상주 컨테이너, 신규 DaemonSet·정적 파드, kubelet manifest 디렉터리 변경
+- 노드에 반복 재생성되는 컨테이너와 외부 통신
+■ 대응
+- 정책 엔진으로 위험 워크로드 차단, 정적 파드 경로·docker 소켓 접근 제한
+- rootless 컨테이너 전환과 노드 파일 무결성 점검</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="17" t="inlineStr">
@@ -25042,7 +26729,8 @@
       </c>
       <c r="E31" s="17" t="inlineStr">
         <is>
-          <t>공격자는 특정 이벤트를 계기로 실행을 일으키는 시스템 메커니즘을 이용해 지속성을 확보하거나 권한을 높일 수 있다. 여러 운영체제에는 로그온이나 특정 애플리케이션·바이너리 실행 같은 사용자 활동 이벤트를 모니터링하고 구독하는 수단이 있다. 클라우드 환경도 특정 클라우드 이벤트를 모니터링하고 이에 대응해 호출되는 다양한 함수와 서비스를 지원할 수 있다.</t>
+          <t>- 공격자는 클라우드 이벤트에 반응하는 함수·웹훅·정책(이벤트 규칙·HTTP 트리거 등)을 등록해 지속성과 권한 상승을 확보할 수 있음
+- 트리거는 관리 ID·서비스 계정 권한으로 실행되고 특정 조건에서만 발동해, 상시 프로세스가 없어 탐지가 어려움</t>
         </is>
       </c>
       <c r="F31" s="17" t="inlineStr">
@@ -25082,7 +26770,16 @@
       <c r="N31" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="O31" s="17" t="inlineStr"/>
+      <c r="O31" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 이벤트 규칙·HTTP 트리거·웹훅·Watcher·정책(DeployIfNotExists) 생성·변경 이벤트
+- 어드미션 컨트롤러·EKS 구성 변경, 트리거가 관리 ID로 수행하는 비정상 작업
+■ 대응
+- 이벤트·정책·자동화 리소스 수정 권한 최소화, 인증 없는 트리거 금지
+- 자동화·정책 목록 정기 검토와 변경 알림</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
@@ -25182,7 +26879,8 @@
       </c>
       <c r="E33" s="17" t="inlineStr">
         <is>
-          <t>공격자는 환경에 접근한 뒤 지속성을 확보하기 위해 클라우드 이미지나 컨테이너 이미지에 악성 코드를 심을 수 있다. AWS의 AMI(Amazon Machine Image), GCP 이미지, Azure 이미지와 Docker 같은 대중적인 컨테이너 런타임 이미지에 악성 코드나 백도어를 심을 수 있다. 악성코드 업로드(Upload Malware)와 달리 이 기법은 공격자가 피해자 환경의 레지스트리에 이미지를 심는 데 초점을 둔다. 인프라 프로비저닝 방식에 따라, 프로비저닝 도구가 항상 최신 이미지를 쓰도록 설정되어 있으면 지속적인 접근을 제공할 수 있다.</t>
+          <t>- 공격자는 피해 환경의 이미지 레지스트리에 악성코드·웹셸을 심은 클라우드·컨테이너 이미지를 저장해 지속성을 확보할 수 있음
+- 프로비저닝 도구가 항상 최신 이미지를 쓰도록 설정돼 있으면 새 인스턴스·파드가 생길 때마다 백도어가 재배포됨</t>
         </is>
       </c>
       <c r="F33" s="17" t="inlineStr">
@@ -25226,7 +26924,16 @@
       <c r="N33" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O33" s="17" t="inlineStr"/>
+      <c r="O33" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 내부 레지스트리 이미지 푸시·태그 변경, 기준에서 벗어난 레이어·웹셸 포함 이미지
+- 프로비저닝이 참조하는 최신 태그 이미지의 예기치 않은 변경
+■ 대응
+- 레지스트리 푸시 권한 최소화·이미지 서명 검증, 배포 시 서명·스캔 통과 이미지만 허용
+- 태그 고정(다이제스트 핀)과 이미지 취약점·악성코드 스캔</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="17" t="inlineStr">
@@ -25251,7 +26958,8 @@
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t>공격자는 침해한 계정에 지속적으로 접근하기 위해 다중 인증(MFA) 메커니즘을 비활성화하거나 수정할 수 있다.</t>
+          <t>- 공격자는 침해 계정 유지를 위해 MFA를 비활성화하거나 취약한 MFA 수단으로 교체할 수 있으며, 탈취한 세션 토큰으로 MFA 자체를 건너뛰기도 함
+- 조건부 액세스에서 사용자 제외·'실패 시 허용(fail open)' 설정을 악용하면 계정 단위를 넘어 그룹 전체의 MFA가 무력화됨</t>
         </is>
       </c>
       <c r="F34" s="17" t="inlineStr">
@@ -25295,7 +27003,16 @@
       <c r="N34" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="O34" s="17" t="inlineStr"/>
+      <c r="O34" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- MFA 비활성화·조건부 액세스 제외·MFA 수단 변경 이벤트, 같은 세션 토큰의 다른 IP 재사용
+- 'fail open' 구성과 MFA 요구가 사라진 로그인 성공
+■ 대응
+- 피싱 저항형 MFA(FIDO2)와 'fail open' 금지, MFA·조건부 액세스 변경에 다중 관리자 승인
+- 토큰 보호·세션 수명 단축, 의심 세션 토큰 즉시 폐기</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="17" t="inlineStr">
@@ -25320,7 +27037,8 @@
       </c>
       <c r="E35" s="17" t="inlineStr">
         <is>
-          <t>공격자는 일반 인증 메커니즘을 우회하고, 자격 증명에 접근하고, 계정에 지속적으로 접근하기 위해 온프레미스 사용자 ID와 연결된 클라우드 인증 절차에 패치를 적용하거나, 이를 수정하거나, 백도어를 심을 수 있다.</t>
+          <t>- 공격자는 온프레미스-클라우드 하이브리드 ID 연결(PHS·PTA·AD FS)에 백도어를 심어 모든 인증을 통과시키고 자격증명을 수집할 수 있음
+- 연동 지점 하나를 장악하면 페더레이션된 모든 클라우드·SaaS에 지속적 특권 접근이 가능해 피해 범위가 테넌트 전체로 확대됨</t>
         </is>
       </c>
       <c r="F35" s="17" t="inlineStr">
@@ -25364,7 +27082,16 @@
       <c r="N35" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="O35" s="17" t="inlineStr"/>
+      <c r="O35" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- PTA 에이전트·AD FS 서버의 DLL 로드·구성 파일 변경, 토큰 서명 인증서의 비정상 사용
+- 온프레미스 조인 서버에서 발급된 토큰의 광범위한 클라우드 접근
+■ 대응
+- 하이브리드 ID 연동 서버를 Tier0로 취급·접근 최소화, 토큰 서명 인증서 보호·정기 교체
+- AD FS → 클라우드 인증의 이상 토큰 탐지, 가능 시 클라우드 인증으로 전환</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="17" t="inlineStr">
@@ -25389,7 +27116,8 @@
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
-          <t>공격자는 침해한 계정에 지속적으로 접근하기 위해 조건부 액세스 정책을 비활성화하거나 수정할 수 있다. 조건부 액세스 정책은 ID 공급자와 ID·접근 관리 시스템이 사용자에게 리소스 접근을 허용할지 판단할 때 쓰는 추가 검증이다.</t>
+          <t>- 공격자는 조건부 액세스·IAM 조건 정책을 수정해(신뢰 IP 추가, MFA 요구 제거, 허용 리전 확대) 침해 계정의 접근을 지속할 수 있음
+- 정책 완화는 정상 관리 변경처럼 보여, 이후 탈취 자격증명이 통제를 그대로 통과하게 만듦</t>
         </is>
       </c>
       <c r="F36" s="17" t="inlineStr">
@@ -25433,7 +27161,16 @@
       <c r="N36" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="O36" s="17" t="inlineStr"/>
+      <c r="O36" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 조건부 액세스·IAM 조건 정책 변경(신뢰 IP 추가·MFA 제거·리전 확대) 이벤트
+- 정책 완화 직후 새 위치·리전에서의 로그인 성공
+■ 대응
+- 조건부 액세스·IAM 정책 변경에 승인 워크플로와 변경 알림
+- 정책을 코드로 관리(IaC)하고 드리프트 자동 복원</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="17" t="inlineStr">
@@ -25458,7 +27195,8 @@
       </c>
       <c r="E37" s="17" t="inlineStr">
         <is>
-          <t>공격자는 Microsoft Office 템플릿을 악용해 침해한 시스템에서 지속성을 확보할 수 있다. Microsoft Office에는 일반 Office 애플리케이션에 포함되어 스타일을 사용자 지정하는 데 쓰이는 템플릿이 있다. 애플리케이션의 기본 템플릿은 애플리케이션이 시작될 때마다 사용된다.</t>
+          <t>- 공격자는 M365 Office의 기본 템플릿(Normal.dotm 등)에 악성 VBA 매크로를 넣어 Office 실행 때마다 코드가 돌게 할 수 있음
+- 공유 템플릿을 원격에서 가져오게 하거나 GlobalDotName을 바꿔 임의 템플릿을 로드시키는 변형이 있음</t>
         </is>
       </c>
       <c r="F37" s="17" t="inlineStr">
@@ -25498,7 +27236,15 @@
       <c r="N37" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O37" s="17" t="inlineStr"/>
+      <c r="O37" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- Normal.dotm 등 기본 템플릿 변경, GlobalDotName 레지스트리 변경, 원격 템플릿 로드
+- Office 프로세스의 매크로 기반 자식 프로세스 생성
+■ 대응
+- 신뢰 위치 외 매크로 차단·인터넷 출처 매크로 차단 정책(M365), 템플릿 파일 무결성 점검</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="17" t="inlineStr">
@@ -25523,7 +27269,8 @@
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t>공격자는 Microsoft Office의 Office Test 레지스트리 키를 악용해 침해한 시스템에서 지속성을 확보할 수 있다. Office Test 레지스트리 위치를 이용하면 Office 애플리케이션이 시작될 때마다 실행될 임의의 DLL을 지정할 수 있다. 이 레지스트리 키는 Microsoft가 Office 애플리케이션을 개발하면서 테스트와 디버깅용 DLL을 불러오는 데 쓰는 것으로 알려져 있으며, Office 설치 시 기본으로 생성되지는 않는다.</t>
+          <t>- 공격자는 Office Test 레지스트리 키에 악성 DLL을 지정해 Office 실행 때마다 로드되게 할 수 있음
+- 기본 생성되지 않는 키라 존재 자체가 이상 징후이며, 단말 지속성 수단으로 쓰임</t>
         </is>
       </c>
       <c r="F38" s="17" t="inlineStr">
@@ -25563,7 +27310,14 @@
       <c r="N38" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O38" s="17" t="inlineStr"/>
+      <c r="O38" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- Office test\Special\Perf 레지스트리 키 생성과 지정 DLL 로드
+■ 대응
+- 해당 레지스트리 키 모니터링·차단, 단말 EDR로 Office의 비정상 DLL 로드 탐지</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="17" t="inlineStr">
@@ -25588,7 +27342,8 @@
       </c>
       <c r="E39" s="17" t="inlineStr">
         <is>
-          <t>공격자는 Microsoft Outlook 양식(form)을 악용해 침해한 시스템에서 지속성을 확보할 수 있다. Outlook 양식은 Outlook 메시지의 표시와 기능을 정의하는 템플릿으로 쓰인다. 사용자 지정 Outlook 양식을 만들어 두면, 공격자가 같은 사용자 지정 양식을 이용해 특수하게 만든 이메일을 보낼 때 코드가 실행되게 할 수 있다.</t>
+          <t>- 공격자는 침해한 사서함에 악성 Outlook 양식을 심어, 특수 제작 메일을 받을 때 코드가 실행되게 지속성을 확보할 수 있음
+- 사서함에 저장되므로 단말을 재설치해도 남고, M365 사서함 침해 후 지속 수단으로 쓰임</t>
         </is>
       </c>
       <c r="F39" s="17" t="inlineStr">
@@ -25628,7 +27383,14 @@
       <c r="N39" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="O39" s="17" t="inlineStr"/>
+      <c r="O39" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 사서함의 사용자 지정 Outlook 양식 추가, Ruler 사용 흔적(비정상 EWS/MAPI 요청)
+■ 대응
+- 사용자 지정 양식 사용 제한, 사서함 규칙·양식 정기 감사, 사서함 권한 최소화</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="17" t="inlineStr">
@@ -25653,7 +27415,8 @@
       </c>
       <c r="E40" s="17" t="inlineStr">
         <is>
-          <t>공격자는 Microsoft Outlook의 홈페이지 기능을 악용해 침해한 시스템에서 지속성을 확보할 수 있다. Outlook 홈페이지는 Outlook 폴더의 표시 방식을 사용자 지정하는 레거시 기능으로, 폴더를 열 때마다 내부 또는 외부 URL을 불러와 표시할 수 있다. Outlook 홈페이지가 불러올 때 코드가 실행되도록 악성 HTML 페이지를 만들 수 있다.</t>
+          <t>- 공격자는 Outlook 홈페이지 기능에 악성 URL을 지정해, 해당 폴더를 열 때마다 원격 코드가 실행되게 할 수 있음
+- 사서함 설정에 저장되어 단말 재설치에도 남으며, M365 사서함 지속성 수단이 됨</t>
         </is>
       </c>
       <c r="F40" s="17" t="inlineStr">
@@ -25693,7 +27456,14 @@
       <c r="N40" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="O40" s="17" t="inlineStr"/>
+      <c r="O40" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 사서함의 Outlook 홈페이지 URL 설정 추가·변경
+■ 대응
+- 홈페이지 기능 비활성화(그룹 정책), 사서함 설정 변경 감사</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="17" t="inlineStr">
@@ -25718,7 +27488,8 @@
       </c>
       <c r="E41" s="17" t="inlineStr">
         <is>
-          <t>공격자는 Microsoft Outlook 규칙을 악용해 침해한 시스템에서 지속성을 확보할 수 있다. Outlook 규칙은 사용자가 이메일 메시지를 관리하는 자동 동작을 정의할 수 있게 한다. 예를 들어 정상적인 규칙은 특정 발신자의 이메일에 특정 단어가 있으면 Outlook의 특정 폴더로 자동 이동시킬 수 있다. 공격자가 특수하게 만든 이메일을 해당 사용자에게 보내면 코드가 실행되도록 악성 Outlook 규칙을 만들 수 있다.</t>
+          <t>- 공격자는 악성 Outlook 규칙을 만들어, 특수 제작 메일 수신을 조건으로 코드가 실행되게 지속성을 확보할 수 있음
+- 사서함에 저장되는 규칙이라 단말과 무관하게 유지되며, 메일 숨김 규칙과 함께 은닉에도 쓰임</t>
         </is>
       </c>
       <c r="F41" s="17" t="inlineStr">
@@ -25758,7 +27529,14 @@
       <c r="N41" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="O41" s="17" t="inlineStr"/>
+      <c r="O41" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 코드 실행과 연계된 Outlook 규칙 생성, Ruler 사용 흔적
+■ 대응
+- 클라이언트 측 규칙 제한, 사서함 규칙 정기 감사와 이상 규칙 알림</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="17" t="inlineStr">
@@ -25783,7 +27561,8 @@
       </c>
       <c r="E42" s="17" t="inlineStr">
         <is>
-          <t>공격자는 Microsoft Office 추가 기능(add-in)을 악용해 침해한 시스템에서 지속성을 확보할 수 있다. Office 추가 기능은 Office 프로그램에 기능을 더하는 데 쓰인다. 여러 Office 제품에서 쓸 수 있는 추가 기능 유형은 다양하며, Word/Excel 추가 기능 라이브러리(WLL/XLL), VBA 추가 기능, Office COM(Component Object Model) 추가 기능, 자동화 추가 기능, VBA 편집기(VBE), VSTO(Visual Studio Tools for Office) 추가 기능, Outlook 추가 기능 등이 있다.</t>
+          <t>- 공격자는 Office 추가 기능(WLL/XLL·VBA·COM·VSTO·Outlook 추가 기능 등)을 등록해 Office 실행 시 코드가 실행되게 할 수 있음
+- 정상 확장 기능으로 보여 탐지가 어렵고, M365 단말 지속성 수단으로 쓰임</t>
         </is>
       </c>
       <c r="F42" s="17" t="inlineStr">
@@ -25823,7 +27602,14 @@
       <c r="N42" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O42" s="17" t="inlineStr"/>
+      <c r="O42" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- Office 추가 기능(WLL/XLL·VSTO·COM 등) 신규 등록과 시작 시 로드
+■ 대응
+- 서명된 추가 기능만 허용, 추가 기능 설치 제한 정책 적용</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="17" t="inlineStr">
@@ -26156,7 +27942,8 @@
       </c>
       <c r="E47" s="17" t="inlineStr">
         <is>
-          <t>공격자는 클라우드 리소스에 대한 일시적으로 높은 접근 권한을 얻을 수 있는 권한 구성을 악용할 수 있다. 많은 클라우드 환경에서는 관리자가 사용자나 서비스 계정에 역할에 대한 JIT(Just-in-Time) 접근 요청, 다른 계정 가장, 리소스·서비스에 역할 전달 등 자신과 다른 권한 집합에 단기간 접근하는 권한을 부여할 수 있다.</t>
+          <t>- 공격자는 JIT 접근 요청·계정 가장·역할 전달 같은 일시적 권한 상승 기능을 악용해 자신에게 없는 권한을 단기간 획득할 수 있음
+- 정상적인 권한 위임 기능을 쓰므로 별도 역할 부여 흔적이 적고, 자동 승인 설정이면 즉시 상승이 가능함</t>
         </is>
       </c>
       <c r="F47" s="17" t="inlineStr">
@@ -26200,7 +27987,16 @@
       <c r="N47" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O47" s="17" t="inlineStr"/>
+      <c r="O47" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- PIM 역할 활성화, 서비스 계정 토큰 생성(serviceAccountTokenCreator), PassRole·역할 전달 이벤트
+- 활성화된 권한으로 수행되는 평소와 다른 고권한 작업
+■ 대응
+- JIT·가장·역할 전달 권한 최소화와 자동 승인 지양(수동 승인), 고권한 역할은 PIM·승인 연계
+- PassRole 대상 역할 범위 제한과 사용 감사</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="17" t="inlineStr">
@@ -26225,7 +28021,8 @@
       </c>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t>공격자는 환경 안의 피해 계정과 인스턴스에 대한 지속적인 접근을 유지하기 위해 클라우드 계정에 공격자가 제어하는 자격 증명을 추가할 수 있다.</t>
+          <t>- 공격자는 장악한 IAM 사용자·서비스 주체·앱에 자신의 액세스 키·비밀·인증서·SSH 키를 추가해 지속 접근 경로를 확보할 수 있음
+- 추가된 자격증명은 원 계정이 회수돼도 유효하고 MFA를 거치지 않으며, 대상이 고권한이면 권한 상승으로도 이어짐</t>
         </is>
       </c>
       <c r="F48" s="17" t="inlineStr">
@@ -26269,7 +28066,16 @@
       <c r="N48" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="O48" s="17" t="inlineStr"/>
+      <c r="O48" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 감사 로그의 CreateAccessKey·CreateLoginProfile·키페어 생성, 서비스 주체·앱 자격증명 추가 이벤트
+- 한 사용자에 다수 액세스 키 존재, 새 키가 낯선 출발지에서 즉시 사용되는 패턴
+■ 대응
+- 사용자당 액세스 키 수 제한·정기 회수, 자격증명 추가 권한(iam:CreateAccessKey 등) 최소화
+- 앱·서비스 주체 자격증명 추가에 대한 알림과 승인 절차</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="17" t="inlineStr">
@@ -26294,7 +28100,8 @@
       </c>
       <c r="E49" s="17" t="inlineStr">
         <is>
-          <t>공격자는 자신이 제어하는 이메일 계정에 대한 지속적인 접근을 유지하기 위해 추가 권한 수준을 부여할 수 있다.</t>
+          <t>- 공격자는 Exchange Online·Google Workspace에서 사서함 위임·폴더 권한·앱 가장 권한을 부여해 다른 계정으로 대상 사서함을 계속 열람할 수 있음
+- 원 계정 비밀번호가 바뀌어도 위임 권한은 남아, 장기 첩보 수집과 BEC의 기반이 됨</t>
         </is>
       </c>
       <c r="F49" s="17" t="inlineStr">
@@ -26338,7 +28145,16 @@
       <c r="N49" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="O49" s="17" t="inlineStr"/>
+      <c r="O49" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- Add-MailboxPermission·위임 추가, 폴더에 Default·Anonymous 권한 부여, 서비스 주체 가장 권한 부여 이벤트
+- 사용자 로그인 없이 서비스 주체로 다수 사서함을 조회하는 패턴
+■ 대응
+- 사서함 위임·가장 권한 정기 검토와 최소화, ApplicationImpersonation 범위 제한
+- 고권한 역할 부여 알림과 조건부 액세스 적용</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="17" t="inlineStr">
@@ -26363,7 +28179,8 @@
       </c>
       <c r="E50" s="17" t="inlineStr">
         <is>
-          <t>공격자는 테넌트에 대한 지속적인 접근을 유지하기 위해 자신이 제어하는 클라우드 계정에 역할이나 권한을 추가할 수 있다. 예를 들어 클라우드 환경에서 IAM 정책을 수정하거나 Office 365 환경에 새 전역 관리자를 추가할 수 있다. 권한이 충분하면 침해된 계정이 데이터와 설정에 거의 무제한으로 접근할 수 있다(다른 관리자의 비밀번호 재설정 포함).</t>
+          <t>- 공격자는 장악·생성한 클라우드 계정에 IAM 역할·정책이나 전역 관리자 역할을 추가해 테넌트 전반에 지속 접근과 권한 상승을 확보할 수 있음
+- 피해 테넌트 밖의 공격자 계정에 역할을 부여하면 계정 생성·수정 없이도 내부 작업이 가능해 추적이 어려움</t>
         </is>
       </c>
       <c r="F50" s="17" t="inlineStr">
@@ -26407,7 +28224,16 @@
       <c r="N50" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="O50" s="17" t="inlineStr"/>
+      <c r="O50" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- IAM 정책 연결·역할 생성·AssumeRolePolicy 변경, elevateAccess, 전역 관리자 추가 이벤트
+- 외부 계정을 신뢰 주체로 추가하는 역할 신뢰 정책 변경, cluster-admin 바인딩 생성
+■ 대응
+- 권한 변경을 PR·승인 워크플로로 통제, 고권한 역할 부여에 PIM·다중 승인
+- 외부 신뢰 계정 허용 목록화, RBAC 정기 검토</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="17" t="inlineStr">
@@ -26432,7 +28258,8 @@
       </c>
       <c r="E51" s="17" t="inlineStr">
         <is>
-          <t>공격자는 SSH authorized_keys 파일을 수정해 피해 호스트에서 지속성을 유지할 수 있다. Linux 배포판, macOS, ESXi 하이퍼바이저는 원격 관리용 SSH 세션의 인증 과정을 보호하기 위해 보통 키 기반 인증을 사용한다. SSH의 authorized_keys 파일은 해당 파일이 설정된 사용자 계정에 로그인할 때 쓸 수 있는 SSH 키를 지정한다. 이 파일은 보통 사용자 홈 디렉터리의 &lt;user-home&gt;/.ssh/authorized_keys에 있다(ESXi는 /etc/ssh/keys-&lt;username&gt;/authorized_keys). 사용자는 시스템의 SSH 설정 파일에서 PubkeyAuthentication과 RSAAuthentication 지시어를 yes로 바꿔 공개 키 인증과 RSA 인증을 활성화하고, PermitRootLogin 지시어를 yes로 바꿔 SSH를 통한 root 인증을 허용할 수 있다. SSH 설정 파일은 보통 /etc/ssh/sshd_config에 있다.</t>
+          <t>- 공격자는 VM의 SSH authorized_keys를 클라우드 CLI·API로 수정해 자신의 공개키로 인스턴스에 지속 접근할 수 있음
+- 더 높은 권한 사용자에 키를 추가하면 권한 상승이 되며, 제어 평면 경유 변경이라 호스트 로그만으로는 탐지가 어려움</t>
         </is>
       </c>
       <c r="F51" s="17" t="inlineStr">
@@ -26476,7 +28303,16 @@
       <c r="N51" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O51" s="17" t="inlineStr"/>
+      <c r="O51" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 제어 평면의 VM 메타데이터·authorized_keys 변경(GCP set-metadata, Azure VM PATCH), EC2 키페어 투입 이벤트
+- VM 내 authorized_keys 파일 변경과 신규 키로의 SSH 로그인
+■ 대응
+- VM 메타데이터·키 변경 권한 최소화, OS Login·중앙 키 관리로 개별 키 투입 차단
+- 불변 인프라·구성 드리프트 점검으로 비인가 키 탐지</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="17" t="inlineStr">
@@ -26501,7 +28337,8 @@
       </c>
       <c r="E52" s="17" t="inlineStr">
         <is>
-          <t>공격자는 자신이 제어하는 계정에 장치를 등록할 수 있다. 장치는 네트워크 인증을 처리하는 다중 인증(MFA) 시스템이나, 장치 접근과 규정 준수를 관리하는 장치 관리 시스템에 등록될 수 있다.</t>
+          <t>- 공격자는 탈취한 자격증명으로 자신의 장치를 피해 계정의 MFA·장치 관리 시스템(Entra ID·Intune·Duo·Okta)에 등록해 지속 접근을 확보할 수 있음
+- 등록된 장치는 조건부 액세스의 '관리 장치' 조건을 충족해 이후 MFA·정책을 통과하고, 내부 발신 메일로 신뢰도 높은 피싱도 가능</t>
         </is>
       </c>
       <c r="F52" s="17" t="inlineStr">
@@ -26545,7 +28382,16 @@
       <c r="N52" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="O52" s="17" t="inlineStr"/>
+      <c r="O52" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 신규 MFA 장치·장치 등록 이벤트, 특히 비활성 계정·암호 추측 직후의 등록
+- 단기간 대량 장치 등록, 신규 등록 장치의 즉시 민감 리소스 접근
+■ 대응
+- 장치 등록에 추가 인증·관리자 승인, 조건부 액세스로 등록 가능 조건 제한
+- MFA 자가 등록 제한과 신규 장치 알림</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="17" t="inlineStr">
@@ -26570,7 +28416,8 @@
       </c>
       <c r="E53" s="17" t="inlineStr">
         <is>
-          <t>공격자는 개별 호스트에서 데몬, 에이전트, 서비스로 실행되는 컨테이너·컨테이너 클러스터 관리 도구를 만들거나 수정할 수 있다. 여기에는 Docker, Podman 같은 컨테이너 생성·관리 소프트웨어와 kubelet 같은 클러스터 노드 에이전트가 포함된다. 이러한 서비스를 수정하면 호스트에서 지속성을 확보하거나 권한을 높일 수 있다.</t>
+          <t>- 공격자는 컨테이너 런타임·노드 에이전트를 재시작 유지 설정으로 만들거나 수정해 호스트에서 지속성을 확보하고 권한을 높일 수 있음
+- DaemonSet·정적 파드·restart=always로 노드마다 자동 상주시키며, rootful Docker 접근은 그대로 호스트 권한 상승 경로가 됨</t>
         </is>
       </c>
       <c r="F53" s="17" t="inlineStr">
@@ -26610,7 +28457,16 @@
       <c r="N53" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O53" s="17" t="inlineStr"/>
+      <c r="O53" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- restart=always 상주 컨테이너, 신규 DaemonSet·정적 파드, kubelet manifest 디렉터리 변경
+- 노드에 반복 재생성되는 컨테이너와 외부 통신
+■ 대응
+- 정책 엔진으로 위험 워크로드 차단, 정적 파드 경로·docker 소켓 접근 제한
+- rootless 컨테이너 전환과 노드 파일 무결성 점검</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="17" t="inlineStr">
@@ -26635,7 +28491,8 @@
       </c>
       <c r="E54" s="17" t="inlineStr">
         <is>
-          <t>공격자는 중앙에서 관리되는 환경에서 방어를 회피하거나 권한을 높이기 위해 도메인이나 ID 테넌트의 구성 설정을 수정할 수 있다. 이러한 서비스는 장치와 계정 같은 ID 리소스를 중앙에서 관리하는 수단을 제공하며, 신뢰 관계, ID 동기화, ID 페더레이션처럼 도메인이나 테넌트 사이에 적용되는 구성 설정을 포함하는 경우가 많다.</t>
+          <t>- 공격자는 ID 테넌트·도메인의 정책 설정(페더레이션 트러스트, ID 동기화, 그룹 정책, Azure Policy)을 수정해 방어를 우회하거나 권한을 높일 수 있음
+- 테넌트 전역에 적용되는 설정이라 한 번의 변경이 광범위한 영향을 미치고, 작업 후 원복해 흔적을 지우기도 함</t>
         </is>
       </c>
       <c r="F54" s="17" t="inlineStr">
@@ -26679,7 +28536,16 @@
       <c r="N54" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O54" s="17" t="inlineStr"/>
+      <c r="O54" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- ID 테넌트 정책·페더레이션 설정 변경, Azure Policy(DeployIfNotExists) 할당·수정 이벤트
+- 짧은 시간 변경 후 원복되는 정책 설정
+■ 대응
+- 테넌트 정책·페더레이션 변경에 다중 관리자 승인과 변경 알림
+- 정책을 코드로 관리하고 드리프트 자동 복원, 전역 관리자 수 최소화</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="17" t="inlineStr">
@@ -26704,7 +28570,8 @@
       </c>
       <c r="E55" s="17" t="inlineStr">
         <is>
-          <t>공격자는 방어를 회피하거나 권한을 높이기 위해 새 도메인 트러스트를 추가하거나, 기존 도메인 트러스트의 속성을 수정하거나, 도메인·테넌트 간 신뢰 관계 구성을 바꿀 수 있다. 사용자 ID의 페더레이션 여부 같은 신뢰 세부 정보에 따라, 공유 리소스 접근을 위해 도메인이나 테넌트 사이에 인증·인가 속성이 적용될 수 있다. 이러한 신뢰 객체에는 서버, 토큰, 도메인에 적용되는 계정, 자격 증명, 기타 인증 자료가 포함될 수 있다.</t>
+          <t>- 공격자는 피해 테넌트에 자신의 페더레이션 ID 공급자·SAML 서명 인증서를 추가하거나 신뢰 관계를 변경해, 임의 사용자로 인증하는 백도어를 만들 수 있음
+- 하나의 신뢰 변경이 그 ID를 쓰는 모든 클라우드·SaaS로 확대되어, AWS Organization에서는 전 구성원 계정에 페더레이션 접근이 가능해짐</t>
         </is>
       </c>
       <c r="F55" s="17" t="inlineStr">
@@ -26748,7 +28615,16 @@
       <c r="N55" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="O55" s="17" t="inlineStr"/>
+      <c r="O55" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 신규 페더레이션 도메인·ID 공급자 추가(CreateSAMLProvider·CreateOpenIDConnectProvider), 클레임 규칙·도메인 전환 이벤트
+- 외부에서 서명된 토큰·새 SAML 인증서로의 인증, 평소와 다른 발행자 토큰
+■ 대응
+- 페더레이션 신뢰·ID 공급자 변경에 강한 승인·알림, 토큰 서명 인증서 보호
+- AWS Organization·Entra의 ID 공급자 목록 정기 검토와 외부 신뢰 허용 목록화</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="17" t="inlineStr">
@@ -26773,7 +28649,8 @@
       </c>
       <c r="E56" s="17" t="inlineStr">
         <is>
-          <t>공격자는 기반 호스트에 접근하기 위해 컨테이너나 가상화 환경을 탈출할 수 있다. 이를 통해 호스트 수준에서 다른 컨테이너·가상화 리소스나 호스트 자체에 접근할 수 있다. 원칙적으로 컨테이너·가상화 리소스는 애플리케이션 기능을 명확히 분리하고 호스트 환경과 격리되어야 한다.</t>
+          <t>- 공격자는 컨테이너·VM 격리를 탈출해 기반 호스트에 접근하고, 같은 호스트의 다른 컨테이너·워크로드나 호스트 자체를 장악할 수 있음
+- 호스트 파일시스템 마운트·권한 있는 컨테이너·docker.sock 노출·하이퍼바이저 취약점이 경로이며, 노드 장악은 곧 클러스터·클라우드 확산으로 이어짐</t>
         </is>
       </c>
       <c r="F56" s="17" t="inlineStr">
@@ -26813,7 +28690,16 @@
       <c r="N56" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O56" s="17" t="inlineStr"/>
+      <c r="O56" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 권한 있는 컨테이너·hostPath 마운트·docker.sock 마운트 파드 생성, 컨테이너에서의 커널 모듈 로드
+- 컨테이너 프로세스의 호스트 네임스페이스 접근, 노드에서의 비정상 자식 프로세스
+■ 대응
+- Pod Security Admission으로 privileged·hostPath·호스트 네임스페이스 차단, docker 소켓 마운트 금지
+- 런타임 샌드박스(gVisor 등)·최신 패치, ESXi 하이퍼바이저 긴급 패치</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="17" t="inlineStr">
@@ -26838,7 +28724,8 @@
       </c>
       <c r="E57" s="17" t="inlineStr">
         <is>
-          <t>공격자는 특정 이벤트를 계기로 실행을 일으키는 시스템 메커니즘을 이용해 지속성을 확보하거나 권한을 높일 수 있다. 여러 운영체제에는 로그온이나 특정 애플리케이션·바이너리 실행 같은 사용자 활동 이벤트를 모니터링하고 구독하는 수단이 있다. 클라우드 환경도 특정 클라우드 이벤트를 모니터링하고 이에 대응해 호출되는 다양한 함수와 서비스를 지원할 수 있다.</t>
+          <t>- 공격자는 클라우드 이벤트에 반응하는 함수·웹훅·정책(이벤트 규칙·HTTP 트리거 등)을 등록해 지속성과 권한 상승을 확보할 수 있음
+- 트리거는 관리 ID·서비스 계정 권한으로 실행되고 특정 조건에서만 발동해, 상시 프로세스가 없어 탐지가 어려움</t>
         </is>
       </c>
       <c r="F57" s="17" t="inlineStr">
@@ -26878,7 +28765,16 @@
       <c r="N57" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="O57" s="17" t="inlineStr"/>
+      <c r="O57" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 이벤트 규칙·HTTP 트리거·웹훅·Watcher·정책(DeployIfNotExists) 생성·변경 이벤트
+- 어드미션 컨트롤러·EKS 구성 변경, 트리거가 관리 ID로 수행하는 비정상 작업
+■ 대응
+- 이벤트·정책·자동화 리소스 수정 권한 최소화, 인증 없는 트리거 금지
+- 자동화·정책 목록 정기 검토와 변경 알림</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="17" t="inlineStr">
@@ -27211,7 +29107,8 @@
       </c>
       <c r="E62" s="17" t="inlineStr">
         <is>
-          <t>공격자는 이메일 규칙을 이용해 침해한 사용자의 사서함에서 수신 이메일을 숨길 수 있다. 많은 이메일 클라이언트는 이메일을 다른 폴더로 옮기기, 읽음으로 표시하기, 삭제하기 등 다양한 받은편지함 규칙을 만들 수 있게 한다. 규칙은 이메일 클라이언트 안에서 만들거나 수정할 수 있고, Windows 시스템의 New-InboxRule이나 Set-InboxRule PowerShell cmdlet 같은 외부 기능으로도 만들거나 수정할 수 있다.</t>
+          <t>- 공격자는 침해한 사서함에 이메일 숨김 규칙을 만들어 보안 경고·C2 응답·내부 피싱 회신을 자동으로 이동·삭제·읽음 처리할 수 있음
+- malware·phish 같은 키워드로 거르며, 조직 전역 전송 규칙(Exchange transport rule)을 악용하면 전사 보안 알림을 일괄 차단함</t>
         </is>
       </c>
       <c r="F62" s="17" t="inlineStr">
@@ -27251,7 +29148,16 @@
       <c r="N62" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="O62" s="17" t="inlineStr"/>
+      <c r="O62" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 보안 키워드로 메일을 이동·삭제하는 사서함 규칙 생성, 조직 전역 전송 규칙 변경
+- New-InboxRule·Set-InboxRule 호출과 알림 메일이 사라지는 패턴
+■ 대응
+- 위험 사서함 규칙 자동 탐지·차단, 전송 규칙 변경 감사
+- 보안 알림을 메일 외 채널로도 전달해 숨김 규칙 우회</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="17" t="inlineStr">
@@ -27276,7 +29182,8 @@
       </c>
       <c r="E63" s="17" t="inlineStr">
         <is>
-          <t>공격자는 자신의 존재 흔적을 줄이고 정상 활동에 섞이기 위해 생성된 산출물을 선택적으로 삭제하거나 수정할 수 있다. 증거를 광범위하게 지우기보다 이상해 보이거나 주목받기 쉬운 특정 산출물만 골라 처리하고, 정상적인 시스템 동작처럼 보이도록 충분한 데이터는 그대로 남겨 둘 수 있다.</t>
+          <t>- 공격자는 흔적을 줄이기 위해 로그·명령 이력·메타데이터나 자신이 만든 IAM 개체·컨테이너 로그 등을 선택적으로 삭제·변조할 수 있음
+- 정상 활동처럼 보이도록 일부만 손대며, 삭제·변조는 타임라인 재구성과 귀속을 어렵게 함</t>
         </is>
       </c>
       <c r="F63" s="17" t="inlineStr">
@@ -27316,7 +29223,16 @@
       <c r="N63" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O63" s="17" t="inlineStr"/>
+      <c r="O63" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- IAM 개체 생성 직후 삭제(DeleteUser·DeleteRole), 컨테이너·클러스터 로그·이벤트 삭제
+- 로그 수집 공백 구간, 명령 이력·메타데이터의 비정상 변경
+■ 대응
+- 감사 로그를 쓰기 방지·별도 계정으로 중앙 집계(변조·삭제 방지), 로그 보존 정책 강제
+- IAM 삭제 이벤트 알림과 컨테이너 로그의 외부 전송</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="17" t="inlineStr">
@@ -27341,7 +29257,8 @@
       </c>
       <c r="E64" s="17" t="inlineStr">
         <is>
-          <t>공격자는 메일과 메일 애플리케이션 데이터를 수정해 자신의 활동 증거를 없앨 수 있다. 이메일 애플리케이션은 사용자와 다른 프로그램이 명령줄 도구나 API로 사서함 데이터를 내보내거나 삭제할 수 있게 한다. 메일 애플리케이션 데이터에는 이메일, 이메일 메타데이터, 내보내기 요청처럼 애플리케이션이나 운영체제가 생성한 로그가 포함될 수 있다.</t>
+          <t>- 공격자는 침해 사서함의 메일·메타데이터·내보내기 로그를 삭제해 피싱·수집·메일 기반 반출의 증거를 없앨 수 있음
+- ExchangePowerShell(Remove-MailboxExportRequest 등)이나 전송 규칙으로 특정 주제 메일을 자동 삭제해 탐지를 어렵게 함</t>
         </is>
       </c>
       <c r="F64" s="17" t="inlineStr">
@@ -27381,7 +29298,15 @@
       <c r="N64" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O64" s="17" t="inlineStr"/>
+      <c r="O64" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- Remove-MailboxExportRequest 등 사서함 내보내기 삭제, 대량 메일 삭제, 전송 규칙 기반 자동 삭제
+■ 대응
+- 사서함 감사 로깅 활성화·중앙 보존, 메일 삭제·내보내기 이벤트 알림
+- 보존(litigation hold)으로 삭제 메일 복구 가능하게 구성</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="17" t="inlineStr">
@@ -27406,7 +29331,8 @@
       </c>
       <c r="E65" s="17" t="inlineStr">
         <is>
-          <t>공격자는 파일, 레지스트리 키 또는 기타 리소스의 이름이나 위치를 정할 때 정상 항목과 같거나 비슷하게 맞출 수 있다. 이는 방어와 관찰을 회피하기 위해서다.</t>
+          <t>- 공격자는 리소스 이름·위치를 정상 항목과 같거나 비슷하게 맞춰 방어·관찰을 회피할 수 있으며, 컨테이너 환경에서는 신뢰 네임스페이스나 파드 명명 규칙을 모방함
+- 정상 명명 규칙에 섞여 들어 운영자가 한눈에 이상을 알아채기 어려움</t>
         </is>
       </c>
       <c r="F65" s="17" t="inlineStr">
@@ -27446,7 +29372,16 @@
       <c r="N65" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O65" s="17" t="inlineStr"/>
+      <c r="O65" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 시스템 네임스페이스의 비인가 리소스, 정상 파드명과 유사하나 소유 컨트롤러가 없는 리소스
+- 신뢰 위치·이름을 모방한 리소스 생성 이벤트
+■ 대응
+- 네임스페이스별 RBAC·정책으로 생성 제한, 리소스 소유권(ownerReferences)·태그 표준 검증
+- 이미지·리소스 인벤토리와 기준 대조</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="17" t="inlineStr">
@@ -27471,7 +29406,8 @@
       </c>
       <c r="E66" s="17" t="inlineStr">
         <is>
-          <t>공격자는 새로 만든 계정이 무해해 보이도록 정상 계정과 같거나 비슷한 이름을 붙일 수 있다. 이는 보통 계정 생성(Create Account) 단계에서 일어나지만 나중에 계정 이름을 바꿀 수도 있다. 공격자가 계정을 먼저 삭제한 뒤 같은 이름으로 다시 만드는 경우에는 계정 접근 제거(Account Access Removal)와 함께 나타날 수도 있다.</t>
+          <t>- 공격자는 새로 만든 계정에 정상 계정·서비스 계정과 비슷한 이름(admin·backup·IT 지원 등)을 붙여 무해해 보이게 할 수 있음
+- 기존 계정명을 모방하거나 삭제 후 같은 이름으로 재생성하기도 하며, 계정 목록에서 이상 탐지를 어렵게 함</t>
         </is>
       </c>
       <c r="F66" s="17" t="inlineStr">
@@ -27511,7 +29447,16 @@
       <c r="N66" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="O66" s="17" t="inlineStr"/>
+      <c r="O66" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- admin·backup·IT 지원 등 정상 명칭을 모방한 신규 계정, 서비스 계정 유사 이름
+- 삭제 직후 같은 이름 재생성, 협업 도구의 지원팀 사칭 계정
+■ 대응
+- 계정 명명 규칙·생성 승인, 서비스 계정 인벤토리와 대조
+- 협업 도구 외부·게스트 계정 표시와 제한</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="17" t="inlineStr">
@@ -27536,7 +29481,8 @@
       </c>
       <c r="E67" s="17" t="inlineStr">
         <is>
-          <t>공격자는 대상을 설득하고 속여 자신을 대신해 어떤 행동을 하게 만들기 위해 신뢰받는 사람이나 조직을 사칭할 수 있다. 예를 들어 임원, 동료, 외부 협력업체처럼 알려진 발신자를 사칭하면서 정보 수집용 피싱(Phishing for Information), 피싱(Phishing), 내부 스피어피싱(Internal Spearphishing)으로 피해자와 소통할 수 있다. 이렇게 쌓은 신뢰를 이용해 공격자의 최종 목표를 달성하며, 여러 피해자를 대상으로 할 수도 있다.</t>
+          <t>- 공격자는 임원·동료·협력업체·IT 지원 등 신뢰 주체를 사칭해 피해자가 송금하거나 정보를 넘기도록 유도할 수 있음
+- 정찰과 유사 도메인 확보로 신뢰를 꾸미며, SaaS 협업 도구(Teams·Salesforce)·메일로 접근해 BEC·금전 탈취로 이어짐</t>
         </is>
       </c>
       <c r="F67" s="17" t="inlineStr">
@@ -27576,7 +29522,16 @@
       <c r="N67" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="O67" s="17" t="inlineStr"/>
+      <c r="O67" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 협업 도구·메일에서 IT 지원·임원 사칭 패턴, 외부 게스트의 지원 사칭 메시지
+- 비밀번호·MFA 재설정 유도, 공급망 저장소의 사칭 커밋
+■ 대응
+- 헬프데스크 본인 확인 강화와 재설정 승인 절차, 외부 발신 표식
+- 사용자 사회공학 인식 교육과 신고 채널, 저장소 커밋 서명 검증</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="17" t="inlineStr">
@@ -27601,7 +29556,8 @@
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t>공격자는 관련 이메일 헤더 값을 수정해 발신자 신원을 위조함으로써 거짓 명분으로 피해자와 접촉할 수 있다. 실제 이메일 내용뿐 아니라 이메일 헤더(예: 발신자 이메일 주소가 담긴 FROM 헤더)도 수정할 수 있다. 이메일 클라이언트는 피해자의 받은편지함에 이메일이 표시될 때 이 헤더를 보여 주므로, 수정된 이메일이 위조한 대상이 보낸 것처럼 보일 수 있다.</t>
+          <t>- 공격자는 FROM 등 메일 헤더를 위조해 신뢰 발신자가 보낸 것처럼 꾸며 피해자와 자동 보안 도구를 속일 수 있음
+- SPF·DKIM·DMARC가 없거나 p=none이면 인증 실패 메일도 받은편지함에 배달되며, M365 Direct Send로 내부 사용자를 사칭하기도 함</t>
         </is>
       </c>
       <c r="F68" s="17" t="inlineStr">
@@ -27641,7 +29597,15 @@
       <c r="N68" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O68" s="17" t="inlineStr"/>
+      <c r="O68" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- SPF·DKIM 실패에도 배달된 메일, 내부 도메인 사칭 발신, Direct Send 경로 메일
+■ 대응
+- DMARC를 p=reject로 강제하고 SPF·DKIM 정합성 확보, M365 Direct Send 제한
+- 외부 발신 표식과 사칭 의심 메일 격리</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="17" t="inlineStr">
@@ -27666,7 +29630,8 @@
       </c>
       <c r="E69" s="17" t="inlineStr">
         <is>
-          <t>공격자는 탐지를 회피하기 위해 사용하지 않는 지역 서비스 리전에 클라우드 인스턴스를 만들 수 있다. 이런 접근은 보통 클라우드 인프라 관리에 쓰이는 계정을 침해해 얻는다.</t>
+          <t>- 공격자는 조직이 쓰지 않거나 모니터링이 약한 클라우드 리전에 인스턴스를 만들어 탐지를 피할 수 있음
+- 고급 탐지 서비스가 없는 리전을 골라 채굴 등 활동을 숨기며, 미사용 리전은 과금·리소스 증가로만 뒤늦게 드러남</t>
         </is>
       </c>
       <c r="F69" s="17" t="inlineStr">
@@ -27710,7 +29675,16 @@
       <c r="N69" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O69" s="17" t="inlineStr"/>
+      <c r="O69" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 미사용 리전의 리소스 생성·실행(RunInstances 등), 평소 사용 리전 밖의 과금·사용량 증가
+- 탐지 서비스가 없는 리전에서의 API 활동
+■ 대응
+- SCP·조직 정책으로 허용 리전 외 배포 차단, 전 리전에 탐지 서비스·로깅 활성화
+- 전 리전 리소스·과금 모니터링</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="17" t="inlineStr">
@@ -27893,7 +29867,8 @@
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t>공격자는 클라우드 리소스 접근을 제한하는 통제를 우회하기 위해 클라우드 환경의 방화벽을 비활성화하거나 수정할 수 있다.</t>
+          <t>- 공격자는 보안 그룹·NSG 등 클라우드 방화벽 규칙을 수정·추가해 피해 환경으로의 접근 경로를 열거나 제어 평면에서 데이터 평면으로 이동할 수 있음
+- 인바운드 전체 허용 규칙을 넣거나 네트워크 제한을 풀어 C2·채굴 트래픽을 통과시키며, 정상 구성 변경처럼 보임</t>
         </is>
       </c>
       <c r="F72" s="17" t="inlineStr">
@@ -27937,7 +29912,16 @@
       <c r="N72" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="O72" s="17" t="inlineStr"/>
+      <c r="O72" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 보안 그룹·NSG·네트워크 ACL에 광범위 허용(0.0.0.0/0) 규칙 추가, 탐지 서비스 허용 목록 변경
+- 방화벽 변경 직후의 새 인바운드 연결
+■ 대응
+- 보안 그룹 변경 권한 최소화·변경 알림, 광범위 개방 규칙 자동 탐지·차단(정책 가드레일)
+- 네트워크 구성을 IaC로 관리하고 드리프트 복원</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="17" t="inlineStr">
@@ -27962,7 +29946,8 @@
       </c>
       <c r="E73" s="17" t="inlineStr">
         <is>
-          <t>공격자는 방어 기능의 가시성을 떨어뜨리거나 무력화하기 위해 보안 도구나 애플리케이션(예: EDR(엔드포인트 탐지 및 대응) 도구, 침입 탐지 시스템(IDS), 백신, 로깅 에이전트, 센서 등)을 비활성화하거나, 성능을 떨어뜨리거나, 변조할 수 있다. 여기에는 특정 서비스 중지, 프로세스 종료, 도구 구성 파일과 레지스트리 키 수정·삭제, 도구 업데이트 차단 등이 포함될 수 있다. 호스트, 네트워크, 클라우드 환경 전반의 예방·탐지·대응 메커니즘을 방해해 방어를 더 광범위하게 무력화하는 것도 포함될 수 있다.</t>
+          <t>- 공격자는 EDR·백신·로깅 에이전트·클라우드 모니터링 에이전트를 중지·삭제·변조해 방어 가시성을 떨어뜨릴 수 있음
+- 클라우드에서는 VM·컨테이너의 보안 에이전트 제거, DNS·iptables 변조로 텔레메트리를 끊어 탐지·대응을 무력화함</t>
         </is>
       </c>
       <c r="F73" s="17" t="inlineStr">
@@ -28006,7 +29991,16 @@
       <c r="N73" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="O73" s="17" t="inlineStr"/>
+      <c r="O73" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 보안·모니터링 에이전트 중지·제거, DNS·iptables 변경, 탐지기(GuardDuty) 삭제·수정
+- 에이전트 텔레메트리 수신 중단 구간
+■ 대응
+- 보안 에이전트 변조 방지·자동 복구, 에이전트 상태 중앙 모니터링
+- 탐지 서비스 삭제·수정에 SCP·알림, CI 환경 네트워크 설정 변경 제한</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="17" t="inlineStr">
@@ -28031,7 +30025,8 @@
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t>공격자는 자신의 활동에 대해 수집되는 데이터를 제한하고 탐지를 피하기 위해 클라우드 로깅 기능과 연동을 비활성화하거나 수정할 수 있다. 클라우드 환경에서는 사용자가 환경 안에서 어떤 활동을 하는지 보여 주는 감사 로그와 애플리케이션 로그를 수집·분석할 수 있다. 공격자는 권한이 충분하면 로깅을 비활성화하거나 수정해 자신의 활동이 탐지되지 않게 할 수 있다.</t>
+          <t>- 공격자는 CloudTrail·CloudWatch·M365 감사 로깅을 중지·삭제·축소해 자신의 활동이 기록되지 않게 할 수 있음
+- 다중 리전 로깅·로그 검증 해제, 특정 사용자 감사 우회, 라이선스 하향 등으로 선택적으로 가시성을 지움</t>
         </is>
       </c>
       <c r="F74" s="17" t="inlineStr">
@@ -28075,7 +30070,16 @@
       <c r="N74" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="O74" s="17" t="inlineStr"/>
+      <c r="O74" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- CloudTrail StopLogging·DeleteTrail·UpdateTrail, VPC Flow Logs·CloudWatch 로그 삭제
+- M365 감사 우회(Set-MailboxAuditBypassAssociation)·라이선스 하향, 로그 수집 공백
+■ 대응
+- 로깅 변경을 SCP로 차단·조직 전역 로깅 강제(불변·별도 계정 저장), 로그 중단 즉시 알림
+- M365 감사 보존·고급 감사 유지</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="17" t="inlineStr">
@@ -28100,7 +30104,8 @@
       </c>
       <c r="E75" s="17" t="inlineStr">
         <is>
-          <t>공격자는 중앙에서 관리되는 환경에서 방어를 회피하거나 권한을 높이기 위해 도메인이나 ID 테넌트의 구성 설정을 수정할 수 있다. 이러한 서비스는 장치와 계정 같은 ID 리소스를 중앙에서 관리하는 수단을 제공하며, 신뢰 관계, ID 동기화, ID 페더레이션처럼 도메인이나 테넌트 사이에 적용되는 구성 설정을 포함하는 경우가 많다.</t>
+          <t>- 공격자는 ID 테넌트·도메인의 정책 설정(페더레이션 트러스트, ID 동기화, 그룹 정책, Azure Policy)을 수정해 방어를 우회하거나 권한을 높일 수 있음
+- 테넌트 전역에 적용되는 설정이라 한 번의 변경이 광범위한 영향을 미치고, 작업 후 원복해 흔적을 지우기도 함</t>
         </is>
       </c>
       <c r="F75" s="17" t="inlineStr">
@@ -28144,7 +30149,16 @@
       <c r="N75" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O75" s="17" t="inlineStr"/>
+      <c r="O75" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- ID 테넌트 정책·페더레이션 설정 변경, Azure Policy(DeployIfNotExists) 할당·수정 이벤트
+- 짧은 시간 변경 후 원복되는 정책 설정
+■ 대응
+- 테넌트 정책·페더레이션 변경에 다중 관리자 승인과 변경 알림
+- 정책을 코드로 관리하고 드리프트 자동 복원, 전역 관리자 수 최소화</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="17" t="inlineStr">
@@ -28169,7 +30183,8 @@
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t>공격자는 방어를 회피하거나 권한을 높이기 위해 새 도메인 트러스트를 추가하거나, 기존 도메인 트러스트의 속성을 수정하거나, 도메인·테넌트 간 신뢰 관계 구성을 바꿀 수 있다. 사용자 ID의 페더레이션 여부 같은 신뢰 세부 정보에 따라, 공유 리소스 접근을 위해 도메인이나 테넌트 사이에 인증·인가 속성이 적용될 수 있다. 이러한 신뢰 객체에는 서버, 토큰, 도메인에 적용되는 계정, 자격 증명, 기타 인증 자료가 포함될 수 있다.</t>
+          <t>- 공격자는 피해 테넌트에 자신의 페더레이션 ID 공급자·SAML 서명 인증서를 추가하거나 신뢰 관계를 변경해, 임의 사용자로 인증하는 백도어를 만들 수 있음
+- 하나의 신뢰 변경이 그 ID를 쓰는 모든 클라우드·SaaS로 확대되어, AWS Organization에서는 전 구성원 계정에 페더레이션 접근이 가능해짐</t>
         </is>
       </c>
       <c r="F76" s="17" t="inlineStr">
@@ -28213,7 +30228,16 @@
       <c r="N76" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="O76" s="17" t="inlineStr"/>
+      <c r="O76" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 신규 페더레이션 도메인·ID 공급자 추가(CreateSAMLProvider·CreateOpenIDConnectProvider), 클레임 규칙·도메인 전환 이벤트
+- 외부에서 서명된 토큰·새 SAML 인증서로의 인증, 평소와 다른 발행자 토큰
+■ 대응
+- 페더레이션 신뢰·ID 공급자 변경에 강한 승인·알림, 토큰 서명 인증서 보호
+- AWS Organization·Entra의 ID 공급자 목록 정기 검토와 외부 신뢰 허용 목록화</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="17" t="inlineStr">
@@ -28238,7 +30262,8 @@
       </c>
       <c r="E77" s="17" t="inlineStr">
         <is>
-          <t>공격자는 침해한 계정에 지속적으로 접근하기 위해 다중 인증(MFA) 메커니즘을 비활성화하거나 수정할 수 있다.</t>
+          <t>- 공격자는 침해 계정 유지를 위해 MFA를 비활성화하거나 취약한 MFA 수단으로 교체할 수 있으며, 탈취한 세션 토큰으로 MFA 자체를 건너뛰기도 함
+- 조건부 액세스에서 사용자 제외·'실패 시 허용(fail open)' 설정을 악용하면 계정 단위를 넘어 그룹 전체의 MFA가 무력화됨</t>
         </is>
       </c>
       <c r="F77" s="17" t="inlineStr">
@@ -28282,7 +30307,16 @@
       <c r="N77" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="O77" s="17" t="inlineStr"/>
+      <c r="O77" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- MFA 비활성화·조건부 액세스 제외·MFA 수단 변경 이벤트, 같은 세션 토큰의 다른 IP 재사용
+- 'fail open' 구성과 MFA 요구가 사라진 로그인 성공
+■ 대응
+- 피싱 저항형 MFA(FIDO2)와 'fail open' 금지, MFA·조건부 액세스 변경에 다중 관리자 승인
+- 토큰 보호·세션 수명 단축, 의심 세션 토큰 즉시 폐기</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="17" t="inlineStr">
@@ -28307,7 +30341,8 @@
       </c>
       <c r="E78" s="17" t="inlineStr">
         <is>
-          <t>공격자는 일반 인증 메커니즘을 우회하고, 자격 증명에 접근하고, 계정에 지속적으로 접근하기 위해 온프레미스 사용자 ID와 연결된 클라우드 인증 절차에 패치를 적용하거나, 이를 수정하거나, 백도어를 심을 수 있다.</t>
+          <t>- 공격자는 온프레미스-클라우드 하이브리드 ID 연결(PHS·PTA·AD FS)에 백도어를 심어 모든 인증을 통과시키고 자격증명을 수집할 수 있음
+- 연동 지점 하나를 장악하면 페더레이션된 모든 클라우드·SaaS에 지속적 특권 접근이 가능해 피해 범위가 테넌트 전체로 확대됨</t>
         </is>
       </c>
       <c r="F78" s="17" t="inlineStr">
@@ -28351,7 +30386,16 @@
       <c r="N78" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="O78" s="17" t="inlineStr"/>
+      <c r="O78" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- PTA 에이전트·AD FS 서버의 DLL 로드·구성 파일 변경, 토큰 서명 인증서의 비정상 사용
+- 온프레미스 조인 서버에서 발급된 토큰의 광범위한 클라우드 접근
+■ 대응
+- 하이브리드 ID 연동 서버를 Tier0로 취급·접근 최소화, 토큰 서명 인증서 보호·정기 교체
+- AD FS → 클라우드 인증의 이상 토큰 탐지, 가능 시 클라우드 인증으로 전환</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="17" t="inlineStr">
@@ -28376,7 +30420,8 @@
       </c>
       <c r="E79" s="17" t="inlineStr">
         <is>
-          <t>공격자는 침해한 계정에 지속적으로 접근하기 위해 조건부 액세스 정책을 비활성화하거나 수정할 수 있다. 조건부 액세스 정책은 ID 공급자와 ID·접근 관리 시스템이 사용자에게 리소스 접근을 허용할지 판단할 때 쓰는 추가 검증이다.</t>
+          <t>- 공격자는 조건부 액세스·IAM 조건 정책을 수정해(신뢰 IP 추가, MFA 요구 제거, 허용 리전 확대) 침해 계정의 접근을 지속할 수 있음
+- 정책 완화는 정상 관리 변경처럼 보여, 이후 탈취 자격증명이 통제를 그대로 통과하게 만듦</t>
         </is>
       </c>
       <c r="F79" s="17" t="inlineStr">
@@ -28420,7 +30465,16 @@
       <c r="N79" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="O79" s="17" t="inlineStr"/>
+      <c r="O79" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 조건부 액세스·IAM 조건 정책 변경(신뢰 IP 추가·MFA 제거·리전 확대) 이벤트
+- 정책 완화 직후 새 위치·리전에서의 로그인 성공
+■ 대응
+- 조건부 액세스·IAM 정책 변경에 승인 워크플로와 변경 알림
+- 정책을 코드로 관리(IaC)하고 드리프트 자동 복원</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="17" t="inlineStr">
@@ -28445,7 +30499,8 @@
       </c>
       <c r="E80" s="17" t="inlineStr">
         <is>
-          <t>공격자는 방어를 회피하기 위해 클라우드 계정 안에 스냅샷이나 데이터 백업을 만들 수 있다. 스냅샷은 가상 머신(VM), 가상 하드 드라이브, 볼륨 같은 기존 클라우드 컴퓨팅 구성 요소의 특정 시점 복사본이다. 공격자는 스냅샷 생성 권한을 이용해 기존 컴퓨팅 서비스 인프라에 대한 접근 제한을 우회할 수 있다. 이는 탐지를 회피하고 존재 증거를 없애기 위해 스냅샷으로 되돌리는 클라우드 인스턴스 되돌리기(Revert Cloud Instance)와는 다르다.</t>
+          <t>- 공격자는 EBS·디스크 볼륨의 스냅샷을 만들어, 기존 인스턴스 접근 제한을 우회해 데이터를 복사·반출할 수 있음
+- 스냅샷을 공격자 인스턴스에 마운트하거나 외부 계정에 공유해 원본 접근 통제를 거치지 않고 내용을 확보함</t>
         </is>
       </c>
       <c r="F80" s="17" t="inlineStr">
@@ -28489,7 +30544,16 @@
       <c r="N80" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="O80" s="17" t="inlineStr"/>
+      <c r="O80" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- EBS·RDS 스냅샷 생성(CreateSnapshot), 스냅샷의 외부 계정 공유·공개 전환
+- 스냅샷을 새 인스턴스에 마운트하는 패턴
+■ 대응
+- 스냅샷 생성·공유 권한 최소화, 스냅샷 공개·외부 공유 차단 정책
+- 스냅샷 암호화와 공유 이벤트 알림</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="17" t="inlineStr">
@@ -28514,7 +30578,8 @@
       </c>
       <c r="E81" s="17" t="inlineStr">
         <is>
-          <t>공격자는 방어를 회피하기 위해 클라우드 계정의 컴퓨팅 서비스 안에 새 인스턴스나 가상 머신(VM)을 만들 수 있다. 새 인스턴스를 만들면 계정에 이미 있는 인스턴스에 적용된 방화벽 규칙과 권한을 우회할 수 있다. 공격자는 계정의 볼륨 하나 이상에 대해 스냅샷 생성(Create Snapshot)을 하고, 새 인스턴스를 만들어 스냅샷을 마운트한 뒤, 덜 제한적인 보안 정책을 적용해 로컬 시스템의 데이터(Data from Local System)를 수집하거나 원격 데이터 스테이징(Remote Data Staging)을 할 수 있다.</t>
+          <t>- 공격자는 피해 계정에 새 인스턴스·VM·클러스터를 만들어 기존 인스턴스에 걸린 방화벽·권한·모니터링을 우회할 수 있음
+- 스냅샷을 마운트해 데이터를 수집하거나 덜 제한적인 정책으로 새 워크로드를 돌려, 운영 중 인스턴스에 영향 없이 활동함</t>
         </is>
       </c>
       <c r="F81" s="17" t="inlineStr">
@@ -28558,7 +30623,16 @@
       <c r="N81" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="O81" s="17" t="inlineStr"/>
+      <c r="O81" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- RunInstances·클러스터/서비스 생성이 평소와 다른 주체·리전·인스턴스 유형으로 발생
+- 새 인스턴스에 덜 제한적인 보안 정책 적용
+■ 대응
+- 인스턴스·클러스터 생성 권한 최소화, 승인된 이미지·구성만 허용(정책 가드레일)
+- 신규 리소스 생성 알림과 과금 모니터링</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="17" t="inlineStr">
@@ -28583,7 +30657,8 @@
       </c>
       <c r="E82" s="17" t="inlineStr">
         <is>
-          <t>공격자는 악의적 활동을 마친 뒤 탐지를 회피하고 존재 증거를 없애기 위해 클라우드 인스턴스를 삭제할 수 있다. 인스턴스를 복구할 수 없으면, 인스턴스나 가상 머신을 삭제하는 것만으로 중요한 포렌식 산출물과 기타 의심 행위 증거가 사라질 수 있다.</t>
+          <t>- 공격자는 작업을 마친 뒤 인스턴스·VM을 삭제해 포렌식 산출물과 활동 증거를 없앨 수 있음
+- 복구 불가능하게 삭제하면 조사 단서가 사라지며, 대량 삭제는 방어 회피를 넘어 업무 중단(파괴) 효과도 냄</t>
         </is>
       </c>
       <c r="F82" s="17" t="inlineStr">
@@ -28627,7 +30702,15 @@
       <c r="N82" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="O82" s="17" t="inlineStr"/>
+      <c r="O82" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 인스턴스·VM 종료·삭제, 특히 작업 직후·대량 삭제, 데이터 저장소 대량 삭제
+■ 대응
+- 종료 방지(termination protection)·삭제 권한 최소화, 중요 리소스 삭제에 승인
+- 백업·스냅샷 별도 계정 보존으로 복구 가능성 확보</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="17" t="inlineStr">
@@ -28652,7 +30735,8 @@
       </c>
       <c r="E83" s="17" t="inlineStr">
         <is>
-          <t>공격자는 악의적 활동을 마친 뒤 탐지를 회피하고 존재 증거를 없애기 위해 클라우드 인스턴스의 변경 사항을 되돌릴 수 있다. 클라우드 기반 인프라처럼 가상화 수준이 높은 환경에서는 클라우드 관리 대시보드나 클라우드 API로 가상 머신(VM)이나 데이터 스토리지 스냅샷을 복원해 이를 수행할 수 있다.</t>
+          <t>- 공격자는 활동 후 VM·스토리지를 이전 스냅샷으로 되돌려 변경·침해 흔적을 제거할 수 있음
+- 클라우드 대시보드·API로 쉽게 복원되고, 임시(ephemeral) 스토리지는 재시작만으로 초기화되어 증거가 사라짐</t>
         </is>
       </c>
       <c r="F83" s="17" t="inlineStr">
@@ -28696,7 +30780,14 @@
       <c r="N83" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O83" s="17" t="inlineStr"/>
+      <c r="O83" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- VM·스토리지 스냅샷 복원(되돌리기) 이벤트, 변경 이력이 사라지는 구간
+■ 대응
+- 복원 권한 최소화와 복원 이벤트 알림, 중요 로그·산출물을 비영속 스토리지 밖에 보존</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="17" t="inlineStr">
@@ -28721,7 +30812,8 @@
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t>공격자는 방어를 회피하기 위해 클라우드 컴퓨팅 인프라의 규모, 위치, 사용 가능한 자원에 직접 영향을 주는 설정을 수정할 수 있다. 이러한 설정에는 서비스 할당량, 구독 연결, 테넌트 전체 정책 등 사용 가능한 컴퓨팅 자원에 영향을 주는 구성이 포함될 수 있다. 이런 수정을 통해 공격자는 실행 중인 인스턴스에 영향을 주거나 피해자에게 활동을 드러내지 않고도 피해자의 컴퓨팅 자원을 악용해 목표를 달성할 수 있다.</t>
+          <t>- 공격자는 서비스 할당량·VM 크기 제한·배포 가능 리전 같은 컴퓨팅 구성을 변경해, 피해자 모르게 자원 사용량을 늘릴 수 있음
+- 할당량 상향·정책 완화로 전체 쿼터를 소진하지 않고 채굴 등을 확대하며, 미사용 리전 활성화로 탐지 사각을 넓힘</t>
         </is>
       </c>
       <c r="F84" s="17" t="inlineStr">
@@ -28765,7 +30857,16 @@
       <c r="N84" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O84" s="17" t="inlineStr"/>
+      <c r="O84" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 서비스 할당량 상향 요청, VM 크기·테넌트 정책 변경, 배포 리전 설정 변경
+- 구성 변경 직후 자원 사용량 급증
+■ 대응
+- 할당량·컴퓨팅 정책 변경 권한 최소화·승인, 쿼터·사용량 급증 알림
+- 리전·인스턴스 유형 허용 목록 유지</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="17" t="inlineStr">
@@ -28790,7 +30891,8 @@
       </c>
       <c r="E85" s="17" t="inlineStr">
         <is>
-          <t>공격자는 방어를 회피하기 위해 IaaS(Infrastructure-as-a-Service) 환경의 계층 구조를 수정하려 할 수 있다.</t>
+          <t>- 공격자는 IaaS 리소스 계층(AWS Organization, Azure 관리 그룹·구독)을 수정해 통제·로깅을 벗어난 공간을 만들 수 있음
+- 신규 구독·계정 생성, Organization 탈퇴로 SCP·가드레일 제거, 구독 하이재킹으로 피해 테넌트 로그 없이 자원을 사용함</t>
         </is>
       </c>
       <c r="F85" s="17" t="inlineStr">
@@ -28834,7 +30936,16 @@
       <c r="N85" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O85" s="17" t="inlineStr"/>
+      <c r="O85" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 신규 계정·구독 생성, LeaveOrganization 호출, 구독 이전(소유자 변경) 이벤트
+- SCP·가드레일이 적용 안 된 계정의 활동
+■ 대응
+- Organization 변경·구독 이전 권한을 최소 인원으로 제한하고 승인·알림
+- 신규 계정에 기준 SCP·로깅 자동 적용, 구독 이전 차단 정책</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="17" t="inlineStr">
@@ -28859,7 +30970,8 @@
       </c>
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t>공격자는 AiTM(adversary-in-the-middle) 기법으로 둘 이상의 네트워크 장치 사이에 자리 잡아 네트워크 스니핑(Network Sniffing), 전송 데이터 조작(Transmitted Data Manipulation), 재전송 공격(자격 증명 접근을 위한 익스플로잇(Exploitation for Credential Access)) 같은 후속 행위를 도울 수 있다. ARP, DNS, LLMNR 등 네트워크 트래픽 흐름을 결정하는 일반 네트워크 프로토콜의 기능을 악용해, 장치가 공격자가 제어하는 시스템을 거쳐 통신하도록 강제하고 정보를 수집하거나 추가 작업을 수행할 수 있다.</t>
+          <t>- 공격자는 네트워크 경로 중간에 자리 잡아(AiTM 프록시, DNS·ARP 조작, 캡티브 포털 침해) 자격증명·세션 토큰·MFA 응답을 가로챌 수 있음
+- 리버스 프록시형 피싱은 MFA를 거친 세션 쿠키까지 탈취해 다단계 인증을 무력화하며, 정상 로그인처럼 보임</t>
         </is>
       </c>
       <c r="F86" s="17" t="inlineStr">
@@ -28899,7 +31011,16 @@
       <c r="N86" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O86" s="17" t="inlineStr"/>
+      <c r="O86" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 알려진 AiTM 프록시 도메인·리버스 프록시 패턴, 같은 세션 토큰의 다른 IP 재사용
+- 비정상 DNS 응답·CoreDNS 설정 변경, 클러스터 내 ARP·IP 스푸핑 징후
+■ 대응
+- 피싱 저항형 MFA(FIDO2)로 AiTM 세션 탈취 무력화, 토큰 바인딩·세션 IP 고정
+- CoreDNS·CNI 보안 설정, 캡티브 포털·네트워크 경로 무결성 점검</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="17" t="inlineStr">
@@ -28924,7 +31045,8 @@
       </c>
       <c r="E87" s="17" t="inlineStr">
         <is>
-          <t>시스템이나 환경의 정상 자격 증명을 전혀 모르는 공격자는 비밀번호를 추측해 계정 접근을 시도할 수 있다. 계정의 비밀번호를 모르면 반복적인 방식으로 비밀번호를 체계적으로 추측할 수 있다. 작전 중에 시스템이나 환경의 비밀번호를 모르는 상태에서 흔히 쓰이는 비밀번호 목록으로 로그인 자격 증명을 추측할 수 있다. 비밀번호 추측은 대상의 비밀번호 복잡도 정책이나 여러 번 실패하면 계정을 잠그는 정책을 고려할 수도 있고 고려하지 않을 수도 있다.</t>
+          <t>- 공격자는 특정 계정에 비밀번호를 반복 추측해 SSO·클라우드 애플리케이션·외부 노출 메일(M365)·관리 서비스에 접근을 시도할 수 있음
+- 계정 잠금·로그인 실패 경보를 유발할 수 있으나, 페더레이션 인증 경로는 고가시성 이벤트를 덜 남겨 탐지가 늦어짐</t>
         </is>
       </c>
       <c r="F87" s="17" t="inlineStr">
@@ -28968,7 +31090,16 @@
       <c r="N87" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="O87" s="17" t="inlineStr"/>
+      <c r="O87" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 계정당 다수 인증 실패, SSO·M365 로그인 실패 급증, 페더레이션 인증의 반복 실패
+- 관리 서비스 포트에 대한 반복 로그인 시도
+■ 대응
+- 계정 잠금·지능형 잠금 정책, 피싱 저항형 MFA, 외부 노출 관리 서비스 최소화
+- 강한 비밀번호 정책과 레거시 인증 프로토콜 차단</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="17" t="inlineStr">
@@ -28993,7 +31124,8 @@
       </c>
       <c r="E88" s="17" t="inlineStr">
         <is>
-          <t>공격자는 흔히 쓰이는 비밀번호 하나 또는 소수의 비밀번호 목록을 여러 계정에 시도해 유효한 계정 자격 증명을 얻으려 할 수 있다. 비밀번호 스프레이는 도메인의 복잡도 정책을 충족할 수 있는 비밀번호 하나(예: Password01)나 흔히 쓰이는 비밀번호 몇 개를 사용한다. 한 계정에 여러 비밀번호로 무차별 대입할 때 발생하는 계정 잠금을 피하기 위해, 같은 비밀번호로 네트워크의 여러 계정에 로그인을 시도한다.</t>
+          <t>- 공격자는 흔한 비밀번호 하나를 여러 계정에 시도해 계정 잠금을 피하면서 유효 자격증명을 찾을 수 있음
+- SSO·M365 대상 스프레이는 임계값을 피하려 속도를 조절하며, 침해한 계정은 곧 크립토재킹·데이터 유출의 발판이 됨</t>
         </is>
       </c>
       <c r="F88" s="17" t="inlineStr">
@@ -29037,7 +31169,16 @@
       <c r="N88" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="O88" s="17" t="inlineStr"/>
+      <c r="O88" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 다수 계정에 동일 비밀번호로의 로그인 시도, 느린 속도로 분산된 인증 실패
+- 레거시 인증 엔드포인트 사용, 비정상 위치·ASN에서의 대량 로그인
+■ 대응
+- 레거시 인증 차단·조건부 액세스, 피싱 저항형 MFA, 지능형 잠금
+- 테스트·레거시 테넌트 계정 정리와 관리자 계정 MFA 강제</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="17" t="inlineStr">
@@ -29062,7 +31203,8 @@
       </c>
       <c r="E89" s="17" t="inlineStr">
         <is>
-          <t>공격자는 관련 없는 계정의 유출 덤프에서 얻은 자격 증명으로 자격 증명이 겹치는 대상 계정에 접근할 수 있다. 웹사이트나 서비스가 침해되어 사용자 계정 자격 증명이 유출되면 대량의 사용자 이름과 비밀번호 쌍이 온라인에 공개되기도 한다. 사용자가 개인 계정과 업무 계정에 같은 비밀번호를 쓰는 경향이 있으므로, 이 정보는 계정을 침해하려는 공격자에게 유용할 수 있다.</t>
+          <t>- 공격자는 타 유출 덤프의 사용자명·비밀번호 쌍을 대상 서비스에 대입해, 비밀번호를 재사용하는 계정에 접근할 수 있음
+- 개인·업무 계정 비밀번호 재사용을 노리며, SSO·M365 등 외부 노출 서비스에서 유효 조합을 찾음</t>
         </is>
       </c>
       <c r="F89" s="17" t="inlineStr">
@@ -29106,7 +31248,16 @@
       <c r="N89" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O89" s="17" t="inlineStr"/>
+      <c r="O89" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 유출 자격증명 목록과 일치하는 로그인, 여러 계정에서 1회 성공 후 멈추는 패턴
+- 비정상 위치·자동화 도구 사용자 에이전트
+■ 대응
+- 유출 비밀번호 검사·차단(비밀번호 보호), 피싱 저항형 MFA
+- 비밀번호 재사용 금지 정책과 침해 자격증명 모니터링</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="17" t="inlineStr">
@@ -29131,7 +31282,8 @@
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t>공격자는 AWS Secrets Manager, GCP Secret Manager, Azure Key Vault, Terraform Vault 같은 클라우드 네이티브 비밀 관리 솔루션에서 자격 증명을 획득할 수 있다.</t>
+          <t>- 공격자는 충분한 권한을 얻으면 AWS Secrets Manager·GCP Secret Manager·Azure Key Vault에서 비밀·API 키·인증서를 직접 조회할 수 있음
+- 비밀 저장소는 다수 서비스 자격증명을 한곳에 모아, 조회 권한 하나가 환경 전반 장악으로 이어짐</t>
         </is>
       </c>
       <c r="F90" s="17" t="inlineStr">
@@ -29175,7 +31327,16 @@
       <c r="N90" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="O90" s="17" t="inlineStr"/>
+      <c r="O90" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 비밀 저장소 대량 조회(get-secret-value·KeyVault getSecret 등), 평소 접근하지 않던 주체의 비밀 조회
+- 짧은 시간 다수 비밀 열람, soft-delete 객체 복구
+■ 대응
+- 비밀 조회 권한 최소화·비밀별 접근 정책, 비밀 접근 로깅·이상 조회 알림
+- 비밀 정기 교체와 접근 가능 주체 정기 검토</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="17" t="inlineStr">
@@ -29200,7 +31361,8 @@
       </c>
       <c r="E91" s="17" t="inlineStr">
         <is>
-          <t>공격자는 웹 애플리케이션이나 인터넷 서비스에 접근하는 데 쓸 수 있는 웹 쿠키를 위조할 수 있다. 클라우드 SaaS 환경이나 온프레미스 서버에 호스팅된 웹 애플리케이션과 서비스는 사용자 접근을 인증·인가하기 위해 세션 쿠키를 쓰는 경우가 많다.</t>
+          <t>- 공격자는 서명 비밀·키를 확보하면 웹 세션 쿠키를 새로 위조해, 탈취 없이도 웹 애플리케이션·SaaS에 접근할 수 있음
+- 위조 쿠키는 정상 발급 쿠키와 구분이 어렵고 MFA 등 인증 통제를 우회함</t>
         </is>
       </c>
       <c r="F91" s="17" t="inlineStr">
@@ -29244,7 +31406,15 @@
       <c r="N91" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O91" s="17" t="inlineStr"/>
+      <c r="O91" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 발급 기록이 없는 세션으로의 접근, 동일 쿠키의 비정상 위치 사용
+■ 대응
+- 쿠키 서명 비밀·키의 안전 보관·정기 교체, 세션 IP·장치 바인딩
+- 민감 작업에 재인증 요구</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="17" t="inlineStr">
@@ -29269,7 +31439,8 @@
       </c>
       <c r="E92" s="17" t="inlineStr">
         <is>
-          <t>공격자는 유효한 SAML 토큰 서명 인증서를 가지고 있으면 임의의 권한 클레임과 유효 기간을 가진 SAML 토큰을 위조할 수 있다. SAML 토큰의 기본 유효 기간은 1시간이지만, 토큰의 conditions 요소에 있는 NotOnOrAfter 값으로 유효 기간을 지정할 수 있다. 이 값은 LifetimeTokenPolicy의 AccessTokenLifetime으로 바꿀 수 있다. 위조된 SAML 토큰을 이용하면 SAML 2.0을 SSO(Single Sign-On) 방식으로 쓰는 여러 서비스에 인증할 수 있다.</t>
+          <t>- 공격자는 유효한 SAML 토큰 서명 인증서를 확보하면 임의 권한·유효기간의 SAML 토큰을 위조해(Golden SAML) SSO 기반 서비스에 인증할 수 있음
+- 고권한 계정을 사칭한 토큰으로 관리자 권한을 얻으며, 비밀번호 재설정·MFA로도 막히지 않음</t>
         </is>
       </c>
       <c r="F92" s="17" t="inlineStr">
@@ -29313,7 +31484,16 @@
       <c r="N92" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="O92" s="17" t="inlineStr"/>
+      <c r="O92" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 발행자·서명 인증서가 평소와 다른 SAML 토큰, 비정상적으로 긴 유효기간 토큰
+- ADFS 토큰 서명 인증서 접근·내보내기, 신규 페더레이션 신뢰 추가
+■ 대응
+- 토큰 서명 인증서 보호(HSM)·정기 교체, ADFS 서버 Tier0 격리
+- 발행자·클레임 이상 탐지, 가능 시 클라우드 인증으로 전환</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="17" t="inlineStr">
@@ -29338,7 +31518,8 @@
       </c>
       <c r="E93" s="17" t="inlineStr">
         <is>
-          <t>공격자는 침해한 계정에 지속적으로 접근하기 위해 다중 인증(MFA) 메커니즘을 비활성화하거나 수정할 수 있다.</t>
+          <t>- 공격자는 침해 계정 유지를 위해 MFA를 비활성화하거나 취약한 MFA 수단으로 교체할 수 있으며, 탈취한 세션 토큰으로 MFA 자체를 건너뛰기도 함
+- 조건부 액세스에서 사용자 제외·'실패 시 허용(fail open)' 설정을 악용하면 계정 단위를 넘어 그룹 전체의 MFA가 무력화됨</t>
         </is>
       </c>
       <c r="F93" s="17" t="inlineStr">
@@ -29382,7 +31563,16 @@
       <c r="N93" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="O93" s="17" t="inlineStr"/>
+      <c r="O93" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- MFA 비활성화·조건부 액세스 제외·MFA 수단 변경 이벤트, 같은 세션 토큰의 다른 IP 재사용
+- 'fail open' 구성과 MFA 요구가 사라진 로그인 성공
+■ 대응
+- 피싱 저항형 MFA(FIDO2)와 'fail open' 금지, MFA·조건부 액세스 변경에 다중 관리자 승인
+- 토큰 보호·세션 수명 단축, 의심 세션 토큰 즉시 폐기</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="17" t="inlineStr">
@@ -29407,7 +31597,8 @@
       </c>
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t>공격자는 일반 인증 메커니즘을 우회하고, 자격 증명에 접근하고, 계정에 지속적으로 접근하기 위해 온프레미스 사용자 ID와 연결된 클라우드 인증 절차에 패치를 적용하거나, 이를 수정하거나, 백도어를 심을 수 있다.</t>
+          <t>- 공격자는 온프레미스-클라우드 하이브리드 ID 연결(PHS·PTA·AD FS)에 백도어를 심어 모든 인증을 통과시키고 자격증명을 수집할 수 있음
+- 연동 지점 하나를 장악하면 페더레이션된 모든 클라우드·SaaS에 지속적 특권 접근이 가능해 피해 범위가 테넌트 전체로 확대됨</t>
         </is>
       </c>
       <c r="F94" s="17" t="inlineStr">
@@ -29451,7 +31642,16 @@
       <c r="N94" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="O94" s="17" t="inlineStr"/>
+      <c r="O94" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- PTA 에이전트·AD FS 서버의 DLL 로드·구성 파일 변경, 토큰 서명 인증서의 비정상 사용
+- 온프레미스 조인 서버에서 발급된 토큰의 광범위한 클라우드 접근
+■ 대응
+- 하이브리드 ID 연동 서버를 Tier0로 취급·접근 최소화, 토큰 서명 인증서 보호·정기 교체
+- AD FS → 클라우드 인증의 이상 토큰 탐지, 가능 시 클라우드 인증으로 전환</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="17" t="inlineStr">
@@ -29476,7 +31676,8 @@
       </c>
       <c r="E95" s="17" t="inlineStr">
         <is>
-          <t>공격자는 침해한 계정에 지속적으로 접근하기 위해 조건부 액세스 정책을 비활성화하거나 수정할 수 있다. 조건부 액세스 정책은 ID 공급자와 ID·접근 관리 시스템이 사용자에게 리소스 접근을 허용할지 판단할 때 쓰는 추가 검증이다.</t>
+          <t>- 공격자는 조건부 액세스·IAM 조건 정책을 수정해(신뢰 IP 추가, MFA 요구 제거, 허용 리전 확대) 침해 계정의 접근을 지속할 수 있음
+- 정책 완화는 정상 관리 변경처럼 보여, 이후 탈취 자격증명이 통제를 그대로 통과하게 만듦</t>
         </is>
       </c>
       <c r="F95" s="17" t="inlineStr">
@@ -29520,7 +31721,16 @@
       <c r="N95" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="O95" s="17" t="inlineStr"/>
+      <c r="O95" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 조건부 액세스·IAM 조건 정책 변경(신뢰 IP 추가·MFA 제거·리전 확대) 이벤트
+- 정책 완화 직후 새 위치·리전에서의 로그인 성공
+■ 대응
+- 조건부 액세스·IAM 정책 변경에 승인 워크플로와 변경 알림
+- 정책을 코드로 관리(IaC)하고 드리프트 자동 복원</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="17" t="inlineStr">
@@ -29545,7 +31755,8 @@
       </c>
       <c r="E96" s="17" t="inlineStr">
         <is>
-          <t>공격자는 사용자에게 다중 인증(MFA) 요청을 보내는 방식으로 MFA 메커니즘을 우회하고 계정에 접근하려 할 수 있다.</t>
+          <t>- 공격자는 유효 자격증명을 가진 상태에서 MFA 푸시 알림을 반복 발생시켜(MFA 피로) 사용자가 승인하도록 유도할 수 있음
+- 자가 비밀번호 재설정(SSPR)의 자동 알림도 악용되며, 반복 푸시·SMS·전화로 사용자의 수락을 노림</t>
         </is>
       </c>
       <c r="F96" s="17" t="inlineStr">
@@ -29589,7 +31800,16 @@
       <c r="N96" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O96" s="17" t="inlineStr"/>
+      <c r="O96" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 짧은 시간 반복되는 MFA 푸시·SMS, 다수 거부 후 1회 승인 패턴
+- SSPR 자동 알림의 비정상 발생
+■ 대응
+- 숫자 매칭 MFA·푸시 횟수 제한, 피싱 저항형 MFA
+- MFA 피로 패턴 알림과 사용자 교육</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="17" t="inlineStr">
@@ -29614,7 +31834,8 @@
       </c>
       <c r="E97" s="17" t="inlineStr">
         <is>
-          <t>공격자는 원격 시스템과 리소스에 접근할 자격 증명을 얻는 수단으로 애플리케이션 액세스 토큰을 탈취할 수 있다.</t>
+          <t>- 공격자는 OAuth 앱 토큰·관리 ID 토큰·K8s 서비스 어카운트 토큰·CI/CD 토큰을 탈취해 사용자·서비스 권한으로 API 작업을 수행할 수 있음
+- 토큰은 MFA를 우회하고 권한 범위만큼 즉시 작동해, 한 건의 토큰 탈취가 다수 조직·서비스로 번짐</t>
         </is>
       </c>
       <c r="F97" s="17" t="inlineStr">
@@ -29658,7 +31879,16 @@
       <c r="N97" s="19" t="n">
         <v>11</v>
       </c>
-      <c r="O97" s="17" t="inlineStr"/>
+      <c r="O97" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 서비스 어카운트·관리 ID·OAuth 토큰의 비정상 출발지 사용, 러너 프로세스 메모리 접근
+- 관리 ID JWT를 반환하도록 리소스 로직 수정, SaaS 통합 토큰의 대량 데이터 조회
+■ 대응
+- 토큰 수명 단축·IMDSv2·토큰 바인딩, 서비스 어카운트 토큰 자동 마운트 최소화
+- CI/CD 비밀 최소화·단기 자격증명, 통합 앱 토큰 범위 제한·이상 사용 알림</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="17" t="inlineStr">
@@ -29683,7 +31913,8 @@
       </c>
       <c r="E98" s="17" t="inlineStr">
         <is>
-          <t>공격자는 원격 시스템이나 리소스에 접근하기 위해 인증에 쓰이는 인증서를 탈취하거나 위조할 수 있다. 디지털 인증서는 메시지나 파일의 서명과 암호화에 자주 쓰이며 인증 자료로도 쓰인다. 예를 들어 Entra ID 장치 인증서와 AD CS(Active Directory Certificate Services) 인증서는 ID에 연결되어 도메인 계정의 자격 증명으로 쓰일 수 있다.</t>
+          <t>- 공격자는 인증 인증서를 탈취하거나 위조해(AD CS, Entra 장치 인증서, 서비스 주체 인증서) 계정·장치를 가장하고 지속·횡적 이동할 수 있음
+- 인증서는 비밀번호 재설정에도 유효기간 동안 유효하며, CA 개인 키를 얻으면 임의 인증서를 위조해 장기 지속성을 확보함</t>
         </is>
       </c>
       <c r="F98" s="17" t="inlineStr">
@@ -29727,7 +31958,16 @@
       <c r="N98" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="O98" s="17" t="inlineStr"/>
+      <c r="O98" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- AD CS 비정상 인증서 발급·등록, 서비스 주체·장치 인증서 생성·내보내기, Key Vault 인증서 덤프
+- 인증서 기반 인증의 비정상 사용(새 SAN·장기 유효기간)
+■ 대응
+- CA 개인 키 보호(HSM)·발급 권한·템플릿 점검, 인증서 정기 교체·폐기
+- 서비스 주체 인증서 접근 로깅과 이상 발급 알림</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="17" t="inlineStr">
@@ -29752,7 +31992,8 @@
       </c>
       <c r="E99" s="17" t="inlineStr">
         <is>
-          <t>공격자는 웹 애플리케이션이나 서비스의 세션 쿠키를 탈취해, 자격 증명 없이도 인증된 사용자로서 웹 애플리케이션이나 인터넷 서비스에 접근할 수 있다. 웹 애플리케이션과 서비스는 사용자가 웹사이트에 인증한 뒤 세션 쿠키를 인증 토큰으로 사용하는 경우가 많다.</t>
+          <t>- 공격자는 브라우저·프로세스 메모리·네트워크에서 웹 세션 쿠키를 탈취해, 자격증명 없이 인증된 사용자로 SaaS·M365에 접근할 수 있음
+- 세션 쿠키는 장기간 유효하고 MFA를 거친 세션을 담고 있어, 탈취 시 다단계 인증을 그대로 우회함</t>
         </is>
       </c>
       <c r="F99" s="17" t="inlineStr">
@@ -29796,7 +32037,16 @@
       <c r="N99" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="O99" s="17" t="inlineStr"/>
+      <c r="O99" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 같은 세션 쿠키의 다른 IP·장치 재사용, 인포스틸러 감염 징후, AiTM 프록시 도메인 접속
+- MFA를 거치지 않은 세션 재개
+■ 대응
+- 피싱 저항형 MFA·세션 토큰 바인딩(장치·IP), 세션 수명 단축
+- 민감 작업 재인증, 의심 세션 즉시 폐기</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="17" t="inlineStr">
@@ -29821,7 +32071,8 @@
       </c>
       <c r="E100" s="17" t="inlineStr">
         <is>
-          <t>공격자는 침해한 시스템을 검색해 안전하지 않게 저장된 자격 증명을 찾아 확보할 수 있다. 이런 자격 증명은 평문 파일(예: 셸 기록(Shell History)), 운영체제나 애플리케이션 전용 저장소(예: 레지스트리의 자격 증명(Credentials in Registry)), 기타 특수 파일·산출물(예: 개인 키(Private Keys)) 등 시스템의 여러 위치에 저장되거나 잘못 놓여 있을 수 있다.</t>
+          <t>- 공격자는 침해 시스템·클라우드 리소스에서 안전하지 않게 저장된 자격증명(구성 파일·환경변수·배포 기록·스토리지 키)을 찾아 확보할 수 있음
+- 클라우드·컨테이너 환경은 자격증명을 로컬 구성·로그에 남기기 쉬워, 코드 실행만으로 추가 접근 수단을 얻게 됨</t>
         </is>
       </c>
       <c r="F100" s="17" t="inlineStr">
@@ -29865,7 +32116,16 @@
       <c r="N100" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="O100" s="17" t="inlineStr"/>
+      <c r="O100" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 서비스 주체 비밀·스토리지 키·배포 기록 열람(listkeys·deployments/read 등), 구성·환경변수 대량 조회
+- Function App 로직 수정 후 비밀 노출
+■ 대응
+- 비밀을 전용 비밀 저장소로 이관(환경변수·구성 파일 지양), 스토리지 키 대신 임시 토큰·RBAC
+- 비밀 접근 로깅과 비밀 스캐닝(코드·배포 기록)</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="17" t="inlineStr">
@@ -29890,7 +32150,8 @@
       </c>
       <c r="E101" s="17" t="inlineStr">
         <is>
-          <t>공격자는 로컬 파일 시스템과 원격 파일 공유를 검색해 안전하지 않게 저장된 자격 증명이 담긴 파일을 찾을 수 있다. 사용자가 자기 자격 증명을 보관하려고 만든 파일, 여러 사람이 함께 쓰는 자격 증명 저장소, 시스템이나 서비스의 비밀번호가 담긴 구성 파일, 비밀번호가 하드코딩된 소스 코드·바이너리 파일 등이 여기에 해당한다.</t>
+          <t>- 공격자는 로컬·공유 파일시스템과 컨테이너·CI 환경을 뒤져 구성 파일·크리덴셜 파일·소스코드의 평문 자격증명을 수집할 수 있음
+- ~/.aws/credentials·kubeconfig·.env·배포 로그 등 정형화된 경로에 키가 남기 쉬워, 공급망 악성코드의 주요 수확 대상이 됨</t>
         </is>
       </c>
       <c r="F101" s="17" t="inlineStr">
@@ -29934,7 +32195,16 @@
       <c r="N101" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="O101" s="17" t="inlineStr"/>
+      <c r="O101" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 자격증명 파일 경로(~/.aws/credentials·kubeconfig·.env 등) 대량 접근, 짧은 시간 다수 파일 읽기
+- CI 러너·컨테이너에서의 비정상 파일 탐색
+■ 대응
+- 비밀 스캐닝(코드·이미지·CI), 하드코딩 금지와 단기 자격증명(OIDC) 전환
+- 크리덴셜 파일 최소화·권한 제한, 노출 시 즉시 교체</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="17" t="inlineStr">
@@ -29959,7 +32229,8 @@
       </c>
       <c r="E102" s="17" t="inlineStr">
         <is>
-          <t>공격자는 자격 증명과 기타 민감한 데이터를 수집하기 위해 클라우드 인스턴스 메타데이터 API에 접근하려 할 수 있다.</t>
+          <t>- 공격자는 인스턴스 메타데이터 API(169.254.169.254)에 접근해 워크로드에 연결된 역할·관리 ID 자격증명과 UserData 비밀을 탈취할 수 있음
+- SSRF 취약점으로 외부에서도 접근 가능하며, 탈취한 역할 자격증명으로 클라우드 API를 호출해 환경 전반으로 확산함</t>
         </is>
       </c>
       <c r="F102" s="17" t="inlineStr">
@@ -30003,7 +32274,16 @@
       <c r="N102" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="O102" s="17" t="inlineStr"/>
+      <c r="O102" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 웹 프로세스에서 169.254.169.254로의 요청(SSRF 징후), IMDS 자격증명이 외부 IP에서 사용됨
+- 다수 메타데이터 엔드포인트(AWS·GCP·Azure) 연속 조회
+■ 대응
+- IMDSv2(세션 토큰) 강제·홉 제한, 워크로드 역할 최소 권한
+- SSRF 방지(출력 URL 검증·메타데이터 차단), 앱에서 메타데이터 접근 차단</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="17" t="inlineStr">
@@ -30028,7 +32308,8 @@
       </c>
       <c r="E103" s="17" t="inlineStr">
         <is>
-          <t>공격자는 컨테이너 환경의 API를 통해 자격 증명을 수집할 수 있다. Docker API, Kubernetes API 같은 이 환경의 API는 사용자가 컨테이너 리소스와 클러스터 구성 요소를 원격으로 관리할 수 있게 한다.</t>
+          <t>- 공격자는 Docker API·Kubernetes API를 통해 컨테이너 로그·클러스터 비밀에서 자격증명을 수집할 수 있음
+- 파드 서비스 어카운트 권한이 과하면 API 서버에서 클러스터 시크릿을 조회할 수 있어, 컨테이너 침해가 클러스터 자격증명 탈취로 이어짐</t>
         </is>
       </c>
       <c r="F103" s="17" t="inlineStr">
@@ -30072,7 +32353,16 @@
       <c r="N103" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O103" s="17" t="inlineStr"/>
+      <c r="O103" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- Kubernetes API의 secrets list·get 요청, Docker API 로그 접근
+- 파드 서비스 어카운트의 비정상 시크릿 조회
+■ 대응
+- 서비스 어카운트 RBAC 최소화(secrets 접근 제한), etcd·시크릿 암호화
+- Docker·K8s API 비공개·인증 강제</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="17" t="inlineStr">
@@ -30097,7 +32387,8 @@
       </c>
       <c r="E104" s="17" t="inlineStr">
         <is>
-          <t>공격자는 사용자 커뮤니케이션 서비스에 저장되거나 전달된 보호되지 않은 자격 증명을 직접 수집할 수 있다. 자격 증명은 이메일, Slack이나 Teams 같은 채팅 서비스, Jira나 Trello 같은 협업 도구 등 사용자 간 소통을 지원하는 서비스를 통해 전송되고 저장될 수 있다. 사용자는 사내 비공개·공개 커뮤니케이션 채널에서 사용자 이름과 비밀번호, API 키, 인증 토큰 등 여러 형태의 자격 증명을 공유할 수 있다.</t>
+          <t>- 공격자는 Slack·Teams·Jira 같은 협업 도구에 공유·저장된 자격증명(비밀번호·API 키·토큰)을 직접 수집할 수 있음
+- 사용자가 채널·이슈에 비밀을 공유하는 관행을 노리며, Slack 워크플로 같은 통합을 악용해 메시지를 자동 검색하기도 함</t>
         </is>
       </c>
       <c r="F104" s="17" t="inlineStr">
@@ -30141,7 +32432,16 @@
       <c r="N104" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="O104" s="17" t="inlineStr"/>
+      <c r="O104" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 협업 도구 메시지의 대량 검색, 통합 워크플로의 비정상 메시지 접근
+- 채널에 공유된 비밀 패턴(키·토큰)
+■ 대응
+- 협업 도구 DLP·비밀 탐지, 채널 내 비밀 공유 금지 정책
+- 통합 앱 권한 최소화와 공유 비밀 즉시 교체</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="17" t="inlineStr">
@@ -30166,7 +32466,8 @@
       </c>
       <c r="E105" s="17" t="inlineStr">
         <is>
-          <t>공격자는 이메일 주소와 계정 목록을 확보하려 할 수 있다. 공격자는 전역 주소 목록(GAL) 같은 Exchange 주소 목록을 덤프하려 할 수 있다.</t>
+          <t>- 공격자는 인증된 세션으로 Exchange·Google Workspace 전역 주소 목록(GAL)·디렉터리를 덤프해 이메일 주소·계정 목록을 수집할 수 있음
+- 수집한 목록은 내부 피싱·BEC·계정 탈취의 표적 선정에 쓰이며, 정상 조회처럼 보여 탐지가 어려움</t>
         </is>
       </c>
       <c r="F105" s="17" t="inlineStr">
@@ -30210,7 +32511,16 @@
       <c r="N105" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="O105" s="17" t="inlineStr"/>
+      <c r="O105" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- GAL 덤프(Get-GlobalAddressList), Graph·관리 모듈의 대량 사서함 열거
+- 디렉터리 사용자 대량 조회
+■ 대응
+- 주소 목록·디렉터리 조회 권한 최소화, 대량 열거 알림
+- 외부·비관리 앱의 디렉터리 접근 제한</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="17" t="inlineStr">
@@ -30235,7 +32545,8 @@
       </c>
       <c r="E106" s="17" t="inlineStr">
         <is>
-          <t>공격자는 클라우드 계정 목록을 확보하려 할 수 있다. 클라우드 계정은 조직이 클라우드 서비스 제공자나 SaaS 애플리케이션 안에서 사용자, 원격 지원, 서비스 또는 리소스 관리 용도로 만들고 구성한 계정이다.</t>
+          <t>- 공격자는 인증된 접근으로 IAM 사용자·역할·서비스 계정·디렉터리 사용자 목록을 열거해 환경의 계정 구조를 파악할 수 있음
+- 고권한 계정·서비스 계정을 식별해 후속 무차별 대입·스피어피싱·계정 탈취의 표적을 좁힘</t>
         </is>
       </c>
       <c r="F106" s="17" t="inlineStr">
@@ -30279,7 +32590,16 @@
       <c r="N106" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="O106" s="17" t="inlineStr"/>
+      <c r="O106" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- IAM·디렉터리 대량 열거(ListUsers·ListRoles·az ad user list), AzureHound·ROADTools 사용 패턴
+- 짧은 시간 다수 사용자·역할 조회
+■ 대응
+- 열거 권한 최소화, 대량 디렉터리·IAM 조회 알림
+- 특권 계정 가시성 제한과 이상 조회 모니터링</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="17" t="inlineStr">
@@ -30304,7 +32624,8 @@
       </c>
       <c r="E107" s="17" t="inlineStr">
         <is>
-          <t>공격자는 IaaS(Infrastructure-as-a-Service) 환경에서 사용 가능한 인프라와 리소스를 파악하려 할 수 있다. 여기에는 인스턴스, 가상 머신, 스냅샷 같은 컴퓨팅 서비스 리소스와 스토리지·데이터베이스 서비스 등 다른 서비스의 리소스가 포함된다.</t>
+          <t>- 공격자는 클라우드 API·CLI로 인스턴스·스토리지·DB·네트워크 등 IaaS 리소스를 열거해 환경 구성과 공격 대상 가치를 파악할 수 있음
+- 탈취한 액세스 키로 접근 가능한 리소스를 식별하고, 버킷·DB의 권한·공개 여부를 확인해 다음 단계(지속성·데이터 접근)를 설계함</t>
         </is>
       </c>
       <c r="F107" s="17" t="inlineStr">
@@ -30348,7 +32669,16 @@
       <c r="N107" s="19" t="n">
         <v>17</v>
       </c>
-      <c r="O107" s="17" t="inlineStr"/>
+      <c r="O107" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 대량 Describe·List 호출(DescribeInstances·ListBuckets 등), 워드리스트 기반 스토리지 스캔
+- 탈취 키의 광범위 리소스 열거, 컨테이너 환경 포트·네트워크 스캔
+■ 대응
+- 최소 권한·열거 API 제한, 대량 탐색 호출 알림
+- 스토리지 공개 차단(퍼블릭 액세스 블록)과 리소스 접근 모니터링</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="17" t="inlineStr">
@@ -30373,7 +32703,8 @@
       </c>
       <c r="E108" s="17" t="inlineStr">
         <is>
-          <t>공격자는 탈취한 자격 증명으로 클라우드 서비스 대시보드 GUI를 사용해 운영 중인 클라우드 환경에서 특정 서비스, 리소스, 기능 같은 유용한 정보를 얻을 수 있다. 예를 들어 GCP Command Center로 모든 자산을 보고, 잠재적 보안 위험에 대한 발견 사항을 검토하고, 공인 IP 주소와 열린 포트 찾기 같은 추가 쿼리를 실행할 수 있다.</t>
+          <t>- 공격자는 탈취한 자격증명으로 클라우드 관리 콘솔 GUI에 로그인해 서비스·리소스·보안 발견 사항을 한눈에 파악할 수 있음
+- 콘솔은 API 요청 없이도 많은 정보를 보여 줘, 수동 API 호출 흔적을 남기지 않고 환경을 정찰함</t>
         </is>
       </c>
       <c r="F108" s="17" t="inlineStr">
@@ -30417,7 +32748,15 @@
       <c r="N108" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="O108" s="17" t="inlineStr"/>
+      <c r="O108" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 콘솔 로그인(ConsoleLogin)의 비정상 위치·시간, 역할 전환(SwitchRole), 보안 콘솔 대량 열람
+■ 대응
+- 콘솔 접근에 피싱 저항형 MFA·조건부 액세스, 콘솔 로그인 알림
+- 관리 콘솔 접근 출발지 제한</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="17" t="inlineStr">
@@ -30442,7 +32781,8 @@
       </c>
       <c r="E109" s="17" t="inlineStr">
         <is>
-          <t>공격자는 접근을 확보한 뒤 시스템에서 실행 중인 클라우드 서비스를 열거하려 할 수 있다. 방법은 PaaS, IaaS, SaaS에 따라 다를 수 있다. 클라우드 제공자마다 다양한 서비스가 있으며, CI/CD(지속적 통합·지속적 전달), Lambda 함수, Entra ID 등이 포함될 수 있다. AWS GuardDuty나 Microsoft Defender for Cloud 같은 보안 서비스와 AWS CloudTrail, Google Cloud Audit Logs 같은 로깅 서비스도 포함될 수 있다.</t>
+          <t>- 공격자는 Graph·Resource Manager API나 열거 도구(Pacu·Stormspotter·ROADTools)로 환경에 활성화된 클라우드 서비스·앱·정책·보안 도구를 파악할 수 있음
+- 어떤 서비스·방어가 있는지 알아내 데이터·자격증명 표적과 방어 무력화 대상을 정하는 선행 정찰 단계임</t>
         </is>
       </c>
       <c r="F109" s="17" t="inlineStr">
@@ -30486,7 +32826,16 @@
       <c r="N109" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="O109" s="17" t="inlineStr"/>
+      <c r="O109" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- Graph·ARM 대량 열거, Pacu·ROADTools·Stormspotter 사용 패턴, 서비스·정책 연속 조회
+- 보안 서비스·로깅 구성 조회 직후의 방어 무력화 시도
+■ 대응
+- 열거 권한 최소화, 대량 서비스·정책 조회 알림
+- 정찰 직후 이어지는 로깅·방어 변경을 연계 탐지</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="17" t="inlineStr">
@@ -30511,7 +32860,8 @@
       </c>
       <c r="E110" s="17" t="inlineStr">
         <is>
-          <t>공격자는 클라우드 스토리지 인프라의 객체를 열거할 수 있다. 자동화된 탐색 과정에서 이 정보를 바탕으로 클라우드 스토리지의 전체 또는 특정 객체를 요청하는 등 후속 행동을 정할 수 있다. 로컬 호스트의 파일 및 디렉터리 탐색(File and Directory Discovery)처럼, 사용 가능한 스토리지 서비스를 파악한 뒤(즉, 클라우드 인프라 탐색(Cloud Infrastructure Discovery)) 클라우드 인프라에 저장된 콘텐츠·객체에 접근할 수 있다.</t>
+          <t>- 공격자는 클라우드 스토리지 객체 열거 API(S3 ListObjects, Azure List Blobs)로 버킷·객체 목록을 파악할 수 있음
+- 어떤 데이터가 어디에 있는지 식별해 유출 대상을 좁히며, 공개 설정된 스토리지를 찾는 선행 정찰로 쓰임</t>
         </is>
       </c>
       <c r="F110" s="17" t="inlineStr">
@@ -30555,7 +32905,16 @@
       <c r="N110" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="O110" s="17" t="inlineStr"/>
+      <c r="O110" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- ListBuckets·ListObjects·List Blobs 대량 호출, 공개 설정 버킷 탐색 패턴
+- 탈취 키의 광범위 객체 열거
+■ 대응
+- 스토리지 열거 권한 최소화, 퍼블릭 액세스 블록·버킷 정책으로 공개 차단
+- 대량 객체 열거 알림과 접근 로깅</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="17" t="inlineStr">
@@ -30580,7 +32939,8 @@
       </c>
       <c r="E111" s="17" t="inlineStr">
         <is>
-          <t>공격자는 컨테이너 환경에서 사용 가능한 컨테이너와 기타 리소스를 파악하려 할 수 있다. 기타 리소스에는 이미지, 배포, 파드, 노드와 클러스터 상태 같은 정보가 포함될 수 있다.</t>
+          <t>- 공격자는 Kubernetes 대시보드·Docker/Kubernetes API로 컨테이너·이미지·파드·노드·클러스터 상태를 열거할 수 있음
+- Docker 로그가 환경 구성·클라우드 제공자 정보를 흘려, 횡적 이동과 실행 방법을 설계하는 단서가 됨</t>
         </is>
       </c>
       <c r="F111" s="17" t="inlineStr">
@@ -30620,7 +32980,16 @@
       <c r="N111" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O111" s="17" t="inlineStr"/>
+      <c r="O111" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- Kubernetes API·kubelet·Docker API의 리소스 열거 요청, 대시보드 접근
+- Docker 로그 조회를 통한 환경 정보 수집
+■ 대응
+- API 서버·kubelet 인증 강제·비공개, RBAC로 조회 권한 제한
+- 대시보드 비공개와 로그 접근 통제</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="17" t="inlineStr">
@@ -30645,7 +33014,8 @@
       </c>
       <c r="E112" s="17" t="inlineStr">
         <is>
-          <t>공격자는 유용한 데이터를 찾기 위해 시스템 및 서비스 로그를 열거할 수 있다. 이러한 로그에서 사용자 인증 기록(계정 탐색(Account Discovery)), 보안 소프트웨어나 취약한 소프트웨어(소프트웨어 탐색(Software Discovery)), 침해한 네트워크 안의 호스트(원격 시스템 탐색(Remote System Discovery)) 등 공격자에게 가치 있는 다양한 정보를 얻을 수 있다.</t>
+          <t>- 공격자는 시스템·서비스 로그를 열거해 인증 기록·보안 소프트웨어·네트워크 호스트 등 가치 있는 정보를 수집할 수 있음
+- 클라우드 로그·SIEM을 표적으로 하며, 사고 대응 로그를 실시간 관찰해 자신의 기법을 조정하기도 함</t>
         </is>
       </c>
       <c r="F112" s="17" t="inlineStr">
@@ -30685,7 +33055,16 @@
       <c r="N112" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="O112" s="17" t="inlineStr"/>
+      <c r="O112" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 로그 대량 조회·내보내기(CloudTrail·CloudWatch), 호스트 로그 수집 유틸리티 실행
+- SIEM·중앙 로깅에 대한 비정상 접근
+■ 대응
+- 로그 조회·내보내기 권한 최소화, 대량 로그 접근 알림
+- 로그를 별도 계정에 불변 저장해 관찰·변조 제한</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="17" t="inlineStr">
@@ -30710,7 +33089,8 @@
       </c>
       <c r="E113" s="17" t="inlineStr">
         <is>
-          <t>공격자는 클라우드 그룹과 권한 설정을 찾으려 할 수 있다. 클라우드 권한 그룹 정보는 환경 안에서 사용자와 그룹이 맡은 역할, 그리고 특정 그룹에 어떤 사용자가 연결되어 있는지 파악하는 데 도움이 된다.</t>
+          <t>- 공격자는 클라우드 그룹·역할·정책·ACL을 열거해 어떤 계정이 어떤 권한을 가지는지 파악할 수 있음
+- 고권한 그룹·객체 접근 권한을 식별해 권한 상승·데이터 접근의 표적 계정을 정하는 선행 정찰 단계임</t>
         </is>
       </c>
       <c r="F113" s="17" t="inlineStr">
@@ -30754,7 +33134,16 @@
       <c r="N113" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="O113" s="17" t="inlineStr"/>
+      <c r="O113" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 역할·그룹·정책·ACL 대량 열거(ListRolePolicies·GetBucketAcl·az ad ... 등)
+- 권한 매핑 도구(ROADTools·AADInternals) 사용 패턴
+■ 대응
+- 권한·그룹 열거 권한 최소화, 대량 조회 알림
+- 특권 그룹 가시성 제한과 정기 권한 검토</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="17" t="inlineStr">
@@ -30779,7 +33168,8 @@
       </c>
       <c r="E114" s="17" t="inlineStr">
         <is>
-          <t>공격자는 네트워크 내부에 들어온 뒤 원격 서비스를 익스플로잇해 내부 시스템에 무단으로 접근할 수 있다. 소프트웨어 취약점 익스플로잇은 공격자가 프로그램, 서비스, 운영체제 소프트웨어나 커널의 프로그래밍 오류를 이용해 자신이 제어하는 코드를 실행하는 것이다. 침해 이후 원격 서비스를 익스플로잇하는 흔한 목적은 원격 시스템에 접근하기 위한 측면 이동이다.</t>
+          <t>- 공격자는 내부망 진입 후 취약한 원격 서비스(SMB·RDP·DB, vCenter·ESXi 등)를 익스플로잇해 다른 시스템으로 횡적 이동할 수 있음
+- 취약 서비스 권한에 따라 권한 상승도 가능하며, vCenter 침해는 VM·하이퍼바이저로의 이동 발판이 됨</t>
         </is>
       </c>
       <c r="F114" s="17" t="inlineStr">
@@ -30823,7 +33213,16 @@
       <c r="N114" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O114" s="17" t="inlineStr"/>
+      <c r="O114" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 내부 서비스(SMB·RDP·DB·vCenter)에 대한 익스플로잇 트래픽, 패치 미적용 서비스로의 비정상 접근
+- 클러스터 내부 파드 간 익스플로잇 시도
+■ 대응
+- 내부 긴급 패치·세분화(마이크로세그멘테이션), vCenter·ESXi 접근 제한
+- K8s 네트워크 정책으로 파드 간 트래픽 제한</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="17" t="inlineStr">
@@ -30848,7 +33247,8 @@
       </c>
       <c r="E115" s="17" t="inlineStr">
         <is>
-          <t>공격자는 환경 안의 계정이나 시스템에 이미 접근한 뒤, 내부 스피어피싱으로 추가 정보에 접근하거나 같은 조직의 다른 사용자를 침해할 수 있다. 내부 스피어피싱은 다단계 캠페인으로, 먼저 사용자의 장치를 장악하거나 사용자의 계정 자격 증명을 침해해 정상 계정을 확보한다. 이후 신뢰받는 내부 계정을 이용해 더 많은 피해자가 피싱에 속을 가능성을 높이며, 사칭(Impersonation)을 함께 쓰는 경우가 많다.</t>
+          <t>- 공격자는 침해한 내부 계정으로 동료에게 스피어피싱을 보내 추가 정보·계정을 확보할 수 있음
+- 신뢰받는 내부 발신자라 수신자가 쉽게 속으며, Teams 같은 내부 협업 채널로도 악성 콘텐츠를 퍼뜨림</t>
         </is>
       </c>
       <c r="F115" s="17" t="inlineStr">
@@ -30888,7 +33288,16 @@
       <c r="N115" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O115" s="17" t="inlineStr"/>
+      <c r="O115" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 내부 계정의 비정상 대량 발송, 내부 메일·Teams의 악성 링크 유포
+- 침해 계정의 평소와 다른 수신자·시간대 발송
+■ 대응
+- 내부 피싱 탐지(링크·첨부 검사), 침해 의심 계정 격리
+- Teams 외부·게스트 제한과 사용자 신고 체계</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="17" t="inlineStr">
@@ -30913,7 +33322,8 @@
       </c>
       <c r="E116" s="17" t="inlineStr">
         <is>
-          <t>공격자는 온프레미스 사용자 ID와 동기화되거나 페더레이션된 유효한 계정(Valid Accounts)으로 침해한 환경에서 접근 가능한 클라우드 서비스에 로그인할 수 있다. 이후 공격자는 로그인한 사용자로서 관리 작업을 수행하거나 클라우드에 호스팅된 리소스에 접근할 수 있다.</t>
+          <t>- 공격자는 동기화·페더레이션된 유효 계정으로 클라우드 서비스에 로그인해 관리 작업·리소스 접근으로 횡적 이동할 수 있음
+- 도메인 자격증명이나 앱 토큰으로 콘솔·CLI에 접속하며, 온프레미스-클라우드를 오가는 이동 경로가 됨</t>
         </is>
       </c>
       <c r="F116" s="17" t="inlineStr">
@@ -30957,7 +33367,16 @@
       <c r="N116" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="O116" s="17" t="inlineStr"/>
+      <c r="O116" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 동기화·페더레이션 계정의 비정상 콘솔·CLI 로그인, 온프레미스↔클라우드 교차 인증
+- 앱 토큰 기반 로그인의 비정상 출발지
+■ 대응
+- 조건부 액세스·피싱 저항형 MFA, 동기화 서버(Entra Connect) Tier0 보호
+- 고권한 동기화 계정 최소화와 이상 로그인 알림</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="17" t="inlineStr">
@@ -30982,7 +33401,8 @@
       </c>
       <c r="E117" s="17" t="inlineStr">
         <is>
-          <t>공격자는 유효한 계정(Valid Accounts)을 이용해 클라우드 네이티브 방식으로 접근 가능한 클라우드 호스팅 컴퓨팅 인프라에 직접 로그인할 수 있다. 많은 클라우드 제공자는 Azure Serial Console, AWS EC2 Instance Connect, AWS System Manager처럼 Cloud API로 접근할 수 있는 가상 인프라 대화형 연결 기능을 제공한다.</t>
+          <t>- 공격자는 유효 계정으로 클라우드 네이티브 대화형 연결(Azure Serial Console, EC2 Instance Connect, SSM)에 직접 로그인해 VM에 접근할 수 있음
+- 이들 연결은 기본적으로 SYSTEM·root 수준 콘솔 접근을 주는 경우가 있어, 환경을 가로질러 피벗하는 데 쓰임</t>
         </is>
       </c>
       <c r="F117" s="17" t="inlineStr">
@@ -31026,7 +33446,16 @@
       <c r="N117" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O117" s="17" t="inlineStr"/>
+      <c r="O117" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- Serial Console·EC2 Instance Connect·SSM 연결 이벤트의 비정상 주체·대상
+- VM 직접 콘솔 접근 직후의 고권한 작업
+■ 대응
+- 네이티브 VM 연결 권한 최소화·승인, 중개 접근(배스천)으로 대체
+- 연결 이벤트 알림과 SSH 키·토큰 관리</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="17" t="inlineStr">
@@ -31130,7 +33559,8 @@
       </c>
       <c r="E119" s="17" t="inlineStr">
         <is>
-          <t>공격자는 네트워크 드라이브나 내부 코드 저장소 같은 공유 저장 위치에 콘텐츠를 추가해 원격 시스템에 페이로드를 전달할 수 있다. 네트워크 드라이브나 기타 공유 위치에 저장된 콘텐츠는 정상 파일에 악성 프로그램, 스크립트, 익스플로잇 코드를 추가하는 방식으로 오염될 수 있다. 사용자가 오염된 공유 콘텐츠를 열면 악성 부분이 실행되어 원격 시스템에서 공격자의 코드가 동작할 수 있다. 공격자는 오염된 공유 콘텐츠를 이용해 측면 이동할 수 있다.</t>
+          <t>- 공격자는 공유 드라이브·코드 저장소·공유 문서에 악성 콘텐츠를 심어, 사용자가 열 때 코드가 실행되게 횡적 이동할 수 있음
+- 정상 파일에 악성 코드·바로가기를 섞어 자주 쓰는 공유 위치에 두면 반복 재감염과 광범위 확산이 일어남</t>
         </is>
       </c>
       <c r="F119" s="17" t="inlineStr">
@@ -31170,7 +33600,16 @@
       <c r="N119" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O119" s="17" t="inlineStr"/>
+      <c r="O119" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 공유 저장소·문서의 악성 매크로·스크립트·위장 .LNK 추가, 공유 바이너리 변경
+- 공유 콘텐츠 열람 직후의 비정상 실행
+■ 대응
+- 공유 저장소 쓰기 권한 최소화·버전 관리, 문서 매크로 차단
+- 공유 코드·문서 무결성 점검과 악성코드 스캔</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="17" t="inlineStr">
@@ -31195,7 +33634,8 @@
       </c>
       <c r="E120" s="17" t="inlineStr">
         <is>
-          <t>공격자는 탈취한 애플리케이션 액세스 토큰으로 일반 인증 절차를 우회해 원격 시스템의 제한된 계정, 정보, 서비스에 접근할 수 있다. 이런 토큰은 보통 사용자나 서비스에게서 탈취되어 로그인 자격 증명 대신 사용된다.</t>
+          <t>- 공격자는 탈취한 OAuth 앱 토큰·서비스 어카운트 토큰·임시 자격증명으로 정상 인증을 우회해 클라우드·SaaS 리소스에 접근·횡적 이동할 수 있음
+- 리프레시 토큰은 장기 백그라운드 접근을 주고 MFA를 우회하며, 한 토큰이 메일·파일·연결 서비스로 접근을 확장함</t>
         </is>
       </c>
       <c r="F120" s="17" t="inlineStr">
@@ -31239,7 +33679,16 @@
       <c r="N120" s="19" t="n">
         <v>11</v>
       </c>
-      <c r="O120" s="17" t="inlineStr"/>
+      <c r="O120" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- OAuth 앱·서비스 어카운트 토큰의 비정상 출발지 사용, 리프레시 토큰의 장기 백그라운드 접근
+- 토큰으로 수행된 평소와 다른 API(메일 검색·연락처 열거 등)
+■ 대응
+- 토큰 수명 단축·범위 최소화, 리프레시 토큰 보호·조건부 액세스
+- 과도 권한 OAuth 앱 제거와 토큰 이상 사용 알림</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="17" t="inlineStr">
@@ -31264,7 +33713,8 @@
       </c>
       <c r="E121" s="17" t="inlineStr">
         <is>
-          <t>공격자는 탈취한 세션 쿠키로 웹 애플리케이션과 서비스에 인증할 수 있다. 세션이 이미 인증된 상태이므로 이 기법은 일부 다중 인증(MFA) 프로토콜을 우회한다.</t>
+          <t>- 공격자는 탈취한 웹 세션 쿠키를 자신의 브라우저에 주입해, 세션이 유효한 동안 피해 사용자로 SaaS·클라우드에 접근할 수 있음
+- 이미 인증된 세션이라 MFA를 우회하며, 쿠키가 장기 유효해 사용자 활동이 없어도 접근이 유지됨</t>
         </is>
       </c>
       <c r="F121" s="17" t="inlineStr">
@@ -31308,7 +33758,16 @@
       <c r="N121" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="O121" s="17" t="inlineStr"/>
+      <c r="O121" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 동일 세션 쿠키의 다른 IP·장치 재사용, 위조 쿠키(비정상 duo-sid 등)로의 접근
+- MFA 없이 재개된 세션
+■ 대응
+- 세션 토큰 장치·IP 바인딩, 세션 수명 단축, 피싱 저항형 MFA
+- 민감 작업 재인증과 의심 세션 폐기</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="17" t="inlineStr">
@@ -31333,7 +33792,8 @@
       </c>
       <c r="E122" s="17" t="inlineStr">
         <is>
-          <t>공격자는 AiTM(adversary-in-the-middle) 기법으로 둘 이상의 네트워크 장치 사이에 자리 잡아 네트워크 스니핑(Network Sniffing), 전송 데이터 조작(Transmitted Data Manipulation), 재전송 공격(자격 증명 접근을 위한 익스플로잇(Exploitation for Credential Access)) 같은 후속 행위를 도울 수 있다. ARP, DNS, LLMNR 등 네트워크 트래픽 흐름을 결정하는 일반 네트워크 프로토콜의 기능을 악용해, 장치가 공격자가 제어하는 시스템을 거쳐 통신하도록 강제하고 정보를 수집하거나 추가 작업을 수행할 수 있다.</t>
+          <t>- 공격자는 네트워크 경로 중간에 자리 잡아(AiTM 프록시, DNS·ARP 조작, 캡티브 포털 침해) 자격증명·세션 토큰·MFA 응답을 가로챌 수 있음
+- 리버스 프록시형 피싱은 MFA를 거친 세션 쿠키까지 탈취해 다단계 인증을 무력화하며, 정상 로그인처럼 보임</t>
         </is>
       </c>
       <c r="F122" s="17" t="inlineStr">
@@ -31373,7 +33833,16 @@
       <c r="N122" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O122" s="17" t="inlineStr"/>
+      <c r="O122" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 알려진 AiTM 프록시 도메인·리버스 프록시 패턴, 같은 세션 토큰의 다른 IP 재사용
+- 비정상 DNS 응답·CoreDNS 설정 변경, 클러스터 내 ARP·IP 스푸핑 징후
+■ 대응
+- 피싱 저항형 MFA(FIDO2)로 AiTM 세션 탈취 무력화, 토큰 바인딩·세션 IP 고정
+- CoreDNS·CNI 보안 설정, 캡티브 포털·네트워크 경로 무결성 점검</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="17" t="inlineStr">
@@ -31398,7 +33867,8 @@
       </c>
       <c r="E123" s="17" t="inlineStr">
         <is>
-          <t>시스템이나 네트워크에 자리를 잡은 공격자는 자동화된 기법으로 내부 데이터를 수집할 수 있다. 예를 들어 명령 및 스크립트 인터프리터(Command and Scripting Interpreter)를 이용해 정해진 시간 간격마다 파일 형식, 위치, 이름 같은 기준에 맞는 정보를 검색하고 복사할 수 있다.</t>
+          <t>- 공격자는 클라우드 API·CLI·데이터 파이프라인·ETL로 내부 데이터를 자동 수집할 수 있음
+- 정해진 기준으로 다수 서비스에서 대량·반복 수집해 유출 규모를 키우며, 정상 데이터 처리와 섞여 탐지가 어려움</t>
         </is>
       </c>
       <c r="F123" s="17" t="inlineStr">
@@ -31442,7 +33912,16 @@
       <c r="N123" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="O123" s="17" t="inlineStr"/>
+      <c r="O123" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 짧은 시간 대량 데이터 조회(Graph·ETL·파이프라인), 다수 서비스에 걸친 반복 수집 패턴
+- 비정상 주체의 대량 파일·메일 수집
+■ 대응
+- 대량 접근 임계값 알림·DLP, 데이터 접근 권한 최소화
+- 파이프라인·ETL 권한 통제와 이상 수집 모니터링</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="17" t="inlineStr">
@@ -31467,7 +33946,8 @@
       </c>
       <c r="E124" s="17" t="inlineStr">
         <is>
-          <t>공격자는 클라우드 스토리지의 데이터에 접근할 수 있다.</t>
+          <t>- 공격자는 S3·Blob·GCS 등 클라우드 스토리지와 OneDrive·Drive의 데이터에 접근해 민감 정보를 대량 수집할 수 있음
+- 공개·과도 허용 설정이나 탈취 키로 API를 통해 직접 접근하며, SAS URI·스냅샷 공유로 인증 없이 반출하기도 함</t>
         </is>
       </c>
       <c r="F124" s="17" t="inlineStr">
@@ -31511,7 +33991,16 @@
       <c r="N124" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="O124" s="17" t="inlineStr"/>
+      <c r="O124" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 대량 GetObject·CopyObject, SAS URI 생성·파일 공유 마운트, soft-delete 객체 복구
+- 공개 전환된 버킷·스토리지, 비정상 주체의 대량 다운로드
+■ 대응
+- 퍼블릭 액세스 블록·버킷 정책으로 공개 차단, SAS·스냅샷 공유 제한
+- 스토리지 암호화·접근 로깅과 대량 반출 알림</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="17" t="inlineStr">
@@ -31536,7 +34025,8 @@
       </c>
       <c r="E125" s="17" t="inlineStr">
         <is>
-          <t>공격자는 정보 저장소를 이용해 가치 있는 정보를 캐낼 수 있다. 정보 저장소는 보통 사용자 간 협업이나 정보 공유를 위해 정보를 저장하는 도구로, 자격 증명 접근(Credential Access), 측면 이동(Lateral Movement), 방어 회피(Defense Evasion) 같은 추가 목표나 목표 정보에 대한 직접 접근에 도움이 되는 다양한 데이터를 담고 있을 수 있다. 공격자는 외부 공유 기능을 악용해 민감한 문서를 조직 외부 수신자와 공유할 수도 있다(즉, 클라우드 계정으로 데이터 전송(Transfer Data to Cloud Account)).</t>
+          <t>- 공격자는 SharePoint·Confluence·코드 저장소·DB·협업 메시지 같은 정보 저장소에서 가치 있는 데이터와 자격증명을 수집할 수 있음
+- 과도 허용·공개 설정된 저장소나 백엔드 API로 직접 접근하며, 외부 공유 기능으로 민감 문서를 조직 밖으로 내보내기도 함</t>
         </is>
       </c>
       <c r="F125" s="17" t="inlineStr">
@@ -31580,7 +34070,16 @@
       <c r="N125" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O125" s="17" t="inlineStr"/>
+      <c r="O125" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 정보 저장소(DB·SharePoint·코드·메시징)의 대량 조회·외부 공유, 백엔드 API 직접 접근
+- 과도 허용·공개 설정된 저장소 접근
+■ 대응
+- 저장소 접근 최소 권한·외부 공유 제한, 공개 설정 점검
+- 대량 조회·외부 공유 알림과 DLP</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="17" t="inlineStr">
@@ -31605,7 +34104,8 @@
       </c>
       <c r="E126" s="17" t="inlineStr">
         <is>
-          <t>공격자는 Confluence 저장소를 이용해 가치 있는 정보를 캐낼 수 있다. Confluence는 개발 환경에서 Atlassian JIRA와 함께 쓰이는 경우가 많고 주로 개발 관련 문서를 저장하지만, 다음과 같이 더 다양한 유용한 정보를 담고 있을 수 있다 (세부 항목은 참조 열 참조)</t>
+          <t>- 공격자는 Confluence 위키에서 네트워크 구성도·시스템 문서·테스트 자격증명·소스코드 조각 등 가치 있는 정보를 수집할 수 있음
+- 개발·운영 문서가 모여 있어 추가 자격증명·고권한 계정 단서를 얻는 수집 대상이 됨</t>
         </is>
       </c>
       <c r="F126" s="17" t="inlineStr">
@@ -31649,7 +34149,15 @@
       <c r="N126" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="O126" s="17" t="inlineStr"/>
+      <c r="O126" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- Confluence 공간 대량 열람·검색, 자격증명 패턴 포함 페이지 접근
+■ 대응
+- 공간 접근 권한 최소화·공개 공간 점검, 문서 내 비밀 제거
+- 대량 열람 알림과 외부 공유 제한</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="17" t="inlineStr">
@@ -31674,7 +34182,8 @@
       </c>
       <c r="E127" s="17" t="inlineStr">
         <is>
-          <t>공격자는 SharePoint 저장소를 가치 있는 정보를 캐내는 출처로 이용할 수 있다. SharePoint에는 내부 네트워크와 시스템의 구조와 기능을 파악하는 데 유용한 정보가 들어 있는 경우가 많다. 예를 들어 공격자에게 잠재적 가치가 있고 SharePoint에서 찾을 수 있는 정보는 다음과 같다 (세부 항목은 참조 열 참조)</t>
+          <t>- 공격자는 SharePoint에서 내부 구조·절차 문서·테스트 자격증명·네트워크 공유 링크 등 민감 정보를 수집할 수 있음
+- 조직 지식이 집중돼 있어 횡적 이동·추가 자격증명 확보의 핵심 수집 대상이 됨</t>
         </is>
       </c>
       <c r="F127" s="17" t="inlineStr">
@@ -31718,7 +34227,15 @@
       <c r="N127" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="O127" s="17" t="inlineStr"/>
+      <c r="O127" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- SharePoint 대량 다운로드·열거(spwebmember 등), 침해 자격증명의 대량 접근
+■ 대응
+- 사이트 접근 권한 최소화·민감 라이브러리 보호, 외부 공유 제한
+- 대량 다운로드 알림과 DLP</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="17" t="inlineStr">
@@ -31743,7 +34260,8 @@
       </c>
       <c r="E128" s="17" t="inlineStr">
         <is>
-          <t>공격자는 코드 저장소를 이용해 가치 있는 정보를 수집할 수 있다. 코드 저장소는 소스 코드를 저장하고 소프트웨어 빌드를 자동화하는 도구·서비스로, 내부에 호스팅하거나 GitHub, GitLab, SourceForge, Bitbucket 같은 외부 사이트에 비공개로 호스팅할 수 있다. 사용자는 보통 웹 애플리케이션이나 git 같은 명령줄 유틸리티로 코드 저장소를 사용한다.</t>
+          <t>- 공격자는 GitHub·GitLab·Bitbucket 등 코드 저장소에서 소스코드와 하드코딩된 자격증명을 수집할 수 있음
+- 소스코드로 익스플로잇을 개발하고, 코드 속 비밀로 클라우드 리소스에 접근하는 고가치 수집 대상임</t>
         </is>
       </c>
       <c r="F128" s="17" t="inlineStr">
@@ -31787,7 +34305,16 @@
       <c r="N128" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="O128" s="17" t="inlineStr"/>
+      <c r="O128" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 코드 저장소 대량 복제·열거, 탈취 토큰(_authToken 등)의 비정상 사용
+- 비밀 패턴 검색·접근
+■ 대응
+- 저장소 접근 최소화·토큰 범위 제한, 비밀 스캐닝으로 하드코딩 제거
+- 대량 복제·다운로드 알림</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="17" t="inlineStr">
@@ -31812,7 +34339,8 @@
       </c>
       <c r="E129" s="17" t="inlineStr">
         <is>
-          <t>공격자는 고객 관계 관리(CRM) 소프트웨어를 이용해 가치 있는 정보를 캐낼 수 있다. CRM 소프트웨어는 조직이 고객과의 상호작용을 추적·관리하고 고객 데이터를 저장하는 데 쓰인다.</t>
+          <t>- 공격자는 Salesforce·Dynamics 365·HubSpot 등 CRM에서 고객 PII·구매 이력·지원 상호작용을 수집할 수 있음
+- 수집한 고객 정보로 맞춤 피싱·SIM 스와핑을 하거나 하위 조직을 노려 금전 이득·추가 침해로 이어감</t>
         </is>
       </c>
       <c r="F129" s="17" t="inlineStr">
@@ -31856,7 +34384,15 @@
       <c r="N129" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="O129" s="17" t="inlineStr"/>
+      <c r="O129" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- CRM 대량 레코드 조회·내보내기, 연결 앱·통합 토큰의 비정상 대량 접근
+■ 대응
+- CRM 접근 최소화·대량 내보내기 제한, 연결 앱 권한 검토
+- 대량 조회 알림과 이상 행위 모니터링</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="17" t="inlineStr">
@@ -31881,7 +34417,8 @@
       </c>
       <c r="E130" s="17" t="inlineStr">
         <is>
-          <t>공격자는 Microsoft Teams, Google Chat, Slack 같은 채팅·메시징 애플리케이션을 이용해 가치 있는 정보를 캐낼 수 있다.</t>
+          <t>- 공격자는 Teams·Slack·Google Chat 등 메시징 앱에서 테스트 자격증명·소스조각·내부 논의·사고 대응 정보를 수집할 수 있음
+- 채팅으로 환경을 파악하고 진행 중인 사고 대응을 관찰해 자신의 기법을 조정함</t>
         </is>
       </c>
       <c r="F130" s="17" t="inlineStr">
@@ -31925,7 +34462,15 @@
       <c r="N130" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="O130" s="17" t="inlineStr"/>
+      <c r="O130" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 메시징 앱 대량 검색·내보내기, 사고 대응 키워드 검색, 침해 계정의 대화 열람
+■ 대응
+- 메시징 DLP·비밀 탐지, 접근 최소화와 통합 앱 권한 통제
+- 대량 검색·내보내기 알림</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="17" t="inlineStr">
@@ -31950,7 +34495,8 @@
       </c>
       <c r="E131" s="17" t="inlineStr">
         <is>
-          <t>공격자는 데이터베이스를 이용해 가치 있는 정보를 캐낼 수 있다. 이러한 데이터베이스는 온프레미스나 클라우드(PaaS와 SaaS 환경 모두)에 호스팅될 수 있다.</t>
+          <t>- 공격자는 관리형·클라우드 DB(RDS·Azure SQL·Firebase·Snowflake, MySQL·MongoDB 등)에서 사용자·해시·PII·금융 데이터를 수집할 수 있음
+- DB 설정 파일의 자격증명으로 접근하거나 과도 허용·공개 DB에 직접 붙으며, 수집 데이터는 횡적 이동·갈취·판매에 쓰임</t>
         </is>
       </c>
       <c r="F131" s="17" t="inlineStr">
@@ -31994,7 +34540,16 @@
       <c r="N131" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="O131" s="17" t="inlineStr"/>
+      <c r="O131" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- DB 대량 조회·덤프, 공개·약인증 DB 접근, DB 설정 파일(~/.pgpass 등) 읽기
+- 관리형 DB의 비정상 대량 SELECT·export
+■ 대응
+- DB 접근 최소 권한·네트워크 격리(프라이빗 엔드포인트), 공개 노출 차단
+- DB 자격증명 비밀 저장소화·암호화, 대량 조회 알림·DLP</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="17" t="inlineStr">
@@ -32019,7 +34574,8 @@
       </c>
       <c r="E132" s="17" t="inlineStr">
         <is>
-          <t>공격자는 유출(Exfiltration)에 앞서 파일 시스템, 구성 파일, 로컬 데이터베이스, 가상 머신 파일, 프로세스 메모리 같은 로컬 시스템 소스를 검색해 관심 파일과 민감한 데이터를 찾을 수 있다.</t>
+          <t>- 공격자는 반출에 앞서 VM·호스트의 파일시스템·구성 파일·로컬 DB·프로세스 메모리에서 관심 데이터를 수집할 수 있음
+- 셸·CLI로 로컬을 뒤지며, 컨테이너 환경에서는 관리 명령으로 파드 내부 데이터를 직접 접근하지 않고도 수집함</t>
         </is>
       </c>
       <c r="F132" s="17" t="inlineStr">
@@ -32059,7 +34615,16 @@
       <c r="N132" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O132" s="17" t="inlineStr"/>
+      <c r="O132" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- VM·컨테이너 내 대량 파일 탐색·읽기, 프로세스 메모리 접근
+- 파드에서의 비정상 데이터 수집 명령
+■ 대응
+- 워크로드 최소 권한·민감 데이터 암호화, EDR로 비정상 파일 접근 탐지
+- 컨테이너 읽기 전용 파일시스템과 수집 도구 차단</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="17" t="inlineStr">
@@ -32084,7 +34649,8 @@
       </c>
       <c r="E133" s="17" t="inlineStr">
         <is>
-          <t>공격자는 유출(Exfiltration)에 앞서 여러 시스템에서 수집한 데이터를 한 시스템의 중앙 위치나 디렉터리에 모아 둘 수 있다. 데이터는 개별 파일로 두거나 수집 데이터 압축(Archive Collected Data) 같은 기법으로 하나의 파일로 합칠 수 있다. 대화형 명령 셸을 쓸 수 있으며, cmd와 bash의 일반 기능으로 데이터를 스테이징 위치에 복사할 수 있다.</t>
+          <t>- 공격자는 반출 전 여러 시스템의 수집 데이터를 한 인스턴스·중앙 DB에 모아 둘 수 있음
+- 공격자가 만든 클라우드 인스턴스에 스테이징하면 C2 연결 수를 줄여 탐지를 피하고 반출을 효율화함</t>
         </is>
       </c>
       <c r="F133" s="17" t="inlineStr">
@@ -32124,7 +34690,16 @@
       <c r="N133" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="O133" s="17" t="inlineStr"/>
+      <c r="O133" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 다수 시스템 데이터가 한 인스턴스·DB로 모이는 패턴, 비정상 대용량 복사·압축
+- 공격자 생성 인스턴스로의 데이터 집결
+■ 대응
+- 대용량 내부 전송·압축 알림, 인스턴스 생성·네트워크 흐름 모니터링
+- 중요 데이터 접근 로깅과 비정상 집결 탐지</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="17" t="inlineStr">
@@ -32149,7 +34724,8 @@
       </c>
       <c r="E134" s="17" t="inlineStr">
         <is>
-          <t>공격자는 민감한 정보를 수집하기 위해 Exchange 서버, Office 365, Google Workspace를 노릴 수 있다. 사용자의 자격 증명을 이용해 Exchange 서버와 직접 상호작용하며 네트워크 안의 정보를 얻을 수 있다. 외부에 공개된 Exchange 서비스, Office 365, Google Workspace에 자격 증명이나 액세스 토큰으로 접근해 이메일을 볼 수도 있다. MailSniper 같은 도구로 특정 키워드 검색을 자동화할 수 있다.</t>
+          <t>- 공격자는 탈취 자격증명·토큰으로 Exchange Online·M365·Google Workspace 사서함에 접근해 이메일을 대량 수집할 수 있음
+- Graph·EWS·MailSniper로 키워드 검색을 자동화하며, 외부 노출 메일 서비스에 직접 붙어 민감 정보를 캐냄</t>
         </is>
       </c>
       <c r="F134" s="17" t="inlineStr">
@@ -32193,7 +34769,16 @@
       <c r="N134" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="O134" s="17" t="inlineStr"/>
+      <c r="O134" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- Graph·EWS 대량 사서함 조회, MailSniper 등 키워드 검색 패턴, 웹셸 기반 메일 반출
+- 침해 계정의 비정상 대량 메일 접근
+■ 대응
+- 사서함 접근 최소화·앱 토큰 범위 제한, 대량 메일 조회 알림·DLP
+- 감사 로깅 유지와 의심 세션 폐기</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="17" t="inlineStr">
@@ -32218,7 +34803,8 @@
       </c>
       <c r="E135" s="17" t="inlineStr">
         <is>
-          <t>공격자는 민감한 정보를 수집하기 위해 이메일 전달 규칙을 설정할 수 있다. 이메일 전달 규칙을 악용해 피해자의 활동을 감시하고, 정보를 탈취하고, 이후 공격이나 작전에 쓸 피해자나 피해 조직에 관한 정보를 더 수집할 수 있다. 또한 이메일 전달 규칙을 이용하면 관리자가 침해된 자격 증명을 재설정한 뒤에도 피해자의 이메일에 계속 접근할 수 있다. 대부분의 이메일 클라이언트는 다른 수신자에게 전달하는 기능을 포함해 다양한 받은편지함 규칙을 만들 수 있게 한다. 이 규칙은 로컬 이메일 애플리케이션, 웹 인터페이스, 명령줄 인터페이스로 만들 수 있다. 메시지는 내부나 외부 수신자에게 전달될 수 있으며 규칙의 범위에 제한이 없다. 관리자도 사용자 계정에 전달 규칙을 만들 수 있으며, 고려 사항과 결과는 같다.</t>
+          <t>- 공격자는 이메일 전달 규칙을 설정해 피해자의 메일을 외부·내부 계정으로 자동 전달받아 지속 수집할 수 있음
+- 규칙은 사서함에 남아 비밀번호 재설정 후에도 유효하고, MAPI로 숨기거나 조직 전역 전송 규칙으로 전사 메일을 전달받기도 함</t>
         </is>
       </c>
       <c r="F135" s="17" t="inlineStr">
@@ -32262,7 +34848,16 @@
       <c r="N135" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="O135" s="17" t="inlineStr"/>
+      <c r="O135" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 외부 전달 규칙 생성, 조직 전역 transport rule 변경, MAPI로 숨겨진 규칙
+- 메일이 외부로 자동 전달되는 패턴
+■ 대응
+- 자동 외부 전달 차단 정책, 전달 규칙 정기 감사(숨김 규칙 포함)
+- 전송 규칙 변경 알림과 외부 전달 모니터링</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="17" t="inlineStr">
@@ -32287,7 +34882,8 @@
       </c>
       <c r="E136" s="17" t="inlineStr">
         <is>
-          <t>공격자는 자신의 인프라에 직접 연결되지 않도록 연결 프록시를 사용해 시스템 간 네트워크 트래픽을 중계하거나 명령 및 제어(C2) 서버와의 네트워크 통신을 중개할 수 있다. HTRAN, ZXProxy, ZXPortMap 등 프록시나 포트 리디렉션으로 트래픽을 우회시키는 도구가 많이 있다. 공격자는 이런 프록시를 이용해 C2 통신을 관리하고, 동시에 발생하는 외부 네트워크 연결 수를 줄이고, 연결이 끊겨도 복원력을 확보하거나, 피해 대상 사이의 기존 신뢰 통신 경로를 타고 의심을 피한다. 공격자는 여러 프록시를 연쇄로 연결해 악성 트래픽의 출처를 더 감출 수 있다.</t>
+          <t>- 공격자는 연결 프록시·포트 리디렉션·CDN 라우팅으로 C2 트래픽을 중계해 자신의 인프라를 숨길 수 있음
+- 여러 프록시를 연쇄해 출처를 감추고, 신뢰 통신 경로에 섞여 외부 연결 수를 줄이며 탐지·차단을 피함</t>
         </is>
       </c>
       <c r="F136" s="17" t="inlineStr">
@@ -32327,7 +34923,16 @@
       <c r="N136" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O136" s="17" t="inlineStr"/>
+      <c r="O136" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 알려진 프록시·리디렉션 도구 패턴, CDN 경유 비정상 C2, 다단 프록시 연쇄
+- 침해 VM에서의 중계 트래픽
+■ 대응
+- 아웃바운드 필터링·허용 목록, 비정상 장기 연결 탐지
+- 침해 VM 격리와 CDN 라우팅 모니터링</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="17" t="inlineStr">
@@ -32352,7 +34957,8 @@
       </c>
       <c r="E137" s="17" t="inlineStr">
         <is>
-          <t>공격자는 침해한 인프라를 통한 데이터 유출을 자동화하기 위해 트래픽 미러링을 악용할 수 있다. 트래픽 미러링은 일부 장비에 기본으로 있는 기능으로 주로 네트워크 분석에 쓰인다. 예를 들어 장비가 네트워크 트래픽을 하나 이상의 목적지로 전달해 네트워크 분석기나 기타 모니터링 장비가 분석하도록 설정될 수 있다.</t>
+          <t>- 공격자는 클라우드·네트워크 장비의 트래픽 미러링 기능(AWS Traffic Mirroring, Azure vTap 등)을 악용해 트래픽을 자신의 대상으로 복제·반출할 수 있음
+- 정상 분석용 기능을 전용해 지속적으로 데이터를 빼내며, 네트워크 스니핑·AiTM과 결합됨</t>
         </is>
       </c>
       <c r="F137" s="17" t="inlineStr">
@@ -32392,7 +34998,16 @@
       <c r="N137" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O137" s="17" t="inlineStr"/>
+      <c r="O137" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 트래픽 미러링 세션 생성·변경(AWS Traffic Mirroring·GCP Packet Mirroring·Azure vTap), 네트워크 장비 이미지 변조
+- 미러 대상이 비인가 리소스로 지정됨
+■ 대응
+- 미러링 세션 생성 권한 최소화·변경 알림, 미러 대상 허용 목록
+- 네트워크 장비 무결성 점검과 설정 드리프트 복원</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="17" t="inlineStr">
@@ -32417,7 +35032,8 @@
       </c>
       <c r="E138" s="17" t="inlineStr">
         <is>
-          <t>공격자는 주 명령 및 제어(C2) 채널 대신 이미 존재하는 정상적인 외부 웹 서비스를 이용해 데이터를 유출할 수 있다. 네트워크 안의 호스트가 침해 전부터 이런 인기 웹 서비스와 통신하고 있을 가능성이 높아, 이를 유출 수단으로 쓰면 상당한 은폐 효과를 얻을 수 있다. 이런 서비스로 가는 트래픽을 허용하는 방화벽 규칙이 이미 있을 수도 있다.</t>
+          <t>- 공격자는 C2 채널 대신 Google Drive·Salesforce·M365 같은 정상 웹 서비스로 데이터를 반출할 수 있음
+- 피해 조직이 평소 쓰는 서비스라 방화벽 허용·TLS 암호화에 묻혀 탐지가 어려움</t>
         </is>
       </c>
       <c r="F138" s="17" t="inlineStr">
@@ -32461,7 +35077,16 @@
       <c r="N138" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="O138" s="17" t="inlineStr"/>
+      <c r="O138" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 정상 SaaS(Drive·Salesforce·M365)로의 비정상 대량 업로드, Data Loader 등 대량 반출 도구 사용
+- 평소와 다른 양·시간대의 외부 서비스 전송
+■ 대응
+- 아웃바운드 DLP·업로드 제한, 승인되지 않은 SaaS로의 전송 차단
+- 대량 업로드 알림과 API 반출 모니터링</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="17" t="inlineStr">
@@ -32486,7 +35111,8 @@
       </c>
       <c r="E139" s="17" t="inlineStr">
         <is>
-          <t>공격자는 주 명령 및 제어(C2) 채널 대신 웹훅 엔드포인트로 데이터를 유출할 수 있다. 웹훅은 클라이언트가 서버를 계속 폴링하지 않아도 서버가 HTTP/S로 클라이언트에 데이터를 보낼 수 있게 하는 간단한 방식이다. Discord, Slack, webhook.site 등 많은 공개·상용 서비스가 GitHub, Jira, Trello 같은 다른 서비스에서 쓸 수 있는 웹훅 엔드포인트 생성을 지원한다. 연결된 서비스에서 변경(저장소 업데이트 푸시, 티켓 수정 등)이 생기면 해당 서비스가 데이터를 웹훅 엔드포인트로 자동 전송하고, 이를 사용하는 애플리케이션이 그 데이터를 활용한다.</t>
+          <t>- 공격자는 Discord·Slack·webhook.site 같은 웹훅 엔드포인트로 데이터를 반출할 수 있음
+- 공격자 환경을 피해 SaaS에 연결해 메일·메시지를 반복 자동 반출하거나, 스테이징 데이터를 URL에 직접 올리며 정상 트래픽에 섞임</t>
         </is>
       </c>
       <c r="F139" s="17" t="inlineStr">
@@ -32530,7 +35156,16 @@
       <c r="N139" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="O139" s="17" t="inlineStr"/>
+      <c r="O139" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 웹훅 엔드포인트(Discord·Slack·webhook.site)로의 비정상 전송, 저장소 비밀의 외부 POST
+- 공격자 환경에 연결된 SaaS 통합
+■ 대응
+- 아웃바운드로의 웹훅 도메인 제한·DLP, 비인가 SaaS 통합 차단
+- 저장소 비밀 유출 탐지와 웹훅 트래픽 모니터링</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="17" t="inlineStr">
@@ -32555,7 +35190,8 @@
       </c>
       <c r="E140" s="17" t="inlineStr">
         <is>
-          <t>공격자는 공유·동기화나 클라우드 환경 백업 생성 등을 통해, 같은 서비스에서 자신이 제어하는 다른 클라우드 계정으로 데이터를 옮겨 유출할 수 있다.</t>
+          <t>- 공격자는 같은 클라우드 제공자 내 자신의 계정으로 스냅샷·백업·공유 링크를 통해 데이터를 전송해 반출할 수 있음
+- 제공자 내부 주소·API를 쓰므로 외부 대량 전송 감시를 피하며, SAS URI·익명 공유 링크로 인증 없이 빼내기도 함</t>
         </is>
       </c>
       <c r="F140" s="17" t="inlineStr">
@@ -32599,7 +35235,16 @@
       <c r="N140" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="O140" s="17" t="inlineStr"/>
+      <c r="O140" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 제공자 내 다른 계정으로의 스냅샷·백업 복사(AzCopy·Replication), SAS URI·익명 공유 링크 생성
+- 스냅샷·이미지의 외부 계정 공유
+■ 대응
+- 스냅샷·백업 공유 권한 최소화·외부 공유 차단, SAS·익명 링크 제한
+- 계정 간 복사 알림과 스냅샷 공유 모니터링</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="17" t="inlineStr">
@@ -32624,7 +35269,8 @@
       </c>
       <c r="E141" s="17" t="inlineStr">
         <is>
-          <t>공격자는 정상 사용자가 쓰는 계정에 대한 접근을 막아 시스템과 네트워크 리소스의 가용성을 방해할 수 있다. 계정 접근을 없애기 위해 계정을 삭제하거나, 잠그거나, 조작할 수 있다(예: 자격 증명 변경, SharePoint 같은 SaaS 플랫폼의 권한 회수). 이후 악의적 변경을 적용하기 위해 로그오프하거나 시스템 종료·재부팅(System Shutdown/Reboot)을 수행할 수도 있다.</t>
+          <t>- 공격자는 계정을 삭제·잠그거나 자격증명·권한을 변경해 정상 사용자의 클라우드·SaaS 접근을 차단할 수 있음
+- 랜섬·파괴 공격 전 관리자 접근을 끊어 사고 대응·복구를 방해하는 용도로 쓰임</t>
         </is>
       </c>
       <c r="F141" s="17" t="inlineStr">
@@ -32664,7 +35310,16 @@
       <c r="N141" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O141" s="17" t="inlineStr"/>
+      <c r="O141" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- IAM 사용자·역할 삭제, 다수 계정 비밀번호·MFA 강제 변경, SaaS 권한 대량 회수
+- 관리자 계정의 비정상 잠금·삭제
+■ 대응
+- 계정 삭제·대량 변경에 승인·알림, 관리자 계정 보호와 복구 경로 분리
+- 변경 불가 감사 로그와 긴급 접근(break-glass) 계정 보존</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="17" t="inlineStr">
@@ -32689,7 +35344,8 @@
       </c>
       <c r="E142" s="17" t="inlineStr">
         <is>
-          <t>공격자는 시스템, 서비스, 네트워크 리소스의 가용성을 방해하기 위해 특정 시스템이나 네트워크 전반의 데이터와 파일을 대량으로 파괴할 수 있다. 데이터 파괴는 로컬·원격 드라이브의 파일이나 데이터를 덮어써서 포렌식 기법으로도 복구할 수 없게 만드는 경우가 많다. del이나 rm 같은 일반적인 운영체제 파일 삭제 명령은 파일 내용을 지우지 않고 파일 포인터만 제거하는 경우가 많아 적절한 포렌식 방법으로 복구할 수 있다. 이 행위는 저장 디스크의 영역이나 디스크의 논리 구조가 아니라 개별 파일을 파괴한다는 점에서 디스크 콘텐츠 삭제(Disk Content Wipe), 디스크 구조 삭제(Disk Structure Wipe)와 구별된다.</t>
+          <t>- 공격자는 클라우드 스토리지 객체·머신 이미지·DB 인스턴스·백업을 대량 삭제해 가용성을 파괴할 수 있음
+- 복구 불가능하게 지우며, 웜 기능으로 전파되거나 랜섬·갈취의 압박 수단으로 쓰임</t>
         </is>
       </c>
       <c r="F142" s="17" t="inlineStr">
@@ -32729,7 +35385,16 @@
       <c r="N142" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="O142" s="17" t="inlineStr"/>
+      <c r="O142" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 스토리지 객체·버킷·스냅샷·DB·AMI 대량 삭제(DeleteObject·DeleteDBInstance·DeregisterImage 등)
+- 권한 있는 DaemonSet의 파일 삭제, 재귀 삭제·와이프 패턴
+■ 대응
+- 버전 관리·객체 잠금·삭제 방지(MFA Delete), 백업을 별도 계정에 불변 보존
+- 대량 삭제 알림과 삭제 권한 최소화</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="17" t="inlineStr">
@@ -32754,7 +35419,8 @@
       </c>
       <c r="E143" s="17" t="inlineStr">
         <is>
-          <t>공격자는 클라우드 스토리지 버킷의 수명 주기 정책을 수정해 버킷에 저장된 모든 객체를 파괴할 수 있다.</t>
+          <t>- 공격자는 스토리지 버킷의 수명주기 정책을 수정해 저장 객체 전체를 자동 삭제되게 만들 수 있음
+- 하루 뒤 전체 삭제 같은 정책을 걸어 한 번에 파괴하며, 로그 버킷에 적용하면 흔적 제거에도 쓰임</t>
         </is>
       </c>
       <c r="F143" s="17" t="inlineStr">
@@ -32794,7 +35460,15 @@
       <c r="N143" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O143" s="17" t="inlineStr"/>
+      <c r="O143" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 버킷 수명주기 정책 생성·변경(PutBucketLifecycleConfiguration), 짧은 만료 기간 설정
+■ 대응
+- 수명주기 정책 변경 권한 최소화·알림, 객체 잠금·버전 관리로 자동 삭제 무력화
+- 로그 버킷에 불변 보존 적용</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="17" t="inlineStr">
@@ -32819,7 +35493,8 @@
       </c>
       <c r="E144" s="17" t="inlineStr">
         <is>
-          <t>공격자는 시스템과 네트워크 리소스의 가용성을 방해하기 위해 대상 시스템이나 네트워크 내 다수 시스템의 데이터를 암호화할 수 있다. 로컬·원격 드라이브의 파일이나 데이터를 암호화하고 복호화 키를 넘겨주지 않는 방식으로 저장된 데이터에 접근하지 못하게 만들 수 있다. 이는 복호화나 복호화 키를 대가로 피해자에게 금전을 요구하기 위해서(랜섬웨어) 하거나, 키를 저장하거나 전송하지 않아 데이터를 영구히 접근 불가능하게 만들기 위해 할 수 있다.</t>
+          <t>- 공격자는 VM·스토리지·DB의 데이터를 암호화해 가용성을 차단하고 복호화 대가로 금전을 요구할 수 있음
+- ESXi·하이퍼바이저 대량 암호화나 SSE-C 같은 클라우드 네이티브 암호화를 악용하며, 웜 기능으로 네트워크 전반에 전파됨</t>
         </is>
       </c>
       <c r="F144" s="17" t="inlineStr">
@@ -32859,7 +35534,16 @@
       <c r="N144" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O144" s="17" t="inlineStr"/>
+      <c r="O144" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- SSE-C 암호화 PUT/Copy, EBS·RDS 암호화 설정·스냅샷 조작, 대량 파일 암호화·확장자 변경
+- ESXi·vCenter에서의 대량 암호화 행위
+■ 대응
+- 백업 불변 보존·오프라인 사본, SSE-C 사용 제한·키 관리 통제
+- 대량 암호화 탐지와 ESXi 접근 강화, 신속 격리·복구 체계</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="17" t="inlineStr">
@@ -32884,7 +35568,8 @@
       </c>
       <c r="E145" s="17" t="inlineStr">
         <is>
-          <t>공격자는 기업 네트워크 내부나 외부에서 볼 수 있는 시각적 콘텐츠를 변조해 원본 콘텐츠의 무결성에 영향을 줄 수 있다. 변조(Defacement)의 목적에는 메시지 전달, 위협, 침입에 대한 (거짓일 수 있는) 공적 주장 등이 있다. 사용자에게 불쾌감을 주거나 함께 게시한 메시지에 따르도록 압박하기 위해 불쾌하거나 혐오스러운 이미지를 사용할 수도 있다.</t>
+          <t>- 공격자는 외부 노출 웹사이트·리소스의 시각적 콘텐츠를 변조하거나 하위 도메인을 탈취해 메시지 전달·협박·선전을 할 수 있음
+- 방치된 DNS 레코드가 가리키는 리소스를 재프로비저닝해 콘텐츠를 장악하며, 시스템 신뢰를 떨어뜨림</t>
         </is>
       </c>
       <c r="F145" s="17" t="inlineStr">
@@ -32924,7 +35609,15 @@
       <c r="N145" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O145" s="17" t="inlineStr"/>
+      <c r="O145" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 외부 웹사이트 콘텐츠 변경, 방치 DNS 레코드가 가리키는 리소스 재생성(하위 도메인 탈취)
+■ 대응
+- 미사용 DNS 레코드 정리·소유권 검증, 웹 콘텐츠 무결성 모니터링
+- 리소스 삭제 시 DNS 레코드 동반 정리</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="17" t="inlineStr">
@@ -32949,7 +35642,8 @@
       </c>
       <c r="E146" s="17" t="inlineStr">
         <is>
-          <t>공격자는 대상 이메일 주소에 감당할 수 없을 만큼 많은 메시지를 퍼부을 수 있다. 이로 인해 정상 이메일이 스팸 더미에 묻히고 업무가 방해받을 수 있다.</t>
+          <t>- 공격자는 대상 이메일 주소에 대량 메시지를 퍼부어 정상 메일을 묻고 업무를 방해할 수 있음
+- 뉴스레터 자동 가입 등으로 수천 통을 발생시켜 보안 경고를 가리며, 이어지는 비싱의 사전 단계로도 쓰임</t>
         </is>
       </c>
       <c r="F146" s="17" t="inlineStr">
@@ -32989,7 +35683,16 @@
       <c r="N146" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O146" s="17" t="inlineStr"/>
+      <c r="O146" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 짧은 시간 대량 수신 메일(뉴스레터 가입 폭주), 특정 사용자 대상 메일량 급증
+- 메일 폭주 직후의 비싱 전화 패턴
+■ 대응
+- 메일 폭주 탐지·격리·레이트 제한, 가입 확인(double opt-in) 활용
+- 폭주 중 보안 알림을 대체 채널로 전달</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="17" t="inlineStr">
@@ -33014,7 +35717,8 @@
       </c>
       <c r="E147" s="17" t="inlineStr">
         <is>
-          <t>공격자는 엔드포인트 서비스 거부(DoS) 공격으로 사용자에 대한 서비스 가용성을 떨어뜨리거나 차단할 수 있다. 엔드포인트 DoS는 서비스가 호스팅된 시스템의 자원을 고갈시키거나 시스템을 익스플로잇해 지속적인 중단 상태를 일으키는 방식으로 수행할 수 있다. 대상 서비스의 예로는 웹사이트, 이메일 서비스, DNS, 웹 기반 애플리케이션이 있다. 공격자가 정치적 목적으로, 또는 주의 분산, 핵티비즘, 금전 갈취 같은 다른 악의적 활동을 돕기 위해 DoS 공격을 수행한 사례가 관찰되었다.</t>
+          <t>- 공격자는 엔드포인트·네트워크 DoS로 클라우드 웹·API·DNS 서비스의 가용성을 떨어뜨리거나 차단할 수 있음
+- 자원 고갈 플러드·애플리케이션 익스플로잇·대역폭 플러드·반사 증폭을 쓰며, 봇넷·IP 스푸핑으로 추적과 필터링을 어렵게 함</t>
         </is>
       </c>
       <c r="F147" s="17" t="inlineStr">
@@ -33054,7 +35758,16 @@
       <c r="N147" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O147" s="17" t="inlineStr"/>
+      <c r="O147" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 웹·API·DNS로의 트래픽 급증, 자원 고갈 플러드·반사 증폭 패턴, 애플리케이션 크래시 반복
+- 자동 스케일링 급증과 과금 급증
+■ 대응
+- WAF·DDoS 보호·레이트 리밋·스케일 상한, 반사 증폭 방지(출발지 검증)
+- 애플리케이션 패치와 자원 고갈 지점 보완</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="17" t="inlineStr">
@@ -33079,7 +35792,8 @@
       </c>
       <c r="E148" s="17" t="inlineStr">
         <is>
-          <t>공격자는 피해자가 해당 자원을 쓸 수 없게 만들면서 자신의 금전적 이득을 얻기 위해 금품 갈취, 사회공학, 기술적 탈취 등의 방법으로 대상의 금전 자원을 탈취할 수 있다. 금전 탈취는 랜섬웨어를 이용한 갈취, 비즈니스 이메일 침해(BEC)와 사기, 돼지 도살(pig butchering) 사기, 은행 해킹, 암호화폐 네트워크 악용 등 여러 대표적인 캠페인 유형의 최종 목표다.</t>
+          <t>- 공격자는 갈취·BEC·사기·암호화폐 악용으로 대상의 금전 자원을 직접 탈취할 수 있음
+- 침해 계정과 신뢰 주체 사칭으로 부정 이체를 유도하거나, 데이터 암호화·유출 후 공개 위협으로 금전을 요구함</t>
         </is>
       </c>
       <c r="F148" s="17" t="inlineStr">
@@ -33119,7 +35833,16 @@
       <c r="N148" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="O148" s="17" t="inlineStr"/>
+      <c r="O148" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 부정 이체·결제 변경 요청, 사칭 메일·BEC 패턴, 암호화폐 지갑 파일 탐색
+- 유출 후 공개 위협·갈취 메시지
+■ 대응
+- 송금·결제 변경 다중 승인·대역외 확인, BEC 탐지와 사칭 메일 차단
+- 지갑·결제 자격증명 보호와 사용자 교육</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="17" t="inlineStr">
@@ -33144,7 +35867,8 @@
       </c>
       <c r="E149" s="17" t="inlineStr">
         <is>
-          <t>공격자는 손상된 시스템의 복구를 막기 위해 복구를 돕는 내장 데이터를 삭제하고 관련 서비스를 끌 수 있다. 이로 인해 사용 가능한 백업과 복구 옵션에 접근하지 못하게 될 수 있다.</t>
+          <t>- 공격자는 스냅샷·백업·복원 지점·섀도 복사본을 삭제·비활성화해 암호화·파괴 후 복구를 막을 수 있음
+- 클라우드 백업 자격증명 삭제, ESXi 스냅샷 삭제·암호화로 복구 옵션을 없애 랜섬 압박을 키움</t>
         </is>
       </c>
       <c r="F149" s="17" t="inlineStr">
@@ -33184,7 +35908,16 @@
       <c r="N149" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="O149" s="17" t="inlineStr"/>
+      <c r="O149" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 스냅샷·복원 지점·백업 서비스 삭제, soft-delete·백업 구성 비활성화
+- ESXi 스냅샷 삭제·암호화, 네트워크 장비 백업 펌웨어 삭제
+■ 대응
+- 백업 불변·삭제 방지·별도 계정 보존, soft-delete·논리적 삭제 방지 강제
+- 백업 삭제·구성 변경 알림과 복구 테스트</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="17" t="inlineStr">
@@ -33209,7 +35942,8 @@
       </c>
       <c r="E150" s="17" t="inlineStr">
         <is>
-          <t>공격자는 장악한 시스템의 자원을 이용해 자원을 많이 소모하는 작업을 수행할 수 있으며, 이는 시스템이나 호스팅된 서비스의 가용성에 영향을 줄 수 있다.</t>
+          <t>- 공격자는 장악한 클라우드 컴퓨팅 자원을 크립토마이닝·LLM 추론(LLMjacking)·SMS 발송·스팸에 악용해 과금·가용성 피해를 입힐 수 있음
+- 노출·약인증 서비스나 탈취 자격증명으로 대량 인스턴스·컨테이너·관리형 AI를 가동하며, 비용이 피해 계정에 청구됨</t>
         </is>
       </c>
       <c r="F150" s="17" t="inlineStr">
@@ -33253,7 +35987,16 @@
       <c r="N150" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O150" s="17" t="inlineStr"/>
+      <c r="O150" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 비정상 대량 인스턴스·컨테이너 생성(RunInstances·ECS·EKS), Bedrock 등 LLM 대량 호출, SES 발송 급증
+- GPU·고사양 인스턴스 급증과 과금 급증, 노출 서비스(Ray·Open WebUI)로의 작업 투입
+■ 대응
+- 할당량·인스턴스 유형 상한과 리전 제한, 노출 AI·관리 서비스 인증 강제·비공개
+- 과금·사용량 이상 알림, SES·Bedrock 권한 최소화</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="17" t="inlineStr">
@@ -33278,7 +36021,8 @@
       </c>
       <c r="E151" s="17" t="inlineStr">
         <is>
-          <t>공격자는 장악한 시스템의 컴퓨팅 자원을 이용해 자원을 많이 소모하는 작업을 수행할 수 있으며, 이는 시스템이나 호스팅된 서비스의 가용성에 영향을 줄 수 있다.</t>
+          <t>- 공격자는 장악한 EC2·컨테이너·클러스터의 컴퓨팅 자원을 크립토마이닝에 악용해 가용성과 과금에 피해를 줄 수 있음
+- 노출 API로 컨테이너를 쉽게 배포·확장하며, 자원을 소진시켜 정상 워크로드를 지연·중단시킴</t>
         </is>
       </c>
       <c r="F151" s="17" t="inlineStr">
@@ -33322,7 +36066,16 @@
       <c r="N151" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="O151" s="17" t="inlineStr"/>
+      <c r="O151" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 비정상 EC2·ECS·컨테이너 생성과 지속적 고CPU, 채굴 풀 도메인·스트라툼 프로토콜 통신
+- 노출 Docker·K8s API로의 컨테이너 대량 배포
+■ 대응
+- 인스턴스·컨테이너 생성 권한 최소화·유형 상한, 노출 API 비공개·인증 강제
+- CPU·과금 이상 알림과 채굴 풀 통신 차단</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="17" t="inlineStr">
@@ -33347,7 +36100,8 @@
       </c>
       <c r="E152" s="17" t="inlineStr">
         <is>
-          <t>공격자는 장악한 시스템의 네트워크 대역폭을 이용해 자원을 많이 소모하는 작업을 수행할 수 있으며, 이는 시스템이나 호스팅된 서비스의 가용성에 영향을 줄 수 있다.</t>
+          <t>- 공격자는 장악한 시스템의 네트워크 대역폭을 봇넷·프록시재킹·토렌트 시딩에 악용할 수 있음
+- 피해 IP·대역폭을 프록시웨어에 팔거나 DDoS에 쓰며, 불법 활동에 쓰여 평판 피해까지 유발함</t>
         </is>
       </c>
       <c r="F152" s="17" t="inlineStr">
@@ -33391,7 +36145,16 @@
       <c r="N152" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O152" s="17" t="inlineStr"/>
+      <c r="O152" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 비정상 대역폭 급증·장기 외부 연결, 프록시웨어·토렌트 트래픽 패턴
+- 피해 IP의 스캔·DDoS 출발 흔적
+■ 대응
+- 아웃바운드 필터링·대역폭 이상 알림, 프록시웨어·토렌트 통신 차단
+- 침해 워크로드 격리와 평판 모니터링</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="17" t="inlineStr">
@@ -33416,7 +36179,8 @@
       </c>
       <c r="E153" s="17" t="inlineStr">
         <is>
-          <t>공격자는 메시징 서비스를 SMS 펌핑에 악용할 수 있으며, 이는 시스템이나 호스팅된 서비스의 가용성에 영향을 줄 수 있다. SMS 펌핑은 통신 사기의 한 유형으로, 위협 행위자가 먼저 통신 사업자로부터 전화번호 묶음을 확보한 뒤 피해자의 메시징 인프라를 이용해 그 번호들로 대량의 SMS를 보내는 방식이다. 위협 행위자는 자신이 확보한 번호로 SMS 트래픽을 발생시켜 통신 사업자로부터 대가를 받을 수 있다.</t>
+          <t>- 공격자는 피해자의 OTP·가입 폼이 쓰는 SMS 발송 인프라(Twilio·SNS·Cognito)를 악용해 자신이 확보한 고요율 번호로 대량 SMS를 발생시킬 수 있음
+- 통신 사업자로부터 대가를 받는 사기이며, 피해자는 급증한 SMS 비용과 통신 채널 과부하를 겪음</t>
         </is>
       </c>
       <c r="F153" s="17" t="inlineStr">
@@ -33460,7 +36224,16 @@
       <c r="N153" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O153" s="17" t="inlineStr"/>
+      <c r="O153" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- OTP·가입 폼의 비정상 대량 요청(cognito:SignUp·sns:Publish), 특정 번호대로의 SMS 급증
+- SMS 비용 급증
+■ 대응
+- 폼 레이트 제한·CAPTCHA·봇 방어, SMS 발송 상한·지역 제한
+- SNS·Cognito 권한 최소화와 비용 알림</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="17" t="inlineStr">
@@ -33485,7 +36258,8 @@
       </c>
       <c r="E154" s="17" t="inlineStr">
         <is>
-          <t>공격자는 침해한 SaaS(Software-as-a-Service) 애플리케이션을 이용해 자원을 많이 소모하는 작업을 수행할 수 있으며, 이는 호스팅된 서비스의 가용성에 영향을 줄 수 있다.</t>
+          <t>- 공격자는 침해한 SaaS·관리형 서비스(SES·SNS·SendGrid·Twilio, 관리형 LLM)를 자원 소모 작업에 악용할 수 있음
+- 대량 스팸·피싱 발송이나 리버스 프록시를 통한 LLMjacking으로 과금·할당량·가용성에 피해를 주며, 필요 시 서비스를 먼저 활성화함</t>
         </is>
       </c>
       <c r="F154" s="17" t="inlineStr">
@@ -33529,7 +36303,16 @@
       <c r="N154" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O154" s="17" t="inlineStr"/>
+      <c r="O154" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- SES·SNS 발송 급증, Bedrock 등 LLM 대량 호출, 비활성 서비스의 갑작스런 활성화
+- 리버스 프록시를 통한 LLM 접근 패턴
+■ 대응
+- 메일·메시징·LLM 서비스 권한 최소화·발송 상한, 샌드박스 해제·서비스 활성화 승인
+- 과금·호출량 이상 알림과 LLMjacking 탐지</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="17" t="inlineStr">
@@ -33554,7 +36337,8 @@
       </c>
       <c r="E155" s="17" t="inlineStr">
         <is>
-          <t>공격자는 시스템의 서비스를 중지하거나 비활성화해 정상 사용자가 해당 서비스를 쓸 수 없게 만들 수 있다. 중요한 서비스나 프로세스를 중지하면 침해 사고 대응을 방해하거나 멈추게 할 수 있고, 환경에 피해를 입히려는 공격자의 전체 목표에 도움이 될 수 있다.</t>
+          <t>- 공격자는 중요한 서비스·프로세스를 중지·비활성화해 가용성을 떨어뜨리고 사고 대응을 방해할 수 있음
+- 데이터 파괴·암호화 전 DB·메일·백업 서비스를 멈춰 효과를 키우며, 클라우드에서는 API로 서비스 접근을 차단하기도 함</t>
         </is>
       </c>
       <c r="F155" s="17" t="inlineStr">
@@ -33594,7 +36378,16 @@
       <c r="N155" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="O155" s="17" t="inlineStr"/>
+      <c r="O155" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 중요 서비스·프로세스 중지(taskkill·net stop 등), 클라우드 서비스 접근 차단 API 호출
+- 데이터 저장소 서비스 중지 직후의 암호화·삭제
+■ 대응
+- 서비스 중지·비활성화 권한 최소화·알림, 중요 서비스 보호·자동 복구
+- 데이터 저장소 접근 변경 모니터링</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="17" t="inlineStr">
@@ -33619,7 +36412,8 @@
       </c>
       <c r="E156" s="17" t="inlineStr">
         <is>
-          <t>공격자는 일시 삭제(soft delete) 상태의 리소스를 찾아 복원한 뒤, 삭제될 예정이던 내용을 가져와 공격을 진전시킬 수 있다.</t>
+          <t>- 공격자는 일시 삭제(soft-delete) 상태의 VM·백업·스토리지·Key Vault 객체를 복원해, 삭제 예정이던 내용을 되살려 공격에 활용할 수 있음
+- 삭제로 끝난 것처럼 보이는 리소스가 복구 기간 동안 남아 있어, 자격증명·데이터를 다시 확보하는 경로가 됨</t>
         </is>
       </c>
       <c r="F156" s="17" t="inlineStr">
@@ -33659,7 +36453,15 @@
       <c r="N156" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O156" s="17" t="inlineStr"/>
+      <c r="O156" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- soft-delete 객체 복원(Recovery Services Vault·Key Vault·스토리지), 삭제 예정 리소스의 재활성화
+■ 대응
+- 복원 권한 최소화·복원 이벤트 알림, soft-delete 보존 기간·접근 통제
+- 삭제 예정 민감 리소스의 조기 영구 삭제·격리</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:O156"/>
